--- a/data/3FEB_25_26/clutch_lineups_25_26_3FEB.xlsx
+++ b/data/3FEB_25_26/clutch_lineups_25_26_3FEB.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X426"/>
+  <dimension ref="A1:X431"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36250,6 +36250,426 @@
         </is>
       </c>
     </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>2487740</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>A. APARICIO IZQUIERDO | A. JIMENEZ FERNANDEZ | D. RODRIGUEZ GARCIA | M. NIANG | P. RODRIGUEZ RIVERO</t>
+        </is>
+      </c>
+      <c r="D427" t="n">
+        <v>5</v>
+      </c>
+      <c r="E427" t="n">
+        <v>69</v>
+      </c>
+      <c r="F427" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="G427" t="n">
+        <v>1</v>
+      </c>
+      <c r="H427" t="n">
+        <v>3</v>
+      </c>
+      <c r="I427" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="J427" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="K427" t="n">
+        <v>113.64</v>
+      </c>
+      <c r="L427" t="n">
+        <v>208.33</v>
+      </c>
+      <c r="M427" t="n">
+        <v>-94.7</v>
+      </c>
+      <c r="N427" t="n">
+        <v>1</v>
+      </c>
+      <c r="O427" t="n">
+        <v>2</v>
+      </c>
+      <c r="P427" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q427" t="n">
+        <v>1</v>
+      </c>
+      <c r="R427" t="n">
+        <v>2</v>
+      </c>
+      <c r="S427" t="n">
+        <v>1</v>
+      </c>
+      <c r="T427" t="n">
+        <v>0</v>
+      </c>
+      <c r="U427" t="n">
+        <v>1</v>
+      </c>
+      <c r="V427" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W427" t="n">
+        <v>24</v>
+      </c>
+      <c r="X427" t="inlineStr">
+        <is>
+          <t>ZENTRO BASKET MADRID vs C. D. MENSAJERO ISLA DE LA PALMA</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>2487740</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>A. APARICIO IZQUIERDO | A. JIMENEZ FERNANDEZ | D. RODRIGUEZ GARCIA | P. RODRIGUEZ RIVERO | Y. RODRÍGUEZ MACHÍN</t>
+        </is>
+      </c>
+      <c r="D428" t="n">
+        <v>5</v>
+      </c>
+      <c r="E428" t="n">
+        <v>63</v>
+      </c>
+      <c r="F428" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="G428" t="n">
+        <v>0</v>
+      </c>
+      <c r="H428" t="n">
+        <v>3</v>
+      </c>
+      <c r="I428" t="n">
+        <v>3</v>
+      </c>
+      <c r="J428" t="n">
+        <v>2</v>
+      </c>
+      <c r="K428" t="n">
+        <v>0</v>
+      </c>
+      <c r="L428" t="n">
+        <v>150</v>
+      </c>
+      <c r="M428" t="n">
+        <v>-150</v>
+      </c>
+      <c r="N428" t="n">
+        <v>1</v>
+      </c>
+      <c r="O428" t="n">
+        <v>0</v>
+      </c>
+      <c r="P428" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q428" t="n">
+        <v>0</v>
+      </c>
+      <c r="R428" t="n">
+        <v>3</v>
+      </c>
+      <c r="S428" t="n">
+        <v>0</v>
+      </c>
+      <c r="T428" t="n">
+        <v>0</v>
+      </c>
+      <c r="U428" t="n">
+        <v>1</v>
+      </c>
+      <c r="V428" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W428" t="n">
+        <v>24</v>
+      </c>
+      <c r="X428" t="inlineStr">
+        <is>
+          <t>ZENTRO BASKET MADRID vs C. D. MENSAJERO ISLA DE LA PALMA</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>2487740</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>A. APARICIO IZQUIERDO | D. RODRIGUEZ GARCIA | M. RODRÍGUEZ RIVEROL | O. PEÑA LOPEZ | Y. RODRÍGUEZ MACHÍN</t>
+        </is>
+      </c>
+      <c r="D429" t="n">
+        <v>5</v>
+      </c>
+      <c r="E429" t="n">
+        <v>30</v>
+      </c>
+      <c r="F429" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G429" t="n">
+        <v>0</v>
+      </c>
+      <c r="H429" t="n">
+        <v>0</v>
+      </c>
+      <c r="I429" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="J429" t="n">
+        <v>0</v>
+      </c>
+      <c r="K429" t="n">
+        <v>0</v>
+      </c>
+      <c r="L429" t="n">
+        <v>0</v>
+      </c>
+      <c r="M429" t="n">
+        <v>0</v>
+      </c>
+      <c r="N429" t="n">
+        <v>0</v>
+      </c>
+      <c r="O429" t="n">
+        <v>2</v>
+      </c>
+      <c r="P429" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q429" t="n">
+        <v>0</v>
+      </c>
+      <c r="R429" t="n">
+        <v>1</v>
+      </c>
+      <c r="S429" t="n">
+        <v>0</v>
+      </c>
+      <c r="T429" t="n">
+        <v>0</v>
+      </c>
+      <c r="U429" t="n">
+        <v>1</v>
+      </c>
+      <c r="V429" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W429" t="n">
+        <v>24</v>
+      </c>
+      <c r="X429" t="inlineStr">
+        <is>
+          <t>ZENTRO BASKET MADRID vs C. D. MENSAJERO ISLA DE LA PALMA</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>2487740</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>ZENTRO BASKET MADRID</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>B. SCHUCH | D. VAL GUTIERREZ | G. GOMA | J. VAQUERO PASCUAL | M. ESTAPE ROIZ</t>
+        </is>
+      </c>
+      <c r="D430" t="n">
+        <v>5</v>
+      </c>
+      <c r="E430" t="n">
+        <v>77</v>
+      </c>
+      <c r="F430" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="G430" t="n">
+        <v>0</v>
+      </c>
+      <c r="H430" t="n">
+        <v>1</v>
+      </c>
+      <c r="I430" t="n">
+        <v>0</v>
+      </c>
+      <c r="J430" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="K430" t="n">
+        <v>0</v>
+      </c>
+      <c r="L430" t="n">
+        <v>56.82</v>
+      </c>
+      <c r="M430" t="n">
+        <v>0</v>
+      </c>
+      <c r="N430" t="n">
+        <v>2</v>
+      </c>
+      <c r="O430" t="n">
+        <v>0</v>
+      </c>
+      <c r="P430" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q430" t="n">
+        <v>2</v>
+      </c>
+      <c r="R430" t="n">
+        <v>1</v>
+      </c>
+      <c r="S430" t="n">
+        <v>4</v>
+      </c>
+      <c r="T430" t="n">
+        <v>0</v>
+      </c>
+      <c r="U430" t="n">
+        <v>1</v>
+      </c>
+      <c r="V430" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W430" t="n">
+        <v>24</v>
+      </c>
+      <c r="X430" t="inlineStr">
+        <is>
+          <t>ZENTRO BASKET MADRID vs C. D. MENSAJERO ISLA DE LA PALMA</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>2487740</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>ZENTRO BASKET MADRID</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>B. SCHUCH | D. VAL GUTIERREZ | G. GOMA | J. VAQUERO PASCUAL | T. VERDERA BENASSAR</t>
+        </is>
+      </c>
+      <c r="D431" t="n">
+        <v>5</v>
+      </c>
+      <c r="E431" t="n">
+        <v>85</v>
+      </c>
+      <c r="F431" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="G431" t="n">
+        <v>6</v>
+      </c>
+      <c r="H431" t="n">
+        <v>0</v>
+      </c>
+      <c r="I431" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="J431" t="n">
+        <v>3</v>
+      </c>
+      <c r="K431" t="n">
+        <v>174.42</v>
+      </c>
+      <c r="L431" t="n">
+        <v>0</v>
+      </c>
+      <c r="M431" t="n">
+        <v>174.42</v>
+      </c>
+      <c r="N431" t="n">
+        <v>4</v>
+      </c>
+      <c r="O431" t="n">
+        <v>1</v>
+      </c>
+      <c r="P431" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q431" t="n">
+        <v>1</v>
+      </c>
+      <c r="R431" t="n">
+        <v>1</v>
+      </c>
+      <c r="S431" t="n">
+        <v>0</v>
+      </c>
+      <c r="T431" t="n">
+        <v>2</v>
+      </c>
+      <c r="U431" t="n">
+        <v>0</v>
+      </c>
+      <c r="V431" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W431" t="n">
+        <v>24</v>
+      </c>
+      <c r="X431" t="inlineStr">
+        <is>
+          <t>ZENTRO BASKET MADRID vs C. D. MENSAJERO ISLA DE LA PALMA</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/3FEB_25_26/clutch_lineups_25_26_3FEB.xlsx
+++ b/data/3FEB_25_26/clutch_lineups_25_26_3FEB.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X431"/>
+  <dimension ref="A1:X449"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36670,6 +36670,1518 @@
         </is>
       </c>
     </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>2487736</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>A. APARICIO IZQUIERDO | A. JIMENEZ FERNANDEZ | D. RODRIGUEZ GARCIA | J. RIES | P. RODRIGUEZ RIVERO</t>
+        </is>
+      </c>
+      <c r="D432" t="n">
+        <v>5</v>
+      </c>
+      <c r="E432" t="n">
+        <v>4</v>
+      </c>
+      <c r="F432" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="G432" t="n">
+        <v>5</v>
+      </c>
+      <c r="H432" t="n">
+        <v>0</v>
+      </c>
+      <c r="I432" t="n">
+        <v>2</v>
+      </c>
+      <c r="J432" t="n">
+        <v>0</v>
+      </c>
+      <c r="K432" t="n">
+        <v>250</v>
+      </c>
+      <c r="L432" t="n">
+        <v>0</v>
+      </c>
+      <c r="M432" t="n">
+        <v>0</v>
+      </c>
+      <c r="N432" t="n">
+        <v>2</v>
+      </c>
+      <c r="O432" t="n">
+        <v>0</v>
+      </c>
+      <c r="P432" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q432" t="n">
+        <v>0</v>
+      </c>
+      <c r="R432" t="n">
+        <v>0</v>
+      </c>
+      <c r="S432" t="n">
+        <v>0</v>
+      </c>
+      <c r="T432" t="n">
+        <v>0</v>
+      </c>
+      <c r="U432" t="n">
+        <v>0</v>
+      </c>
+      <c r="V432" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W432" t="n">
+        <v>23</v>
+      </c>
+      <c r="X432" t="inlineStr">
+        <is>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA vs EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>2487736</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>A. APARICIO IZQUIERDO | A. JIMENEZ FERNANDEZ | D. RODRIGUEZ GARCIA | M. NIANG | P. RODRIGUEZ RIVERO</t>
+        </is>
+      </c>
+      <c r="D433" t="n">
+        <v>5</v>
+      </c>
+      <c r="E433" t="n">
+        <v>46</v>
+      </c>
+      <c r="F433" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="G433" t="n">
+        <v>0</v>
+      </c>
+      <c r="H433" t="n">
+        <v>0</v>
+      </c>
+      <c r="I433" t="n">
+        <v>1</v>
+      </c>
+      <c r="J433" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K433" t="n">
+        <v>0</v>
+      </c>
+      <c r="L433" t="n">
+        <v>0</v>
+      </c>
+      <c r="M433" t="n">
+        <v>0</v>
+      </c>
+      <c r="N433" t="n">
+        <v>1</v>
+      </c>
+      <c r="O433" t="n">
+        <v>0</v>
+      </c>
+      <c r="P433" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q433" t="n">
+        <v>0</v>
+      </c>
+      <c r="R433" t="n">
+        <v>0</v>
+      </c>
+      <c r="S433" t="n">
+        <v>0</v>
+      </c>
+      <c r="T433" t="n">
+        <v>0</v>
+      </c>
+      <c r="U433" t="n">
+        <v>1</v>
+      </c>
+      <c r="V433" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W433" t="n">
+        <v>23</v>
+      </c>
+      <c r="X433" t="inlineStr">
+        <is>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA vs EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>2487736</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>A. APARICIO IZQUIERDO | D. RODRIGUEZ GARCIA | J. RIES | M. NIANG | P. RODRIGUEZ RIVERO</t>
+        </is>
+      </c>
+      <c r="D434" t="n">
+        <v>5</v>
+      </c>
+      <c r="E434" t="n">
+        <v>236</v>
+      </c>
+      <c r="F434" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="G434" t="n">
+        <v>5</v>
+      </c>
+      <c r="H434" t="n">
+        <v>9</v>
+      </c>
+      <c r="I434" t="n">
+        <v>7</v>
+      </c>
+      <c r="J434" t="n">
+        <v>9.52</v>
+      </c>
+      <c r="K434" t="n">
+        <v>71.43000000000001</v>
+      </c>
+      <c r="L434" t="n">
+        <v>94.54000000000001</v>
+      </c>
+      <c r="M434" t="n">
+        <v>-23.11</v>
+      </c>
+      <c r="N434" t="n">
+        <v>8</v>
+      </c>
+      <c r="O434" t="n">
+        <v>0</v>
+      </c>
+      <c r="P434" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q434" t="n">
+        <v>2</v>
+      </c>
+      <c r="R434" t="n">
+        <v>6</v>
+      </c>
+      <c r="S434" t="n">
+        <v>8</v>
+      </c>
+      <c r="T434" t="n">
+        <v>2</v>
+      </c>
+      <c r="U434" t="n">
+        <v>2</v>
+      </c>
+      <c r="V434" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W434" t="n">
+        <v>23</v>
+      </c>
+      <c r="X434" t="inlineStr">
+        <is>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA vs EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>2487736</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>A. SISTAC RODRIGUEZ | B. FERNANDEZ SHEPHARD | K. RIVEROL DE LAS CASAS | P. ARGÜELLES ELORZA</t>
+        </is>
+      </c>
+      <c r="D435" t="n">
+        <v>4</v>
+      </c>
+      <c r="E435" t="n">
+        <v>4</v>
+      </c>
+      <c r="F435" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="G435" t="n">
+        <v>0</v>
+      </c>
+      <c r="H435" t="n">
+        <v>5</v>
+      </c>
+      <c r="I435" t="n">
+        <v>0</v>
+      </c>
+      <c r="J435" t="n">
+        <v>2</v>
+      </c>
+      <c r="K435" t="n">
+        <v>0</v>
+      </c>
+      <c r="L435" t="n">
+        <v>250</v>
+      </c>
+      <c r="M435" t="n">
+        <v>0</v>
+      </c>
+      <c r="N435" t="n">
+        <v>0</v>
+      </c>
+      <c r="O435" t="n">
+        <v>0</v>
+      </c>
+      <c r="P435" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q435" t="n">
+        <v>0</v>
+      </c>
+      <c r="R435" t="n">
+        <v>2</v>
+      </c>
+      <c r="S435" t="n">
+        <v>0</v>
+      </c>
+      <c r="T435" t="n">
+        <v>0</v>
+      </c>
+      <c r="U435" t="n">
+        <v>0</v>
+      </c>
+      <c r="V435" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W435" t="n">
+        <v>23</v>
+      </c>
+      <c r="X435" t="inlineStr">
+        <is>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA vs EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>2487736</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>A. SISTAC RODRIGUEZ | B. FERNANDEZ SHEPHARD | M. KHIVRENKO | P. ARGÜELLES ELORZA</t>
+        </is>
+      </c>
+      <c r="D436" t="n">
+        <v>4</v>
+      </c>
+      <c r="E436" t="n">
+        <v>17</v>
+      </c>
+      <c r="F436" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="G436" t="n">
+        <v>5</v>
+      </c>
+      <c r="H436" t="n">
+        <v>0</v>
+      </c>
+      <c r="I436" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="J436" t="n">
+        <v>0</v>
+      </c>
+      <c r="K436" t="n">
+        <v>189.39</v>
+      </c>
+      <c r="L436" t="n">
+        <v>0</v>
+      </c>
+      <c r="M436" t="n">
+        <v>0</v>
+      </c>
+      <c r="N436" t="n">
+        <v>1</v>
+      </c>
+      <c r="O436" t="n">
+        <v>6</v>
+      </c>
+      <c r="P436" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q436" t="n">
+        <v>1</v>
+      </c>
+      <c r="R436" t="n">
+        <v>1</v>
+      </c>
+      <c r="S436" t="n">
+        <v>0</v>
+      </c>
+      <c r="T436" t="n">
+        <v>0</v>
+      </c>
+      <c r="U436" t="n">
+        <v>1</v>
+      </c>
+      <c r="V436" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W436" t="n">
+        <v>23</v>
+      </c>
+      <c r="X436" t="inlineStr">
+        <is>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA vs EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>2487736</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>A. SISTAC RODRIGUEZ | E. DUQUE NEGRÍN | M. KHIVRENKO | P. ARGÜELLES ELORZA | P. HERNANDEZ RODRIGUEZ</t>
+        </is>
+      </c>
+      <c r="D437" t="n">
+        <v>5</v>
+      </c>
+      <c r="E437" t="n">
+        <v>17</v>
+      </c>
+      <c r="F437" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="G437" t="n">
+        <v>0</v>
+      </c>
+      <c r="H437" t="n">
+        <v>2</v>
+      </c>
+      <c r="I437" t="n">
+        <v>0</v>
+      </c>
+      <c r="J437" t="n">
+        <v>2</v>
+      </c>
+      <c r="K437" t="n">
+        <v>0</v>
+      </c>
+      <c r="L437" t="n">
+        <v>100</v>
+      </c>
+      <c r="M437" t="n">
+        <v>0</v>
+      </c>
+      <c r="N437" t="n">
+        <v>0</v>
+      </c>
+      <c r="O437" t="n">
+        <v>0</v>
+      </c>
+      <c r="P437" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q437" t="n">
+        <v>0</v>
+      </c>
+      <c r="R437" t="n">
+        <v>2</v>
+      </c>
+      <c r="S437" t="n">
+        <v>0</v>
+      </c>
+      <c r="T437" t="n">
+        <v>0</v>
+      </c>
+      <c r="U437" t="n">
+        <v>0</v>
+      </c>
+      <c r="V437" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W437" t="n">
+        <v>23</v>
+      </c>
+      <c r="X437" t="inlineStr">
+        <is>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA vs EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>2487736</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>A. SISTAC RODRIGUEZ | K. RIVEROL DE LAS CASAS | M. KHIVRENKO | P. ARGÜELLES ELORZA</t>
+        </is>
+      </c>
+      <c r="D438" t="n">
+        <v>4</v>
+      </c>
+      <c r="E438" t="n">
+        <v>42</v>
+      </c>
+      <c r="F438" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G438" t="n">
+        <v>1</v>
+      </c>
+      <c r="H438" t="n">
+        <v>0</v>
+      </c>
+      <c r="I438" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="J438" t="n">
+        <v>2</v>
+      </c>
+      <c r="K438" t="n">
+        <v>113.64</v>
+      </c>
+      <c r="L438" t="n">
+        <v>0</v>
+      </c>
+      <c r="M438" t="n">
+        <v>113.64</v>
+      </c>
+      <c r="N438" t="n">
+        <v>0</v>
+      </c>
+      <c r="O438" t="n">
+        <v>2</v>
+      </c>
+      <c r="P438" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q438" t="n">
+        <v>0</v>
+      </c>
+      <c r="R438" t="n">
+        <v>1</v>
+      </c>
+      <c r="S438" t="n">
+        <v>0</v>
+      </c>
+      <c r="T438" t="n">
+        <v>1</v>
+      </c>
+      <c r="U438" t="n">
+        <v>0</v>
+      </c>
+      <c r="V438" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W438" t="n">
+        <v>23</v>
+      </c>
+      <c r="X438" t="inlineStr">
+        <is>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA vs EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>2487736</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>B. FERNANDEZ SHEPHARD | E. DUQUE NEGRÍN | J. GALLETTO LAMELA | K. RIVEROL DE LAS CASAS | M. KHIVRENKO</t>
+        </is>
+      </c>
+      <c r="D439" t="n">
+        <v>5</v>
+      </c>
+      <c r="E439" t="n">
+        <v>22</v>
+      </c>
+      <c r="F439" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="G439" t="n">
+        <v>0</v>
+      </c>
+      <c r="H439" t="n">
+        <v>0</v>
+      </c>
+      <c r="I439" t="n">
+        <v>1</v>
+      </c>
+      <c r="J439" t="n">
+        <v>0</v>
+      </c>
+      <c r="K439" t="n">
+        <v>0</v>
+      </c>
+      <c r="L439" t="n">
+        <v>0</v>
+      </c>
+      <c r="M439" t="n">
+        <v>0</v>
+      </c>
+      <c r="N439" t="n">
+        <v>0</v>
+      </c>
+      <c r="O439" t="n">
+        <v>0</v>
+      </c>
+      <c r="P439" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q439" t="n">
+        <v>0</v>
+      </c>
+      <c r="R439" t="n">
+        <v>0</v>
+      </c>
+      <c r="S439" t="n">
+        <v>0</v>
+      </c>
+      <c r="T439" t="n">
+        <v>0</v>
+      </c>
+      <c r="U439" t="n">
+        <v>0</v>
+      </c>
+      <c r="V439" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W439" t="n">
+        <v>23</v>
+      </c>
+      <c r="X439" t="inlineStr">
+        <is>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA vs EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>2487736</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>B. FERNANDEZ SHEPHARD | E. DUQUE NEGRÍN | K. RIVEROL DE LAS CASAS | M. KHIVRENKO | P. ARGÜELLES ELORZA</t>
+        </is>
+      </c>
+      <c r="D440" t="n">
+        <v>5</v>
+      </c>
+      <c r="E440" t="n">
+        <v>32</v>
+      </c>
+      <c r="F440" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="G440" t="n">
+        <v>0</v>
+      </c>
+      <c r="H440" t="n">
+        <v>0</v>
+      </c>
+      <c r="I440" t="n">
+        <v>1</v>
+      </c>
+      <c r="J440" t="n">
+        <v>1</v>
+      </c>
+      <c r="K440" t="n">
+        <v>0</v>
+      </c>
+      <c r="L440" t="n">
+        <v>0</v>
+      </c>
+      <c r="M440" t="n">
+        <v>0</v>
+      </c>
+      <c r="N440" t="n">
+        <v>1</v>
+      </c>
+      <c r="O440" t="n">
+        <v>0</v>
+      </c>
+      <c r="P440" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q440" t="n">
+        <v>0</v>
+      </c>
+      <c r="R440" t="n">
+        <v>1</v>
+      </c>
+      <c r="S440" t="n">
+        <v>0</v>
+      </c>
+      <c r="T440" t="n">
+        <v>0</v>
+      </c>
+      <c r="U440" t="n">
+        <v>0</v>
+      </c>
+      <c r="V440" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W440" t="n">
+        <v>23</v>
+      </c>
+      <c r="X440" t="inlineStr">
+        <is>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA vs EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>2487736</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>B. FERNANDEZ SHEPHARD | J. GALLETTO LAMELA | K. RIVEROL DE LAS CASAS | M. KHIVRENKO | P. ARGÜELLES ELORZA</t>
+        </is>
+      </c>
+      <c r="D441" t="n">
+        <v>5</v>
+      </c>
+      <c r="E441" t="n">
+        <v>120</v>
+      </c>
+      <c r="F441" t="n">
+        <v>2</v>
+      </c>
+      <c r="G441" t="n">
+        <v>0</v>
+      </c>
+      <c r="H441" t="n">
+        <v>0</v>
+      </c>
+      <c r="I441" t="n">
+        <v>2</v>
+      </c>
+      <c r="J441" t="n">
+        <v>2</v>
+      </c>
+      <c r="K441" t="n">
+        <v>0</v>
+      </c>
+      <c r="L441" t="n">
+        <v>0</v>
+      </c>
+      <c r="M441" t="n">
+        <v>0</v>
+      </c>
+      <c r="N441" t="n">
+        <v>3</v>
+      </c>
+      <c r="O441" t="n">
+        <v>0</v>
+      </c>
+      <c r="P441" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q441" t="n">
+        <v>2</v>
+      </c>
+      <c r="R441" t="n">
+        <v>3</v>
+      </c>
+      <c r="S441" t="n">
+        <v>0</v>
+      </c>
+      <c r="T441" t="n">
+        <v>0</v>
+      </c>
+      <c r="U441" t="n">
+        <v>1</v>
+      </c>
+      <c r="V441" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W441" t="n">
+        <v>23</v>
+      </c>
+      <c r="X441" t="inlineStr">
+        <is>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA vs EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>2487736</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>B. FERNANDEZ SHEPHARD | J. GALLETTO LAMELA | M. KHIVRENKO | P. ARGÜELLES ELORZA | P. HERNANDEZ RODRIGUEZ</t>
+        </is>
+      </c>
+      <c r="D442" t="n">
+        <v>5</v>
+      </c>
+      <c r="E442" t="n">
+        <v>32</v>
+      </c>
+      <c r="F442" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="G442" t="n">
+        <v>3</v>
+      </c>
+      <c r="H442" t="n">
+        <v>3</v>
+      </c>
+      <c r="I442" t="n">
+        <v>1</v>
+      </c>
+      <c r="J442" t="n">
+        <v>1</v>
+      </c>
+      <c r="K442" t="n">
+        <v>300</v>
+      </c>
+      <c r="L442" t="n">
+        <v>300</v>
+      </c>
+      <c r="M442" t="n">
+        <v>0</v>
+      </c>
+      <c r="N442" t="n">
+        <v>1</v>
+      </c>
+      <c r="O442" t="n">
+        <v>0</v>
+      </c>
+      <c r="P442" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q442" t="n">
+        <v>0</v>
+      </c>
+      <c r="R442" t="n">
+        <v>1</v>
+      </c>
+      <c r="S442" t="n">
+        <v>0</v>
+      </c>
+      <c r="T442" t="n">
+        <v>0</v>
+      </c>
+      <c r="U442" t="n">
+        <v>0</v>
+      </c>
+      <c r="V442" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W442" t="n">
+        <v>23</v>
+      </c>
+      <c r="X442" t="inlineStr">
+        <is>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA vs EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>2487738</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>BALONCESTO TALAVERA</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>A. VICENTE VIANA | C. UNANUE CEGARRA | D. LORENZO NEGRETE | J. FRANCES PASCUAL | S. GACIC</t>
+        </is>
+      </c>
+      <c r="D443" t="n">
+        <v>5</v>
+      </c>
+      <c r="E443" t="n">
+        <v>133</v>
+      </c>
+      <c r="F443" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="G443" t="n">
+        <v>2</v>
+      </c>
+      <c r="H443" t="n">
+        <v>3</v>
+      </c>
+      <c r="I443" t="n">
+        <v>5</v>
+      </c>
+      <c r="J443" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="K443" t="n">
+        <v>40</v>
+      </c>
+      <c r="L443" t="n">
+        <v>108.7</v>
+      </c>
+      <c r="M443" t="n">
+        <v>-68.7</v>
+      </c>
+      <c r="N443" t="n">
+        <v>4</v>
+      </c>
+      <c r="O443" t="n">
+        <v>0</v>
+      </c>
+      <c r="P443" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q443" t="n">
+        <v>1</v>
+      </c>
+      <c r="R443" t="n">
+        <v>3</v>
+      </c>
+      <c r="S443" t="n">
+        <v>4</v>
+      </c>
+      <c r="T443" t="n">
+        <v>0</v>
+      </c>
+      <c r="U443" t="n">
+        <v>2</v>
+      </c>
+      <c r="V443" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W443" t="n">
+        <v>24</v>
+      </c>
+      <c r="X443" t="inlineStr">
+        <is>
+          <t>BALONCESTO TALAVERA vs BALONCESTO TELDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>2487738</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>BALONCESTO TALAVERA</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>B. GUEYE | C. UNANUE CEGARRA | D. LORENZO NEGRETE | J. FRANCES PASCUAL | S. GACIC</t>
+        </is>
+      </c>
+      <c r="D444" t="n">
+        <v>5</v>
+      </c>
+      <c r="E444" t="n">
+        <v>75</v>
+      </c>
+      <c r="F444" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="G444" t="n">
+        <v>2</v>
+      </c>
+      <c r="H444" t="n">
+        <v>2</v>
+      </c>
+      <c r="I444" t="n">
+        <v>2</v>
+      </c>
+      <c r="J444" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="K444" t="n">
+        <v>100</v>
+      </c>
+      <c r="L444" t="n">
+        <v>69.44</v>
+      </c>
+      <c r="M444" t="n">
+        <v>30.56</v>
+      </c>
+      <c r="N444" t="n">
+        <v>1</v>
+      </c>
+      <c r="O444" t="n">
+        <v>0</v>
+      </c>
+      <c r="P444" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q444" t="n">
+        <v>1</v>
+      </c>
+      <c r="R444" t="n">
+        <v>1</v>
+      </c>
+      <c r="S444" t="n">
+        <v>2</v>
+      </c>
+      <c r="T444" t="n">
+        <v>1</v>
+      </c>
+      <c r="U444" t="n">
+        <v>0</v>
+      </c>
+      <c r="V444" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W444" t="n">
+        <v>24</v>
+      </c>
+      <c r="X444" t="inlineStr">
+        <is>
+          <t>BALONCESTO TALAVERA vs BALONCESTO TELDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>2487738</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>BALONCESTO TALAVERA</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>C. KLOTZ MAROTO | D. LORENZO NEGRETE | J. FRANCES PASCUAL | S. GACIC | V. ALONSO PASCUAL</t>
+        </is>
+      </c>
+      <c r="D445" t="n">
+        <v>5</v>
+      </c>
+      <c r="E445" t="n">
+        <v>49</v>
+      </c>
+      <c r="F445" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="G445" t="n">
+        <v>0</v>
+      </c>
+      <c r="H445" t="n">
+        <v>2</v>
+      </c>
+      <c r="I445" t="n">
+        <v>1</v>
+      </c>
+      <c r="J445" t="n">
+        <v>2</v>
+      </c>
+      <c r="K445" t="n">
+        <v>0</v>
+      </c>
+      <c r="L445" t="n">
+        <v>100</v>
+      </c>
+      <c r="M445" t="n">
+        <v>-100</v>
+      </c>
+      <c r="N445" t="n">
+        <v>1</v>
+      </c>
+      <c r="O445" t="n">
+        <v>0</v>
+      </c>
+      <c r="P445" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q445" t="n">
+        <v>1</v>
+      </c>
+      <c r="R445" t="n">
+        <v>2</v>
+      </c>
+      <c r="S445" t="n">
+        <v>0</v>
+      </c>
+      <c r="T445" t="n">
+        <v>0</v>
+      </c>
+      <c r="U445" t="n">
+        <v>0</v>
+      </c>
+      <c r="V445" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W445" t="n">
+        <v>24</v>
+      </c>
+      <c r="X445" t="inlineStr">
+        <is>
+          <t>BALONCESTO TALAVERA vs BALONCESTO TELDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>2487738</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>BALONCESTO TALAVERA</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>C. UNANUE CEGARRA | D. LORENZO NEGRETE | J. FRANCES PASCUAL | S. GACIC | V. ALONSO PASCUAL</t>
+        </is>
+      </c>
+      <c r="D446" t="n">
+        <v>5</v>
+      </c>
+      <c r="E446" t="n">
+        <v>38</v>
+      </c>
+      <c r="F446" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="G446" t="n">
+        <v>3</v>
+      </c>
+      <c r="H446" t="n">
+        <v>3</v>
+      </c>
+      <c r="I446" t="n">
+        <v>2</v>
+      </c>
+      <c r="J446" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="K446" t="n">
+        <v>150</v>
+      </c>
+      <c r="L446" t="n">
+        <v>340.91</v>
+      </c>
+      <c r="M446" t="n">
+        <v>-190.91</v>
+      </c>
+      <c r="N446" t="n">
+        <v>2</v>
+      </c>
+      <c r="O446" t="n">
+        <v>0</v>
+      </c>
+      <c r="P446" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q446" t="n">
+        <v>0</v>
+      </c>
+      <c r="R446" t="n">
+        <v>1</v>
+      </c>
+      <c r="S446" t="n">
+        <v>2</v>
+      </c>
+      <c r="T446" t="n">
+        <v>0</v>
+      </c>
+      <c r="U446" t="n">
+        <v>1</v>
+      </c>
+      <c r="V446" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W446" t="n">
+        <v>24</v>
+      </c>
+      <c r="X446" t="inlineStr">
+        <is>
+          <t>BALONCESTO TALAVERA vs BALONCESTO TELDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>2487738</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>BALONCESTO TELDE</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>A. FERNÁNDEZ GÓMEZ | A. MARTIN GONZALEZ | A. SANTANA OJEDA | A. VIDAL RODRIGUEZ | G. ARTILES ROMERO</t>
+        </is>
+      </c>
+      <c r="D447" t="n">
+        <v>5</v>
+      </c>
+      <c r="E447" t="n">
+        <v>34</v>
+      </c>
+      <c r="F447" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="G447" t="n">
+        <v>2</v>
+      </c>
+      <c r="H447" t="n">
+        <v>0</v>
+      </c>
+      <c r="I447" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="J447" t="n">
+        <v>1</v>
+      </c>
+      <c r="K447" t="n">
+        <v>106.38</v>
+      </c>
+      <c r="L447" t="n">
+        <v>0</v>
+      </c>
+      <c r="M447" t="n">
+        <v>106.38</v>
+      </c>
+      <c r="N447" t="n">
+        <v>2</v>
+      </c>
+      <c r="O447" t="n">
+        <v>2</v>
+      </c>
+      <c r="P447" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q447" t="n">
+        <v>1</v>
+      </c>
+      <c r="R447" t="n">
+        <v>1</v>
+      </c>
+      <c r="S447" t="n">
+        <v>0</v>
+      </c>
+      <c r="T447" t="n">
+        <v>1</v>
+      </c>
+      <c r="U447" t="n">
+        <v>1</v>
+      </c>
+      <c r="V447" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W447" t="n">
+        <v>24</v>
+      </c>
+      <c r="X447" t="inlineStr">
+        <is>
+          <t>BALONCESTO TALAVERA vs BALONCESTO TELDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>2487738</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>BALONCESTO TELDE</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>A. FERNÁNDEZ GÓMEZ | A. SANTANA OJEDA | A. VIDAL RODRIGUEZ | G. ARTILES ROMERO | J. JIMENEZ HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D448" t="n">
+        <v>5</v>
+      </c>
+      <c r="E448" t="n">
+        <v>233</v>
+      </c>
+      <c r="F448" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="G448" t="n">
+        <v>8</v>
+      </c>
+      <c r="H448" t="n">
+        <v>7</v>
+      </c>
+      <c r="I448" t="n">
+        <v>6.64</v>
+      </c>
+      <c r="J448" t="n">
+        <v>8</v>
+      </c>
+      <c r="K448" t="n">
+        <v>120.48</v>
+      </c>
+      <c r="L448" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="M448" t="n">
+        <v>32.98</v>
+      </c>
+      <c r="N448" t="n">
+        <v>5</v>
+      </c>
+      <c r="O448" t="n">
+        <v>6</v>
+      </c>
+      <c r="P448" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q448" t="n">
+        <v>2</v>
+      </c>
+      <c r="R448" t="n">
+        <v>6</v>
+      </c>
+      <c r="S448" t="n">
+        <v>0</v>
+      </c>
+      <c r="T448" t="n">
+        <v>4</v>
+      </c>
+      <c r="U448" t="n">
+        <v>2</v>
+      </c>
+      <c r="V448" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W448" t="n">
+        <v>24</v>
+      </c>
+      <c r="X448" t="inlineStr">
+        <is>
+          <t>BALONCESTO TALAVERA vs BALONCESTO TELDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>2487738</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>BALONCESTO TELDE</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>A. MARTIN GONZALEZ | A. SANTANA OJEDA | A. VIDAL RODRIGUEZ | G. ARTILES ROMERO | J. JIMENEZ HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D449" t="n">
+        <v>5</v>
+      </c>
+      <c r="E449" t="n">
+        <v>28</v>
+      </c>
+      <c r="F449" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="G449" t="n">
+        <v>0</v>
+      </c>
+      <c r="H449" t="n">
+        <v>0</v>
+      </c>
+      <c r="I449" t="n">
+        <v>0</v>
+      </c>
+      <c r="J449" t="n">
+        <v>1</v>
+      </c>
+      <c r="K449" t="n">
+        <v>0</v>
+      </c>
+      <c r="L449" t="n">
+        <v>0</v>
+      </c>
+      <c r="M449" t="n">
+        <v>0</v>
+      </c>
+      <c r="N449" t="n">
+        <v>0</v>
+      </c>
+      <c r="O449" t="n">
+        <v>0</v>
+      </c>
+      <c r="P449" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q449" t="n">
+        <v>0</v>
+      </c>
+      <c r="R449" t="n">
+        <v>1</v>
+      </c>
+      <c r="S449" t="n">
+        <v>0</v>
+      </c>
+      <c r="T449" t="n">
+        <v>0</v>
+      </c>
+      <c r="U449" t="n">
+        <v>0</v>
+      </c>
+      <c r="V449" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W449" t="n">
+        <v>24</v>
+      </c>
+      <c r="X449" t="inlineStr">
+        <is>
+          <t>BALONCESTO TALAVERA vs BALONCESTO TELDE</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/3FEB_25_26/clutch_lineups_25_26_3FEB.xlsx
+++ b/data/3FEB_25_26/clutch_lineups_25_26_3FEB.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X431"/>
+  <dimension ref="A1:X482"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36670,6 +36670,4290 @@
         </is>
       </c>
     </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>2487736</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>A. APARICIO IZQUIERDO | A. JIMENEZ FERNANDEZ | D. RODRIGUEZ GARCIA | J. RIES | P. RODRIGUEZ RIVERO</t>
+        </is>
+      </c>
+      <c r="D432" t="n">
+        <v>5</v>
+      </c>
+      <c r="E432" t="n">
+        <v>4</v>
+      </c>
+      <c r="F432" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="G432" t="n">
+        <v>5</v>
+      </c>
+      <c r="H432" t="n">
+        <v>0</v>
+      </c>
+      <c r="I432" t="n">
+        <v>2</v>
+      </c>
+      <c r="J432" t="n">
+        <v>0</v>
+      </c>
+      <c r="K432" t="n">
+        <v>250</v>
+      </c>
+      <c r="L432" t="n">
+        <v>0</v>
+      </c>
+      <c r="M432" t="n">
+        <v>0</v>
+      </c>
+      <c r="N432" t="n">
+        <v>2</v>
+      </c>
+      <c r="O432" t="n">
+        <v>0</v>
+      </c>
+      <c r="P432" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q432" t="n">
+        <v>0</v>
+      </c>
+      <c r="R432" t="n">
+        <v>0</v>
+      </c>
+      <c r="S432" t="n">
+        <v>0</v>
+      </c>
+      <c r="T432" t="n">
+        <v>0</v>
+      </c>
+      <c r="U432" t="n">
+        <v>0</v>
+      </c>
+      <c r="V432" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W432" t="n">
+        <v>23</v>
+      </c>
+      <c r="X432" t="inlineStr">
+        <is>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA vs EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>2487736</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>A. APARICIO IZQUIERDO | A. JIMENEZ FERNANDEZ | D. RODRIGUEZ GARCIA | M. NIANG | P. RODRIGUEZ RIVERO</t>
+        </is>
+      </c>
+      <c r="D433" t="n">
+        <v>5</v>
+      </c>
+      <c r="E433" t="n">
+        <v>46</v>
+      </c>
+      <c r="F433" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="G433" t="n">
+        <v>0</v>
+      </c>
+      <c r="H433" t="n">
+        <v>0</v>
+      </c>
+      <c r="I433" t="n">
+        <v>1</v>
+      </c>
+      <c r="J433" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K433" t="n">
+        <v>0</v>
+      </c>
+      <c r="L433" t="n">
+        <v>0</v>
+      </c>
+      <c r="M433" t="n">
+        <v>0</v>
+      </c>
+      <c r="N433" t="n">
+        <v>1</v>
+      </c>
+      <c r="O433" t="n">
+        <v>0</v>
+      </c>
+      <c r="P433" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q433" t="n">
+        <v>0</v>
+      </c>
+      <c r="R433" t="n">
+        <v>0</v>
+      </c>
+      <c r="S433" t="n">
+        <v>0</v>
+      </c>
+      <c r="T433" t="n">
+        <v>0</v>
+      </c>
+      <c r="U433" t="n">
+        <v>1</v>
+      </c>
+      <c r="V433" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W433" t="n">
+        <v>23</v>
+      </c>
+      <c r="X433" t="inlineStr">
+        <is>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA vs EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>2487736</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>A. APARICIO IZQUIERDO | D. RODRIGUEZ GARCIA | J. RIES | M. NIANG | P. RODRIGUEZ RIVERO</t>
+        </is>
+      </c>
+      <c r="D434" t="n">
+        <v>5</v>
+      </c>
+      <c r="E434" t="n">
+        <v>236</v>
+      </c>
+      <c r="F434" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="G434" t="n">
+        <v>5</v>
+      </c>
+      <c r="H434" t="n">
+        <v>9</v>
+      </c>
+      <c r="I434" t="n">
+        <v>7</v>
+      </c>
+      <c r="J434" t="n">
+        <v>9.52</v>
+      </c>
+      <c r="K434" t="n">
+        <v>71.43000000000001</v>
+      </c>
+      <c r="L434" t="n">
+        <v>94.54000000000001</v>
+      </c>
+      <c r="M434" t="n">
+        <v>-23.11</v>
+      </c>
+      <c r="N434" t="n">
+        <v>8</v>
+      </c>
+      <c r="O434" t="n">
+        <v>0</v>
+      </c>
+      <c r="P434" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q434" t="n">
+        <v>2</v>
+      </c>
+      <c r="R434" t="n">
+        <v>6</v>
+      </c>
+      <c r="S434" t="n">
+        <v>8</v>
+      </c>
+      <c r="T434" t="n">
+        <v>2</v>
+      </c>
+      <c r="U434" t="n">
+        <v>2</v>
+      </c>
+      <c r="V434" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W434" t="n">
+        <v>23</v>
+      </c>
+      <c r="X434" t="inlineStr">
+        <is>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA vs EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>2487736</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>A. SISTAC RODRIGUEZ | B. FERNANDEZ SHEPHARD | K. RIVEROL DE LAS CASAS | P. ARGÜELLES ELORZA</t>
+        </is>
+      </c>
+      <c r="D435" t="n">
+        <v>4</v>
+      </c>
+      <c r="E435" t="n">
+        <v>4</v>
+      </c>
+      <c r="F435" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="G435" t="n">
+        <v>0</v>
+      </c>
+      <c r="H435" t="n">
+        <v>5</v>
+      </c>
+      <c r="I435" t="n">
+        <v>0</v>
+      </c>
+      <c r="J435" t="n">
+        <v>2</v>
+      </c>
+      <c r="K435" t="n">
+        <v>0</v>
+      </c>
+      <c r="L435" t="n">
+        <v>250</v>
+      </c>
+      <c r="M435" t="n">
+        <v>0</v>
+      </c>
+      <c r="N435" t="n">
+        <v>0</v>
+      </c>
+      <c r="O435" t="n">
+        <v>0</v>
+      </c>
+      <c r="P435" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q435" t="n">
+        <v>0</v>
+      </c>
+      <c r="R435" t="n">
+        <v>2</v>
+      </c>
+      <c r="S435" t="n">
+        <v>0</v>
+      </c>
+      <c r="T435" t="n">
+        <v>0</v>
+      </c>
+      <c r="U435" t="n">
+        <v>0</v>
+      </c>
+      <c r="V435" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W435" t="n">
+        <v>23</v>
+      </c>
+      <c r="X435" t="inlineStr">
+        <is>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA vs EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>2487736</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>A. SISTAC RODRIGUEZ | B. FERNANDEZ SHEPHARD | M. KHIVRENKO | P. ARGÜELLES ELORZA</t>
+        </is>
+      </c>
+      <c r="D436" t="n">
+        <v>4</v>
+      </c>
+      <c r="E436" t="n">
+        <v>17</v>
+      </c>
+      <c r="F436" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="G436" t="n">
+        <v>5</v>
+      </c>
+      <c r="H436" t="n">
+        <v>0</v>
+      </c>
+      <c r="I436" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="J436" t="n">
+        <v>0</v>
+      </c>
+      <c r="K436" t="n">
+        <v>189.39</v>
+      </c>
+      <c r="L436" t="n">
+        <v>0</v>
+      </c>
+      <c r="M436" t="n">
+        <v>0</v>
+      </c>
+      <c r="N436" t="n">
+        <v>1</v>
+      </c>
+      <c r="O436" t="n">
+        <v>6</v>
+      </c>
+      <c r="P436" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q436" t="n">
+        <v>1</v>
+      </c>
+      <c r="R436" t="n">
+        <v>1</v>
+      </c>
+      <c r="S436" t="n">
+        <v>0</v>
+      </c>
+      <c r="T436" t="n">
+        <v>0</v>
+      </c>
+      <c r="U436" t="n">
+        <v>1</v>
+      </c>
+      <c r="V436" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W436" t="n">
+        <v>23</v>
+      </c>
+      <c r="X436" t="inlineStr">
+        <is>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA vs EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>2487736</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>A. SISTAC RODRIGUEZ | E. DUQUE NEGRÍN | M. KHIVRENKO | P. ARGÜELLES ELORZA | P. HERNANDEZ RODRIGUEZ</t>
+        </is>
+      </c>
+      <c r="D437" t="n">
+        <v>5</v>
+      </c>
+      <c r="E437" t="n">
+        <v>17</v>
+      </c>
+      <c r="F437" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="G437" t="n">
+        <v>0</v>
+      </c>
+      <c r="H437" t="n">
+        <v>2</v>
+      </c>
+      <c r="I437" t="n">
+        <v>0</v>
+      </c>
+      <c r="J437" t="n">
+        <v>2</v>
+      </c>
+      <c r="K437" t="n">
+        <v>0</v>
+      </c>
+      <c r="L437" t="n">
+        <v>100</v>
+      </c>
+      <c r="M437" t="n">
+        <v>0</v>
+      </c>
+      <c r="N437" t="n">
+        <v>0</v>
+      </c>
+      <c r="O437" t="n">
+        <v>0</v>
+      </c>
+      <c r="P437" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q437" t="n">
+        <v>0</v>
+      </c>
+      <c r="R437" t="n">
+        <v>2</v>
+      </c>
+      <c r="S437" t="n">
+        <v>0</v>
+      </c>
+      <c r="T437" t="n">
+        <v>0</v>
+      </c>
+      <c r="U437" t="n">
+        <v>0</v>
+      </c>
+      <c r="V437" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W437" t="n">
+        <v>23</v>
+      </c>
+      <c r="X437" t="inlineStr">
+        <is>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA vs EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>2487736</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>A. SISTAC RODRIGUEZ | K. RIVEROL DE LAS CASAS | M. KHIVRENKO | P. ARGÜELLES ELORZA</t>
+        </is>
+      </c>
+      <c r="D438" t="n">
+        <v>4</v>
+      </c>
+      <c r="E438" t="n">
+        <v>42</v>
+      </c>
+      <c r="F438" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G438" t="n">
+        <v>1</v>
+      </c>
+      <c r="H438" t="n">
+        <v>0</v>
+      </c>
+      <c r="I438" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="J438" t="n">
+        <v>2</v>
+      </c>
+      <c r="K438" t="n">
+        <v>113.64</v>
+      </c>
+      <c r="L438" t="n">
+        <v>0</v>
+      </c>
+      <c r="M438" t="n">
+        <v>113.64</v>
+      </c>
+      <c r="N438" t="n">
+        <v>0</v>
+      </c>
+      <c r="O438" t="n">
+        <v>2</v>
+      </c>
+      <c r="P438" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q438" t="n">
+        <v>0</v>
+      </c>
+      <c r="R438" t="n">
+        <v>1</v>
+      </c>
+      <c r="S438" t="n">
+        <v>0</v>
+      </c>
+      <c r="T438" t="n">
+        <v>1</v>
+      </c>
+      <c r="U438" t="n">
+        <v>0</v>
+      </c>
+      <c r="V438" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W438" t="n">
+        <v>23</v>
+      </c>
+      <c r="X438" t="inlineStr">
+        <is>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA vs EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>2487736</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>B. FERNANDEZ SHEPHARD | E. DUQUE NEGRÍN | J. GALLETTO LAMELA | K. RIVEROL DE LAS CASAS | M. KHIVRENKO</t>
+        </is>
+      </c>
+      <c r="D439" t="n">
+        <v>5</v>
+      </c>
+      <c r="E439" t="n">
+        <v>22</v>
+      </c>
+      <c r="F439" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="G439" t="n">
+        <v>0</v>
+      </c>
+      <c r="H439" t="n">
+        <v>0</v>
+      </c>
+      <c r="I439" t="n">
+        <v>1</v>
+      </c>
+      <c r="J439" t="n">
+        <v>0</v>
+      </c>
+      <c r="K439" t="n">
+        <v>0</v>
+      </c>
+      <c r="L439" t="n">
+        <v>0</v>
+      </c>
+      <c r="M439" t="n">
+        <v>0</v>
+      </c>
+      <c r="N439" t="n">
+        <v>0</v>
+      </c>
+      <c r="O439" t="n">
+        <v>0</v>
+      </c>
+      <c r="P439" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q439" t="n">
+        <v>0</v>
+      </c>
+      <c r="R439" t="n">
+        <v>0</v>
+      </c>
+      <c r="S439" t="n">
+        <v>0</v>
+      </c>
+      <c r="T439" t="n">
+        <v>0</v>
+      </c>
+      <c r="U439" t="n">
+        <v>0</v>
+      </c>
+      <c r="V439" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W439" t="n">
+        <v>23</v>
+      </c>
+      <c r="X439" t="inlineStr">
+        <is>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA vs EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>2487736</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>B. FERNANDEZ SHEPHARD | E. DUQUE NEGRÍN | K. RIVEROL DE LAS CASAS | M. KHIVRENKO | P. ARGÜELLES ELORZA</t>
+        </is>
+      </c>
+      <c r="D440" t="n">
+        <v>5</v>
+      </c>
+      <c r="E440" t="n">
+        <v>32</v>
+      </c>
+      <c r="F440" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="G440" t="n">
+        <v>0</v>
+      </c>
+      <c r="H440" t="n">
+        <v>0</v>
+      </c>
+      <c r="I440" t="n">
+        <v>1</v>
+      </c>
+      <c r="J440" t="n">
+        <v>1</v>
+      </c>
+      <c r="K440" t="n">
+        <v>0</v>
+      </c>
+      <c r="L440" t="n">
+        <v>0</v>
+      </c>
+      <c r="M440" t="n">
+        <v>0</v>
+      </c>
+      <c r="N440" t="n">
+        <v>1</v>
+      </c>
+      <c r="O440" t="n">
+        <v>0</v>
+      </c>
+      <c r="P440" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q440" t="n">
+        <v>0</v>
+      </c>
+      <c r="R440" t="n">
+        <v>1</v>
+      </c>
+      <c r="S440" t="n">
+        <v>0</v>
+      </c>
+      <c r="T440" t="n">
+        <v>0</v>
+      </c>
+      <c r="U440" t="n">
+        <v>0</v>
+      </c>
+      <c r="V440" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W440" t="n">
+        <v>23</v>
+      </c>
+      <c r="X440" t="inlineStr">
+        <is>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA vs EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>2487736</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>B. FERNANDEZ SHEPHARD | J. GALLETTO LAMELA | K. RIVEROL DE LAS CASAS | M. KHIVRENKO | P. ARGÜELLES ELORZA</t>
+        </is>
+      </c>
+      <c r="D441" t="n">
+        <v>5</v>
+      </c>
+      <c r="E441" t="n">
+        <v>120</v>
+      </c>
+      <c r="F441" t="n">
+        <v>2</v>
+      </c>
+      <c r="G441" t="n">
+        <v>0</v>
+      </c>
+      <c r="H441" t="n">
+        <v>0</v>
+      </c>
+      <c r="I441" t="n">
+        <v>2</v>
+      </c>
+      <c r="J441" t="n">
+        <v>2</v>
+      </c>
+      <c r="K441" t="n">
+        <v>0</v>
+      </c>
+      <c r="L441" t="n">
+        <v>0</v>
+      </c>
+      <c r="M441" t="n">
+        <v>0</v>
+      </c>
+      <c r="N441" t="n">
+        <v>3</v>
+      </c>
+      <c r="O441" t="n">
+        <v>0</v>
+      </c>
+      <c r="P441" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q441" t="n">
+        <v>2</v>
+      </c>
+      <c r="R441" t="n">
+        <v>3</v>
+      </c>
+      <c r="S441" t="n">
+        <v>0</v>
+      </c>
+      <c r="T441" t="n">
+        <v>0</v>
+      </c>
+      <c r="U441" t="n">
+        <v>1</v>
+      </c>
+      <c r="V441" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W441" t="n">
+        <v>23</v>
+      </c>
+      <c r="X441" t="inlineStr">
+        <is>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA vs EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>2487736</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>B. FERNANDEZ SHEPHARD | J. GALLETTO LAMELA | M. KHIVRENKO | P. ARGÜELLES ELORZA | P. HERNANDEZ RODRIGUEZ</t>
+        </is>
+      </c>
+      <c r="D442" t="n">
+        <v>5</v>
+      </c>
+      <c r="E442" t="n">
+        <v>32</v>
+      </c>
+      <c r="F442" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="G442" t="n">
+        <v>3</v>
+      </c>
+      <c r="H442" t="n">
+        <v>3</v>
+      </c>
+      <c r="I442" t="n">
+        <v>1</v>
+      </c>
+      <c r="J442" t="n">
+        <v>1</v>
+      </c>
+      <c r="K442" t="n">
+        <v>300</v>
+      </c>
+      <c r="L442" t="n">
+        <v>300</v>
+      </c>
+      <c r="M442" t="n">
+        <v>0</v>
+      </c>
+      <c r="N442" t="n">
+        <v>1</v>
+      </c>
+      <c r="O442" t="n">
+        <v>0</v>
+      </c>
+      <c r="P442" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q442" t="n">
+        <v>0</v>
+      </c>
+      <c r="R442" t="n">
+        <v>1</v>
+      </c>
+      <c r="S442" t="n">
+        <v>0</v>
+      </c>
+      <c r="T442" t="n">
+        <v>0</v>
+      </c>
+      <c r="U442" t="n">
+        <v>0</v>
+      </c>
+      <c r="V442" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W442" t="n">
+        <v>23</v>
+      </c>
+      <c r="X442" t="inlineStr">
+        <is>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA vs EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>2487737</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>BALONCESTO TELDE</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>A. FERNÁNDEZ GÓMEZ | A. MARTIN GONZALEZ | A. SANTANA OJEDA | G. ARTILES ROMERO | J. JIMENEZ HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D443" t="n">
+        <v>5</v>
+      </c>
+      <c r="E443" t="n">
+        <v>159</v>
+      </c>
+      <c r="F443" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="G443" t="n">
+        <v>4</v>
+      </c>
+      <c r="H443" t="n">
+        <v>7</v>
+      </c>
+      <c r="I443" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="J443" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="K443" t="n">
+        <v>68.03</v>
+      </c>
+      <c r="L443" t="n">
+        <v>253.62</v>
+      </c>
+      <c r="M443" t="n">
+        <v>-185.6</v>
+      </c>
+      <c r="N443" t="n">
+        <v>7</v>
+      </c>
+      <c r="O443" t="n">
+        <v>2</v>
+      </c>
+      <c r="P443" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q443" t="n">
+        <v>2</v>
+      </c>
+      <c r="R443" t="n">
+        <v>3</v>
+      </c>
+      <c r="S443" t="n">
+        <v>4</v>
+      </c>
+      <c r="T443" t="n">
+        <v>1</v>
+      </c>
+      <c r="U443" t="n">
+        <v>3</v>
+      </c>
+      <c r="V443" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W443" t="n">
+        <v>23</v>
+      </c>
+      <c r="X443" t="inlineStr">
+        <is>
+          <t>C.B. TRES CANTOS vs BALONCESTO TELDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>2487737</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>C.B. TRES CANTOS</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>A. SIMON DEL CORRAL | D. FERNANDEZ CAÑAS | G. DIAZ MONTERO | J. ATIENZA PEREA | N. MAIGA</t>
+        </is>
+      </c>
+      <c r="D444" t="n">
+        <v>5</v>
+      </c>
+      <c r="E444" t="n">
+        <v>65</v>
+      </c>
+      <c r="F444" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="G444" t="n">
+        <v>3</v>
+      </c>
+      <c r="H444" t="n">
+        <v>0</v>
+      </c>
+      <c r="I444" t="n">
+        <v>2</v>
+      </c>
+      <c r="J444" t="n">
+        <v>1</v>
+      </c>
+      <c r="K444" t="n">
+        <v>150</v>
+      </c>
+      <c r="L444" t="n">
+        <v>0</v>
+      </c>
+      <c r="M444" t="n">
+        <v>150</v>
+      </c>
+      <c r="N444" t="n">
+        <v>2</v>
+      </c>
+      <c r="O444" t="n">
+        <v>0</v>
+      </c>
+      <c r="P444" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q444" t="n">
+        <v>1</v>
+      </c>
+      <c r="R444" t="n">
+        <v>2</v>
+      </c>
+      <c r="S444" t="n">
+        <v>0</v>
+      </c>
+      <c r="T444" t="n">
+        <v>0</v>
+      </c>
+      <c r="U444" t="n">
+        <v>1</v>
+      </c>
+      <c r="V444" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W444" t="n">
+        <v>23</v>
+      </c>
+      <c r="X444" t="inlineStr">
+        <is>
+          <t>C.B. TRES CANTOS vs BALONCESTO TELDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>2487737</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>C.B. TRES CANTOS</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>A. SIMON DEL CORRAL | G. DIAZ MONTERO | G. LARDIES GUILLEN | J. ATIENZA PEREA | N. MAIGA</t>
+        </is>
+      </c>
+      <c r="D445" t="n">
+        <v>5</v>
+      </c>
+      <c r="E445" t="n">
+        <v>91</v>
+      </c>
+      <c r="F445" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="G445" t="n">
+        <v>4</v>
+      </c>
+      <c r="H445" t="n">
+        <v>4</v>
+      </c>
+      <c r="I445" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="J445" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="K445" t="n">
+        <v>526.3200000000001</v>
+      </c>
+      <c r="L445" t="n">
+        <v>81.97</v>
+      </c>
+      <c r="M445" t="n">
+        <v>444.35</v>
+      </c>
+      <c r="N445" t="n">
+        <v>1</v>
+      </c>
+      <c r="O445" t="n">
+        <v>4</v>
+      </c>
+      <c r="P445" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q445" t="n">
+        <v>2</v>
+      </c>
+      <c r="R445" t="n">
+        <v>5</v>
+      </c>
+      <c r="S445" t="n">
+        <v>2</v>
+      </c>
+      <c r="T445" t="n">
+        <v>0</v>
+      </c>
+      <c r="U445" t="n">
+        <v>1</v>
+      </c>
+      <c r="V445" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W445" t="n">
+        <v>23</v>
+      </c>
+      <c r="X445" t="inlineStr">
+        <is>
+          <t>C.B. TRES CANTOS vs BALONCESTO TELDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>2487737</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>C.B. TRES CANTOS</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>D. FERNANDEZ CAÑAS | G. DIAZ MONTERO | G. LARDIES GUILLEN | J. ATIENZA PEREA | N. MAIGA</t>
+        </is>
+      </c>
+      <c r="D446" t="n">
+        <v>5</v>
+      </c>
+      <c r="E446" t="n">
+        <v>3</v>
+      </c>
+      <c r="F446" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G446" t="n">
+        <v>0</v>
+      </c>
+      <c r="H446" t="n">
+        <v>0</v>
+      </c>
+      <c r="I446" t="n">
+        <v>0</v>
+      </c>
+      <c r="J446" t="n">
+        <v>0</v>
+      </c>
+      <c r="K446" t="n">
+        <v>0</v>
+      </c>
+      <c r="L446" t="n">
+        <v>0</v>
+      </c>
+      <c r="M446" t="n">
+        <v>0</v>
+      </c>
+      <c r="N446" t="n">
+        <v>0</v>
+      </c>
+      <c r="O446" t="n">
+        <v>0</v>
+      </c>
+      <c r="P446" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q446" t="n">
+        <v>0</v>
+      </c>
+      <c r="R446" t="n">
+        <v>0</v>
+      </c>
+      <c r="S446" t="n">
+        <v>0</v>
+      </c>
+      <c r="T446" t="n">
+        <v>0</v>
+      </c>
+      <c r="U446" t="n">
+        <v>0</v>
+      </c>
+      <c r="V446" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W446" t="n">
+        <v>23</v>
+      </c>
+      <c r="X446" t="inlineStr">
+        <is>
+          <t>C.B. TRES CANTOS vs BALONCESTO TELDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>2487732</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>CB ARIDANE</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>A. GASE SECO | D. VIERA LOPEZ | K. SKUTYELNIK | O. BALSELLS PLAZA | S. GUEYE</t>
+        </is>
+      </c>
+      <c r="D447" t="n">
+        <v>5</v>
+      </c>
+      <c r="E447" t="n">
+        <v>64</v>
+      </c>
+      <c r="F447" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="G447" t="n">
+        <v>0</v>
+      </c>
+      <c r="H447" t="n">
+        <v>3</v>
+      </c>
+      <c r="I447" t="n">
+        <v>2</v>
+      </c>
+      <c r="J447" t="n">
+        <v>2</v>
+      </c>
+      <c r="K447" t="n">
+        <v>0</v>
+      </c>
+      <c r="L447" t="n">
+        <v>150</v>
+      </c>
+      <c r="M447" t="n">
+        <v>-150</v>
+      </c>
+      <c r="N447" t="n">
+        <v>2</v>
+      </c>
+      <c r="O447" t="n">
+        <v>0</v>
+      </c>
+      <c r="P447" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q447" t="n">
+        <v>0</v>
+      </c>
+      <c r="R447" t="n">
+        <v>3</v>
+      </c>
+      <c r="S447" t="n">
+        <v>0</v>
+      </c>
+      <c r="T447" t="n">
+        <v>0</v>
+      </c>
+      <c r="U447" t="n">
+        <v>1</v>
+      </c>
+      <c r="V447" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W447" t="n">
+        <v>23</v>
+      </c>
+      <c r="X447" t="inlineStr">
+        <is>
+          <t>CB ARIDANE vs REAL CANOE N.C.</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>2487732</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>CB ARIDANE</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>A. GASE SECO | G. MEJÍA ACOSTA | G. PIERRE-GABRIEL ANDREA GASTON | K. SKUTYELNIK | O. BALSELLS PLAZA</t>
+        </is>
+      </c>
+      <c r="D448" t="n">
+        <v>5</v>
+      </c>
+      <c r="E448" t="n">
+        <v>13</v>
+      </c>
+      <c r="F448" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="G448" t="n">
+        <v>0</v>
+      </c>
+      <c r="H448" t="n">
+        <v>2</v>
+      </c>
+      <c r="I448" t="n">
+        <v>0</v>
+      </c>
+      <c r="J448" t="n">
+        <v>1</v>
+      </c>
+      <c r="K448" t="n">
+        <v>0</v>
+      </c>
+      <c r="L448" t="n">
+        <v>200</v>
+      </c>
+      <c r="M448" t="n">
+        <v>0</v>
+      </c>
+      <c r="N448" t="n">
+        <v>0</v>
+      </c>
+      <c r="O448" t="n">
+        <v>0</v>
+      </c>
+      <c r="P448" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q448" t="n">
+        <v>0</v>
+      </c>
+      <c r="R448" t="n">
+        <v>1</v>
+      </c>
+      <c r="S448" t="n">
+        <v>0</v>
+      </c>
+      <c r="T448" t="n">
+        <v>0</v>
+      </c>
+      <c r="U448" t="n">
+        <v>0</v>
+      </c>
+      <c r="V448" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W448" t="n">
+        <v>23</v>
+      </c>
+      <c r="X448" t="inlineStr">
+        <is>
+          <t>CB ARIDANE vs REAL CANOE N.C.</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>2487732</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>CB ARIDANE</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>A. GASE SECO | G. MEJÍA ACOSTA | K. SKUTYELNIK | O. BALSELLS PLAZA | S. GUEYE</t>
+        </is>
+      </c>
+      <c r="D449" t="n">
+        <v>5</v>
+      </c>
+      <c r="E449" t="n">
+        <v>55</v>
+      </c>
+      <c r="F449" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="G449" t="n">
+        <v>2</v>
+      </c>
+      <c r="H449" t="n">
+        <v>3</v>
+      </c>
+      <c r="I449" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="J449" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="K449" t="n">
+        <v>106.38</v>
+      </c>
+      <c r="L449" t="n">
+        <v>159.57</v>
+      </c>
+      <c r="M449" t="n">
+        <v>-53.19</v>
+      </c>
+      <c r="N449" t="n">
+        <v>1</v>
+      </c>
+      <c r="O449" t="n">
+        <v>2</v>
+      </c>
+      <c r="P449" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q449" t="n">
+        <v>0</v>
+      </c>
+      <c r="R449" t="n">
+        <v>2</v>
+      </c>
+      <c r="S449" t="n">
+        <v>2</v>
+      </c>
+      <c r="T449" t="n">
+        <v>0</v>
+      </c>
+      <c r="U449" t="n">
+        <v>1</v>
+      </c>
+      <c r="V449" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W449" t="n">
+        <v>23</v>
+      </c>
+      <c r="X449" t="inlineStr">
+        <is>
+          <t>CB ARIDANE vs REAL CANOE N.C.</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>2487732</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>REAL CANOE N.C.</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>D. MANZANERO CAMACHO | E. PASCUAL COZAR | J. LAPASTORA ARACIL | J. MARTINEZ SANTOS | N. LASUNCION MARIBLANCA</t>
+        </is>
+      </c>
+      <c r="D450" t="n">
+        <v>5</v>
+      </c>
+      <c r="E450" t="n">
+        <v>23</v>
+      </c>
+      <c r="F450" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="G450" t="n">
+        <v>0</v>
+      </c>
+      <c r="H450" t="n">
+        <v>0</v>
+      </c>
+      <c r="I450" t="n">
+        <v>1</v>
+      </c>
+      <c r="J450" t="n">
+        <v>1</v>
+      </c>
+      <c r="K450" t="n">
+        <v>0</v>
+      </c>
+      <c r="L450" t="n">
+        <v>0</v>
+      </c>
+      <c r="M450" t="n">
+        <v>0</v>
+      </c>
+      <c r="N450" t="n">
+        <v>2</v>
+      </c>
+      <c r="O450" t="n">
+        <v>0</v>
+      </c>
+      <c r="P450" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q450" t="n">
+        <v>1</v>
+      </c>
+      <c r="R450" t="n">
+        <v>1</v>
+      </c>
+      <c r="S450" t="n">
+        <v>0</v>
+      </c>
+      <c r="T450" t="n">
+        <v>0</v>
+      </c>
+      <c r="U450" t="n">
+        <v>0</v>
+      </c>
+      <c r="V450" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W450" t="n">
+        <v>23</v>
+      </c>
+      <c r="X450" t="inlineStr">
+        <is>
+          <t>CB ARIDANE vs REAL CANOE N.C.</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>2487732</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>REAL CANOE N.C.</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>D. MANZANERO CAMACHO | J. LAPASTORA ARACIL | J. MARTINEZ SANTOS | L. GARCIA LARRACHE SEGURA | N. LASUNCION MARIBLANCA</t>
+        </is>
+      </c>
+      <c r="D451" t="n">
+        <v>5</v>
+      </c>
+      <c r="E451" t="n">
+        <v>44</v>
+      </c>
+      <c r="F451" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="G451" t="n">
+        <v>3</v>
+      </c>
+      <c r="H451" t="n">
+        <v>0</v>
+      </c>
+      <c r="I451" t="n">
+        <v>1</v>
+      </c>
+      <c r="J451" t="n">
+        <v>1</v>
+      </c>
+      <c r="K451" t="n">
+        <v>300</v>
+      </c>
+      <c r="L451" t="n">
+        <v>0</v>
+      </c>
+      <c r="M451" t="n">
+        <v>300</v>
+      </c>
+      <c r="N451" t="n">
+        <v>2</v>
+      </c>
+      <c r="O451" t="n">
+        <v>0</v>
+      </c>
+      <c r="P451" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q451" t="n">
+        <v>1</v>
+      </c>
+      <c r="R451" t="n">
+        <v>1</v>
+      </c>
+      <c r="S451" t="n">
+        <v>0</v>
+      </c>
+      <c r="T451" t="n">
+        <v>0</v>
+      </c>
+      <c r="U451" t="n">
+        <v>0</v>
+      </c>
+      <c r="V451" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W451" t="n">
+        <v>23</v>
+      </c>
+      <c r="X451" t="inlineStr">
+        <is>
+          <t>CB ARIDANE vs REAL CANOE N.C.</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>2487732</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>REAL CANOE N.C.</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>J. LAPASTORA ARACIL | J. MARTINEZ SANTOS | L. GARCIA LARRACHE SEGURA | M. HERMOSO ALCUBILLA | N. LASUNCION MARIBLANCA</t>
+        </is>
+      </c>
+      <c r="D452" t="n">
+        <v>5</v>
+      </c>
+      <c r="E452" t="n">
+        <v>65</v>
+      </c>
+      <c r="F452" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="G452" t="n">
+        <v>5</v>
+      </c>
+      <c r="H452" t="n">
+        <v>2</v>
+      </c>
+      <c r="I452" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="J452" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="K452" t="n">
+        <v>173.61</v>
+      </c>
+      <c r="L452" t="n">
+        <v>106.38</v>
+      </c>
+      <c r="M452" t="n">
+        <v>67.23</v>
+      </c>
+      <c r="N452" t="n">
+        <v>2</v>
+      </c>
+      <c r="O452" t="n">
+        <v>2</v>
+      </c>
+      <c r="P452" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q452" t="n">
+        <v>0</v>
+      </c>
+      <c r="R452" t="n">
+        <v>1</v>
+      </c>
+      <c r="S452" t="n">
+        <v>2</v>
+      </c>
+      <c r="T452" t="n">
+        <v>0</v>
+      </c>
+      <c r="U452" t="n">
+        <v>0</v>
+      </c>
+      <c r="V452" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W452" t="n">
+        <v>23</v>
+      </c>
+      <c r="X452" t="inlineStr">
+        <is>
+          <t>CB ARIDANE vs REAL CANOE N.C.</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>2487738</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>BALONCESTO TALAVERA</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>A. VICENTE VIANA | C. UNANUE CEGARRA | D. LORENZO NEGRETE | J. FRANCES PASCUAL | S. GACIC</t>
+        </is>
+      </c>
+      <c r="D453" t="n">
+        <v>5</v>
+      </c>
+      <c r="E453" t="n">
+        <v>133</v>
+      </c>
+      <c r="F453" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="G453" t="n">
+        <v>2</v>
+      </c>
+      <c r="H453" t="n">
+        <v>3</v>
+      </c>
+      <c r="I453" t="n">
+        <v>5</v>
+      </c>
+      <c r="J453" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="K453" t="n">
+        <v>40</v>
+      </c>
+      <c r="L453" t="n">
+        <v>108.7</v>
+      </c>
+      <c r="M453" t="n">
+        <v>-68.7</v>
+      </c>
+      <c r="N453" t="n">
+        <v>4</v>
+      </c>
+      <c r="O453" t="n">
+        <v>0</v>
+      </c>
+      <c r="P453" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q453" t="n">
+        <v>1</v>
+      </c>
+      <c r="R453" t="n">
+        <v>3</v>
+      </c>
+      <c r="S453" t="n">
+        <v>4</v>
+      </c>
+      <c r="T453" t="n">
+        <v>0</v>
+      </c>
+      <c r="U453" t="n">
+        <v>2</v>
+      </c>
+      <c r="V453" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W453" t="n">
+        <v>24</v>
+      </c>
+      <c r="X453" t="inlineStr">
+        <is>
+          <t>BALONCESTO TALAVERA vs BALONCESTO TELDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>2487738</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>BALONCESTO TALAVERA</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>B. GUEYE | C. UNANUE CEGARRA | D. LORENZO NEGRETE | J. FRANCES PASCUAL | S. GACIC</t>
+        </is>
+      </c>
+      <c r="D454" t="n">
+        <v>5</v>
+      </c>
+      <c r="E454" t="n">
+        <v>75</v>
+      </c>
+      <c r="F454" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="G454" t="n">
+        <v>2</v>
+      </c>
+      <c r="H454" t="n">
+        <v>2</v>
+      </c>
+      <c r="I454" t="n">
+        <v>2</v>
+      </c>
+      <c r="J454" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="K454" t="n">
+        <v>100</v>
+      </c>
+      <c r="L454" t="n">
+        <v>69.44</v>
+      </c>
+      <c r="M454" t="n">
+        <v>30.56</v>
+      </c>
+      <c r="N454" t="n">
+        <v>1</v>
+      </c>
+      <c r="O454" t="n">
+        <v>0</v>
+      </c>
+      <c r="P454" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q454" t="n">
+        <v>1</v>
+      </c>
+      <c r="R454" t="n">
+        <v>1</v>
+      </c>
+      <c r="S454" t="n">
+        <v>2</v>
+      </c>
+      <c r="T454" t="n">
+        <v>1</v>
+      </c>
+      <c r="U454" t="n">
+        <v>0</v>
+      </c>
+      <c r="V454" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W454" t="n">
+        <v>24</v>
+      </c>
+      <c r="X454" t="inlineStr">
+        <is>
+          <t>BALONCESTO TALAVERA vs BALONCESTO TELDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>2487738</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>BALONCESTO TALAVERA</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>C. KLOTZ MAROTO | D. LORENZO NEGRETE | J. FRANCES PASCUAL | S. GACIC | V. ALONSO PASCUAL</t>
+        </is>
+      </c>
+      <c r="D455" t="n">
+        <v>5</v>
+      </c>
+      <c r="E455" t="n">
+        <v>49</v>
+      </c>
+      <c r="F455" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="G455" t="n">
+        <v>0</v>
+      </c>
+      <c r="H455" t="n">
+        <v>2</v>
+      </c>
+      <c r="I455" t="n">
+        <v>1</v>
+      </c>
+      <c r="J455" t="n">
+        <v>2</v>
+      </c>
+      <c r="K455" t="n">
+        <v>0</v>
+      </c>
+      <c r="L455" t="n">
+        <v>100</v>
+      </c>
+      <c r="M455" t="n">
+        <v>-100</v>
+      </c>
+      <c r="N455" t="n">
+        <v>1</v>
+      </c>
+      <c r="O455" t="n">
+        <v>0</v>
+      </c>
+      <c r="P455" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q455" t="n">
+        <v>1</v>
+      </c>
+      <c r="R455" t="n">
+        <v>2</v>
+      </c>
+      <c r="S455" t="n">
+        <v>0</v>
+      </c>
+      <c r="T455" t="n">
+        <v>0</v>
+      </c>
+      <c r="U455" t="n">
+        <v>0</v>
+      </c>
+      <c r="V455" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W455" t="n">
+        <v>24</v>
+      </c>
+      <c r="X455" t="inlineStr">
+        <is>
+          <t>BALONCESTO TALAVERA vs BALONCESTO TELDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>2487738</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>BALONCESTO TALAVERA</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>C. UNANUE CEGARRA | D. LORENZO NEGRETE | J. FRANCES PASCUAL | S. GACIC | V. ALONSO PASCUAL</t>
+        </is>
+      </c>
+      <c r="D456" t="n">
+        <v>5</v>
+      </c>
+      <c r="E456" t="n">
+        <v>38</v>
+      </c>
+      <c r="F456" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="G456" t="n">
+        <v>3</v>
+      </c>
+      <c r="H456" t="n">
+        <v>3</v>
+      </c>
+      <c r="I456" t="n">
+        <v>2</v>
+      </c>
+      <c r="J456" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="K456" t="n">
+        <v>150</v>
+      </c>
+      <c r="L456" t="n">
+        <v>340.91</v>
+      </c>
+      <c r="M456" t="n">
+        <v>-190.91</v>
+      </c>
+      <c r="N456" t="n">
+        <v>2</v>
+      </c>
+      <c r="O456" t="n">
+        <v>0</v>
+      </c>
+      <c r="P456" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q456" t="n">
+        <v>0</v>
+      </c>
+      <c r="R456" t="n">
+        <v>1</v>
+      </c>
+      <c r="S456" t="n">
+        <v>2</v>
+      </c>
+      <c r="T456" t="n">
+        <v>0</v>
+      </c>
+      <c r="U456" t="n">
+        <v>1</v>
+      </c>
+      <c r="V456" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W456" t="n">
+        <v>24</v>
+      </c>
+      <c r="X456" t="inlineStr">
+        <is>
+          <t>BALONCESTO TALAVERA vs BALONCESTO TELDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>2487738</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>BALONCESTO TELDE</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>A. FERNÁNDEZ GÓMEZ | A. MARTIN GONZALEZ | A. SANTANA OJEDA | A. VIDAL RODRIGUEZ | G. ARTILES ROMERO</t>
+        </is>
+      </c>
+      <c r="D457" t="n">
+        <v>5</v>
+      </c>
+      <c r="E457" t="n">
+        <v>34</v>
+      </c>
+      <c r="F457" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="G457" t="n">
+        <v>2</v>
+      </c>
+      <c r="H457" t="n">
+        <v>0</v>
+      </c>
+      <c r="I457" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="J457" t="n">
+        <v>1</v>
+      </c>
+      <c r="K457" t="n">
+        <v>106.38</v>
+      </c>
+      <c r="L457" t="n">
+        <v>0</v>
+      </c>
+      <c r="M457" t="n">
+        <v>106.38</v>
+      </c>
+      <c r="N457" t="n">
+        <v>2</v>
+      </c>
+      <c r="O457" t="n">
+        <v>2</v>
+      </c>
+      <c r="P457" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q457" t="n">
+        <v>1</v>
+      </c>
+      <c r="R457" t="n">
+        <v>1</v>
+      </c>
+      <c r="S457" t="n">
+        <v>0</v>
+      </c>
+      <c r="T457" t="n">
+        <v>1</v>
+      </c>
+      <c r="U457" t="n">
+        <v>1</v>
+      </c>
+      <c r="V457" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W457" t="n">
+        <v>24</v>
+      </c>
+      <c r="X457" t="inlineStr">
+        <is>
+          <t>BALONCESTO TALAVERA vs BALONCESTO TELDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>2487738</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>BALONCESTO TELDE</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>A. FERNÁNDEZ GÓMEZ | A. SANTANA OJEDA | A. VIDAL RODRIGUEZ | G. ARTILES ROMERO | J. JIMENEZ HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D458" t="n">
+        <v>5</v>
+      </c>
+      <c r="E458" t="n">
+        <v>233</v>
+      </c>
+      <c r="F458" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="G458" t="n">
+        <v>8</v>
+      </c>
+      <c r="H458" t="n">
+        <v>7</v>
+      </c>
+      <c r="I458" t="n">
+        <v>6.64</v>
+      </c>
+      <c r="J458" t="n">
+        <v>8</v>
+      </c>
+      <c r="K458" t="n">
+        <v>120.48</v>
+      </c>
+      <c r="L458" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="M458" t="n">
+        <v>32.98</v>
+      </c>
+      <c r="N458" t="n">
+        <v>5</v>
+      </c>
+      <c r="O458" t="n">
+        <v>6</v>
+      </c>
+      <c r="P458" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q458" t="n">
+        <v>2</v>
+      </c>
+      <c r="R458" t="n">
+        <v>6</v>
+      </c>
+      <c r="S458" t="n">
+        <v>0</v>
+      </c>
+      <c r="T458" t="n">
+        <v>4</v>
+      </c>
+      <c r="U458" t="n">
+        <v>2</v>
+      </c>
+      <c r="V458" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W458" t="n">
+        <v>24</v>
+      </c>
+      <c r="X458" t="inlineStr">
+        <is>
+          <t>BALONCESTO TALAVERA vs BALONCESTO TELDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>2487738</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>BALONCESTO TELDE</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>A. MARTIN GONZALEZ | A. SANTANA OJEDA | A. VIDAL RODRIGUEZ | G. ARTILES ROMERO | J. JIMENEZ HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D459" t="n">
+        <v>5</v>
+      </c>
+      <c r="E459" t="n">
+        <v>28</v>
+      </c>
+      <c r="F459" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="G459" t="n">
+        <v>0</v>
+      </c>
+      <c r="H459" t="n">
+        <v>0</v>
+      </c>
+      <c r="I459" t="n">
+        <v>0</v>
+      </c>
+      <c r="J459" t="n">
+        <v>1</v>
+      </c>
+      <c r="K459" t="n">
+        <v>0</v>
+      </c>
+      <c r="L459" t="n">
+        <v>0</v>
+      </c>
+      <c r="M459" t="n">
+        <v>0</v>
+      </c>
+      <c r="N459" t="n">
+        <v>0</v>
+      </c>
+      <c r="O459" t="n">
+        <v>0</v>
+      </c>
+      <c r="P459" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q459" t="n">
+        <v>0</v>
+      </c>
+      <c r="R459" t="n">
+        <v>1</v>
+      </c>
+      <c r="S459" t="n">
+        <v>0</v>
+      </c>
+      <c r="T459" t="n">
+        <v>0</v>
+      </c>
+      <c r="U459" t="n">
+        <v>0</v>
+      </c>
+      <c r="V459" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W459" t="n">
+        <v>24</v>
+      </c>
+      <c r="X459" t="inlineStr">
+        <is>
+          <t>BALONCESTO TALAVERA vs BALONCESTO TELDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>2487751</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>BALONCESTO TELDE</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>A. FERNÁNDEZ GÓMEZ | A. MARTIN GONZALEZ | A. SANTANA OJEDA | A. VIDAL RODRIGUEZ | G. ARTILES ROMERO</t>
+        </is>
+      </c>
+      <c r="D460" t="n">
+        <v>5</v>
+      </c>
+      <c r="E460" t="n">
+        <v>61</v>
+      </c>
+      <c r="F460" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="G460" t="n">
+        <v>2</v>
+      </c>
+      <c r="H460" t="n">
+        <v>3</v>
+      </c>
+      <c r="I460" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="J460" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="K460" t="n">
+        <v>106.38</v>
+      </c>
+      <c r="L460" t="n">
+        <v>159.57</v>
+      </c>
+      <c r="M460" t="n">
+        <v>-53.19</v>
+      </c>
+      <c r="N460" t="n">
+        <v>1</v>
+      </c>
+      <c r="O460" t="n">
+        <v>2</v>
+      </c>
+      <c r="P460" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q460" t="n">
+        <v>0</v>
+      </c>
+      <c r="R460" t="n">
+        <v>2</v>
+      </c>
+      <c r="S460" t="n">
+        <v>2</v>
+      </c>
+      <c r="T460" t="n">
+        <v>0</v>
+      </c>
+      <c r="U460" t="n">
+        <v>1</v>
+      </c>
+      <c r="V460" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W460" t="n">
+        <v>25</v>
+      </c>
+      <c r="X460" t="inlineStr">
+        <is>
+          <t>BALONCESTO TELDE vs EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>2487751</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>BALONCESTO TELDE</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>A. FERNÁNDEZ GÓMEZ | A. MARTIN GONZALEZ | A. VIDAL RODRIGUEZ | G. ARTILES ROMERO | P. SÁNCHEZ GUTIERREZ</t>
+        </is>
+      </c>
+      <c r="D461" t="n">
+        <v>5</v>
+      </c>
+      <c r="E461" t="n">
+        <v>131</v>
+      </c>
+      <c r="F461" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="G461" t="n">
+        <v>3</v>
+      </c>
+      <c r="H461" t="n">
+        <v>7</v>
+      </c>
+      <c r="I461" t="n">
+        <v>3</v>
+      </c>
+      <c r="J461" t="n">
+        <v>6</v>
+      </c>
+      <c r="K461" t="n">
+        <v>100</v>
+      </c>
+      <c r="L461" t="n">
+        <v>116.67</v>
+      </c>
+      <c r="M461" t="n">
+        <v>-16.67</v>
+      </c>
+      <c r="N461" t="n">
+        <v>3</v>
+      </c>
+      <c r="O461" t="n">
+        <v>0</v>
+      </c>
+      <c r="P461" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q461" t="n">
+        <v>1</v>
+      </c>
+      <c r="R461" t="n">
+        <v>4</v>
+      </c>
+      <c r="S461" t="n">
+        <v>0</v>
+      </c>
+      <c r="T461" t="n">
+        <v>2</v>
+      </c>
+      <c r="U461" t="n">
+        <v>0</v>
+      </c>
+      <c r="V461" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W461" t="n">
+        <v>25</v>
+      </c>
+      <c r="X461" t="inlineStr">
+        <is>
+          <t>BALONCESTO TELDE vs EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>2487751</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>A. SISTAC RODRIGUEZ | E. DUQUE NEGRÍN | J. GALLETTO LAMELA | M. NIMAGA | S. MANERO GUZMAN</t>
+        </is>
+      </c>
+      <c r="D462" t="n">
+        <v>5</v>
+      </c>
+      <c r="E462" t="n">
+        <v>87</v>
+      </c>
+      <c r="F462" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="G462" t="n">
+        <v>4</v>
+      </c>
+      <c r="H462" t="n">
+        <v>2</v>
+      </c>
+      <c r="I462" t="n">
+        <v>3</v>
+      </c>
+      <c r="J462" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="K462" t="n">
+        <v>133.33</v>
+      </c>
+      <c r="L462" t="n">
+        <v>69.44</v>
+      </c>
+      <c r="M462" t="n">
+        <v>63.89</v>
+      </c>
+      <c r="N462" t="n">
+        <v>4</v>
+      </c>
+      <c r="O462" t="n">
+        <v>0</v>
+      </c>
+      <c r="P462" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q462" t="n">
+        <v>1</v>
+      </c>
+      <c r="R462" t="n">
+        <v>1</v>
+      </c>
+      <c r="S462" t="n">
+        <v>2</v>
+      </c>
+      <c r="T462" t="n">
+        <v>1</v>
+      </c>
+      <c r="U462" t="n">
+        <v>0</v>
+      </c>
+      <c r="V462" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W462" t="n">
+        <v>25</v>
+      </c>
+      <c r="X462" t="inlineStr">
+        <is>
+          <t>BALONCESTO TELDE vs EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>2487751</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>A. SISTAC RODRIGUEZ | E. DUQUE NEGRÍN | J. GALLETTO LAMELA | P. ARGÜELLES ELORZA | S. MANERO GUZMAN</t>
+        </is>
+      </c>
+      <c r="D463" t="n">
+        <v>5</v>
+      </c>
+      <c r="E463" t="n">
+        <v>27</v>
+      </c>
+      <c r="F463" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="G463" t="n">
+        <v>3</v>
+      </c>
+      <c r="H463" t="n">
+        <v>0</v>
+      </c>
+      <c r="I463" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="J463" t="n">
+        <v>0</v>
+      </c>
+      <c r="K463" t="n">
+        <v>159.57</v>
+      </c>
+      <c r="L463" t="n">
+        <v>0</v>
+      </c>
+      <c r="M463" t="n">
+        <v>0</v>
+      </c>
+      <c r="N463" t="n">
+        <v>1</v>
+      </c>
+      <c r="O463" t="n">
+        <v>2</v>
+      </c>
+      <c r="P463" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q463" t="n">
+        <v>0</v>
+      </c>
+      <c r="R463" t="n">
+        <v>0</v>
+      </c>
+      <c r="S463" t="n">
+        <v>0</v>
+      </c>
+      <c r="T463" t="n">
+        <v>0</v>
+      </c>
+      <c r="U463" t="n">
+        <v>0</v>
+      </c>
+      <c r="V463" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W463" t="n">
+        <v>25</v>
+      </c>
+      <c r="X463" t="inlineStr">
+        <is>
+          <t>BALONCESTO TELDE vs EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>2487751</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>A. SISTAC RODRIGUEZ | E. DUQUE NEGRÍN | M. NIMAGA | P. HERNANDEZ RODRIGUEZ | S. MANERO GUZMAN</t>
+        </is>
+      </c>
+      <c r="D464" t="n">
+        <v>5</v>
+      </c>
+      <c r="E464" t="n">
+        <v>78</v>
+      </c>
+      <c r="F464" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="G464" t="n">
+        <v>3</v>
+      </c>
+      <c r="H464" t="n">
+        <v>3</v>
+      </c>
+      <c r="I464" t="n">
+        <v>3</v>
+      </c>
+      <c r="J464" t="n">
+        <v>2</v>
+      </c>
+      <c r="K464" t="n">
+        <v>100</v>
+      </c>
+      <c r="L464" t="n">
+        <v>150</v>
+      </c>
+      <c r="M464" t="n">
+        <v>-50</v>
+      </c>
+      <c r="N464" t="n">
+        <v>1</v>
+      </c>
+      <c r="O464" t="n">
+        <v>0</v>
+      </c>
+      <c r="P464" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q464" t="n">
+        <v>0</v>
+      </c>
+      <c r="R464" t="n">
+        <v>3</v>
+      </c>
+      <c r="S464" t="n">
+        <v>0</v>
+      </c>
+      <c r="T464" t="n">
+        <v>0</v>
+      </c>
+      <c r="U464" t="n">
+        <v>1</v>
+      </c>
+      <c r="V464" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W464" t="n">
+        <v>25</v>
+      </c>
+      <c r="X464" t="inlineStr">
+        <is>
+          <t>BALONCESTO TELDE vs EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>2487749</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>ADC BOADILLA</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>A. GOMEZ SERRANO | A. OLMEDO VELASCO | I. BLANCO-ARGIBAY GONZALEZ | M. SANCHEZ SANCHEZ | P. DOMINGUEZ LORENZO</t>
+        </is>
+      </c>
+      <c r="D465" t="n">
+        <v>5</v>
+      </c>
+      <c r="E465" t="n">
+        <v>85</v>
+      </c>
+      <c r="F465" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="G465" t="n">
+        <v>5</v>
+      </c>
+      <c r="H465" t="n">
+        <v>2</v>
+      </c>
+      <c r="I465" t="n">
+        <v>3</v>
+      </c>
+      <c r="J465" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="K465" t="n">
+        <v>166.67</v>
+      </c>
+      <c r="L465" t="n">
+        <v>86.20999999999999</v>
+      </c>
+      <c r="M465" t="n">
+        <v>80.45999999999999</v>
+      </c>
+      <c r="N465" t="n">
+        <v>3</v>
+      </c>
+      <c r="O465" t="n">
+        <v>0</v>
+      </c>
+      <c r="P465" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q465" t="n">
+        <v>0</v>
+      </c>
+      <c r="R465" t="n">
+        <v>0</v>
+      </c>
+      <c r="S465" t="n">
+        <v>3</v>
+      </c>
+      <c r="T465" t="n">
+        <v>2</v>
+      </c>
+      <c r="U465" t="n">
+        <v>1</v>
+      </c>
+      <c r="V465" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W465" t="n">
+        <v>25</v>
+      </c>
+      <c r="X465" t="inlineStr">
+        <is>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA vs ADC BOADILLA</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>2487749</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>A. APARICIO IZQUIERDO | A. JIMENEZ FERNANDEZ | D. RODRIGUEZ GARCIA | M. NIANG | M. RODRÍGUEZ RIVEROL</t>
+        </is>
+      </c>
+      <c r="D466" t="n">
+        <v>5</v>
+      </c>
+      <c r="E466" t="n">
+        <v>37</v>
+      </c>
+      <c r="F466" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="G466" t="n">
+        <v>2</v>
+      </c>
+      <c r="H466" t="n">
+        <v>3</v>
+      </c>
+      <c r="I466" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="J466" t="n">
+        <v>1</v>
+      </c>
+      <c r="K466" t="n">
+        <v>151.52</v>
+      </c>
+      <c r="L466" t="n">
+        <v>300</v>
+      </c>
+      <c r="M466" t="n">
+        <v>-148.48</v>
+      </c>
+      <c r="N466" t="n">
+        <v>0</v>
+      </c>
+      <c r="O466" t="n">
+        <v>3</v>
+      </c>
+      <c r="P466" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q466" t="n">
+        <v>0</v>
+      </c>
+      <c r="R466" t="n">
+        <v>1</v>
+      </c>
+      <c r="S466" t="n">
+        <v>0</v>
+      </c>
+      <c r="T466" t="n">
+        <v>0</v>
+      </c>
+      <c r="U466" t="n">
+        <v>0</v>
+      </c>
+      <c r="V466" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W466" t="n">
+        <v>25</v>
+      </c>
+      <c r="X466" t="inlineStr">
+        <is>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA vs ADC BOADILLA</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>2487749</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>A. APARICIO IZQUIERDO | D. RODRIGUEZ GARCIA | J. RIES | M. NIANG | M. RODRÍGUEZ RIVEROL</t>
+        </is>
+      </c>
+      <c r="D467" t="n">
+        <v>5</v>
+      </c>
+      <c r="E467" t="n">
+        <v>48</v>
+      </c>
+      <c r="F467" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G467" t="n">
+        <v>0</v>
+      </c>
+      <c r="H467" t="n">
+        <v>2</v>
+      </c>
+      <c r="I467" t="n">
+        <v>1</v>
+      </c>
+      <c r="J467" t="n">
+        <v>2</v>
+      </c>
+      <c r="K467" t="n">
+        <v>0</v>
+      </c>
+      <c r="L467" t="n">
+        <v>100</v>
+      </c>
+      <c r="M467" t="n">
+        <v>-100</v>
+      </c>
+      <c r="N467" t="n">
+        <v>0</v>
+      </c>
+      <c r="O467" t="n">
+        <v>0</v>
+      </c>
+      <c r="P467" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q467" t="n">
+        <v>1</v>
+      </c>
+      <c r="R467" t="n">
+        <v>2</v>
+      </c>
+      <c r="S467" t="n">
+        <v>0</v>
+      </c>
+      <c r="T467" t="n">
+        <v>0</v>
+      </c>
+      <c r="U467" t="n">
+        <v>0</v>
+      </c>
+      <c r="V467" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W467" t="n">
+        <v>25</v>
+      </c>
+      <c r="X467" t="inlineStr">
+        <is>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA vs ADC BOADILLA</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>2487748</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>GRUPO EGIDO PINTOBASKET</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>J. AYALA AYLLÓN | L. BERMEJO ALCALDE | M. ALARCON ORTIZ | M. BATLLE BERNARDO | S. RODRIGUEZ GREGORIO</t>
+        </is>
+      </c>
+      <c r="D468" t="n">
+        <v>5</v>
+      </c>
+      <c r="E468" t="n">
+        <v>6</v>
+      </c>
+      <c r="F468" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G468" t="n">
+        <v>0</v>
+      </c>
+      <c r="H468" t="n">
+        <v>0</v>
+      </c>
+      <c r="I468" t="n">
+        <v>1</v>
+      </c>
+      <c r="J468" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K468" t="n">
+        <v>0</v>
+      </c>
+      <c r="L468" t="n">
+        <v>0</v>
+      </c>
+      <c r="M468" t="n">
+        <v>0</v>
+      </c>
+      <c r="N468" t="n">
+        <v>1</v>
+      </c>
+      <c r="O468" t="n">
+        <v>0</v>
+      </c>
+      <c r="P468" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q468" t="n">
+        <v>0</v>
+      </c>
+      <c r="R468" t="n">
+        <v>0</v>
+      </c>
+      <c r="S468" t="n">
+        <v>0</v>
+      </c>
+      <c r="T468" t="n">
+        <v>0</v>
+      </c>
+      <c r="U468" t="n">
+        <v>1</v>
+      </c>
+      <c r="V468" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W468" t="n">
+        <v>25</v>
+      </c>
+      <c r="X468" t="inlineStr">
+        <is>
+          <t>GRUPO EGIDO PINTOBASKET vs RECUCYM BAZU</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>2487748</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>RECUCYM BAZU</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>E. ECHEVERRIA MATEO | G. HIERRO ABAD | J. BARRA DE LA CRUZ | J. MUNRO | V. FERNANDEZ MORAN</t>
+        </is>
+      </c>
+      <c r="D469" t="n">
+        <v>5</v>
+      </c>
+      <c r="E469" t="n">
+        <v>6</v>
+      </c>
+      <c r="F469" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G469" t="n">
+        <v>0</v>
+      </c>
+      <c r="H469" t="n">
+        <v>0</v>
+      </c>
+      <c r="I469" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J469" t="n">
+        <v>1</v>
+      </c>
+      <c r="K469" t="n">
+        <v>0</v>
+      </c>
+      <c r="L469" t="n">
+        <v>0</v>
+      </c>
+      <c r="M469" t="n">
+        <v>0</v>
+      </c>
+      <c r="N469" t="n">
+        <v>0</v>
+      </c>
+      <c r="O469" t="n">
+        <v>0</v>
+      </c>
+      <c r="P469" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q469" t="n">
+        <v>1</v>
+      </c>
+      <c r="R469" t="n">
+        <v>1</v>
+      </c>
+      <c r="S469" t="n">
+        <v>0</v>
+      </c>
+      <c r="T469" t="n">
+        <v>0</v>
+      </c>
+      <c r="U469" t="n">
+        <v>0</v>
+      </c>
+      <c r="V469" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W469" t="n">
+        <v>25</v>
+      </c>
+      <c r="X469" t="inlineStr">
+        <is>
+          <t>GRUPO EGIDO PINTOBASKET vs RECUCYM BAZU</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>2487746</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>LUJISA GUADALAJARA BASKET</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>A. ARMSTRONG | D. EBOLO OLU-ELIJAH | J. HOYA MARTINEZ | L. VALERA VILLEGAS | M. DIALLO</t>
+        </is>
+      </c>
+      <c r="D470" t="n">
+        <v>5</v>
+      </c>
+      <c r="E470" t="n">
+        <v>219</v>
+      </c>
+      <c r="F470" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="G470" t="n">
+        <v>5</v>
+      </c>
+      <c r="H470" t="n">
+        <v>8</v>
+      </c>
+      <c r="I470" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="J470" t="n">
+        <v>7.88</v>
+      </c>
+      <c r="K470" t="n">
+        <v>56.31</v>
+      </c>
+      <c r="L470" t="n">
+        <v>101.52</v>
+      </c>
+      <c r="M470" t="n">
+        <v>-45.22</v>
+      </c>
+      <c r="N470" t="n">
+        <v>4</v>
+      </c>
+      <c r="O470" t="n">
+        <v>2</v>
+      </c>
+      <c r="P470" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q470" t="n">
+        <v>0</v>
+      </c>
+      <c r="R470" t="n">
+        <v>5</v>
+      </c>
+      <c r="S470" t="n">
+        <v>2</v>
+      </c>
+      <c r="T470" t="n">
+        <v>2</v>
+      </c>
+      <c r="U470" t="n">
+        <v>0</v>
+      </c>
+      <c r="V470" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W470" t="n">
+        <v>25</v>
+      </c>
+      <c r="X470" t="inlineStr">
+        <is>
+          <t>UROS DE RIVAS vs LUJISA GUADALAJARA BASKET</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>2487746</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>UROS DE RIVAS</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>A. BIERSACK LOPEZ | A. PEREZ CONTI | C. CRESPO MONTESINOS | P. ESTEBANEZ GONZALEZ | P. ROSSI</t>
+        </is>
+      </c>
+      <c r="D471" t="n">
+        <v>5</v>
+      </c>
+      <c r="E471" t="n">
+        <v>23</v>
+      </c>
+      <c r="F471" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="G471" t="n">
+        <v>0</v>
+      </c>
+      <c r="H471" t="n">
+        <v>0</v>
+      </c>
+      <c r="I471" t="n">
+        <v>0</v>
+      </c>
+      <c r="J471" t="n">
+        <v>1</v>
+      </c>
+      <c r="K471" t="n">
+        <v>0</v>
+      </c>
+      <c r="L471" t="n">
+        <v>0</v>
+      </c>
+      <c r="M471" t="n">
+        <v>0</v>
+      </c>
+      <c r="N471" t="n">
+        <v>0</v>
+      </c>
+      <c r="O471" t="n">
+        <v>0</v>
+      </c>
+      <c r="P471" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q471" t="n">
+        <v>0</v>
+      </c>
+      <c r="R471" t="n">
+        <v>0</v>
+      </c>
+      <c r="S471" t="n">
+        <v>0</v>
+      </c>
+      <c r="T471" t="n">
+        <v>1</v>
+      </c>
+      <c r="U471" t="n">
+        <v>0</v>
+      </c>
+      <c r="V471" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W471" t="n">
+        <v>25</v>
+      </c>
+      <c r="X471" t="inlineStr">
+        <is>
+          <t>UROS DE RIVAS vs LUJISA GUADALAJARA BASKET</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>2487746</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>UROS DE RIVAS</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>A. BIERSACK LOPEZ | D. MARINEZ FERNANDEZ-URRUTIA | O. MENDEZ BLANCO | P. ESTEBANEZ GONZALEZ | P. ROSSI</t>
+        </is>
+      </c>
+      <c r="D472" t="n">
+        <v>5</v>
+      </c>
+      <c r="E472" t="n">
+        <v>74</v>
+      </c>
+      <c r="F472" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="G472" t="n">
+        <v>5</v>
+      </c>
+      <c r="H472" t="n">
+        <v>2</v>
+      </c>
+      <c r="I472" t="n">
+        <v>2</v>
+      </c>
+      <c r="J472" t="n">
+        <v>2</v>
+      </c>
+      <c r="K472" t="n">
+        <v>250</v>
+      </c>
+      <c r="L472" t="n">
+        <v>100</v>
+      </c>
+      <c r="M472" t="n">
+        <v>150</v>
+      </c>
+      <c r="N472" t="n">
+        <v>2</v>
+      </c>
+      <c r="O472" t="n">
+        <v>0</v>
+      </c>
+      <c r="P472" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q472" t="n">
+        <v>0</v>
+      </c>
+      <c r="R472" t="n">
+        <v>1</v>
+      </c>
+      <c r="S472" t="n">
+        <v>0</v>
+      </c>
+      <c r="T472" t="n">
+        <v>1</v>
+      </c>
+      <c r="U472" t="n">
+        <v>0</v>
+      </c>
+      <c r="V472" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W472" t="n">
+        <v>25</v>
+      </c>
+      <c r="X472" t="inlineStr">
+        <is>
+          <t>UROS DE RIVAS vs LUJISA GUADALAJARA BASKET</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>2487746</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>UROS DE RIVAS</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>A. PEREZ CONTI | C. CRESPO MONTESINOS | D. MARINEZ FERNANDEZ-URRUTIA | P. ESTEBANEZ GONZALEZ | P. ROSSI</t>
+        </is>
+      </c>
+      <c r="D473" t="n">
+        <v>5</v>
+      </c>
+      <c r="E473" t="n">
+        <v>79</v>
+      </c>
+      <c r="F473" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="G473" t="n">
+        <v>2</v>
+      </c>
+      <c r="H473" t="n">
+        <v>2</v>
+      </c>
+      <c r="I473" t="n">
+        <v>3</v>
+      </c>
+      <c r="J473" t="n">
+        <v>3</v>
+      </c>
+      <c r="K473" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="L473" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="M473" t="n">
+        <v>0</v>
+      </c>
+      <c r="N473" t="n">
+        <v>3</v>
+      </c>
+      <c r="O473" t="n">
+        <v>0</v>
+      </c>
+      <c r="P473" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q473" t="n">
+        <v>0</v>
+      </c>
+      <c r="R473" t="n">
+        <v>2</v>
+      </c>
+      <c r="S473" t="n">
+        <v>0</v>
+      </c>
+      <c r="T473" t="n">
+        <v>1</v>
+      </c>
+      <c r="U473" t="n">
+        <v>0</v>
+      </c>
+      <c r="V473" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W473" t="n">
+        <v>25</v>
+      </c>
+      <c r="X473" t="inlineStr">
+        <is>
+          <t>UROS DE RIVAS vs LUJISA GUADALAJARA BASKET</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>2487746</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>UROS DE RIVAS</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>A. PEREZ CONTI | C. CRESPO MONTESINOS | G. MARTIN LOPEZ-LAGO | O. MENDEZ BLANCO | P. ESTEBANEZ GONZALEZ</t>
+        </is>
+      </c>
+      <c r="D474" t="n">
+        <v>5</v>
+      </c>
+      <c r="E474" t="n">
+        <v>10</v>
+      </c>
+      <c r="F474" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="G474" t="n">
+        <v>0</v>
+      </c>
+      <c r="H474" t="n">
+        <v>1</v>
+      </c>
+      <c r="I474" t="n">
+        <v>1</v>
+      </c>
+      <c r="J474" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="K474" t="n">
+        <v>0</v>
+      </c>
+      <c r="L474" t="n">
+        <v>53.19</v>
+      </c>
+      <c r="M474" t="n">
+        <v>-53.19</v>
+      </c>
+      <c r="N474" t="n">
+        <v>0</v>
+      </c>
+      <c r="O474" t="n">
+        <v>0</v>
+      </c>
+      <c r="P474" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q474" t="n">
+        <v>0</v>
+      </c>
+      <c r="R474" t="n">
+        <v>0</v>
+      </c>
+      <c r="S474" t="n">
+        <v>2</v>
+      </c>
+      <c r="T474" t="n">
+        <v>1</v>
+      </c>
+      <c r="U474" t="n">
+        <v>0</v>
+      </c>
+      <c r="V474" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W474" t="n">
+        <v>25</v>
+      </c>
+      <c r="X474" t="inlineStr">
+        <is>
+          <t>UROS DE RIVAS vs LUJISA GUADALAJARA BASKET</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>2487746</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>UROS DE RIVAS</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>A. PEREZ CONTI | D. MARINEZ FERNANDEZ-URRUTIA | O. MENDEZ BLANCO | P. ESTEBANEZ GONZALEZ | P. ROSSI</t>
+        </is>
+      </c>
+      <c r="D475" t="n">
+        <v>5</v>
+      </c>
+      <c r="E475" t="n">
+        <v>33</v>
+      </c>
+      <c r="F475" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="G475" t="n">
+        <v>1</v>
+      </c>
+      <c r="H475" t="n">
+        <v>0</v>
+      </c>
+      <c r="I475" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="J475" t="n">
+        <v>1</v>
+      </c>
+      <c r="K475" t="n">
+        <v>53.19</v>
+      </c>
+      <c r="L475" t="n">
+        <v>0</v>
+      </c>
+      <c r="M475" t="n">
+        <v>53.19</v>
+      </c>
+      <c r="N475" t="n">
+        <v>0</v>
+      </c>
+      <c r="O475" t="n">
+        <v>2</v>
+      </c>
+      <c r="P475" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q475" t="n">
+        <v>0</v>
+      </c>
+      <c r="R475" t="n">
+        <v>1</v>
+      </c>
+      <c r="S475" t="n">
+        <v>0</v>
+      </c>
+      <c r="T475" t="n">
+        <v>0</v>
+      </c>
+      <c r="U475" t="n">
+        <v>0</v>
+      </c>
+      <c r="V475" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W475" t="n">
+        <v>25</v>
+      </c>
+      <c r="X475" t="inlineStr">
+        <is>
+          <t>UROS DE RIVAS vs LUJISA GUADALAJARA BASKET</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>2487750</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>C.B. TRES CANTOS</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>D. GONZALEZ LONGARELA | G. DIAZ MONTERO | J. ATIENZA PEREA | J. DE DOMINGO GARAY | N. MAIGA</t>
+        </is>
+      </c>
+      <c r="D476" t="n">
+        <v>5</v>
+      </c>
+      <c r="E476" t="n">
+        <v>71</v>
+      </c>
+      <c r="F476" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="G476" t="n">
+        <v>2</v>
+      </c>
+      <c r="H476" t="n">
+        <v>0</v>
+      </c>
+      <c r="I476" t="n">
+        <v>2</v>
+      </c>
+      <c r="J476" t="n">
+        <v>0</v>
+      </c>
+      <c r="K476" t="n">
+        <v>100</v>
+      </c>
+      <c r="L476" t="n">
+        <v>0</v>
+      </c>
+      <c r="M476" t="n">
+        <v>0</v>
+      </c>
+      <c r="N476" t="n">
+        <v>3</v>
+      </c>
+      <c r="O476" t="n">
+        <v>0</v>
+      </c>
+      <c r="P476" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q476" t="n">
+        <v>1</v>
+      </c>
+      <c r="R476" t="n">
+        <v>1</v>
+      </c>
+      <c r="S476" t="n">
+        <v>0</v>
+      </c>
+      <c r="T476" t="n">
+        <v>1</v>
+      </c>
+      <c r="U476" t="n">
+        <v>2</v>
+      </c>
+      <c r="V476" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W476" t="n">
+        <v>25</v>
+      </c>
+      <c r="X476" t="inlineStr">
+        <is>
+          <t>C.B. TRES CANTOS vs ZENTRO BASKET MADRID</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>2487750</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>C.B. TRES CANTOS</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>D. GONZALEZ LONGARELA | G. DIAZ MONTERO | J. ATIENZA PEREA | J. DOMINGUEZ LARRE | N. MAIGA</t>
+        </is>
+      </c>
+      <c r="D477" t="n">
+        <v>5</v>
+      </c>
+      <c r="E477" t="n">
+        <v>226</v>
+      </c>
+      <c r="F477" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="G477" t="n">
+        <v>5</v>
+      </c>
+      <c r="H477" t="n">
+        <v>8</v>
+      </c>
+      <c r="I477" t="n">
+        <v>6.88</v>
+      </c>
+      <c r="J477" t="n">
+        <v>9.880000000000001</v>
+      </c>
+      <c r="K477" t="n">
+        <v>72.67</v>
+      </c>
+      <c r="L477" t="n">
+        <v>80.97</v>
+      </c>
+      <c r="M477" t="n">
+        <v>-8.300000000000001</v>
+      </c>
+      <c r="N477" t="n">
+        <v>5</v>
+      </c>
+      <c r="O477" t="n">
+        <v>2</v>
+      </c>
+      <c r="P477" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q477" t="n">
+        <v>1</v>
+      </c>
+      <c r="R477" t="n">
+        <v>8</v>
+      </c>
+      <c r="S477" t="n">
+        <v>2</v>
+      </c>
+      <c r="T477" t="n">
+        <v>2</v>
+      </c>
+      <c r="U477" t="n">
+        <v>1</v>
+      </c>
+      <c r="V477" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W477" t="n">
+        <v>25</v>
+      </c>
+      <c r="X477" t="inlineStr">
+        <is>
+          <t>C.B. TRES CANTOS vs ZENTRO BASKET MADRID</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>2487750</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>C.B. TRES CANTOS</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>G. DIAZ MONTERO | G. LARDIES GUILLEN | J. ATIENZA PEREA | J. DE DOMINGO GARAY | N. MAIGA</t>
+        </is>
+      </c>
+      <c r="D478" t="n">
+        <v>5</v>
+      </c>
+      <c r="E478" t="n">
+        <v>108</v>
+      </c>
+      <c r="F478" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G478" t="n">
+        <v>6</v>
+      </c>
+      <c r="H478" t="n">
+        <v>6</v>
+      </c>
+      <c r="I478" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="J478" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="K478" t="n">
+        <v>126.05</v>
+      </c>
+      <c r="L478" t="n">
+        <v>208.33</v>
+      </c>
+      <c r="M478" t="n">
+        <v>-82.28</v>
+      </c>
+      <c r="N478" t="n">
+        <v>3</v>
+      </c>
+      <c r="O478" t="n">
+        <v>4</v>
+      </c>
+      <c r="P478" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q478" t="n">
+        <v>0</v>
+      </c>
+      <c r="R478" t="n">
+        <v>3</v>
+      </c>
+      <c r="S478" t="n">
+        <v>2</v>
+      </c>
+      <c r="T478" t="n">
+        <v>0</v>
+      </c>
+      <c r="U478" t="n">
+        <v>1</v>
+      </c>
+      <c r="V478" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W478" t="n">
+        <v>25</v>
+      </c>
+      <c r="X478" t="inlineStr">
+        <is>
+          <t>C.B. TRES CANTOS vs ZENTRO BASKET MADRID</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>2487750</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>C.B. TRES CANTOS</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>G. DIAZ MONTERO | G. LARDIES GUILLEN | J. ATIENZA PEREA | J. DOMINGUEZ LARRE | N. MAIGA</t>
+        </is>
+      </c>
+      <c r="D479" t="n">
+        <v>5</v>
+      </c>
+      <c r="E479" t="n">
+        <v>7</v>
+      </c>
+      <c r="F479" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="G479" t="n">
+        <v>0</v>
+      </c>
+      <c r="H479" t="n">
+        <v>3</v>
+      </c>
+      <c r="I479" t="n">
+        <v>0</v>
+      </c>
+      <c r="J479" t="n">
+        <v>1</v>
+      </c>
+      <c r="K479" t="n">
+        <v>0</v>
+      </c>
+      <c r="L479" t="n">
+        <v>300</v>
+      </c>
+      <c r="M479" t="n">
+        <v>0</v>
+      </c>
+      <c r="N479" t="n">
+        <v>0</v>
+      </c>
+      <c r="O479" t="n">
+        <v>0</v>
+      </c>
+      <c r="P479" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q479" t="n">
+        <v>0</v>
+      </c>
+      <c r="R479" t="n">
+        <v>1</v>
+      </c>
+      <c r="S479" t="n">
+        <v>0</v>
+      </c>
+      <c r="T479" t="n">
+        <v>0</v>
+      </c>
+      <c r="U479" t="n">
+        <v>0</v>
+      </c>
+      <c r="V479" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W479" t="n">
+        <v>25</v>
+      </c>
+      <c r="X479" t="inlineStr">
+        <is>
+          <t>C.B. TRES CANTOS vs ZENTRO BASKET MADRID</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>2487750</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>C.B. TRES CANTOS</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>G. LARDIES GUILLEN | J. ATIENZA PEREA | J. DE DOMINGO GARAY | J. DOMINGUEZ LARRE | N. MAIGA</t>
+        </is>
+      </c>
+      <c r="D480" t="n">
+        <v>5</v>
+      </c>
+      <c r="E480" t="n">
+        <v>185</v>
+      </c>
+      <c r="F480" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="G480" t="n">
+        <v>5</v>
+      </c>
+      <c r="H480" t="n">
+        <v>4</v>
+      </c>
+      <c r="I480" t="n">
+        <v>3</v>
+      </c>
+      <c r="J480" t="n">
+        <v>5</v>
+      </c>
+      <c r="K480" t="n">
+        <v>166.67</v>
+      </c>
+      <c r="L480" t="n">
+        <v>80</v>
+      </c>
+      <c r="M480" t="n">
+        <v>86.67</v>
+      </c>
+      <c r="N480" t="n">
+        <v>5</v>
+      </c>
+      <c r="O480" t="n">
+        <v>0</v>
+      </c>
+      <c r="P480" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q480" t="n">
+        <v>3</v>
+      </c>
+      <c r="R480" t="n">
+        <v>9</v>
+      </c>
+      <c r="S480" t="n">
+        <v>0</v>
+      </c>
+      <c r="T480" t="n">
+        <v>0</v>
+      </c>
+      <c r="U480" t="n">
+        <v>4</v>
+      </c>
+      <c r="V480" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W480" t="n">
+        <v>25</v>
+      </c>
+      <c r="X480" t="inlineStr">
+        <is>
+          <t>C.B. TRES CANTOS vs ZENTRO BASKET MADRID</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>2487750</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>ZENTRO BASKET MADRID</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>B. SCHUCH | D. VAL GUTIERREZ | G. GOMA | L. SCHIEBELHUT LUIS | M. ESTAPE ROIZ</t>
+        </is>
+      </c>
+      <c r="D481" t="n">
+        <v>5</v>
+      </c>
+      <c r="E481" t="n">
+        <v>541</v>
+      </c>
+      <c r="F481" t="n">
+        <v>9.02</v>
+      </c>
+      <c r="G481" t="n">
+        <v>14</v>
+      </c>
+      <c r="H481" t="n">
+        <v>14</v>
+      </c>
+      <c r="I481" t="n">
+        <v>15.88</v>
+      </c>
+      <c r="J481" t="n">
+        <v>13.88</v>
+      </c>
+      <c r="K481" t="n">
+        <v>88.16</v>
+      </c>
+      <c r="L481" t="n">
+        <v>100.86</v>
+      </c>
+      <c r="M481" t="n">
+        <v>-12.7</v>
+      </c>
+      <c r="N481" t="n">
+        <v>19</v>
+      </c>
+      <c r="O481" t="n">
+        <v>2</v>
+      </c>
+      <c r="P481" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q481" t="n">
+        <v>7</v>
+      </c>
+      <c r="R481" t="n">
+        <v>15</v>
+      </c>
+      <c r="S481" t="n">
+        <v>2</v>
+      </c>
+      <c r="T481" t="n">
+        <v>3</v>
+      </c>
+      <c r="U481" t="n">
+        <v>5</v>
+      </c>
+      <c r="V481" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W481" t="n">
+        <v>25</v>
+      </c>
+      <c r="X481" t="inlineStr">
+        <is>
+          <t>C.B. TRES CANTOS vs ZENTRO BASKET MADRID</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>2487750</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>ZENTRO BASKET MADRID</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>D. VAL GUTIERREZ | G. GOMA | L. SCHIEBELHUT LUIS | M. ESTAPE ROIZ | T. VERDERA BENASSAR</t>
+        </is>
+      </c>
+      <c r="D482" t="n">
+        <v>5</v>
+      </c>
+      <c r="E482" t="n">
+        <v>56</v>
+      </c>
+      <c r="F482" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="G482" t="n">
+        <v>7</v>
+      </c>
+      <c r="H482" t="n">
+        <v>4</v>
+      </c>
+      <c r="I482" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="J482" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="K482" t="n">
+        <v>243.06</v>
+      </c>
+      <c r="L482" t="n">
+        <v>144.93</v>
+      </c>
+      <c r="M482" t="n">
+        <v>98.13</v>
+      </c>
+      <c r="N482" t="n">
+        <v>3</v>
+      </c>
+      <c r="O482" t="n">
+        <v>2</v>
+      </c>
+      <c r="P482" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q482" t="n">
+        <v>1</v>
+      </c>
+      <c r="R482" t="n">
+        <v>1</v>
+      </c>
+      <c r="S482" t="n">
+        <v>4</v>
+      </c>
+      <c r="T482" t="n">
+        <v>0</v>
+      </c>
+      <c r="U482" t="n">
+        <v>0</v>
+      </c>
+      <c r="V482" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W482" t="n">
+        <v>25</v>
+      </c>
+      <c r="X482" t="inlineStr">
+        <is>
+          <t>C.B. TRES CANTOS vs ZENTRO BASKET MADRID</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/3FEB_25_26/clutch_lineups_25_26_3FEB.xlsx
+++ b/data/3FEB_25_26/clutch_lineups_25_26_3FEB.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X482"/>
+  <dimension ref="A1:X514"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40954,6 +40954,2694 @@
         </is>
       </c>
     </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>2487754</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>ADC BOADILLA</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>A. GOMEZ SERRANO | A. OLMEDO VELASCO | I. BLANCO-ARGIBAY GONZALEZ | J. VILASANCHEZ FREIJOMIL | P. DOMINGUEZ LORENZO</t>
+        </is>
+      </c>
+      <c r="D483" t="n">
+        <v>5</v>
+      </c>
+      <c r="E483" t="n">
+        <v>93</v>
+      </c>
+      <c r="F483" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="G483" t="n">
+        <v>4</v>
+      </c>
+      <c r="H483" t="n">
+        <v>6</v>
+      </c>
+      <c r="I483" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="J483" t="n">
+        <v>3</v>
+      </c>
+      <c r="K483" t="n">
+        <v>138.89</v>
+      </c>
+      <c r="L483" t="n">
+        <v>200</v>
+      </c>
+      <c r="M483" t="n">
+        <v>-61.11</v>
+      </c>
+      <c r="N483" t="n">
+        <v>2</v>
+      </c>
+      <c r="O483" t="n">
+        <v>2</v>
+      </c>
+      <c r="P483" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q483" t="n">
+        <v>0</v>
+      </c>
+      <c r="R483" t="n">
+        <v>4</v>
+      </c>
+      <c r="S483" t="n">
+        <v>0</v>
+      </c>
+      <c r="T483" t="n">
+        <v>0</v>
+      </c>
+      <c r="U483" t="n">
+        <v>1</v>
+      </c>
+      <c r="V483" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W483" t="n">
+        <v>26</v>
+      </c>
+      <c r="X483" t="inlineStr">
+        <is>
+          <t>ADC BOADILLA vs C.B. TRES CANTOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>2487754</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>ADC BOADILLA</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>A. OLMEDO VELASCO | C. CUESTA DE SANTOS | E. BOADA MONTESDEOCA | I. BLANCO-ARGIBAY GONZALEZ | J. VILASANCHEZ FREIJOMIL</t>
+        </is>
+      </c>
+      <c r="D484" t="n">
+        <v>5</v>
+      </c>
+      <c r="E484" t="n">
+        <v>41</v>
+      </c>
+      <c r="F484" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="G484" t="n">
+        <v>0</v>
+      </c>
+      <c r="H484" t="n">
+        <v>0</v>
+      </c>
+      <c r="I484" t="n">
+        <v>2</v>
+      </c>
+      <c r="J484" t="n">
+        <v>0</v>
+      </c>
+      <c r="K484" t="n">
+        <v>0</v>
+      </c>
+      <c r="L484" t="n">
+        <v>0</v>
+      </c>
+      <c r="M484" t="n">
+        <v>0</v>
+      </c>
+      <c r="N484" t="n">
+        <v>1</v>
+      </c>
+      <c r="O484" t="n">
+        <v>0</v>
+      </c>
+      <c r="P484" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q484" t="n">
+        <v>0</v>
+      </c>
+      <c r="R484" t="n">
+        <v>0</v>
+      </c>
+      <c r="S484" t="n">
+        <v>0</v>
+      </c>
+      <c r="T484" t="n">
+        <v>0</v>
+      </c>
+      <c r="U484" t="n">
+        <v>0</v>
+      </c>
+      <c r="V484" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W484" t="n">
+        <v>26</v>
+      </c>
+      <c r="X484" t="inlineStr">
+        <is>
+          <t>ADC BOADILLA vs C.B. TRES CANTOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>2487754</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>ADC BOADILLA</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>A. OLMEDO VELASCO | C. CUESTA DE SANTOS | I. BLANCO-ARGIBAY GONZALEZ | J. VILASANCHEZ FREIJOMIL | P. DOMINGUEZ LORENZO</t>
+        </is>
+      </c>
+      <c r="D485" t="n">
+        <v>5</v>
+      </c>
+      <c r="E485" t="n">
+        <v>106</v>
+      </c>
+      <c r="F485" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="G485" t="n">
+        <v>4</v>
+      </c>
+      <c r="H485" t="n">
+        <v>1</v>
+      </c>
+      <c r="I485" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="J485" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="K485" t="n">
+        <v>172.41</v>
+      </c>
+      <c r="L485" t="n">
+        <v>25.77</v>
+      </c>
+      <c r="M485" t="n">
+        <v>146.64</v>
+      </c>
+      <c r="N485" t="n">
+        <v>1</v>
+      </c>
+      <c r="O485" t="n">
+        <v>3</v>
+      </c>
+      <c r="P485" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q485" t="n">
+        <v>1</v>
+      </c>
+      <c r="R485" t="n">
+        <v>1</v>
+      </c>
+      <c r="S485" t="n">
+        <v>2</v>
+      </c>
+      <c r="T485" t="n">
+        <v>2</v>
+      </c>
+      <c r="U485" t="n">
+        <v>0</v>
+      </c>
+      <c r="V485" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W485" t="n">
+        <v>26</v>
+      </c>
+      <c r="X485" t="inlineStr">
+        <is>
+          <t>ADC BOADILLA vs C.B. TRES CANTOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>2487754</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>C.B. TRES CANTOS</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>A. SIMON DEL CORRAL | D. FERNANDEZ CAÑAS | G. LARDIES GUILLEN | H. PEREZ SANCHEZ | J. ATIENZA PEREA</t>
+        </is>
+      </c>
+      <c r="D486" t="n">
+        <v>5</v>
+      </c>
+      <c r="E486" t="n">
+        <v>33</v>
+      </c>
+      <c r="F486" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="G486" t="n">
+        <v>2</v>
+      </c>
+      <c r="H486" t="n">
+        <v>2</v>
+      </c>
+      <c r="I486" t="n">
+        <v>1</v>
+      </c>
+      <c r="J486" t="n">
+        <v>1</v>
+      </c>
+      <c r="K486" t="n">
+        <v>200</v>
+      </c>
+      <c r="L486" t="n">
+        <v>200</v>
+      </c>
+      <c r="M486" t="n">
+        <v>0</v>
+      </c>
+      <c r="N486" t="n">
+        <v>2</v>
+      </c>
+      <c r="O486" t="n">
+        <v>0</v>
+      </c>
+      <c r="P486" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q486" t="n">
+        <v>1</v>
+      </c>
+      <c r="R486" t="n">
+        <v>1</v>
+      </c>
+      <c r="S486" t="n">
+        <v>0</v>
+      </c>
+      <c r="T486" t="n">
+        <v>0</v>
+      </c>
+      <c r="U486" t="n">
+        <v>0</v>
+      </c>
+      <c r="V486" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W486" t="n">
+        <v>26</v>
+      </c>
+      <c r="X486" t="inlineStr">
+        <is>
+          <t>ADC BOADILLA vs C.B. TRES CANTOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>2487754</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>C.B. TRES CANTOS</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>D. FERNANDEZ CAÑAS | G. DIAZ MONTERO | G. LARDIES GUILLEN | J. ATIENZA PEREA | J. DE DOMINGO GARAY</t>
+        </is>
+      </c>
+      <c r="D487" t="n">
+        <v>5</v>
+      </c>
+      <c r="E487" t="n">
+        <v>60</v>
+      </c>
+      <c r="F487" t="n">
+        <v>1</v>
+      </c>
+      <c r="G487" t="n">
+        <v>4</v>
+      </c>
+      <c r="H487" t="n">
+        <v>2</v>
+      </c>
+      <c r="I487" t="n">
+        <v>2</v>
+      </c>
+      <c r="J487" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="K487" t="n">
+        <v>200</v>
+      </c>
+      <c r="L487" t="n">
+        <v>106.38</v>
+      </c>
+      <c r="M487" t="n">
+        <v>93.62</v>
+      </c>
+      <c r="N487" t="n">
+        <v>2</v>
+      </c>
+      <c r="O487" t="n">
+        <v>0</v>
+      </c>
+      <c r="P487" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q487" t="n">
+        <v>0</v>
+      </c>
+      <c r="R487" t="n">
+        <v>1</v>
+      </c>
+      <c r="S487" t="n">
+        <v>2</v>
+      </c>
+      <c r="T487" t="n">
+        <v>0</v>
+      </c>
+      <c r="U487" t="n">
+        <v>0</v>
+      </c>
+      <c r="V487" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W487" t="n">
+        <v>26</v>
+      </c>
+      <c r="X487" t="inlineStr">
+        <is>
+          <t>ADC BOADILLA vs C.B. TRES CANTOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>2487754</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>C.B. TRES CANTOS</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>D. FERNANDEZ CAÑAS | G. DIAZ MONTERO | J. ATIENZA PEREA | J. DE DOMINGO GARAY | N. MAIGA</t>
+        </is>
+      </c>
+      <c r="D488" t="n">
+        <v>5</v>
+      </c>
+      <c r="E488" t="n">
+        <v>80</v>
+      </c>
+      <c r="F488" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="G488" t="n">
+        <v>0</v>
+      </c>
+      <c r="H488" t="n">
+        <v>2</v>
+      </c>
+      <c r="I488" t="n">
+        <v>2</v>
+      </c>
+      <c r="J488" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="K488" t="n">
+        <v>0</v>
+      </c>
+      <c r="L488" t="n">
+        <v>227.27</v>
+      </c>
+      <c r="M488" t="n">
+        <v>-227.27</v>
+      </c>
+      <c r="N488" t="n">
+        <v>1</v>
+      </c>
+      <c r="O488" t="n">
+        <v>0</v>
+      </c>
+      <c r="P488" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q488" t="n">
+        <v>0</v>
+      </c>
+      <c r="R488" t="n">
+        <v>0</v>
+      </c>
+      <c r="S488" t="n">
+        <v>2</v>
+      </c>
+      <c r="T488" t="n">
+        <v>1</v>
+      </c>
+      <c r="U488" t="n">
+        <v>1</v>
+      </c>
+      <c r="V488" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W488" t="n">
+        <v>26</v>
+      </c>
+      <c r="X488" t="inlineStr">
+        <is>
+          <t>ADC BOADILLA vs C.B. TRES CANTOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>2487754</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>C.B. TRES CANTOS</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>G. DIAZ MONTERO | G. LARDIES GUILLEN | J. ATIENZA PEREA | J. DE DOMINGO GARAY | N. MAIGA</t>
+        </is>
+      </c>
+      <c r="D489" t="n">
+        <v>5</v>
+      </c>
+      <c r="E489" t="n">
+        <v>67</v>
+      </c>
+      <c r="F489" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="G489" t="n">
+        <v>1</v>
+      </c>
+      <c r="H489" t="n">
+        <v>2</v>
+      </c>
+      <c r="I489" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="J489" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="K489" t="n">
+        <v>53.19</v>
+      </c>
+      <c r="L489" t="n">
+        <v>58.14</v>
+      </c>
+      <c r="M489" t="n">
+        <v>-4.95</v>
+      </c>
+      <c r="N489" t="n">
+        <v>0</v>
+      </c>
+      <c r="O489" t="n">
+        <v>2</v>
+      </c>
+      <c r="P489" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q489" t="n">
+        <v>0</v>
+      </c>
+      <c r="R489" t="n">
+        <v>2</v>
+      </c>
+      <c r="S489" t="n">
+        <v>1</v>
+      </c>
+      <c r="T489" t="n">
+        <v>1</v>
+      </c>
+      <c r="U489" t="n">
+        <v>0</v>
+      </c>
+      <c r="V489" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W489" t="n">
+        <v>26</v>
+      </c>
+      <c r="X489" t="inlineStr">
+        <is>
+          <t>ADC BOADILLA vs C.B. TRES CANTOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>2487756</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>GRUPO EGIDO PINTOBASKET</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>J. AYALA AYLLÓN | J. SAEZ BENITO | L. BERMEJO ALCALDE | M. ALARCON ORTIZ | M. BATLLE BERNARDO</t>
+        </is>
+      </c>
+      <c r="D490" t="n">
+        <v>5</v>
+      </c>
+      <c r="E490" t="n">
+        <v>51</v>
+      </c>
+      <c r="F490" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G490" t="n">
+        <v>2</v>
+      </c>
+      <c r="H490" t="n">
+        <v>0</v>
+      </c>
+      <c r="I490" t="n">
+        <v>0</v>
+      </c>
+      <c r="J490" t="n">
+        <v>2</v>
+      </c>
+      <c r="K490" t="n">
+        <v>0</v>
+      </c>
+      <c r="L490" t="n">
+        <v>0</v>
+      </c>
+      <c r="M490" t="n">
+        <v>0</v>
+      </c>
+      <c r="N490" t="n">
+        <v>1</v>
+      </c>
+      <c r="O490" t="n">
+        <v>0</v>
+      </c>
+      <c r="P490" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q490" t="n">
+        <v>1</v>
+      </c>
+      <c r="R490" t="n">
+        <v>1</v>
+      </c>
+      <c r="S490" t="n">
+        <v>0</v>
+      </c>
+      <c r="T490" t="n">
+        <v>1</v>
+      </c>
+      <c r="U490" t="n">
+        <v>0</v>
+      </c>
+      <c r="V490" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W490" t="n">
+        <v>26</v>
+      </c>
+      <c r="X490" t="inlineStr">
+        <is>
+          <t>REAL CANOE N.C. vs GRUPO EGIDO PINTOBASKET</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>2487756</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>GRUPO EGIDO PINTOBASKET</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>J. AYALA AYLLÓN | J. SAEZ BENITO | L. BERMEJO ALCALDE | M. BATLLE BERNARDO | S. RODRIGUEZ GREGORIO</t>
+        </is>
+      </c>
+      <c r="D491" t="n">
+        <v>5</v>
+      </c>
+      <c r="E491" t="n">
+        <v>121</v>
+      </c>
+      <c r="F491" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="G491" t="n">
+        <v>2</v>
+      </c>
+      <c r="H491" t="n">
+        <v>5</v>
+      </c>
+      <c r="I491" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="J491" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="K491" t="n">
+        <v>53.19</v>
+      </c>
+      <c r="L491" t="n">
+        <v>215.52</v>
+      </c>
+      <c r="M491" t="n">
+        <v>-162.33</v>
+      </c>
+      <c r="N491" t="n">
+        <v>2</v>
+      </c>
+      <c r="O491" t="n">
+        <v>4</v>
+      </c>
+      <c r="P491" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q491" t="n">
+        <v>1</v>
+      </c>
+      <c r="R491" t="n">
+        <v>3</v>
+      </c>
+      <c r="S491" t="n">
+        <v>3</v>
+      </c>
+      <c r="T491" t="n">
+        <v>0</v>
+      </c>
+      <c r="U491" t="n">
+        <v>2</v>
+      </c>
+      <c r="V491" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W491" t="n">
+        <v>26</v>
+      </c>
+      <c r="X491" t="inlineStr">
+        <is>
+          <t>REAL CANOE N.C. vs GRUPO EGIDO PINTOBASKET</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>2487756</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>GRUPO EGIDO PINTOBASKET</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>J. AYALA AYLLÓN | J. SAEZ BENITO | M. ALARCON ORTIZ | M. BATLLE BERNARDO | M. DEL VALLE REGALADO</t>
+        </is>
+      </c>
+      <c r="D492" t="n">
+        <v>5</v>
+      </c>
+      <c r="E492" t="n">
+        <v>52</v>
+      </c>
+      <c r="F492" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="G492" t="n">
+        <v>2</v>
+      </c>
+      <c r="H492" t="n">
+        <v>2</v>
+      </c>
+      <c r="I492" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="J492" t="n">
+        <v>1</v>
+      </c>
+      <c r="K492" t="n">
+        <v>69.44</v>
+      </c>
+      <c r="L492" t="n">
+        <v>200</v>
+      </c>
+      <c r="M492" t="n">
+        <v>-130.56</v>
+      </c>
+      <c r="N492" t="n">
+        <v>1</v>
+      </c>
+      <c r="O492" t="n">
+        <v>2</v>
+      </c>
+      <c r="P492" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q492" t="n">
+        <v>0</v>
+      </c>
+      <c r="R492" t="n">
+        <v>1</v>
+      </c>
+      <c r="S492" t="n">
+        <v>0</v>
+      </c>
+      <c r="T492" t="n">
+        <v>1</v>
+      </c>
+      <c r="U492" t="n">
+        <v>1</v>
+      </c>
+      <c r="V492" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W492" t="n">
+        <v>26</v>
+      </c>
+      <c r="X492" t="inlineStr">
+        <is>
+          <t>REAL CANOE N.C. vs GRUPO EGIDO PINTOBASKET</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>2487756</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>GRUPO EGIDO PINTOBASKET</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>J. AYALA AYLLÓN | L. BERMEJO ALCALDE | M. ALARCON ORTIZ | M. BATLLE BERNARDO | S. RODRIGUEZ GREGORIO</t>
+        </is>
+      </c>
+      <c r="D493" t="n">
+        <v>5</v>
+      </c>
+      <c r="E493" t="n">
+        <v>64</v>
+      </c>
+      <c r="F493" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="G493" t="n">
+        <v>0</v>
+      </c>
+      <c r="H493" t="n">
+        <v>0</v>
+      </c>
+      <c r="I493" t="n">
+        <v>2</v>
+      </c>
+      <c r="J493" t="n">
+        <v>2</v>
+      </c>
+      <c r="K493" t="n">
+        <v>0</v>
+      </c>
+      <c r="L493" t="n">
+        <v>0</v>
+      </c>
+      <c r="M493" t="n">
+        <v>0</v>
+      </c>
+      <c r="N493" t="n">
+        <v>1</v>
+      </c>
+      <c r="O493" t="n">
+        <v>0</v>
+      </c>
+      <c r="P493" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q493" t="n">
+        <v>0</v>
+      </c>
+      <c r="R493" t="n">
+        <v>3</v>
+      </c>
+      <c r="S493" t="n">
+        <v>0</v>
+      </c>
+      <c r="T493" t="n">
+        <v>0</v>
+      </c>
+      <c r="U493" t="n">
+        <v>1</v>
+      </c>
+      <c r="V493" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W493" t="n">
+        <v>26</v>
+      </c>
+      <c r="X493" t="inlineStr">
+        <is>
+          <t>REAL CANOE N.C. vs GRUPO EGIDO PINTOBASKET</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>2487756</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>REAL CANOE N.C.</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>D. MANZANERO CAMACHO | J. GARCIA-LARRACHE SEGURA | J. LAPASTORA ARACIL | L. GARCIA LARRACHE SEGURA | M. KREISLER LORENTE</t>
+        </is>
+      </c>
+      <c r="D494" t="n">
+        <v>5</v>
+      </c>
+      <c r="E494" t="n">
+        <v>139</v>
+      </c>
+      <c r="F494" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="G494" t="n">
+        <v>5</v>
+      </c>
+      <c r="H494" t="n">
+        <v>2</v>
+      </c>
+      <c r="I494" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="J494" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="K494" t="n">
+        <v>150.6</v>
+      </c>
+      <c r="L494" t="n">
+        <v>53.19</v>
+      </c>
+      <c r="M494" t="n">
+        <v>97.41</v>
+      </c>
+      <c r="N494" t="n">
+        <v>4</v>
+      </c>
+      <c r="O494" t="n">
+        <v>3</v>
+      </c>
+      <c r="P494" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q494" t="n">
+        <v>2</v>
+      </c>
+      <c r="R494" t="n">
+        <v>2</v>
+      </c>
+      <c r="S494" t="n">
+        <v>4</v>
+      </c>
+      <c r="T494" t="n">
+        <v>1</v>
+      </c>
+      <c r="U494" t="n">
+        <v>1</v>
+      </c>
+      <c r="V494" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W494" t="n">
+        <v>26</v>
+      </c>
+      <c r="X494" t="inlineStr">
+        <is>
+          <t>REAL CANOE N.C. vs GRUPO EGIDO PINTOBASKET</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>2487756</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>REAL CANOE N.C.</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>D. MANZANERO CAMACHO | J. GARCIA-LARRACHE SEGURA | L. GARCIA LARRACHE SEGURA | M. HERMOSO ALCUBILLA | P. FUENTE DIEZ</t>
+        </is>
+      </c>
+      <c r="D495" t="n">
+        <v>5</v>
+      </c>
+      <c r="E495" t="n">
+        <v>52</v>
+      </c>
+      <c r="F495" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="G495" t="n">
+        <v>2</v>
+      </c>
+      <c r="H495" t="n">
+        <v>2</v>
+      </c>
+      <c r="I495" t="n">
+        <v>1</v>
+      </c>
+      <c r="J495" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="K495" t="n">
+        <v>200</v>
+      </c>
+      <c r="L495" t="n">
+        <v>69.44</v>
+      </c>
+      <c r="M495" t="n">
+        <v>130.56</v>
+      </c>
+      <c r="N495" t="n">
+        <v>1</v>
+      </c>
+      <c r="O495" t="n">
+        <v>0</v>
+      </c>
+      <c r="P495" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q495" t="n">
+        <v>1</v>
+      </c>
+      <c r="R495" t="n">
+        <v>1</v>
+      </c>
+      <c r="S495" t="n">
+        <v>2</v>
+      </c>
+      <c r="T495" t="n">
+        <v>1</v>
+      </c>
+      <c r="U495" t="n">
+        <v>0</v>
+      </c>
+      <c r="V495" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W495" t="n">
+        <v>26</v>
+      </c>
+      <c r="X495" t="inlineStr">
+        <is>
+          <t>REAL CANOE N.C. vs GRUPO EGIDO PINTOBASKET</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>2487756</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>REAL CANOE N.C.</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>D. MANZANERO CAMACHO | J. LAPASTORA ARACIL | L. GARCIA LARRACHE SEGURA | M. HERMOSO ALCUBILLA | P. FUENTE DIEZ</t>
+        </is>
+      </c>
+      <c r="D496" t="n">
+        <v>5</v>
+      </c>
+      <c r="E496" t="n">
+        <v>97</v>
+      </c>
+      <c r="F496" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="G496" t="n">
+        <v>0</v>
+      </c>
+      <c r="H496" t="n">
+        <v>2</v>
+      </c>
+      <c r="I496" t="n">
+        <v>3</v>
+      </c>
+      <c r="J496" t="n">
+        <v>2</v>
+      </c>
+      <c r="K496" t="n">
+        <v>0</v>
+      </c>
+      <c r="L496" t="n">
+        <v>100</v>
+      </c>
+      <c r="M496" t="n">
+        <v>-100</v>
+      </c>
+      <c r="N496" t="n">
+        <v>3</v>
+      </c>
+      <c r="O496" t="n">
+        <v>0</v>
+      </c>
+      <c r="P496" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q496" t="n">
+        <v>1</v>
+      </c>
+      <c r="R496" t="n">
+        <v>2</v>
+      </c>
+      <c r="S496" t="n">
+        <v>0</v>
+      </c>
+      <c r="T496" t="n">
+        <v>1</v>
+      </c>
+      <c r="U496" t="n">
+        <v>1</v>
+      </c>
+      <c r="V496" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W496" t="n">
+        <v>26</v>
+      </c>
+      <c r="X496" t="inlineStr">
+        <is>
+          <t>REAL CANOE N.C. vs GRUPO EGIDO PINTOBASKET</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>2487758</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>CB ARIDANE</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>A. GASE SECO | G. MEJÍA ACOSTA | G. PIERRE-GABRIEL ANDREA GASTON | J. ABRIL RAMIRO | O. BALSELLS PLAZA</t>
+        </is>
+      </c>
+      <c r="D497" t="n">
+        <v>5</v>
+      </c>
+      <c r="E497" t="n">
+        <v>82</v>
+      </c>
+      <c r="F497" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="G497" t="n">
+        <v>0</v>
+      </c>
+      <c r="H497" t="n">
+        <v>2</v>
+      </c>
+      <c r="I497" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="J497" t="n">
+        <v>3</v>
+      </c>
+      <c r="K497" t="n">
+        <v>0</v>
+      </c>
+      <c r="L497" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="M497" t="n">
+        <v>-66.67</v>
+      </c>
+      <c r="N497" t="n">
+        <v>0</v>
+      </c>
+      <c r="O497" t="n">
+        <v>2</v>
+      </c>
+      <c r="P497" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q497" t="n">
+        <v>0</v>
+      </c>
+      <c r="R497" t="n">
+        <v>5</v>
+      </c>
+      <c r="S497" t="n">
+        <v>0</v>
+      </c>
+      <c r="T497" t="n">
+        <v>0</v>
+      </c>
+      <c r="U497" t="n">
+        <v>2</v>
+      </c>
+      <c r="V497" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W497" t="n">
+        <v>26</v>
+      </c>
+      <c r="X497" t="inlineStr">
+        <is>
+          <t>CB ARIDANE vs UROS DE RIVAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>2487758</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>CB ARIDANE</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>A. GASE SECO | G. MEJÍA ACOSTA | G. PIERRE-GABRIEL ANDREA GASTON | J. GONZÁLEZ CHÁVEZ | K. SKUTYELNIK</t>
+        </is>
+      </c>
+      <c r="D498" t="n">
+        <v>5</v>
+      </c>
+      <c r="E498" t="n">
+        <v>3</v>
+      </c>
+      <c r="F498" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G498" t="n">
+        <v>2</v>
+      </c>
+      <c r="H498" t="n">
+        <v>0</v>
+      </c>
+      <c r="I498" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="J498" t="n">
+        <v>0</v>
+      </c>
+      <c r="K498" t="n">
+        <v>227.27</v>
+      </c>
+      <c r="L498" t="n">
+        <v>0</v>
+      </c>
+      <c r="M498" t="n">
+        <v>0</v>
+      </c>
+      <c r="N498" t="n">
+        <v>0</v>
+      </c>
+      <c r="O498" t="n">
+        <v>2</v>
+      </c>
+      <c r="P498" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q498" t="n">
+        <v>0</v>
+      </c>
+      <c r="R498" t="n">
+        <v>0</v>
+      </c>
+      <c r="S498" t="n">
+        <v>0</v>
+      </c>
+      <c r="T498" t="n">
+        <v>0</v>
+      </c>
+      <c r="U498" t="n">
+        <v>0</v>
+      </c>
+      <c r="V498" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W498" t="n">
+        <v>26</v>
+      </c>
+      <c r="X498" t="inlineStr">
+        <is>
+          <t>CB ARIDANE vs UROS DE RIVAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>2487758</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>CB ARIDANE</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>A. GASE SECO | G. MEJÍA ACOSTA | G. PIERRE-GABRIEL ANDREA GASTON | J. GONZÁLEZ CHÁVEZ | O. BALSELLS PLAZA</t>
+        </is>
+      </c>
+      <c r="D499" t="n">
+        <v>5</v>
+      </c>
+      <c r="E499" t="n">
+        <v>180</v>
+      </c>
+      <c r="F499" t="n">
+        <v>3</v>
+      </c>
+      <c r="G499" t="n">
+        <v>7</v>
+      </c>
+      <c r="H499" t="n">
+        <v>0</v>
+      </c>
+      <c r="I499" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="J499" t="n">
+        <v>5</v>
+      </c>
+      <c r="K499" t="n">
+        <v>180.41</v>
+      </c>
+      <c r="L499" t="n">
+        <v>0</v>
+      </c>
+      <c r="M499" t="n">
+        <v>180.41</v>
+      </c>
+      <c r="N499" t="n">
+        <v>4</v>
+      </c>
+      <c r="O499" t="n">
+        <v>2</v>
+      </c>
+      <c r="P499" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q499" t="n">
+        <v>3</v>
+      </c>
+      <c r="R499" t="n">
+        <v>6</v>
+      </c>
+      <c r="S499" t="n">
+        <v>0</v>
+      </c>
+      <c r="T499" t="n">
+        <v>0</v>
+      </c>
+      <c r="U499" t="n">
+        <v>1</v>
+      </c>
+      <c r="V499" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W499" t="n">
+        <v>26</v>
+      </c>
+      <c r="X499" t="inlineStr">
+        <is>
+          <t>CB ARIDANE vs UROS DE RIVAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>2487758</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>CB ARIDANE</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>A. GASE SECO | G. MEJÍA ACOSTA | G. PIERRE-GABRIEL ANDREA GASTON | K. SKUTYELNIK | O. BALSELLS PLAZA</t>
+        </is>
+      </c>
+      <c r="D500" t="n">
+        <v>5</v>
+      </c>
+      <c r="E500" t="n">
+        <v>8</v>
+      </c>
+      <c r="F500" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="G500" t="n">
+        <v>2</v>
+      </c>
+      <c r="H500" t="n">
+        <v>4</v>
+      </c>
+      <c r="I500" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="J500" t="n">
+        <v>2</v>
+      </c>
+      <c r="K500" t="n">
+        <v>227.27</v>
+      </c>
+      <c r="L500" t="n">
+        <v>200</v>
+      </c>
+      <c r="M500" t="n">
+        <v>27.27</v>
+      </c>
+      <c r="N500" t="n">
+        <v>0</v>
+      </c>
+      <c r="O500" t="n">
+        <v>2</v>
+      </c>
+      <c r="P500" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q500" t="n">
+        <v>0</v>
+      </c>
+      <c r="R500" t="n">
+        <v>2</v>
+      </c>
+      <c r="S500" t="n">
+        <v>0</v>
+      </c>
+      <c r="T500" t="n">
+        <v>0</v>
+      </c>
+      <c r="U500" t="n">
+        <v>0</v>
+      </c>
+      <c r="V500" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W500" t="n">
+        <v>26</v>
+      </c>
+      <c r="X500" t="inlineStr">
+        <is>
+          <t>CB ARIDANE vs UROS DE RIVAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>2487758</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>CB ARIDANE</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>A. GASE SECO | G. MEJÍA ACOSTA | J. GONZÁLEZ CHÁVEZ | O. BALSELLS PLAZA | S. GUEYE</t>
+        </is>
+      </c>
+      <c r="D501" t="n">
+        <v>5</v>
+      </c>
+      <c r="E501" t="n">
+        <v>19</v>
+      </c>
+      <c r="F501" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="G501" t="n">
+        <v>1</v>
+      </c>
+      <c r="H501" t="n">
+        <v>0</v>
+      </c>
+      <c r="I501" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="J501" t="n">
+        <v>0</v>
+      </c>
+      <c r="K501" t="n">
+        <v>113.64</v>
+      </c>
+      <c r="L501" t="n">
+        <v>0</v>
+      </c>
+      <c r="M501" t="n">
+        <v>0</v>
+      </c>
+      <c r="N501" t="n">
+        <v>1</v>
+      </c>
+      <c r="O501" t="n">
+        <v>2</v>
+      </c>
+      <c r="P501" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q501" t="n">
+        <v>1</v>
+      </c>
+      <c r="R501" t="n">
+        <v>0</v>
+      </c>
+      <c r="S501" t="n">
+        <v>0</v>
+      </c>
+      <c r="T501" t="n">
+        <v>0</v>
+      </c>
+      <c r="U501" t="n">
+        <v>0</v>
+      </c>
+      <c r="V501" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W501" t="n">
+        <v>26</v>
+      </c>
+      <c r="X501" t="inlineStr">
+        <is>
+          <t>CB ARIDANE vs UROS DE RIVAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>2487758</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>UROS DE RIVAS</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>A. BIERSACK LOPEZ | A. GARCIA QUILEZ CUERVAS | A. PEREZ CONTI | O. MENDEZ BLANCO | P. ESTEBANEZ GONZALEZ</t>
+        </is>
+      </c>
+      <c r="D502" t="n">
+        <v>5</v>
+      </c>
+      <c r="E502" t="n">
+        <v>151</v>
+      </c>
+      <c r="F502" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="G502" t="n">
+        <v>0</v>
+      </c>
+      <c r="H502" t="n">
+        <v>3</v>
+      </c>
+      <c r="I502" t="n">
+        <v>4</v>
+      </c>
+      <c r="J502" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="K502" t="n">
+        <v>0</v>
+      </c>
+      <c r="L502" t="n">
+        <v>77.31999999999999</v>
+      </c>
+      <c r="M502" t="n">
+        <v>-77.31999999999999</v>
+      </c>
+      <c r="N502" t="n">
+        <v>7</v>
+      </c>
+      <c r="O502" t="n">
+        <v>0</v>
+      </c>
+      <c r="P502" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q502" t="n">
+        <v>3</v>
+      </c>
+      <c r="R502" t="n">
+        <v>3</v>
+      </c>
+      <c r="S502" t="n">
+        <v>2</v>
+      </c>
+      <c r="T502" t="n">
+        <v>1</v>
+      </c>
+      <c r="U502" t="n">
+        <v>1</v>
+      </c>
+      <c r="V502" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W502" t="n">
+        <v>26</v>
+      </c>
+      <c r="X502" t="inlineStr">
+        <is>
+          <t>CB ARIDANE vs UROS DE RIVAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>2487758</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>UROS DE RIVAS</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>A. BIERSACK LOPEZ | C. CRESPO MONTESINOS | D. MARINEZ FERNANDEZ-URRUTIA | G. MARTIN LOPEZ-LAGO | O. HADI ADEGBITE</t>
+        </is>
+      </c>
+      <c r="D503" t="n">
+        <v>5</v>
+      </c>
+      <c r="E503" t="n">
+        <v>66</v>
+      </c>
+      <c r="F503" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="G503" t="n">
+        <v>0</v>
+      </c>
+      <c r="H503" t="n">
+        <v>3</v>
+      </c>
+      <c r="I503" t="n">
+        <v>2</v>
+      </c>
+      <c r="J503" t="n">
+        <v>1</v>
+      </c>
+      <c r="K503" t="n">
+        <v>0</v>
+      </c>
+      <c r="L503" t="n">
+        <v>300</v>
+      </c>
+      <c r="M503" t="n">
+        <v>-300</v>
+      </c>
+      <c r="N503" t="n">
+        <v>2</v>
+      </c>
+      <c r="O503" t="n">
+        <v>0</v>
+      </c>
+      <c r="P503" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q503" t="n">
+        <v>0</v>
+      </c>
+      <c r="R503" t="n">
+        <v>2</v>
+      </c>
+      <c r="S503" t="n">
+        <v>0</v>
+      </c>
+      <c r="T503" t="n">
+        <v>0</v>
+      </c>
+      <c r="U503" t="n">
+        <v>1</v>
+      </c>
+      <c r="V503" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W503" t="n">
+        <v>26</v>
+      </c>
+      <c r="X503" t="inlineStr">
+        <is>
+          <t>CB ARIDANE vs UROS DE RIVAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>2487758</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>UROS DE RIVAS</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>A. BIERSACK LOPEZ | C. CRESPO MONTESINOS | D. MARINEZ FERNANDEZ-URRUTIA | G. MARTIN LOPEZ-LAGO | O. MENDEZ BLANCO</t>
+        </is>
+      </c>
+      <c r="D504" t="n">
+        <v>5</v>
+      </c>
+      <c r="E504" t="n">
+        <v>41</v>
+      </c>
+      <c r="F504" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="G504" t="n">
+        <v>0</v>
+      </c>
+      <c r="H504" t="n">
+        <v>1</v>
+      </c>
+      <c r="I504" t="n">
+        <v>1</v>
+      </c>
+      <c r="J504" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="K504" t="n">
+        <v>0</v>
+      </c>
+      <c r="L504" t="n">
+        <v>113.64</v>
+      </c>
+      <c r="M504" t="n">
+        <v>-113.64</v>
+      </c>
+      <c r="N504" t="n">
+        <v>1</v>
+      </c>
+      <c r="O504" t="n">
+        <v>0</v>
+      </c>
+      <c r="P504" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q504" t="n">
+        <v>0</v>
+      </c>
+      <c r="R504" t="n">
+        <v>0</v>
+      </c>
+      <c r="S504" t="n">
+        <v>2</v>
+      </c>
+      <c r="T504" t="n">
+        <v>1</v>
+      </c>
+      <c r="U504" t="n">
+        <v>1</v>
+      </c>
+      <c r="V504" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W504" t="n">
+        <v>26</v>
+      </c>
+      <c r="X504" t="inlineStr">
+        <is>
+          <t>CB ARIDANE vs UROS DE RIVAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>2487758</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>UROS DE RIVAS</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>A. BIERSACK LOPEZ | C. CRESPO MONTESINOS | D. MARINEZ FERNANDEZ-URRUTIA | O. HADI ADEGBITE | O. MENDEZ BLANCO</t>
+        </is>
+      </c>
+      <c r="D505" t="n">
+        <v>5</v>
+      </c>
+      <c r="E505" t="n">
+        <v>1</v>
+      </c>
+      <c r="F505" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G505" t="n">
+        <v>0</v>
+      </c>
+      <c r="H505" t="n">
+        <v>1</v>
+      </c>
+      <c r="I505" t="n">
+        <v>0</v>
+      </c>
+      <c r="J505" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="K505" t="n">
+        <v>0</v>
+      </c>
+      <c r="L505" t="n">
+        <v>0</v>
+      </c>
+      <c r="M505" t="n">
+        <v>0</v>
+      </c>
+      <c r="N505" t="n">
+        <v>0</v>
+      </c>
+      <c r="O505" t="n">
+        <v>0</v>
+      </c>
+      <c r="P505" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q505" t="n">
+        <v>0</v>
+      </c>
+      <c r="R505" t="n">
+        <v>0</v>
+      </c>
+      <c r="S505" t="n">
+        <v>2</v>
+      </c>
+      <c r="T505" t="n">
+        <v>0</v>
+      </c>
+      <c r="U505" t="n">
+        <v>1</v>
+      </c>
+      <c r="V505" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W505" t="n">
+        <v>26</v>
+      </c>
+      <c r="X505" t="inlineStr">
+        <is>
+          <t>CB ARIDANE vs UROS DE RIVAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>2487758</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>UROS DE RIVAS</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>A. GARCIA QUILEZ CUERVAS | A. PEREZ CONTI | O. HADI ADEGBITE | O. MENDEZ BLANCO | P. ESTEBANEZ GONZALEZ</t>
+        </is>
+      </c>
+      <c r="D506" t="n">
+        <v>5</v>
+      </c>
+      <c r="E506" t="n">
+        <v>22</v>
+      </c>
+      <c r="F506" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="G506" t="n">
+        <v>2</v>
+      </c>
+      <c r="H506" t="n">
+        <v>0</v>
+      </c>
+      <c r="I506" t="n">
+        <v>1</v>
+      </c>
+      <c r="J506" t="n">
+        <v>1</v>
+      </c>
+      <c r="K506" t="n">
+        <v>200</v>
+      </c>
+      <c r="L506" t="n">
+        <v>0</v>
+      </c>
+      <c r="M506" t="n">
+        <v>200</v>
+      </c>
+      <c r="N506" t="n">
+        <v>1</v>
+      </c>
+      <c r="O506" t="n">
+        <v>0</v>
+      </c>
+      <c r="P506" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q506" t="n">
+        <v>0</v>
+      </c>
+      <c r="R506" t="n">
+        <v>0</v>
+      </c>
+      <c r="S506" t="n">
+        <v>0</v>
+      </c>
+      <c r="T506" t="n">
+        <v>1</v>
+      </c>
+      <c r="U506" t="n">
+        <v>0</v>
+      </c>
+      <c r="V506" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W506" t="n">
+        <v>26</v>
+      </c>
+      <c r="X506" t="inlineStr">
+        <is>
+          <t>CB ARIDANE vs UROS DE RIVAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>2487758</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>UROS DE RIVAS</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>A. PEREZ CONTI | C. CRESPO MONTESINOS | G. MARTIN LOPEZ-LAGO | O. MENDEZ BLANCO | P. ESTEBANEZ GONZALEZ</t>
+        </is>
+      </c>
+      <c r="D507" t="n">
+        <v>5</v>
+      </c>
+      <c r="E507" t="n">
+        <v>6</v>
+      </c>
+      <c r="F507" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G507" t="n">
+        <v>2</v>
+      </c>
+      <c r="H507" t="n">
+        <v>2</v>
+      </c>
+      <c r="I507" t="n">
+        <v>1</v>
+      </c>
+      <c r="J507" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="K507" t="n">
+        <v>200</v>
+      </c>
+      <c r="L507" t="n">
+        <v>227.27</v>
+      </c>
+      <c r="M507" t="n">
+        <v>-27.27</v>
+      </c>
+      <c r="N507" t="n">
+        <v>1</v>
+      </c>
+      <c r="O507" t="n">
+        <v>0</v>
+      </c>
+      <c r="P507" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q507" t="n">
+        <v>0</v>
+      </c>
+      <c r="R507" t="n">
+        <v>0</v>
+      </c>
+      <c r="S507" t="n">
+        <v>2</v>
+      </c>
+      <c r="T507" t="n">
+        <v>0</v>
+      </c>
+      <c r="U507" t="n">
+        <v>0</v>
+      </c>
+      <c r="V507" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W507" t="n">
+        <v>26</v>
+      </c>
+      <c r="X507" t="inlineStr">
+        <is>
+          <t>CB ARIDANE vs UROS DE RIVAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>2487758</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>UROS DE RIVAS</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>C. CRESPO MONTESINOS | D. MARINEZ FERNANDEZ-URRUTIA | G. MARTIN LOPEZ-LAGO | O. MENDEZ BLANCO | P. ESTEBANEZ GONZALEZ</t>
+        </is>
+      </c>
+      <c r="D508" t="n">
+        <v>5</v>
+      </c>
+      <c r="E508" t="n">
+        <v>5</v>
+      </c>
+      <c r="F508" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="G508" t="n">
+        <v>2</v>
+      </c>
+      <c r="H508" t="n">
+        <v>2</v>
+      </c>
+      <c r="I508" t="n">
+        <v>1</v>
+      </c>
+      <c r="J508" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="K508" t="n">
+        <v>200</v>
+      </c>
+      <c r="L508" t="n">
+        <v>227.27</v>
+      </c>
+      <c r="M508" t="n">
+        <v>-27.27</v>
+      </c>
+      <c r="N508" t="n">
+        <v>1</v>
+      </c>
+      <c r="O508" t="n">
+        <v>0</v>
+      </c>
+      <c r="P508" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q508" t="n">
+        <v>0</v>
+      </c>
+      <c r="R508" t="n">
+        <v>0</v>
+      </c>
+      <c r="S508" t="n">
+        <v>2</v>
+      </c>
+      <c r="T508" t="n">
+        <v>0</v>
+      </c>
+      <c r="U508" t="n">
+        <v>0</v>
+      </c>
+      <c r="V508" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W508" t="n">
+        <v>26</v>
+      </c>
+      <c r="X508" t="inlineStr">
+        <is>
+          <t>CB ARIDANE vs UROS DE RIVAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>2487752</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>BALONCESTO TALAVERA</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>A. VICENTE VIANA | B. GUEYE | C. KLOTZ MAROTO | C. UNANUE CEGARRA | D. LORENZO NEGRETE</t>
+        </is>
+      </c>
+      <c r="D509" t="n">
+        <v>5</v>
+      </c>
+      <c r="E509" t="n">
+        <v>51</v>
+      </c>
+      <c r="F509" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G509" t="n">
+        <v>3</v>
+      </c>
+      <c r="H509" t="n">
+        <v>2</v>
+      </c>
+      <c r="I509" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="J509" t="n">
+        <v>2</v>
+      </c>
+      <c r="K509" t="n">
+        <v>170.45</v>
+      </c>
+      <c r="L509" t="n">
+        <v>100</v>
+      </c>
+      <c r="M509" t="n">
+        <v>70.45</v>
+      </c>
+      <c r="N509" t="n">
+        <v>1</v>
+      </c>
+      <c r="O509" t="n">
+        <v>4</v>
+      </c>
+      <c r="P509" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q509" t="n">
+        <v>1</v>
+      </c>
+      <c r="R509" t="n">
+        <v>2</v>
+      </c>
+      <c r="S509" t="n">
+        <v>0</v>
+      </c>
+      <c r="T509" t="n">
+        <v>0</v>
+      </c>
+      <c r="U509" t="n">
+        <v>0</v>
+      </c>
+      <c r="V509" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W509" t="n">
+        <v>26</v>
+      </c>
+      <c r="X509" t="inlineStr">
+        <is>
+          <t>EB FELIPE ANTÓN vs BALONCESTO TALAVERA</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>2487752</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>BALONCESTO TALAVERA</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>A. VICENTE VIANA | B. GUEYE | C. KLOTZ MAROTO | D. LORENZO NEGRETE | S. GACIC</t>
+        </is>
+      </c>
+      <c r="D510" t="n">
+        <v>5</v>
+      </c>
+      <c r="E510" t="n">
+        <v>25</v>
+      </c>
+      <c r="F510" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="G510" t="n">
+        <v>0</v>
+      </c>
+      <c r="H510" t="n">
+        <v>2</v>
+      </c>
+      <c r="I510" t="n">
+        <v>1</v>
+      </c>
+      <c r="J510" t="n">
+        <v>2</v>
+      </c>
+      <c r="K510" t="n">
+        <v>0</v>
+      </c>
+      <c r="L510" t="n">
+        <v>100</v>
+      </c>
+      <c r="M510" t="n">
+        <v>-100</v>
+      </c>
+      <c r="N510" t="n">
+        <v>0</v>
+      </c>
+      <c r="O510" t="n">
+        <v>0</v>
+      </c>
+      <c r="P510" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q510" t="n">
+        <v>0</v>
+      </c>
+      <c r="R510" t="n">
+        <v>2</v>
+      </c>
+      <c r="S510" t="n">
+        <v>0</v>
+      </c>
+      <c r="T510" t="n">
+        <v>0</v>
+      </c>
+      <c r="U510" t="n">
+        <v>0</v>
+      </c>
+      <c r="V510" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W510" t="n">
+        <v>26</v>
+      </c>
+      <c r="X510" t="inlineStr">
+        <is>
+          <t>EB FELIPE ANTÓN vs BALONCESTO TALAVERA</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>2487752</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>BALONCESTO TALAVERA</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>A. VICENTE VIANA | B. GUEYE | D. LORENZO NEGRETE | S. GACIC | V. ALONSO PASCUAL</t>
+        </is>
+      </c>
+      <c r="D511" t="n">
+        <v>5</v>
+      </c>
+      <c r="E511" t="n">
+        <v>55</v>
+      </c>
+      <c r="F511" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="G511" t="n">
+        <v>1</v>
+      </c>
+      <c r="H511" t="n">
+        <v>2</v>
+      </c>
+      <c r="I511" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="J511" t="n">
+        <v>1</v>
+      </c>
+      <c r="K511" t="n">
+        <v>53.19</v>
+      </c>
+      <c r="L511" t="n">
+        <v>200</v>
+      </c>
+      <c r="M511" t="n">
+        <v>-146.81</v>
+      </c>
+      <c r="N511" t="n">
+        <v>1</v>
+      </c>
+      <c r="O511" t="n">
+        <v>2</v>
+      </c>
+      <c r="P511" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q511" t="n">
+        <v>0</v>
+      </c>
+      <c r="R511" t="n">
+        <v>1</v>
+      </c>
+      <c r="S511" t="n">
+        <v>0</v>
+      </c>
+      <c r="T511" t="n">
+        <v>0</v>
+      </c>
+      <c r="U511" t="n">
+        <v>0</v>
+      </c>
+      <c r="V511" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W511" t="n">
+        <v>26</v>
+      </c>
+      <c r="X511" t="inlineStr">
+        <is>
+          <t>EB FELIPE ANTÓN vs BALONCESTO TALAVERA</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>2487752</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>A. SISTAC RODRIGUEZ | B. FERNANDEZ SHEPHARD | J. GALLETTO LAMELA | K. RIVEROL DE LAS CASAS | S. MANERO GUZMAN</t>
+        </is>
+      </c>
+      <c r="D512" t="n">
+        <v>5</v>
+      </c>
+      <c r="E512" t="n">
+        <v>39</v>
+      </c>
+      <c r="F512" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G512" t="n">
+        <v>2</v>
+      </c>
+      <c r="H512" t="n">
+        <v>1</v>
+      </c>
+      <c r="I512" t="n">
+        <v>1</v>
+      </c>
+      <c r="J512" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="K512" t="n">
+        <v>200</v>
+      </c>
+      <c r="L512" t="n">
+        <v>53.19</v>
+      </c>
+      <c r="M512" t="n">
+        <v>146.81</v>
+      </c>
+      <c r="N512" t="n">
+        <v>1</v>
+      </c>
+      <c r="O512" t="n">
+        <v>0</v>
+      </c>
+      <c r="P512" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q512" t="n">
+        <v>0</v>
+      </c>
+      <c r="R512" t="n">
+        <v>1</v>
+      </c>
+      <c r="S512" t="n">
+        <v>2</v>
+      </c>
+      <c r="T512" t="n">
+        <v>0</v>
+      </c>
+      <c r="U512" t="n">
+        <v>0</v>
+      </c>
+      <c r="V512" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W512" t="n">
+        <v>26</v>
+      </c>
+      <c r="X512" t="inlineStr">
+        <is>
+          <t>EB FELIPE ANTÓN vs BALONCESTO TALAVERA</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>2487752</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>A. SISTAC RODRIGUEZ | J. GALLETTO LAMELA | K. RIVEROL DE LAS CASAS | M. NIMAGA | S. MANERO GUZMAN</t>
+        </is>
+      </c>
+      <c r="D513" t="n">
+        <v>5</v>
+      </c>
+      <c r="E513" t="n">
+        <v>90</v>
+      </c>
+      <c r="F513" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G513" t="n">
+        <v>4</v>
+      </c>
+      <c r="H513" t="n">
+        <v>3</v>
+      </c>
+      <c r="I513" t="n">
+        <v>3</v>
+      </c>
+      <c r="J513" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="K513" t="n">
+        <v>133.33</v>
+      </c>
+      <c r="L513" t="n">
+        <v>79.79000000000001</v>
+      </c>
+      <c r="M513" t="n">
+        <v>53.55</v>
+      </c>
+      <c r="N513" t="n">
+        <v>3</v>
+      </c>
+      <c r="O513" t="n">
+        <v>0</v>
+      </c>
+      <c r="P513" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q513" t="n">
+        <v>0</v>
+      </c>
+      <c r="R513" t="n">
+        <v>1</v>
+      </c>
+      <c r="S513" t="n">
+        <v>4</v>
+      </c>
+      <c r="T513" t="n">
+        <v>1</v>
+      </c>
+      <c r="U513" t="n">
+        <v>0</v>
+      </c>
+      <c r="V513" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W513" t="n">
+        <v>26</v>
+      </c>
+      <c r="X513" t="inlineStr">
+        <is>
+          <t>EB FELIPE ANTÓN vs BALONCESTO TALAVERA</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>2487752</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>J. GALLETTO LAMELA | K. RIVEROL DE LAS CASAS | M. NIMAGA | P. ARGÜELLES ELORZA | S. MANERO GUZMAN</t>
+        </is>
+      </c>
+      <c r="D514" t="n">
+        <v>5</v>
+      </c>
+      <c r="E514" t="n">
+        <v>2</v>
+      </c>
+      <c r="F514" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G514" t="n">
+        <v>0</v>
+      </c>
+      <c r="H514" t="n">
+        <v>0</v>
+      </c>
+      <c r="I514" t="n">
+        <v>1</v>
+      </c>
+      <c r="J514" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K514" t="n">
+        <v>0</v>
+      </c>
+      <c r="L514" t="n">
+        <v>0</v>
+      </c>
+      <c r="M514" t="n">
+        <v>0</v>
+      </c>
+      <c r="N514" t="n">
+        <v>1</v>
+      </c>
+      <c r="O514" t="n">
+        <v>0</v>
+      </c>
+      <c r="P514" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q514" t="n">
+        <v>0</v>
+      </c>
+      <c r="R514" t="n">
+        <v>0</v>
+      </c>
+      <c r="S514" t="n">
+        <v>0</v>
+      </c>
+      <c r="T514" t="n">
+        <v>0</v>
+      </c>
+      <c r="U514" t="n">
+        <v>1</v>
+      </c>
+      <c r="V514" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W514" t="n">
+        <v>26</v>
+      </c>
+      <c r="X514" t="inlineStr">
+        <is>
+          <t>EB FELIPE ANTÓN vs BALONCESTO TALAVERA</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/3FEB_25_26/clutch_lineups_25_26_3FEB.xlsx
+++ b/data/3FEB_25_26/clutch_lineups_25_26_3FEB.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X514"/>
+  <dimension ref="A1:X431"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36670,6978 +36670,6 @@
         </is>
       </c>
     </row>
-    <row r="432">
-      <c r="A432" t="inlineStr">
-        <is>
-          <t>2487736</t>
-        </is>
-      </c>
-      <c r="B432" t="inlineStr">
-        <is>
-          <t>C. D. MENSAJERO ISLA DE LA PALMA</t>
-        </is>
-      </c>
-      <c r="C432" t="inlineStr">
-        <is>
-          <t>A. APARICIO IZQUIERDO | A. JIMENEZ FERNANDEZ | D. RODRIGUEZ GARCIA | J. RIES | P. RODRIGUEZ RIVERO</t>
-        </is>
-      </c>
-      <c r="D432" t="n">
-        <v>5</v>
-      </c>
-      <c r="E432" t="n">
-        <v>4</v>
-      </c>
-      <c r="F432" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="G432" t="n">
-        <v>5</v>
-      </c>
-      <c r="H432" t="n">
-        <v>0</v>
-      </c>
-      <c r="I432" t="n">
-        <v>2</v>
-      </c>
-      <c r="J432" t="n">
-        <v>0</v>
-      </c>
-      <c r="K432" t="n">
-        <v>250</v>
-      </c>
-      <c r="L432" t="n">
-        <v>0</v>
-      </c>
-      <c r="M432" t="n">
-        <v>0</v>
-      </c>
-      <c r="N432" t="n">
-        <v>2</v>
-      </c>
-      <c r="O432" t="n">
-        <v>0</v>
-      </c>
-      <c r="P432" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q432" t="n">
-        <v>0</v>
-      </c>
-      <c r="R432" t="n">
-        <v>0</v>
-      </c>
-      <c r="S432" t="n">
-        <v>0</v>
-      </c>
-      <c r="T432" t="n">
-        <v>0</v>
-      </c>
-      <c r="U432" t="n">
-        <v>0</v>
-      </c>
-      <c r="V432" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="W432" t="n">
-        <v>23</v>
-      </c>
-      <c r="X432" t="inlineStr">
-        <is>
-          <t>C. D. MENSAJERO ISLA DE LA PALMA vs EB FELIPE ANTÓN</t>
-        </is>
-      </c>
-    </row>
-    <row r="433">
-      <c r="A433" t="inlineStr">
-        <is>
-          <t>2487736</t>
-        </is>
-      </c>
-      <c r="B433" t="inlineStr">
-        <is>
-          <t>C. D. MENSAJERO ISLA DE LA PALMA</t>
-        </is>
-      </c>
-      <c r="C433" t="inlineStr">
-        <is>
-          <t>A. APARICIO IZQUIERDO | A. JIMENEZ FERNANDEZ | D. RODRIGUEZ GARCIA | M. NIANG | P. RODRIGUEZ RIVERO</t>
-        </is>
-      </c>
-      <c r="D433" t="n">
-        <v>5</v>
-      </c>
-      <c r="E433" t="n">
-        <v>46</v>
-      </c>
-      <c r="F433" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="G433" t="n">
-        <v>0</v>
-      </c>
-      <c r="H433" t="n">
-        <v>0</v>
-      </c>
-      <c r="I433" t="n">
-        <v>1</v>
-      </c>
-      <c r="J433" t="n">
-        <v>-1</v>
-      </c>
-      <c r="K433" t="n">
-        <v>0</v>
-      </c>
-      <c r="L433" t="n">
-        <v>0</v>
-      </c>
-      <c r="M433" t="n">
-        <v>0</v>
-      </c>
-      <c r="N433" t="n">
-        <v>1</v>
-      </c>
-      <c r="O433" t="n">
-        <v>0</v>
-      </c>
-      <c r="P433" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q433" t="n">
-        <v>0</v>
-      </c>
-      <c r="R433" t="n">
-        <v>0</v>
-      </c>
-      <c r="S433" t="n">
-        <v>0</v>
-      </c>
-      <c r="T433" t="n">
-        <v>0</v>
-      </c>
-      <c r="U433" t="n">
-        <v>1</v>
-      </c>
-      <c r="V433" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="W433" t="n">
-        <v>23</v>
-      </c>
-      <c r="X433" t="inlineStr">
-        <is>
-          <t>C. D. MENSAJERO ISLA DE LA PALMA vs EB FELIPE ANTÓN</t>
-        </is>
-      </c>
-    </row>
-    <row r="434">
-      <c r="A434" t="inlineStr">
-        <is>
-          <t>2487736</t>
-        </is>
-      </c>
-      <c r="B434" t="inlineStr">
-        <is>
-          <t>C. D. MENSAJERO ISLA DE LA PALMA</t>
-        </is>
-      </c>
-      <c r="C434" t="inlineStr">
-        <is>
-          <t>A. APARICIO IZQUIERDO | D. RODRIGUEZ GARCIA | J. RIES | M. NIANG | P. RODRIGUEZ RIVERO</t>
-        </is>
-      </c>
-      <c r="D434" t="n">
-        <v>5</v>
-      </c>
-      <c r="E434" t="n">
-        <v>236</v>
-      </c>
-      <c r="F434" t="n">
-        <v>3.93</v>
-      </c>
-      <c r="G434" t="n">
-        <v>5</v>
-      </c>
-      <c r="H434" t="n">
-        <v>9</v>
-      </c>
-      <c r="I434" t="n">
-        <v>7</v>
-      </c>
-      <c r="J434" t="n">
-        <v>9.52</v>
-      </c>
-      <c r="K434" t="n">
-        <v>71.43000000000001</v>
-      </c>
-      <c r="L434" t="n">
-        <v>94.54000000000001</v>
-      </c>
-      <c r="M434" t="n">
-        <v>-23.11</v>
-      </c>
-      <c r="N434" t="n">
-        <v>8</v>
-      </c>
-      <c r="O434" t="n">
-        <v>0</v>
-      </c>
-      <c r="P434" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q434" t="n">
-        <v>2</v>
-      </c>
-      <c r="R434" t="n">
-        <v>6</v>
-      </c>
-      <c r="S434" t="n">
-        <v>8</v>
-      </c>
-      <c r="T434" t="n">
-        <v>2</v>
-      </c>
-      <c r="U434" t="n">
-        <v>2</v>
-      </c>
-      <c r="V434" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="W434" t="n">
-        <v>23</v>
-      </c>
-      <c r="X434" t="inlineStr">
-        <is>
-          <t>C. D. MENSAJERO ISLA DE LA PALMA vs EB FELIPE ANTÓN</t>
-        </is>
-      </c>
-    </row>
-    <row r="435">
-      <c r="A435" t="inlineStr">
-        <is>
-          <t>2487736</t>
-        </is>
-      </c>
-      <c r="B435" t="inlineStr">
-        <is>
-          <t>EB FELIPE ANTÓN</t>
-        </is>
-      </c>
-      <c r="C435" t="inlineStr">
-        <is>
-          <t>A. SISTAC RODRIGUEZ | B. FERNANDEZ SHEPHARD | K. RIVEROL DE LAS CASAS | P. ARGÜELLES ELORZA</t>
-        </is>
-      </c>
-      <c r="D435" t="n">
-        <v>4</v>
-      </c>
-      <c r="E435" t="n">
-        <v>4</v>
-      </c>
-      <c r="F435" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="G435" t="n">
-        <v>0</v>
-      </c>
-      <c r="H435" t="n">
-        <v>5</v>
-      </c>
-      <c r="I435" t="n">
-        <v>0</v>
-      </c>
-      <c r="J435" t="n">
-        <v>2</v>
-      </c>
-      <c r="K435" t="n">
-        <v>0</v>
-      </c>
-      <c r="L435" t="n">
-        <v>250</v>
-      </c>
-      <c r="M435" t="n">
-        <v>0</v>
-      </c>
-      <c r="N435" t="n">
-        <v>0</v>
-      </c>
-      <c r="O435" t="n">
-        <v>0</v>
-      </c>
-      <c r="P435" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q435" t="n">
-        <v>0</v>
-      </c>
-      <c r="R435" t="n">
-        <v>2</v>
-      </c>
-      <c r="S435" t="n">
-        <v>0</v>
-      </c>
-      <c r="T435" t="n">
-        <v>0</v>
-      </c>
-      <c r="U435" t="n">
-        <v>0</v>
-      </c>
-      <c r="V435" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="W435" t="n">
-        <v>23</v>
-      </c>
-      <c r="X435" t="inlineStr">
-        <is>
-          <t>C. D. MENSAJERO ISLA DE LA PALMA vs EB FELIPE ANTÓN</t>
-        </is>
-      </c>
-    </row>
-    <row r="436">
-      <c r="A436" t="inlineStr">
-        <is>
-          <t>2487736</t>
-        </is>
-      </c>
-      <c r="B436" t="inlineStr">
-        <is>
-          <t>EB FELIPE ANTÓN</t>
-        </is>
-      </c>
-      <c r="C436" t="inlineStr">
-        <is>
-          <t>A. SISTAC RODRIGUEZ | B. FERNANDEZ SHEPHARD | M. KHIVRENKO | P. ARGÜELLES ELORZA</t>
-        </is>
-      </c>
-      <c r="D436" t="n">
-        <v>4</v>
-      </c>
-      <c r="E436" t="n">
-        <v>17</v>
-      </c>
-      <c r="F436" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="G436" t="n">
-        <v>5</v>
-      </c>
-      <c r="H436" t="n">
-        <v>0</v>
-      </c>
-      <c r="I436" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="J436" t="n">
-        <v>0</v>
-      </c>
-      <c r="K436" t="n">
-        <v>189.39</v>
-      </c>
-      <c r="L436" t="n">
-        <v>0</v>
-      </c>
-      <c r="M436" t="n">
-        <v>0</v>
-      </c>
-      <c r="N436" t="n">
-        <v>1</v>
-      </c>
-      <c r="O436" t="n">
-        <v>6</v>
-      </c>
-      <c r="P436" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q436" t="n">
-        <v>1</v>
-      </c>
-      <c r="R436" t="n">
-        <v>1</v>
-      </c>
-      <c r="S436" t="n">
-        <v>0</v>
-      </c>
-      <c r="T436" t="n">
-        <v>0</v>
-      </c>
-      <c r="U436" t="n">
-        <v>1</v>
-      </c>
-      <c r="V436" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="W436" t="n">
-        <v>23</v>
-      </c>
-      <c r="X436" t="inlineStr">
-        <is>
-          <t>C. D. MENSAJERO ISLA DE LA PALMA vs EB FELIPE ANTÓN</t>
-        </is>
-      </c>
-    </row>
-    <row r="437">
-      <c r="A437" t="inlineStr">
-        <is>
-          <t>2487736</t>
-        </is>
-      </c>
-      <c r="B437" t="inlineStr">
-        <is>
-          <t>EB FELIPE ANTÓN</t>
-        </is>
-      </c>
-      <c r="C437" t="inlineStr">
-        <is>
-          <t>A. SISTAC RODRIGUEZ | E. DUQUE NEGRÍN | M. KHIVRENKO | P. ARGÜELLES ELORZA | P. HERNANDEZ RODRIGUEZ</t>
-        </is>
-      </c>
-      <c r="D437" t="n">
-        <v>5</v>
-      </c>
-      <c r="E437" t="n">
-        <v>17</v>
-      </c>
-      <c r="F437" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="G437" t="n">
-        <v>0</v>
-      </c>
-      <c r="H437" t="n">
-        <v>2</v>
-      </c>
-      <c r="I437" t="n">
-        <v>0</v>
-      </c>
-      <c r="J437" t="n">
-        <v>2</v>
-      </c>
-      <c r="K437" t="n">
-        <v>0</v>
-      </c>
-      <c r="L437" t="n">
-        <v>100</v>
-      </c>
-      <c r="M437" t="n">
-        <v>0</v>
-      </c>
-      <c r="N437" t="n">
-        <v>0</v>
-      </c>
-      <c r="O437" t="n">
-        <v>0</v>
-      </c>
-      <c r="P437" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q437" t="n">
-        <v>0</v>
-      </c>
-      <c r="R437" t="n">
-        <v>2</v>
-      </c>
-      <c r="S437" t="n">
-        <v>0</v>
-      </c>
-      <c r="T437" t="n">
-        <v>0</v>
-      </c>
-      <c r="U437" t="n">
-        <v>0</v>
-      </c>
-      <c r="V437" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="W437" t="n">
-        <v>23</v>
-      </c>
-      <c r="X437" t="inlineStr">
-        <is>
-          <t>C. D. MENSAJERO ISLA DE LA PALMA vs EB FELIPE ANTÓN</t>
-        </is>
-      </c>
-    </row>
-    <row r="438">
-      <c r="A438" t="inlineStr">
-        <is>
-          <t>2487736</t>
-        </is>
-      </c>
-      <c r="B438" t="inlineStr">
-        <is>
-          <t>EB FELIPE ANTÓN</t>
-        </is>
-      </c>
-      <c r="C438" t="inlineStr">
-        <is>
-          <t>A. SISTAC RODRIGUEZ | K. RIVEROL DE LAS CASAS | M. KHIVRENKO | P. ARGÜELLES ELORZA</t>
-        </is>
-      </c>
-      <c r="D438" t="n">
-        <v>4</v>
-      </c>
-      <c r="E438" t="n">
-        <v>42</v>
-      </c>
-      <c r="F438" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="G438" t="n">
-        <v>1</v>
-      </c>
-      <c r="H438" t="n">
-        <v>0</v>
-      </c>
-      <c r="I438" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="J438" t="n">
-        <v>2</v>
-      </c>
-      <c r="K438" t="n">
-        <v>113.64</v>
-      </c>
-      <c r="L438" t="n">
-        <v>0</v>
-      </c>
-      <c r="M438" t="n">
-        <v>113.64</v>
-      </c>
-      <c r="N438" t="n">
-        <v>0</v>
-      </c>
-      <c r="O438" t="n">
-        <v>2</v>
-      </c>
-      <c r="P438" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q438" t="n">
-        <v>0</v>
-      </c>
-      <c r="R438" t="n">
-        <v>1</v>
-      </c>
-      <c r="S438" t="n">
-        <v>0</v>
-      </c>
-      <c r="T438" t="n">
-        <v>1</v>
-      </c>
-      <c r="U438" t="n">
-        <v>0</v>
-      </c>
-      <c r="V438" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="W438" t="n">
-        <v>23</v>
-      </c>
-      <c r="X438" t="inlineStr">
-        <is>
-          <t>C. D. MENSAJERO ISLA DE LA PALMA vs EB FELIPE ANTÓN</t>
-        </is>
-      </c>
-    </row>
-    <row r="439">
-      <c r="A439" t="inlineStr">
-        <is>
-          <t>2487736</t>
-        </is>
-      </c>
-      <c r="B439" t="inlineStr">
-        <is>
-          <t>EB FELIPE ANTÓN</t>
-        </is>
-      </c>
-      <c r="C439" t="inlineStr">
-        <is>
-          <t>B. FERNANDEZ SHEPHARD | E. DUQUE NEGRÍN | J. GALLETTO LAMELA | K. RIVEROL DE LAS CASAS | M. KHIVRENKO</t>
-        </is>
-      </c>
-      <c r="D439" t="n">
-        <v>5</v>
-      </c>
-      <c r="E439" t="n">
-        <v>22</v>
-      </c>
-      <c r="F439" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="G439" t="n">
-        <v>0</v>
-      </c>
-      <c r="H439" t="n">
-        <v>0</v>
-      </c>
-      <c r="I439" t="n">
-        <v>1</v>
-      </c>
-      <c r="J439" t="n">
-        <v>0</v>
-      </c>
-      <c r="K439" t="n">
-        <v>0</v>
-      </c>
-      <c r="L439" t="n">
-        <v>0</v>
-      </c>
-      <c r="M439" t="n">
-        <v>0</v>
-      </c>
-      <c r="N439" t="n">
-        <v>0</v>
-      </c>
-      <c r="O439" t="n">
-        <v>0</v>
-      </c>
-      <c r="P439" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q439" t="n">
-        <v>0</v>
-      </c>
-      <c r="R439" t="n">
-        <v>0</v>
-      </c>
-      <c r="S439" t="n">
-        <v>0</v>
-      </c>
-      <c r="T439" t="n">
-        <v>0</v>
-      </c>
-      <c r="U439" t="n">
-        <v>0</v>
-      </c>
-      <c r="V439" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="W439" t="n">
-        <v>23</v>
-      </c>
-      <c r="X439" t="inlineStr">
-        <is>
-          <t>C. D. MENSAJERO ISLA DE LA PALMA vs EB FELIPE ANTÓN</t>
-        </is>
-      </c>
-    </row>
-    <row r="440">
-      <c r="A440" t="inlineStr">
-        <is>
-          <t>2487736</t>
-        </is>
-      </c>
-      <c r="B440" t="inlineStr">
-        <is>
-          <t>EB FELIPE ANTÓN</t>
-        </is>
-      </c>
-      <c r="C440" t="inlineStr">
-        <is>
-          <t>B. FERNANDEZ SHEPHARD | E. DUQUE NEGRÍN | K. RIVEROL DE LAS CASAS | M. KHIVRENKO | P. ARGÜELLES ELORZA</t>
-        </is>
-      </c>
-      <c r="D440" t="n">
-        <v>5</v>
-      </c>
-      <c r="E440" t="n">
-        <v>32</v>
-      </c>
-      <c r="F440" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="G440" t="n">
-        <v>0</v>
-      </c>
-      <c r="H440" t="n">
-        <v>0</v>
-      </c>
-      <c r="I440" t="n">
-        <v>1</v>
-      </c>
-      <c r="J440" t="n">
-        <v>1</v>
-      </c>
-      <c r="K440" t="n">
-        <v>0</v>
-      </c>
-      <c r="L440" t="n">
-        <v>0</v>
-      </c>
-      <c r="M440" t="n">
-        <v>0</v>
-      </c>
-      <c r="N440" t="n">
-        <v>1</v>
-      </c>
-      <c r="O440" t="n">
-        <v>0</v>
-      </c>
-      <c r="P440" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q440" t="n">
-        <v>0</v>
-      </c>
-      <c r="R440" t="n">
-        <v>1</v>
-      </c>
-      <c r="S440" t="n">
-        <v>0</v>
-      </c>
-      <c r="T440" t="n">
-        <v>0</v>
-      </c>
-      <c r="U440" t="n">
-        <v>0</v>
-      </c>
-      <c r="V440" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="W440" t="n">
-        <v>23</v>
-      </c>
-      <c r="X440" t="inlineStr">
-        <is>
-          <t>C. D. MENSAJERO ISLA DE LA PALMA vs EB FELIPE ANTÓN</t>
-        </is>
-      </c>
-    </row>
-    <row r="441">
-      <c r="A441" t="inlineStr">
-        <is>
-          <t>2487736</t>
-        </is>
-      </c>
-      <c r="B441" t="inlineStr">
-        <is>
-          <t>EB FELIPE ANTÓN</t>
-        </is>
-      </c>
-      <c r="C441" t="inlineStr">
-        <is>
-          <t>B. FERNANDEZ SHEPHARD | J. GALLETTO LAMELA | K. RIVEROL DE LAS CASAS | M. KHIVRENKO | P. ARGÜELLES ELORZA</t>
-        </is>
-      </c>
-      <c r="D441" t="n">
-        <v>5</v>
-      </c>
-      <c r="E441" t="n">
-        <v>120</v>
-      </c>
-      <c r="F441" t="n">
-        <v>2</v>
-      </c>
-      <c r="G441" t="n">
-        <v>0</v>
-      </c>
-      <c r="H441" t="n">
-        <v>0</v>
-      </c>
-      <c r="I441" t="n">
-        <v>2</v>
-      </c>
-      <c r="J441" t="n">
-        <v>2</v>
-      </c>
-      <c r="K441" t="n">
-        <v>0</v>
-      </c>
-      <c r="L441" t="n">
-        <v>0</v>
-      </c>
-      <c r="M441" t="n">
-        <v>0</v>
-      </c>
-      <c r="N441" t="n">
-        <v>3</v>
-      </c>
-      <c r="O441" t="n">
-        <v>0</v>
-      </c>
-      <c r="P441" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q441" t="n">
-        <v>2</v>
-      </c>
-      <c r="R441" t="n">
-        <v>3</v>
-      </c>
-      <c r="S441" t="n">
-        <v>0</v>
-      </c>
-      <c r="T441" t="n">
-        <v>0</v>
-      </c>
-      <c r="U441" t="n">
-        <v>1</v>
-      </c>
-      <c r="V441" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="W441" t="n">
-        <v>23</v>
-      </c>
-      <c r="X441" t="inlineStr">
-        <is>
-          <t>C. D. MENSAJERO ISLA DE LA PALMA vs EB FELIPE ANTÓN</t>
-        </is>
-      </c>
-    </row>
-    <row r="442">
-      <c r="A442" t="inlineStr">
-        <is>
-          <t>2487736</t>
-        </is>
-      </c>
-      <c r="B442" t="inlineStr">
-        <is>
-          <t>EB FELIPE ANTÓN</t>
-        </is>
-      </c>
-      <c r="C442" t="inlineStr">
-        <is>
-          <t>B. FERNANDEZ SHEPHARD | J. GALLETTO LAMELA | M. KHIVRENKO | P. ARGÜELLES ELORZA | P. HERNANDEZ RODRIGUEZ</t>
-        </is>
-      </c>
-      <c r="D442" t="n">
-        <v>5</v>
-      </c>
-      <c r="E442" t="n">
-        <v>32</v>
-      </c>
-      <c r="F442" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="G442" t="n">
-        <v>3</v>
-      </c>
-      <c r="H442" t="n">
-        <v>3</v>
-      </c>
-      <c r="I442" t="n">
-        <v>1</v>
-      </c>
-      <c r="J442" t="n">
-        <v>1</v>
-      </c>
-      <c r="K442" t="n">
-        <v>300</v>
-      </c>
-      <c r="L442" t="n">
-        <v>300</v>
-      </c>
-      <c r="M442" t="n">
-        <v>0</v>
-      </c>
-      <c r="N442" t="n">
-        <v>1</v>
-      </c>
-      <c r="O442" t="n">
-        <v>0</v>
-      </c>
-      <c r="P442" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q442" t="n">
-        <v>0</v>
-      </c>
-      <c r="R442" t="n">
-        <v>1</v>
-      </c>
-      <c r="S442" t="n">
-        <v>0</v>
-      </c>
-      <c r="T442" t="n">
-        <v>0</v>
-      </c>
-      <c r="U442" t="n">
-        <v>0</v>
-      </c>
-      <c r="V442" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="W442" t="n">
-        <v>23</v>
-      </c>
-      <c r="X442" t="inlineStr">
-        <is>
-          <t>C. D. MENSAJERO ISLA DE LA PALMA vs EB FELIPE ANTÓN</t>
-        </is>
-      </c>
-    </row>
-    <row r="443">
-      <c r="A443" t="inlineStr">
-        <is>
-          <t>2487737</t>
-        </is>
-      </c>
-      <c r="B443" t="inlineStr">
-        <is>
-          <t>BALONCESTO TELDE</t>
-        </is>
-      </c>
-      <c r="C443" t="inlineStr">
-        <is>
-          <t>A. FERNÁNDEZ GÓMEZ | A. MARTIN GONZALEZ | A. SANTANA OJEDA | G. ARTILES ROMERO | J. JIMENEZ HERNANDEZ</t>
-        </is>
-      </c>
-      <c r="D443" t="n">
-        <v>5</v>
-      </c>
-      <c r="E443" t="n">
-        <v>159</v>
-      </c>
-      <c r="F443" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="G443" t="n">
-        <v>4</v>
-      </c>
-      <c r="H443" t="n">
-        <v>7</v>
-      </c>
-      <c r="I443" t="n">
-        <v>5.88</v>
-      </c>
-      <c r="J443" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="K443" t="n">
-        <v>68.03</v>
-      </c>
-      <c r="L443" t="n">
-        <v>253.62</v>
-      </c>
-      <c r="M443" t="n">
-        <v>-185.6</v>
-      </c>
-      <c r="N443" t="n">
-        <v>7</v>
-      </c>
-      <c r="O443" t="n">
-        <v>2</v>
-      </c>
-      <c r="P443" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q443" t="n">
-        <v>2</v>
-      </c>
-      <c r="R443" t="n">
-        <v>3</v>
-      </c>
-      <c r="S443" t="n">
-        <v>4</v>
-      </c>
-      <c r="T443" t="n">
-        <v>1</v>
-      </c>
-      <c r="U443" t="n">
-        <v>3</v>
-      </c>
-      <c r="V443" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="W443" t="n">
-        <v>23</v>
-      </c>
-      <c r="X443" t="inlineStr">
-        <is>
-          <t>C.B. TRES CANTOS vs BALONCESTO TELDE</t>
-        </is>
-      </c>
-    </row>
-    <row r="444">
-      <c r="A444" t="inlineStr">
-        <is>
-          <t>2487737</t>
-        </is>
-      </c>
-      <c r="B444" t="inlineStr">
-        <is>
-          <t>C.B. TRES CANTOS</t>
-        </is>
-      </c>
-      <c r="C444" t="inlineStr">
-        <is>
-          <t>A. SIMON DEL CORRAL | D. FERNANDEZ CAÑAS | G. DIAZ MONTERO | J. ATIENZA PEREA | N. MAIGA</t>
-        </is>
-      </c>
-      <c r="D444" t="n">
-        <v>5</v>
-      </c>
-      <c r="E444" t="n">
-        <v>65</v>
-      </c>
-      <c r="F444" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="G444" t="n">
-        <v>3</v>
-      </c>
-      <c r="H444" t="n">
-        <v>0</v>
-      </c>
-      <c r="I444" t="n">
-        <v>2</v>
-      </c>
-      <c r="J444" t="n">
-        <v>1</v>
-      </c>
-      <c r="K444" t="n">
-        <v>150</v>
-      </c>
-      <c r="L444" t="n">
-        <v>0</v>
-      </c>
-      <c r="M444" t="n">
-        <v>150</v>
-      </c>
-      <c r="N444" t="n">
-        <v>2</v>
-      </c>
-      <c r="O444" t="n">
-        <v>0</v>
-      </c>
-      <c r="P444" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q444" t="n">
-        <v>1</v>
-      </c>
-      <c r="R444" t="n">
-        <v>2</v>
-      </c>
-      <c r="S444" t="n">
-        <v>0</v>
-      </c>
-      <c r="T444" t="n">
-        <v>0</v>
-      </c>
-      <c r="U444" t="n">
-        <v>1</v>
-      </c>
-      <c r="V444" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="W444" t="n">
-        <v>23</v>
-      </c>
-      <c r="X444" t="inlineStr">
-        <is>
-          <t>C.B. TRES CANTOS vs BALONCESTO TELDE</t>
-        </is>
-      </c>
-    </row>
-    <row r="445">
-      <c r="A445" t="inlineStr">
-        <is>
-          <t>2487737</t>
-        </is>
-      </c>
-      <c r="B445" t="inlineStr">
-        <is>
-          <t>C.B. TRES CANTOS</t>
-        </is>
-      </c>
-      <c r="C445" t="inlineStr">
-        <is>
-          <t>A. SIMON DEL CORRAL | G. DIAZ MONTERO | G. LARDIES GUILLEN | J. ATIENZA PEREA | N. MAIGA</t>
-        </is>
-      </c>
-      <c r="D445" t="n">
-        <v>5</v>
-      </c>
-      <c r="E445" t="n">
-        <v>91</v>
-      </c>
-      <c r="F445" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="G445" t="n">
-        <v>4</v>
-      </c>
-      <c r="H445" t="n">
-        <v>4</v>
-      </c>
-      <c r="I445" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="J445" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="K445" t="n">
-        <v>526.3200000000001</v>
-      </c>
-      <c r="L445" t="n">
-        <v>81.97</v>
-      </c>
-      <c r="M445" t="n">
-        <v>444.35</v>
-      </c>
-      <c r="N445" t="n">
-        <v>1</v>
-      </c>
-      <c r="O445" t="n">
-        <v>4</v>
-      </c>
-      <c r="P445" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q445" t="n">
-        <v>2</v>
-      </c>
-      <c r="R445" t="n">
-        <v>5</v>
-      </c>
-      <c r="S445" t="n">
-        <v>2</v>
-      </c>
-      <c r="T445" t="n">
-        <v>0</v>
-      </c>
-      <c r="U445" t="n">
-        <v>1</v>
-      </c>
-      <c r="V445" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="W445" t="n">
-        <v>23</v>
-      </c>
-      <c r="X445" t="inlineStr">
-        <is>
-          <t>C.B. TRES CANTOS vs BALONCESTO TELDE</t>
-        </is>
-      </c>
-    </row>
-    <row r="446">
-      <c r="A446" t="inlineStr">
-        <is>
-          <t>2487737</t>
-        </is>
-      </c>
-      <c r="B446" t="inlineStr">
-        <is>
-          <t>C.B. TRES CANTOS</t>
-        </is>
-      </c>
-      <c r="C446" t="inlineStr">
-        <is>
-          <t>D. FERNANDEZ CAÑAS | G. DIAZ MONTERO | G. LARDIES GUILLEN | J. ATIENZA PEREA | N. MAIGA</t>
-        </is>
-      </c>
-      <c r="D446" t="n">
-        <v>5</v>
-      </c>
-      <c r="E446" t="n">
-        <v>3</v>
-      </c>
-      <c r="F446" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="G446" t="n">
-        <v>0</v>
-      </c>
-      <c r="H446" t="n">
-        <v>0</v>
-      </c>
-      <c r="I446" t="n">
-        <v>0</v>
-      </c>
-      <c r="J446" t="n">
-        <v>0</v>
-      </c>
-      <c r="K446" t="n">
-        <v>0</v>
-      </c>
-      <c r="L446" t="n">
-        <v>0</v>
-      </c>
-      <c r="M446" t="n">
-        <v>0</v>
-      </c>
-      <c r="N446" t="n">
-        <v>0</v>
-      </c>
-      <c r="O446" t="n">
-        <v>0</v>
-      </c>
-      <c r="P446" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q446" t="n">
-        <v>0</v>
-      </c>
-      <c r="R446" t="n">
-        <v>0</v>
-      </c>
-      <c r="S446" t="n">
-        <v>0</v>
-      </c>
-      <c r="T446" t="n">
-        <v>0</v>
-      </c>
-      <c r="U446" t="n">
-        <v>0</v>
-      </c>
-      <c r="V446" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="W446" t="n">
-        <v>23</v>
-      </c>
-      <c r="X446" t="inlineStr">
-        <is>
-          <t>C.B. TRES CANTOS vs BALONCESTO TELDE</t>
-        </is>
-      </c>
-    </row>
-    <row r="447">
-      <c r="A447" t="inlineStr">
-        <is>
-          <t>2487732</t>
-        </is>
-      </c>
-      <c r="B447" t="inlineStr">
-        <is>
-          <t>CB ARIDANE</t>
-        </is>
-      </c>
-      <c r="C447" t="inlineStr">
-        <is>
-          <t>A. GASE SECO | D. VIERA LOPEZ | K. SKUTYELNIK | O. BALSELLS PLAZA | S. GUEYE</t>
-        </is>
-      </c>
-      <c r="D447" t="n">
-        <v>5</v>
-      </c>
-      <c r="E447" t="n">
-        <v>64</v>
-      </c>
-      <c r="F447" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="G447" t="n">
-        <v>0</v>
-      </c>
-      <c r="H447" t="n">
-        <v>3</v>
-      </c>
-      <c r="I447" t="n">
-        <v>2</v>
-      </c>
-      <c r="J447" t="n">
-        <v>2</v>
-      </c>
-      <c r="K447" t="n">
-        <v>0</v>
-      </c>
-      <c r="L447" t="n">
-        <v>150</v>
-      </c>
-      <c r="M447" t="n">
-        <v>-150</v>
-      </c>
-      <c r="N447" t="n">
-        <v>2</v>
-      </c>
-      <c r="O447" t="n">
-        <v>0</v>
-      </c>
-      <c r="P447" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q447" t="n">
-        <v>0</v>
-      </c>
-      <c r="R447" t="n">
-        <v>3</v>
-      </c>
-      <c r="S447" t="n">
-        <v>0</v>
-      </c>
-      <c r="T447" t="n">
-        <v>0</v>
-      </c>
-      <c r="U447" t="n">
-        <v>1</v>
-      </c>
-      <c r="V447" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="W447" t="n">
-        <v>23</v>
-      </c>
-      <c r="X447" t="inlineStr">
-        <is>
-          <t>CB ARIDANE vs REAL CANOE N.C.</t>
-        </is>
-      </c>
-    </row>
-    <row r="448">
-      <c r="A448" t="inlineStr">
-        <is>
-          <t>2487732</t>
-        </is>
-      </c>
-      <c r="B448" t="inlineStr">
-        <is>
-          <t>CB ARIDANE</t>
-        </is>
-      </c>
-      <c r="C448" t="inlineStr">
-        <is>
-          <t>A. GASE SECO | G. MEJÍA ACOSTA | G. PIERRE-GABRIEL ANDREA GASTON | K. SKUTYELNIK | O. BALSELLS PLAZA</t>
-        </is>
-      </c>
-      <c r="D448" t="n">
-        <v>5</v>
-      </c>
-      <c r="E448" t="n">
-        <v>13</v>
-      </c>
-      <c r="F448" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="G448" t="n">
-        <v>0</v>
-      </c>
-      <c r="H448" t="n">
-        <v>2</v>
-      </c>
-      <c r="I448" t="n">
-        <v>0</v>
-      </c>
-      <c r="J448" t="n">
-        <v>1</v>
-      </c>
-      <c r="K448" t="n">
-        <v>0</v>
-      </c>
-      <c r="L448" t="n">
-        <v>200</v>
-      </c>
-      <c r="M448" t="n">
-        <v>0</v>
-      </c>
-      <c r="N448" t="n">
-        <v>0</v>
-      </c>
-      <c r="O448" t="n">
-        <v>0</v>
-      </c>
-      <c r="P448" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q448" t="n">
-        <v>0</v>
-      </c>
-      <c r="R448" t="n">
-        <v>1</v>
-      </c>
-      <c r="S448" t="n">
-        <v>0</v>
-      </c>
-      <c r="T448" t="n">
-        <v>0</v>
-      </c>
-      <c r="U448" t="n">
-        <v>0</v>
-      </c>
-      <c r="V448" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="W448" t="n">
-        <v>23</v>
-      </c>
-      <c r="X448" t="inlineStr">
-        <is>
-          <t>CB ARIDANE vs REAL CANOE N.C.</t>
-        </is>
-      </c>
-    </row>
-    <row r="449">
-      <c r="A449" t="inlineStr">
-        <is>
-          <t>2487732</t>
-        </is>
-      </c>
-      <c r="B449" t="inlineStr">
-        <is>
-          <t>CB ARIDANE</t>
-        </is>
-      </c>
-      <c r="C449" t="inlineStr">
-        <is>
-          <t>A. GASE SECO | G. MEJÍA ACOSTA | K. SKUTYELNIK | O. BALSELLS PLAZA | S. GUEYE</t>
-        </is>
-      </c>
-      <c r="D449" t="n">
-        <v>5</v>
-      </c>
-      <c r="E449" t="n">
-        <v>55</v>
-      </c>
-      <c r="F449" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="G449" t="n">
-        <v>2</v>
-      </c>
-      <c r="H449" t="n">
-        <v>3</v>
-      </c>
-      <c r="I449" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="J449" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="K449" t="n">
-        <v>106.38</v>
-      </c>
-      <c r="L449" t="n">
-        <v>159.57</v>
-      </c>
-      <c r="M449" t="n">
-        <v>-53.19</v>
-      </c>
-      <c r="N449" t="n">
-        <v>1</v>
-      </c>
-      <c r="O449" t="n">
-        <v>2</v>
-      </c>
-      <c r="P449" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q449" t="n">
-        <v>0</v>
-      </c>
-      <c r="R449" t="n">
-        <v>2</v>
-      </c>
-      <c r="S449" t="n">
-        <v>2</v>
-      </c>
-      <c r="T449" t="n">
-        <v>0</v>
-      </c>
-      <c r="U449" t="n">
-        <v>1</v>
-      </c>
-      <c r="V449" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="W449" t="n">
-        <v>23</v>
-      </c>
-      <c r="X449" t="inlineStr">
-        <is>
-          <t>CB ARIDANE vs REAL CANOE N.C.</t>
-        </is>
-      </c>
-    </row>
-    <row r="450">
-      <c r="A450" t="inlineStr">
-        <is>
-          <t>2487732</t>
-        </is>
-      </c>
-      <c r="B450" t="inlineStr">
-        <is>
-          <t>REAL CANOE N.C.</t>
-        </is>
-      </c>
-      <c r="C450" t="inlineStr">
-        <is>
-          <t>D. MANZANERO CAMACHO | E. PASCUAL COZAR | J. LAPASTORA ARACIL | J. MARTINEZ SANTOS | N. LASUNCION MARIBLANCA</t>
-        </is>
-      </c>
-      <c r="D450" t="n">
-        <v>5</v>
-      </c>
-      <c r="E450" t="n">
-        <v>23</v>
-      </c>
-      <c r="F450" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="G450" t="n">
-        <v>0</v>
-      </c>
-      <c r="H450" t="n">
-        <v>0</v>
-      </c>
-      <c r="I450" t="n">
-        <v>1</v>
-      </c>
-      <c r="J450" t="n">
-        <v>1</v>
-      </c>
-      <c r="K450" t="n">
-        <v>0</v>
-      </c>
-      <c r="L450" t="n">
-        <v>0</v>
-      </c>
-      <c r="M450" t="n">
-        <v>0</v>
-      </c>
-      <c r="N450" t="n">
-        <v>2</v>
-      </c>
-      <c r="O450" t="n">
-        <v>0</v>
-      </c>
-      <c r="P450" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q450" t="n">
-        <v>1</v>
-      </c>
-      <c r="R450" t="n">
-        <v>1</v>
-      </c>
-      <c r="S450" t="n">
-        <v>0</v>
-      </c>
-      <c r="T450" t="n">
-        <v>0</v>
-      </c>
-      <c r="U450" t="n">
-        <v>0</v>
-      </c>
-      <c r="V450" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="W450" t="n">
-        <v>23</v>
-      </c>
-      <c r="X450" t="inlineStr">
-        <is>
-          <t>CB ARIDANE vs REAL CANOE N.C.</t>
-        </is>
-      </c>
-    </row>
-    <row r="451">
-      <c r="A451" t="inlineStr">
-        <is>
-          <t>2487732</t>
-        </is>
-      </c>
-      <c r="B451" t="inlineStr">
-        <is>
-          <t>REAL CANOE N.C.</t>
-        </is>
-      </c>
-      <c r="C451" t="inlineStr">
-        <is>
-          <t>D. MANZANERO CAMACHO | J. LAPASTORA ARACIL | J. MARTINEZ SANTOS | L. GARCIA LARRACHE SEGURA | N. LASUNCION MARIBLANCA</t>
-        </is>
-      </c>
-      <c r="D451" t="n">
-        <v>5</v>
-      </c>
-      <c r="E451" t="n">
-        <v>44</v>
-      </c>
-      <c r="F451" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="G451" t="n">
-        <v>3</v>
-      </c>
-      <c r="H451" t="n">
-        <v>0</v>
-      </c>
-      <c r="I451" t="n">
-        <v>1</v>
-      </c>
-      <c r="J451" t="n">
-        <v>1</v>
-      </c>
-      <c r="K451" t="n">
-        <v>300</v>
-      </c>
-      <c r="L451" t="n">
-        <v>0</v>
-      </c>
-      <c r="M451" t="n">
-        <v>300</v>
-      </c>
-      <c r="N451" t="n">
-        <v>2</v>
-      </c>
-      <c r="O451" t="n">
-        <v>0</v>
-      </c>
-      <c r="P451" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q451" t="n">
-        <v>1</v>
-      </c>
-      <c r="R451" t="n">
-        <v>1</v>
-      </c>
-      <c r="S451" t="n">
-        <v>0</v>
-      </c>
-      <c r="T451" t="n">
-        <v>0</v>
-      </c>
-      <c r="U451" t="n">
-        <v>0</v>
-      </c>
-      <c r="V451" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="W451" t="n">
-        <v>23</v>
-      </c>
-      <c r="X451" t="inlineStr">
-        <is>
-          <t>CB ARIDANE vs REAL CANOE N.C.</t>
-        </is>
-      </c>
-    </row>
-    <row r="452">
-      <c r="A452" t="inlineStr">
-        <is>
-          <t>2487732</t>
-        </is>
-      </c>
-      <c r="B452" t="inlineStr">
-        <is>
-          <t>REAL CANOE N.C.</t>
-        </is>
-      </c>
-      <c r="C452" t="inlineStr">
-        <is>
-          <t>J. LAPASTORA ARACIL | J. MARTINEZ SANTOS | L. GARCIA LARRACHE SEGURA | M. HERMOSO ALCUBILLA | N. LASUNCION MARIBLANCA</t>
-        </is>
-      </c>
-      <c r="D452" t="n">
-        <v>5</v>
-      </c>
-      <c r="E452" t="n">
-        <v>65</v>
-      </c>
-      <c r="F452" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="G452" t="n">
-        <v>5</v>
-      </c>
-      <c r="H452" t="n">
-        <v>2</v>
-      </c>
-      <c r="I452" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="J452" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="K452" t="n">
-        <v>173.61</v>
-      </c>
-      <c r="L452" t="n">
-        <v>106.38</v>
-      </c>
-      <c r="M452" t="n">
-        <v>67.23</v>
-      </c>
-      <c r="N452" t="n">
-        <v>2</v>
-      </c>
-      <c r="O452" t="n">
-        <v>2</v>
-      </c>
-      <c r="P452" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q452" t="n">
-        <v>0</v>
-      </c>
-      <c r="R452" t="n">
-        <v>1</v>
-      </c>
-      <c r="S452" t="n">
-        <v>2</v>
-      </c>
-      <c r="T452" t="n">
-        <v>0</v>
-      </c>
-      <c r="U452" t="n">
-        <v>0</v>
-      </c>
-      <c r="V452" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="W452" t="n">
-        <v>23</v>
-      </c>
-      <c r="X452" t="inlineStr">
-        <is>
-          <t>CB ARIDANE vs REAL CANOE N.C.</t>
-        </is>
-      </c>
-    </row>
-    <row r="453">
-      <c r="A453" t="inlineStr">
-        <is>
-          <t>2487738</t>
-        </is>
-      </c>
-      <c r="B453" t="inlineStr">
-        <is>
-          <t>BALONCESTO TALAVERA</t>
-        </is>
-      </c>
-      <c r="C453" t="inlineStr">
-        <is>
-          <t>A. VICENTE VIANA | C. UNANUE CEGARRA | D. LORENZO NEGRETE | J. FRANCES PASCUAL | S. GACIC</t>
-        </is>
-      </c>
-      <c r="D453" t="n">
-        <v>5</v>
-      </c>
-      <c r="E453" t="n">
-        <v>133</v>
-      </c>
-      <c r="F453" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="G453" t="n">
-        <v>2</v>
-      </c>
-      <c r="H453" t="n">
-        <v>3</v>
-      </c>
-      <c r="I453" t="n">
-        <v>5</v>
-      </c>
-      <c r="J453" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="K453" t="n">
-        <v>40</v>
-      </c>
-      <c r="L453" t="n">
-        <v>108.7</v>
-      </c>
-      <c r="M453" t="n">
-        <v>-68.7</v>
-      </c>
-      <c r="N453" t="n">
-        <v>4</v>
-      </c>
-      <c r="O453" t="n">
-        <v>0</v>
-      </c>
-      <c r="P453" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q453" t="n">
-        <v>1</v>
-      </c>
-      <c r="R453" t="n">
-        <v>3</v>
-      </c>
-      <c r="S453" t="n">
-        <v>4</v>
-      </c>
-      <c r="T453" t="n">
-        <v>0</v>
-      </c>
-      <c r="U453" t="n">
-        <v>2</v>
-      </c>
-      <c r="V453" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="W453" t="n">
-        <v>24</v>
-      </c>
-      <c r="X453" t="inlineStr">
-        <is>
-          <t>BALONCESTO TALAVERA vs BALONCESTO TELDE</t>
-        </is>
-      </c>
-    </row>
-    <row r="454">
-      <c r="A454" t="inlineStr">
-        <is>
-          <t>2487738</t>
-        </is>
-      </c>
-      <c r="B454" t="inlineStr">
-        <is>
-          <t>BALONCESTO TALAVERA</t>
-        </is>
-      </c>
-      <c r="C454" t="inlineStr">
-        <is>
-          <t>B. GUEYE | C. UNANUE CEGARRA | D. LORENZO NEGRETE | J. FRANCES PASCUAL | S. GACIC</t>
-        </is>
-      </c>
-      <c r="D454" t="n">
-        <v>5</v>
-      </c>
-      <c r="E454" t="n">
-        <v>75</v>
-      </c>
-      <c r="F454" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="G454" t="n">
-        <v>2</v>
-      </c>
-      <c r="H454" t="n">
-        <v>2</v>
-      </c>
-      <c r="I454" t="n">
-        <v>2</v>
-      </c>
-      <c r="J454" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="K454" t="n">
-        <v>100</v>
-      </c>
-      <c r="L454" t="n">
-        <v>69.44</v>
-      </c>
-      <c r="M454" t="n">
-        <v>30.56</v>
-      </c>
-      <c r="N454" t="n">
-        <v>1</v>
-      </c>
-      <c r="O454" t="n">
-        <v>0</v>
-      </c>
-      <c r="P454" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q454" t="n">
-        <v>1</v>
-      </c>
-      <c r="R454" t="n">
-        <v>1</v>
-      </c>
-      <c r="S454" t="n">
-        <v>2</v>
-      </c>
-      <c r="T454" t="n">
-        <v>1</v>
-      </c>
-      <c r="U454" t="n">
-        <v>0</v>
-      </c>
-      <c r="V454" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="W454" t="n">
-        <v>24</v>
-      </c>
-      <c r="X454" t="inlineStr">
-        <is>
-          <t>BALONCESTO TALAVERA vs BALONCESTO TELDE</t>
-        </is>
-      </c>
-    </row>
-    <row r="455">
-      <c r="A455" t="inlineStr">
-        <is>
-          <t>2487738</t>
-        </is>
-      </c>
-      <c r="B455" t="inlineStr">
-        <is>
-          <t>BALONCESTO TALAVERA</t>
-        </is>
-      </c>
-      <c r="C455" t="inlineStr">
-        <is>
-          <t>C. KLOTZ MAROTO | D. LORENZO NEGRETE | J. FRANCES PASCUAL | S. GACIC | V. ALONSO PASCUAL</t>
-        </is>
-      </c>
-      <c r="D455" t="n">
-        <v>5</v>
-      </c>
-      <c r="E455" t="n">
-        <v>49</v>
-      </c>
-      <c r="F455" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="G455" t="n">
-        <v>0</v>
-      </c>
-      <c r="H455" t="n">
-        <v>2</v>
-      </c>
-      <c r="I455" t="n">
-        <v>1</v>
-      </c>
-      <c r="J455" t="n">
-        <v>2</v>
-      </c>
-      <c r="K455" t="n">
-        <v>0</v>
-      </c>
-      <c r="L455" t="n">
-        <v>100</v>
-      </c>
-      <c r="M455" t="n">
-        <v>-100</v>
-      </c>
-      <c r="N455" t="n">
-        <v>1</v>
-      </c>
-      <c r="O455" t="n">
-        <v>0</v>
-      </c>
-      <c r="P455" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q455" t="n">
-        <v>1</v>
-      </c>
-      <c r="R455" t="n">
-        <v>2</v>
-      </c>
-      <c r="S455" t="n">
-        <v>0</v>
-      </c>
-      <c r="T455" t="n">
-        <v>0</v>
-      </c>
-      <c r="U455" t="n">
-        <v>0</v>
-      </c>
-      <c r="V455" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="W455" t="n">
-        <v>24</v>
-      </c>
-      <c r="X455" t="inlineStr">
-        <is>
-          <t>BALONCESTO TALAVERA vs BALONCESTO TELDE</t>
-        </is>
-      </c>
-    </row>
-    <row r="456">
-      <c r="A456" t="inlineStr">
-        <is>
-          <t>2487738</t>
-        </is>
-      </c>
-      <c r="B456" t="inlineStr">
-        <is>
-          <t>BALONCESTO TALAVERA</t>
-        </is>
-      </c>
-      <c r="C456" t="inlineStr">
-        <is>
-          <t>C. UNANUE CEGARRA | D. LORENZO NEGRETE | J. FRANCES PASCUAL | S. GACIC | V. ALONSO PASCUAL</t>
-        </is>
-      </c>
-      <c r="D456" t="n">
-        <v>5</v>
-      </c>
-      <c r="E456" t="n">
-        <v>38</v>
-      </c>
-      <c r="F456" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="G456" t="n">
-        <v>3</v>
-      </c>
-      <c r="H456" t="n">
-        <v>3</v>
-      </c>
-      <c r="I456" t="n">
-        <v>2</v>
-      </c>
-      <c r="J456" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="K456" t="n">
-        <v>150</v>
-      </c>
-      <c r="L456" t="n">
-        <v>340.91</v>
-      </c>
-      <c r="M456" t="n">
-        <v>-190.91</v>
-      </c>
-      <c r="N456" t="n">
-        <v>2</v>
-      </c>
-      <c r="O456" t="n">
-        <v>0</v>
-      </c>
-      <c r="P456" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q456" t="n">
-        <v>0</v>
-      </c>
-      <c r="R456" t="n">
-        <v>1</v>
-      </c>
-      <c r="S456" t="n">
-        <v>2</v>
-      </c>
-      <c r="T456" t="n">
-        <v>0</v>
-      </c>
-      <c r="U456" t="n">
-        <v>1</v>
-      </c>
-      <c r="V456" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="W456" t="n">
-        <v>24</v>
-      </c>
-      <c r="X456" t="inlineStr">
-        <is>
-          <t>BALONCESTO TALAVERA vs BALONCESTO TELDE</t>
-        </is>
-      </c>
-    </row>
-    <row r="457">
-      <c r="A457" t="inlineStr">
-        <is>
-          <t>2487738</t>
-        </is>
-      </c>
-      <c r="B457" t="inlineStr">
-        <is>
-          <t>BALONCESTO TELDE</t>
-        </is>
-      </c>
-      <c r="C457" t="inlineStr">
-        <is>
-          <t>A. FERNÁNDEZ GÓMEZ | A. MARTIN GONZALEZ | A. SANTANA OJEDA | A. VIDAL RODRIGUEZ | G. ARTILES ROMERO</t>
-        </is>
-      </c>
-      <c r="D457" t="n">
-        <v>5</v>
-      </c>
-      <c r="E457" t="n">
-        <v>34</v>
-      </c>
-      <c r="F457" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="G457" t="n">
-        <v>2</v>
-      </c>
-      <c r="H457" t="n">
-        <v>0</v>
-      </c>
-      <c r="I457" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="J457" t="n">
-        <v>1</v>
-      </c>
-      <c r="K457" t="n">
-        <v>106.38</v>
-      </c>
-      <c r="L457" t="n">
-        <v>0</v>
-      </c>
-      <c r="M457" t="n">
-        <v>106.38</v>
-      </c>
-      <c r="N457" t="n">
-        <v>2</v>
-      </c>
-      <c r="O457" t="n">
-        <v>2</v>
-      </c>
-      <c r="P457" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q457" t="n">
-        <v>1</v>
-      </c>
-      <c r="R457" t="n">
-        <v>1</v>
-      </c>
-      <c r="S457" t="n">
-        <v>0</v>
-      </c>
-      <c r="T457" t="n">
-        <v>1</v>
-      </c>
-      <c r="U457" t="n">
-        <v>1</v>
-      </c>
-      <c r="V457" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="W457" t="n">
-        <v>24</v>
-      </c>
-      <c r="X457" t="inlineStr">
-        <is>
-          <t>BALONCESTO TALAVERA vs BALONCESTO TELDE</t>
-        </is>
-      </c>
-    </row>
-    <row r="458">
-      <c r="A458" t="inlineStr">
-        <is>
-          <t>2487738</t>
-        </is>
-      </c>
-      <c r="B458" t="inlineStr">
-        <is>
-          <t>BALONCESTO TELDE</t>
-        </is>
-      </c>
-      <c r="C458" t="inlineStr">
-        <is>
-          <t>A. FERNÁNDEZ GÓMEZ | A. SANTANA OJEDA | A. VIDAL RODRIGUEZ | G. ARTILES ROMERO | J. JIMENEZ HERNANDEZ</t>
-        </is>
-      </c>
-      <c r="D458" t="n">
-        <v>5</v>
-      </c>
-      <c r="E458" t="n">
-        <v>233</v>
-      </c>
-      <c r="F458" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="G458" t="n">
-        <v>8</v>
-      </c>
-      <c r="H458" t="n">
-        <v>7</v>
-      </c>
-      <c r="I458" t="n">
-        <v>6.64</v>
-      </c>
-      <c r="J458" t="n">
-        <v>8</v>
-      </c>
-      <c r="K458" t="n">
-        <v>120.48</v>
-      </c>
-      <c r="L458" t="n">
-        <v>87.5</v>
-      </c>
-      <c r="M458" t="n">
-        <v>32.98</v>
-      </c>
-      <c r="N458" t="n">
-        <v>5</v>
-      </c>
-      <c r="O458" t="n">
-        <v>6</v>
-      </c>
-      <c r="P458" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q458" t="n">
-        <v>2</v>
-      </c>
-      <c r="R458" t="n">
-        <v>6</v>
-      </c>
-      <c r="S458" t="n">
-        <v>0</v>
-      </c>
-      <c r="T458" t="n">
-        <v>4</v>
-      </c>
-      <c r="U458" t="n">
-        <v>2</v>
-      </c>
-      <c r="V458" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="W458" t="n">
-        <v>24</v>
-      </c>
-      <c r="X458" t="inlineStr">
-        <is>
-          <t>BALONCESTO TALAVERA vs BALONCESTO TELDE</t>
-        </is>
-      </c>
-    </row>
-    <row r="459">
-      <c r="A459" t="inlineStr">
-        <is>
-          <t>2487738</t>
-        </is>
-      </c>
-      <c r="B459" t="inlineStr">
-        <is>
-          <t>BALONCESTO TELDE</t>
-        </is>
-      </c>
-      <c r="C459" t="inlineStr">
-        <is>
-          <t>A. MARTIN GONZALEZ | A. SANTANA OJEDA | A. VIDAL RODRIGUEZ | G. ARTILES ROMERO | J. JIMENEZ HERNANDEZ</t>
-        </is>
-      </c>
-      <c r="D459" t="n">
-        <v>5</v>
-      </c>
-      <c r="E459" t="n">
-        <v>28</v>
-      </c>
-      <c r="F459" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="G459" t="n">
-        <v>0</v>
-      </c>
-      <c r="H459" t="n">
-        <v>0</v>
-      </c>
-      <c r="I459" t="n">
-        <v>0</v>
-      </c>
-      <c r="J459" t="n">
-        <v>1</v>
-      </c>
-      <c r="K459" t="n">
-        <v>0</v>
-      </c>
-      <c r="L459" t="n">
-        <v>0</v>
-      </c>
-      <c r="M459" t="n">
-        <v>0</v>
-      </c>
-      <c r="N459" t="n">
-        <v>0</v>
-      </c>
-      <c r="O459" t="n">
-        <v>0</v>
-      </c>
-      <c r="P459" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q459" t="n">
-        <v>0</v>
-      </c>
-      <c r="R459" t="n">
-        <v>1</v>
-      </c>
-      <c r="S459" t="n">
-        <v>0</v>
-      </c>
-      <c r="T459" t="n">
-        <v>0</v>
-      </c>
-      <c r="U459" t="n">
-        <v>0</v>
-      </c>
-      <c r="V459" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="W459" t="n">
-        <v>24</v>
-      </c>
-      <c r="X459" t="inlineStr">
-        <is>
-          <t>BALONCESTO TALAVERA vs BALONCESTO TELDE</t>
-        </is>
-      </c>
-    </row>
-    <row r="460">
-      <c r="A460" t="inlineStr">
-        <is>
-          <t>2487751</t>
-        </is>
-      </c>
-      <c r="B460" t="inlineStr">
-        <is>
-          <t>BALONCESTO TELDE</t>
-        </is>
-      </c>
-      <c r="C460" t="inlineStr">
-        <is>
-          <t>A. FERNÁNDEZ GÓMEZ | A. MARTIN GONZALEZ | A. SANTANA OJEDA | A. VIDAL RODRIGUEZ | G. ARTILES ROMERO</t>
-        </is>
-      </c>
-      <c r="D460" t="n">
-        <v>5</v>
-      </c>
-      <c r="E460" t="n">
-        <v>61</v>
-      </c>
-      <c r="F460" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="G460" t="n">
-        <v>2</v>
-      </c>
-      <c r="H460" t="n">
-        <v>3</v>
-      </c>
-      <c r="I460" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="J460" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="K460" t="n">
-        <v>106.38</v>
-      </c>
-      <c r="L460" t="n">
-        <v>159.57</v>
-      </c>
-      <c r="M460" t="n">
-        <v>-53.19</v>
-      </c>
-      <c r="N460" t="n">
-        <v>1</v>
-      </c>
-      <c r="O460" t="n">
-        <v>2</v>
-      </c>
-      <c r="P460" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q460" t="n">
-        <v>0</v>
-      </c>
-      <c r="R460" t="n">
-        <v>2</v>
-      </c>
-      <c r="S460" t="n">
-        <v>2</v>
-      </c>
-      <c r="T460" t="n">
-        <v>0</v>
-      </c>
-      <c r="U460" t="n">
-        <v>1</v>
-      </c>
-      <c r="V460" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="W460" t="n">
-        <v>25</v>
-      </c>
-      <c r="X460" t="inlineStr">
-        <is>
-          <t>BALONCESTO TELDE vs EB FELIPE ANTÓN</t>
-        </is>
-      </c>
-    </row>
-    <row r="461">
-      <c r="A461" t="inlineStr">
-        <is>
-          <t>2487751</t>
-        </is>
-      </c>
-      <c r="B461" t="inlineStr">
-        <is>
-          <t>BALONCESTO TELDE</t>
-        </is>
-      </c>
-      <c r="C461" t="inlineStr">
-        <is>
-          <t>A. FERNÁNDEZ GÓMEZ | A. MARTIN GONZALEZ | A. VIDAL RODRIGUEZ | G. ARTILES ROMERO | P. SÁNCHEZ GUTIERREZ</t>
-        </is>
-      </c>
-      <c r="D461" t="n">
-        <v>5</v>
-      </c>
-      <c r="E461" t="n">
-        <v>131</v>
-      </c>
-      <c r="F461" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="G461" t="n">
-        <v>3</v>
-      </c>
-      <c r="H461" t="n">
-        <v>7</v>
-      </c>
-      <c r="I461" t="n">
-        <v>3</v>
-      </c>
-      <c r="J461" t="n">
-        <v>6</v>
-      </c>
-      <c r="K461" t="n">
-        <v>100</v>
-      </c>
-      <c r="L461" t="n">
-        <v>116.67</v>
-      </c>
-      <c r="M461" t="n">
-        <v>-16.67</v>
-      </c>
-      <c r="N461" t="n">
-        <v>3</v>
-      </c>
-      <c r="O461" t="n">
-        <v>0</v>
-      </c>
-      <c r="P461" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q461" t="n">
-        <v>1</v>
-      </c>
-      <c r="R461" t="n">
-        <v>4</v>
-      </c>
-      <c r="S461" t="n">
-        <v>0</v>
-      </c>
-      <c r="T461" t="n">
-        <v>2</v>
-      </c>
-      <c r="U461" t="n">
-        <v>0</v>
-      </c>
-      <c r="V461" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="W461" t="n">
-        <v>25</v>
-      </c>
-      <c r="X461" t="inlineStr">
-        <is>
-          <t>BALONCESTO TELDE vs EB FELIPE ANTÓN</t>
-        </is>
-      </c>
-    </row>
-    <row r="462">
-      <c r="A462" t="inlineStr">
-        <is>
-          <t>2487751</t>
-        </is>
-      </c>
-      <c r="B462" t="inlineStr">
-        <is>
-          <t>EB FELIPE ANTÓN</t>
-        </is>
-      </c>
-      <c r="C462" t="inlineStr">
-        <is>
-          <t>A. SISTAC RODRIGUEZ | E. DUQUE NEGRÍN | J. GALLETTO LAMELA | M. NIMAGA | S. MANERO GUZMAN</t>
-        </is>
-      </c>
-      <c r="D462" t="n">
-        <v>5</v>
-      </c>
-      <c r="E462" t="n">
-        <v>87</v>
-      </c>
-      <c r="F462" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="G462" t="n">
-        <v>4</v>
-      </c>
-      <c r="H462" t="n">
-        <v>2</v>
-      </c>
-      <c r="I462" t="n">
-        <v>3</v>
-      </c>
-      <c r="J462" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="K462" t="n">
-        <v>133.33</v>
-      </c>
-      <c r="L462" t="n">
-        <v>69.44</v>
-      </c>
-      <c r="M462" t="n">
-        <v>63.89</v>
-      </c>
-      <c r="N462" t="n">
-        <v>4</v>
-      </c>
-      <c r="O462" t="n">
-        <v>0</v>
-      </c>
-      <c r="P462" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q462" t="n">
-        <v>1</v>
-      </c>
-      <c r="R462" t="n">
-        <v>1</v>
-      </c>
-      <c r="S462" t="n">
-        <v>2</v>
-      </c>
-      <c r="T462" t="n">
-        <v>1</v>
-      </c>
-      <c r="U462" t="n">
-        <v>0</v>
-      </c>
-      <c r="V462" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="W462" t="n">
-        <v>25</v>
-      </c>
-      <c r="X462" t="inlineStr">
-        <is>
-          <t>BALONCESTO TELDE vs EB FELIPE ANTÓN</t>
-        </is>
-      </c>
-    </row>
-    <row r="463">
-      <c r="A463" t="inlineStr">
-        <is>
-          <t>2487751</t>
-        </is>
-      </c>
-      <c r="B463" t="inlineStr">
-        <is>
-          <t>EB FELIPE ANTÓN</t>
-        </is>
-      </c>
-      <c r="C463" t="inlineStr">
-        <is>
-          <t>A. SISTAC RODRIGUEZ | E. DUQUE NEGRÍN | J. GALLETTO LAMELA | P. ARGÜELLES ELORZA | S. MANERO GUZMAN</t>
-        </is>
-      </c>
-      <c r="D463" t="n">
-        <v>5</v>
-      </c>
-      <c r="E463" t="n">
-        <v>27</v>
-      </c>
-      <c r="F463" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="G463" t="n">
-        <v>3</v>
-      </c>
-      <c r="H463" t="n">
-        <v>0</v>
-      </c>
-      <c r="I463" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="J463" t="n">
-        <v>0</v>
-      </c>
-      <c r="K463" t="n">
-        <v>159.57</v>
-      </c>
-      <c r="L463" t="n">
-        <v>0</v>
-      </c>
-      <c r="M463" t="n">
-        <v>0</v>
-      </c>
-      <c r="N463" t="n">
-        <v>1</v>
-      </c>
-      <c r="O463" t="n">
-        <v>2</v>
-      </c>
-      <c r="P463" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q463" t="n">
-        <v>0</v>
-      </c>
-      <c r="R463" t="n">
-        <v>0</v>
-      </c>
-      <c r="S463" t="n">
-        <v>0</v>
-      </c>
-      <c r="T463" t="n">
-        <v>0</v>
-      </c>
-      <c r="U463" t="n">
-        <v>0</v>
-      </c>
-      <c r="V463" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="W463" t="n">
-        <v>25</v>
-      </c>
-      <c r="X463" t="inlineStr">
-        <is>
-          <t>BALONCESTO TELDE vs EB FELIPE ANTÓN</t>
-        </is>
-      </c>
-    </row>
-    <row r="464">
-      <c r="A464" t="inlineStr">
-        <is>
-          <t>2487751</t>
-        </is>
-      </c>
-      <c r="B464" t="inlineStr">
-        <is>
-          <t>EB FELIPE ANTÓN</t>
-        </is>
-      </c>
-      <c r="C464" t="inlineStr">
-        <is>
-          <t>A. SISTAC RODRIGUEZ | E. DUQUE NEGRÍN | M. NIMAGA | P. HERNANDEZ RODRIGUEZ | S. MANERO GUZMAN</t>
-        </is>
-      </c>
-      <c r="D464" t="n">
-        <v>5</v>
-      </c>
-      <c r="E464" t="n">
-        <v>78</v>
-      </c>
-      <c r="F464" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="G464" t="n">
-        <v>3</v>
-      </c>
-      <c r="H464" t="n">
-        <v>3</v>
-      </c>
-      <c r="I464" t="n">
-        <v>3</v>
-      </c>
-      <c r="J464" t="n">
-        <v>2</v>
-      </c>
-      <c r="K464" t="n">
-        <v>100</v>
-      </c>
-      <c r="L464" t="n">
-        <v>150</v>
-      </c>
-      <c r="M464" t="n">
-        <v>-50</v>
-      </c>
-      <c r="N464" t="n">
-        <v>1</v>
-      </c>
-      <c r="O464" t="n">
-        <v>0</v>
-      </c>
-      <c r="P464" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q464" t="n">
-        <v>0</v>
-      </c>
-      <c r="R464" t="n">
-        <v>3</v>
-      </c>
-      <c r="S464" t="n">
-        <v>0</v>
-      </c>
-      <c r="T464" t="n">
-        <v>0</v>
-      </c>
-      <c r="U464" t="n">
-        <v>1</v>
-      </c>
-      <c r="V464" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="W464" t="n">
-        <v>25</v>
-      </c>
-      <c r="X464" t="inlineStr">
-        <is>
-          <t>BALONCESTO TELDE vs EB FELIPE ANTÓN</t>
-        </is>
-      </c>
-    </row>
-    <row r="465">
-      <c r="A465" t="inlineStr">
-        <is>
-          <t>2487749</t>
-        </is>
-      </c>
-      <c r="B465" t="inlineStr">
-        <is>
-          <t>ADC BOADILLA</t>
-        </is>
-      </c>
-      <c r="C465" t="inlineStr">
-        <is>
-          <t>A. GOMEZ SERRANO | A. OLMEDO VELASCO | I. BLANCO-ARGIBAY GONZALEZ | M. SANCHEZ SANCHEZ | P. DOMINGUEZ LORENZO</t>
-        </is>
-      </c>
-      <c r="D465" t="n">
-        <v>5</v>
-      </c>
-      <c r="E465" t="n">
-        <v>85</v>
-      </c>
-      <c r="F465" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="G465" t="n">
-        <v>5</v>
-      </c>
-      <c r="H465" t="n">
-        <v>2</v>
-      </c>
-      <c r="I465" t="n">
-        <v>3</v>
-      </c>
-      <c r="J465" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="K465" t="n">
-        <v>166.67</v>
-      </c>
-      <c r="L465" t="n">
-        <v>86.20999999999999</v>
-      </c>
-      <c r="M465" t="n">
-        <v>80.45999999999999</v>
-      </c>
-      <c r="N465" t="n">
-        <v>3</v>
-      </c>
-      <c r="O465" t="n">
-        <v>0</v>
-      </c>
-      <c r="P465" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q465" t="n">
-        <v>0</v>
-      </c>
-      <c r="R465" t="n">
-        <v>0</v>
-      </c>
-      <c r="S465" t="n">
-        <v>3</v>
-      </c>
-      <c r="T465" t="n">
-        <v>2</v>
-      </c>
-      <c r="U465" t="n">
-        <v>1</v>
-      </c>
-      <c r="V465" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="W465" t="n">
-        <v>25</v>
-      </c>
-      <c r="X465" t="inlineStr">
-        <is>
-          <t>C. D. MENSAJERO ISLA DE LA PALMA vs ADC BOADILLA</t>
-        </is>
-      </c>
-    </row>
-    <row r="466">
-      <c r="A466" t="inlineStr">
-        <is>
-          <t>2487749</t>
-        </is>
-      </c>
-      <c r="B466" t="inlineStr">
-        <is>
-          <t>C. D. MENSAJERO ISLA DE LA PALMA</t>
-        </is>
-      </c>
-      <c r="C466" t="inlineStr">
-        <is>
-          <t>A. APARICIO IZQUIERDO | A. JIMENEZ FERNANDEZ | D. RODRIGUEZ GARCIA | M. NIANG | M. RODRÍGUEZ RIVEROL</t>
-        </is>
-      </c>
-      <c r="D466" t="n">
-        <v>5</v>
-      </c>
-      <c r="E466" t="n">
-        <v>37</v>
-      </c>
-      <c r="F466" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="G466" t="n">
-        <v>2</v>
-      </c>
-      <c r="H466" t="n">
-        <v>3</v>
-      </c>
-      <c r="I466" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="J466" t="n">
-        <v>1</v>
-      </c>
-      <c r="K466" t="n">
-        <v>151.52</v>
-      </c>
-      <c r="L466" t="n">
-        <v>300</v>
-      </c>
-      <c r="M466" t="n">
-        <v>-148.48</v>
-      </c>
-      <c r="N466" t="n">
-        <v>0</v>
-      </c>
-      <c r="O466" t="n">
-        <v>3</v>
-      </c>
-      <c r="P466" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q466" t="n">
-        <v>0</v>
-      </c>
-      <c r="R466" t="n">
-        <v>1</v>
-      </c>
-      <c r="S466" t="n">
-        <v>0</v>
-      </c>
-      <c r="T466" t="n">
-        <v>0</v>
-      </c>
-      <c r="U466" t="n">
-        <v>0</v>
-      </c>
-      <c r="V466" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="W466" t="n">
-        <v>25</v>
-      </c>
-      <c r="X466" t="inlineStr">
-        <is>
-          <t>C. D. MENSAJERO ISLA DE LA PALMA vs ADC BOADILLA</t>
-        </is>
-      </c>
-    </row>
-    <row r="467">
-      <c r="A467" t="inlineStr">
-        <is>
-          <t>2487749</t>
-        </is>
-      </c>
-      <c r="B467" t="inlineStr">
-        <is>
-          <t>C. D. MENSAJERO ISLA DE LA PALMA</t>
-        </is>
-      </c>
-      <c r="C467" t="inlineStr">
-        <is>
-          <t>A. APARICIO IZQUIERDO | D. RODRIGUEZ GARCIA | J. RIES | M. NIANG | M. RODRÍGUEZ RIVEROL</t>
-        </is>
-      </c>
-      <c r="D467" t="n">
-        <v>5</v>
-      </c>
-      <c r="E467" t="n">
-        <v>48</v>
-      </c>
-      <c r="F467" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="G467" t="n">
-        <v>0</v>
-      </c>
-      <c r="H467" t="n">
-        <v>2</v>
-      </c>
-      <c r="I467" t="n">
-        <v>1</v>
-      </c>
-      <c r="J467" t="n">
-        <v>2</v>
-      </c>
-      <c r="K467" t="n">
-        <v>0</v>
-      </c>
-      <c r="L467" t="n">
-        <v>100</v>
-      </c>
-      <c r="M467" t="n">
-        <v>-100</v>
-      </c>
-      <c r="N467" t="n">
-        <v>0</v>
-      </c>
-      <c r="O467" t="n">
-        <v>0</v>
-      </c>
-      <c r="P467" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q467" t="n">
-        <v>1</v>
-      </c>
-      <c r="R467" t="n">
-        <v>2</v>
-      </c>
-      <c r="S467" t="n">
-        <v>0</v>
-      </c>
-      <c r="T467" t="n">
-        <v>0</v>
-      </c>
-      <c r="U467" t="n">
-        <v>0</v>
-      </c>
-      <c r="V467" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="W467" t="n">
-        <v>25</v>
-      </c>
-      <c r="X467" t="inlineStr">
-        <is>
-          <t>C. D. MENSAJERO ISLA DE LA PALMA vs ADC BOADILLA</t>
-        </is>
-      </c>
-    </row>
-    <row r="468">
-      <c r="A468" t="inlineStr">
-        <is>
-          <t>2487748</t>
-        </is>
-      </c>
-      <c r="B468" t="inlineStr">
-        <is>
-          <t>GRUPO EGIDO PINTOBASKET</t>
-        </is>
-      </c>
-      <c r="C468" t="inlineStr">
-        <is>
-          <t>J. AYALA AYLLÓN | L. BERMEJO ALCALDE | M. ALARCON ORTIZ | M. BATLLE BERNARDO | S. RODRIGUEZ GREGORIO</t>
-        </is>
-      </c>
-      <c r="D468" t="n">
-        <v>5</v>
-      </c>
-      <c r="E468" t="n">
-        <v>6</v>
-      </c>
-      <c r="F468" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G468" t="n">
-        <v>0</v>
-      </c>
-      <c r="H468" t="n">
-        <v>0</v>
-      </c>
-      <c r="I468" t="n">
-        <v>1</v>
-      </c>
-      <c r="J468" t="n">
-        <v>-1</v>
-      </c>
-      <c r="K468" t="n">
-        <v>0</v>
-      </c>
-      <c r="L468" t="n">
-        <v>0</v>
-      </c>
-      <c r="M468" t="n">
-        <v>0</v>
-      </c>
-      <c r="N468" t="n">
-        <v>1</v>
-      </c>
-      <c r="O468" t="n">
-        <v>0</v>
-      </c>
-      <c r="P468" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q468" t="n">
-        <v>0</v>
-      </c>
-      <c r="R468" t="n">
-        <v>0</v>
-      </c>
-      <c r="S468" t="n">
-        <v>0</v>
-      </c>
-      <c r="T468" t="n">
-        <v>0</v>
-      </c>
-      <c r="U468" t="n">
-        <v>1</v>
-      </c>
-      <c r="V468" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="W468" t="n">
-        <v>25</v>
-      </c>
-      <c r="X468" t="inlineStr">
-        <is>
-          <t>GRUPO EGIDO PINTOBASKET vs RECUCYM BAZU</t>
-        </is>
-      </c>
-    </row>
-    <row r="469">
-      <c r="A469" t="inlineStr">
-        <is>
-          <t>2487748</t>
-        </is>
-      </c>
-      <c r="B469" t="inlineStr">
-        <is>
-          <t>RECUCYM BAZU</t>
-        </is>
-      </c>
-      <c r="C469" t="inlineStr">
-        <is>
-          <t>E. ECHEVERRIA MATEO | G. HIERRO ABAD | J. BARRA DE LA CRUZ | J. MUNRO | V. FERNANDEZ MORAN</t>
-        </is>
-      </c>
-      <c r="D469" t="n">
-        <v>5</v>
-      </c>
-      <c r="E469" t="n">
-        <v>6</v>
-      </c>
-      <c r="F469" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G469" t="n">
-        <v>0</v>
-      </c>
-      <c r="H469" t="n">
-        <v>0</v>
-      </c>
-      <c r="I469" t="n">
-        <v>-1</v>
-      </c>
-      <c r="J469" t="n">
-        <v>1</v>
-      </c>
-      <c r="K469" t="n">
-        <v>0</v>
-      </c>
-      <c r="L469" t="n">
-        <v>0</v>
-      </c>
-      <c r="M469" t="n">
-        <v>0</v>
-      </c>
-      <c r="N469" t="n">
-        <v>0</v>
-      </c>
-      <c r="O469" t="n">
-        <v>0</v>
-      </c>
-      <c r="P469" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q469" t="n">
-        <v>1</v>
-      </c>
-      <c r="R469" t="n">
-        <v>1</v>
-      </c>
-      <c r="S469" t="n">
-        <v>0</v>
-      </c>
-      <c r="T469" t="n">
-        <v>0</v>
-      </c>
-      <c r="U469" t="n">
-        <v>0</v>
-      </c>
-      <c r="V469" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="W469" t="n">
-        <v>25</v>
-      </c>
-      <c r="X469" t="inlineStr">
-        <is>
-          <t>GRUPO EGIDO PINTOBASKET vs RECUCYM BAZU</t>
-        </is>
-      </c>
-    </row>
-    <row r="470">
-      <c r="A470" t="inlineStr">
-        <is>
-          <t>2487746</t>
-        </is>
-      </c>
-      <c r="B470" t="inlineStr">
-        <is>
-          <t>LUJISA GUADALAJARA BASKET</t>
-        </is>
-      </c>
-      <c r="C470" t="inlineStr">
-        <is>
-          <t>A. ARMSTRONG | D. EBOLO OLU-ELIJAH | J. HOYA MARTINEZ | L. VALERA VILLEGAS | M. DIALLO</t>
-        </is>
-      </c>
-      <c r="D470" t="n">
-        <v>5</v>
-      </c>
-      <c r="E470" t="n">
-        <v>219</v>
-      </c>
-      <c r="F470" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="G470" t="n">
-        <v>5</v>
-      </c>
-      <c r="H470" t="n">
-        <v>8</v>
-      </c>
-      <c r="I470" t="n">
-        <v>8.880000000000001</v>
-      </c>
-      <c r="J470" t="n">
-        <v>7.88</v>
-      </c>
-      <c r="K470" t="n">
-        <v>56.31</v>
-      </c>
-      <c r="L470" t="n">
-        <v>101.52</v>
-      </c>
-      <c r="M470" t="n">
-        <v>-45.22</v>
-      </c>
-      <c r="N470" t="n">
-        <v>4</v>
-      </c>
-      <c r="O470" t="n">
-        <v>2</v>
-      </c>
-      <c r="P470" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q470" t="n">
-        <v>0</v>
-      </c>
-      <c r="R470" t="n">
-        <v>5</v>
-      </c>
-      <c r="S470" t="n">
-        <v>2</v>
-      </c>
-      <c r="T470" t="n">
-        <v>2</v>
-      </c>
-      <c r="U470" t="n">
-        <v>0</v>
-      </c>
-      <c r="V470" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="W470" t="n">
-        <v>25</v>
-      </c>
-      <c r="X470" t="inlineStr">
-        <is>
-          <t>UROS DE RIVAS vs LUJISA GUADALAJARA BASKET</t>
-        </is>
-      </c>
-    </row>
-    <row r="471">
-      <c r="A471" t="inlineStr">
-        <is>
-          <t>2487746</t>
-        </is>
-      </c>
-      <c r="B471" t="inlineStr">
-        <is>
-          <t>UROS DE RIVAS</t>
-        </is>
-      </c>
-      <c r="C471" t="inlineStr">
-        <is>
-          <t>A. BIERSACK LOPEZ | A. PEREZ CONTI | C. CRESPO MONTESINOS | P. ESTEBANEZ GONZALEZ | P. ROSSI</t>
-        </is>
-      </c>
-      <c r="D471" t="n">
-        <v>5</v>
-      </c>
-      <c r="E471" t="n">
-        <v>23</v>
-      </c>
-      <c r="F471" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="G471" t="n">
-        <v>0</v>
-      </c>
-      <c r="H471" t="n">
-        <v>0</v>
-      </c>
-      <c r="I471" t="n">
-        <v>0</v>
-      </c>
-      <c r="J471" t="n">
-        <v>1</v>
-      </c>
-      <c r="K471" t="n">
-        <v>0</v>
-      </c>
-      <c r="L471" t="n">
-        <v>0</v>
-      </c>
-      <c r="M471" t="n">
-        <v>0</v>
-      </c>
-      <c r="N471" t="n">
-        <v>0</v>
-      </c>
-      <c r="O471" t="n">
-        <v>0</v>
-      </c>
-      <c r="P471" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q471" t="n">
-        <v>0</v>
-      </c>
-      <c r="R471" t="n">
-        <v>0</v>
-      </c>
-      <c r="S471" t="n">
-        <v>0</v>
-      </c>
-      <c r="T471" t="n">
-        <v>1</v>
-      </c>
-      <c r="U471" t="n">
-        <v>0</v>
-      </c>
-      <c r="V471" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="W471" t="n">
-        <v>25</v>
-      </c>
-      <c r="X471" t="inlineStr">
-        <is>
-          <t>UROS DE RIVAS vs LUJISA GUADALAJARA BASKET</t>
-        </is>
-      </c>
-    </row>
-    <row r="472">
-      <c r="A472" t="inlineStr">
-        <is>
-          <t>2487746</t>
-        </is>
-      </c>
-      <c r="B472" t="inlineStr">
-        <is>
-          <t>UROS DE RIVAS</t>
-        </is>
-      </c>
-      <c r="C472" t="inlineStr">
-        <is>
-          <t>A. BIERSACK LOPEZ | D. MARINEZ FERNANDEZ-URRUTIA | O. MENDEZ BLANCO | P. ESTEBANEZ GONZALEZ | P. ROSSI</t>
-        </is>
-      </c>
-      <c r="D472" t="n">
-        <v>5</v>
-      </c>
-      <c r="E472" t="n">
-        <v>74</v>
-      </c>
-      <c r="F472" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="G472" t="n">
-        <v>5</v>
-      </c>
-      <c r="H472" t="n">
-        <v>2</v>
-      </c>
-      <c r="I472" t="n">
-        <v>2</v>
-      </c>
-      <c r="J472" t="n">
-        <v>2</v>
-      </c>
-      <c r="K472" t="n">
-        <v>250</v>
-      </c>
-      <c r="L472" t="n">
-        <v>100</v>
-      </c>
-      <c r="M472" t="n">
-        <v>150</v>
-      </c>
-      <c r="N472" t="n">
-        <v>2</v>
-      </c>
-      <c r="O472" t="n">
-        <v>0</v>
-      </c>
-      <c r="P472" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q472" t="n">
-        <v>0</v>
-      </c>
-      <c r="R472" t="n">
-        <v>1</v>
-      </c>
-      <c r="S472" t="n">
-        <v>0</v>
-      </c>
-      <c r="T472" t="n">
-        <v>1</v>
-      </c>
-      <c r="U472" t="n">
-        <v>0</v>
-      </c>
-      <c r="V472" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="W472" t="n">
-        <v>25</v>
-      </c>
-      <c r="X472" t="inlineStr">
-        <is>
-          <t>UROS DE RIVAS vs LUJISA GUADALAJARA BASKET</t>
-        </is>
-      </c>
-    </row>
-    <row r="473">
-      <c r="A473" t="inlineStr">
-        <is>
-          <t>2487746</t>
-        </is>
-      </c>
-      <c r="B473" t="inlineStr">
-        <is>
-          <t>UROS DE RIVAS</t>
-        </is>
-      </c>
-      <c r="C473" t="inlineStr">
-        <is>
-          <t>A. PEREZ CONTI | C. CRESPO MONTESINOS | D. MARINEZ FERNANDEZ-URRUTIA | P. ESTEBANEZ GONZALEZ | P. ROSSI</t>
-        </is>
-      </c>
-      <c r="D473" t="n">
-        <v>5</v>
-      </c>
-      <c r="E473" t="n">
-        <v>79</v>
-      </c>
-      <c r="F473" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="G473" t="n">
-        <v>2</v>
-      </c>
-      <c r="H473" t="n">
-        <v>2</v>
-      </c>
-      <c r="I473" t="n">
-        <v>3</v>
-      </c>
-      <c r="J473" t="n">
-        <v>3</v>
-      </c>
-      <c r="K473" t="n">
-        <v>66.67</v>
-      </c>
-      <c r="L473" t="n">
-        <v>66.67</v>
-      </c>
-      <c r="M473" t="n">
-        <v>0</v>
-      </c>
-      <c r="N473" t="n">
-        <v>3</v>
-      </c>
-      <c r="O473" t="n">
-        <v>0</v>
-      </c>
-      <c r="P473" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q473" t="n">
-        <v>0</v>
-      </c>
-      <c r="R473" t="n">
-        <v>2</v>
-      </c>
-      <c r="S473" t="n">
-        <v>0</v>
-      </c>
-      <c r="T473" t="n">
-        <v>1</v>
-      </c>
-      <c r="U473" t="n">
-        <v>0</v>
-      </c>
-      <c r="V473" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="W473" t="n">
-        <v>25</v>
-      </c>
-      <c r="X473" t="inlineStr">
-        <is>
-          <t>UROS DE RIVAS vs LUJISA GUADALAJARA BASKET</t>
-        </is>
-      </c>
-    </row>
-    <row r="474">
-      <c r="A474" t="inlineStr">
-        <is>
-          <t>2487746</t>
-        </is>
-      </c>
-      <c r="B474" t="inlineStr">
-        <is>
-          <t>UROS DE RIVAS</t>
-        </is>
-      </c>
-      <c r="C474" t="inlineStr">
-        <is>
-          <t>A. PEREZ CONTI | C. CRESPO MONTESINOS | G. MARTIN LOPEZ-LAGO | O. MENDEZ BLANCO | P. ESTEBANEZ GONZALEZ</t>
-        </is>
-      </c>
-      <c r="D474" t="n">
-        <v>5</v>
-      </c>
-      <c r="E474" t="n">
-        <v>10</v>
-      </c>
-      <c r="F474" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="G474" t="n">
-        <v>0</v>
-      </c>
-      <c r="H474" t="n">
-        <v>1</v>
-      </c>
-      <c r="I474" t="n">
-        <v>1</v>
-      </c>
-      <c r="J474" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="K474" t="n">
-        <v>0</v>
-      </c>
-      <c r="L474" t="n">
-        <v>53.19</v>
-      </c>
-      <c r="M474" t="n">
-        <v>-53.19</v>
-      </c>
-      <c r="N474" t="n">
-        <v>0</v>
-      </c>
-      <c r="O474" t="n">
-        <v>0</v>
-      </c>
-      <c r="P474" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q474" t="n">
-        <v>0</v>
-      </c>
-      <c r="R474" t="n">
-        <v>0</v>
-      </c>
-      <c r="S474" t="n">
-        <v>2</v>
-      </c>
-      <c r="T474" t="n">
-        <v>1</v>
-      </c>
-      <c r="U474" t="n">
-        <v>0</v>
-      </c>
-      <c r="V474" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="W474" t="n">
-        <v>25</v>
-      </c>
-      <c r="X474" t="inlineStr">
-        <is>
-          <t>UROS DE RIVAS vs LUJISA GUADALAJARA BASKET</t>
-        </is>
-      </c>
-    </row>
-    <row r="475">
-      <c r="A475" t="inlineStr">
-        <is>
-          <t>2487746</t>
-        </is>
-      </c>
-      <c r="B475" t="inlineStr">
-        <is>
-          <t>UROS DE RIVAS</t>
-        </is>
-      </c>
-      <c r="C475" t="inlineStr">
-        <is>
-          <t>A. PEREZ CONTI | D. MARINEZ FERNANDEZ-URRUTIA | O. MENDEZ BLANCO | P. ESTEBANEZ GONZALEZ | P. ROSSI</t>
-        </is>
-      </c>
-      <c r="D475" t="n">
-        <v>5</v>
-      </c>
-      <c r="E475" t="n">
-        <v>33</v>
-      </c>
-      <c r="F475" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="G475" t="n">
-        <v>1</v>
-      </c>
-      <c r="H475" t="n">
-        <v>0</v>
-      </c>
-      <c r="I475" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="J475" t="n">
-        <v>1</v>
-      </c>
-      <c r="K475" t="n">
-        <v>53.19</v>
-      </c>
-      <c r="L475" t="n">
-        <v>0</v>
-      </c>
-      <c r="M475" t="n">
-        <v>53.19</v>
-      </c>
-      <c r="N475" t="n">
-        <v>0</v>
-      </c>
-      <c r="O475" t="n">
-        <v>2</v>
-      </c>
-      <c r="P475" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q475" t="n">
-        <v>0</v>
-      </c>
-      <c r="R475" t="n">
-        <v>1</v>
-      </c>
-      <c r="S475" t="n">
-        <v>0</v>
-      </c>
-      <c r="T475" t="n">
-        <v>0</v>
-      </c>
-      <c r="U475" t="n">
-        <v>0</v>
-      </c>
-      <c r="V475" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="W475" t="n">
-        <v>25</v>
-      </c>
-      <c r="X475" t="inlineStr">
-        <is>
-          <t>UROS DE RIVAS vs LUJISA GUADALAJARA BASKET</t>
-        </is>
-      </c>
-    </row>
-    <row r="476">
-      <c r="A476" t="inlineStr">
-        <is>
-          <t>2487750</t>
-        </is>
-      </c>
-      <c r="B476" t="inlineStr">
-        <is>
-          <t>C.B. TRES CANTOS</t>
-        </is>
-      </c>
-      <c r="C476" t="inlineStr">
-        <is>
-          <t>D. GONZALEZ LONGARELA | G. DIAZ MONTERO | J. ATIENZA PEREA | J. DE DOMINGO GARAY | N. MAIGA</t>
-        </is>
-      </c>
-      <c r="D476" t="n">
-        <v>5</v>
-      </c>
-      <c r="E476" t="n">
-        <v>71</v>
-      </c>
-      <c r="F476" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="G476" t="n">
-        <v>2</v>
-      </c>
-      <c r="H476" t="n">
-        <v>0</v>
-      </c>
-      <c r="I476" t="n">
-        <v>2</v>
-      </c>
-      <c r="J476" t="n">
-        <v>0</v>
-      </c>
-      <c r="K476" t="n">
-        <v>100</v>
-      </c>
-      <c r="L476" t="n">
-        <v>0</v>
-      </c>
-      <c r="M476" t="n">
-        <v>0</v>
-      </c>
-      <c r="N476" t="n">
-        <v>3</v>
-      </c>
-      <c r="O476" t="n">
-        <v>0</v>
-      </c>
-      <c r="P476" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q476" t="n">
-        <v>1</v>
-      </c>
-      <c r="R476" t="n">
-        <v>1</v>
-      </c>
-      <c r="S476" t="n">
-        <v>0</v>
-      </c>
-      <c r="T476" t="n">
-        <v>1</v>
-      </c>
-      <c r="U476" t="n">
-        <v>2</v>
-      </c>
-      <c r="V476" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="W476" t="n">
-        <v>25</v>
-      </c>
-      <c r="X476" t="inlineStr">
-        <is>
-          <t>C.B. TRES CANTOS vs ZENTRO BASKET MADRID</t>
-        </is>
-      </c>
-    </row>
-    <row r="477">
-      <c r="A477" t="inlineStr">
-        <is>
-          <t>2487750</t>
-        </is>
-      </c>
-      <c r="B477" t="inlineStr">
-        <is>
-          <t>C.B. TRES CANTOS</t>
-        </is>
-      </c>
-      <c r="C477" t="inlineStr">
-        <is>
-          <t>D. GONZALEZ LONGARELA | G. DIAZ MONTERO | J. ATIENZA PEREA | J. DOMINGUEZ LARRE | N. MAIGA</t>
-        </is>
-      </c>
-      <c r="D477" t="n">
-        <v>5</v>
-      </c>
-      <c r="E477" t="n">
-        <v>226</v>
-      </c>
-      <c r="F477" t="n">
-        <v>3.77</v>
-      </c>
-      <c r="G477" t="n">
-        <v>5</v>
-      </c>
-      <c r="H477" t="n">
-        <v>8</v>
-      </c>
-      <c r="I477" t="n">
-        <v>6.88</v>
-      </c>
-      <c r="J477" t="n">
-        <v>9.880000000000001</v>
-      </c>
-      <c r="K477" t="n">
-        <v>72.67</v>
-      </c>
-      <c r="L477" t="n">
-        <v>80.97</v>
-      </c>
-      <c r="M477" t="n">
-        <v>-8.300000000000001</v>
-      </c>
-      <c r="N477" t="n">
-        <v>5</v>
-      </c>
-      <c r="O477" t="n">
-        <v>2</v>
-      </c>
-      <c r="P477" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q477" t="n">
-        <v>1</v>
-      </c>
-      <c r="R477" t="n">
-        <v>8</v>
-      </c>
-      <c r="S477" t="n">
-        <v>2</v>
-      </c>
-      <c r="T477" t="n">
-        <v>2</v>
-      </c>
-      <c r="U477" t="n">
-        <v>1</v>
-      </c>
-      <c r="V477" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="W477" t="n">
-        <v>25</v>
-      </c>
-      <c r="X477" t="inlineStr">
-        <is>
-          <t>C.B. TRES CANTOS vs ZENTRO BASKET MADRID</t>
-        </is>
-      </c>
-    </row>
-    <row r="478">
-      <c r="A478" t="inlineStr">
-        <is>
-          <t>2487750</t>
-        </is>
-      </c>
-      <c r="B478" t="inlineStr">
-        <is>
-          <t>C.B. TRES CANTOS</t>
-        </is>
-      </c>
-      <c r="C478" t="inlineStr">
-        <is>
-          <t>G. DIAZ MONTERO | G. LARDIES GUILLEN | J. ATIENZA PEREA | J. DE DOMINGO GARAY | N. MAIGA</t>
-        </is>
-      </c>
-      <c r="D478" t="n">
-        <v>5</v>
-      </c>
-      <c r="E478" t="n">
-        <v>108</v>
-      </c>
-      <c r="F478" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="G478" t="n">
-        <v>6</v>
-      </c>
-      <c r="H478" t="n">
-        <v>6</v>
-      </c>
-      <c r="I478" t="n">
-        <v>4.76</v>
-      </c>
-      <c r="J478" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="K478" t="n">
-        <v>126.05</v>
-      </c>
-      <c r="L478" t="n">
-        <v>208.33</v>
-      </c>
-      <c r="M478" t="n">
-        <v>-82.28</v>
-      </c>
-      <c r="N478" t="n">
-        <v>3</v>
-      </c>
-      <c r="O478" t="n">
-        <v>4</v>
-      </c>
-      <c r="P478" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q478" t="n">
-        <v>0</v>
-      </c>
-      <c r="R478" t="n">
-        <v>3</v>
-      </c>
-      <c r="S478" t="n">
-        <v>2</v>
-      </c>
-      <c r="T478" t="n">
-        <v>0</v>
-      </c>
-      <c r="U478" t="n">
-        <v>1</v>
-      </c>
-      <c r="V478" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="W478" t="n">
-        <v>25</v>
-      </c>
-      <c r="X478" t="inlineStr">
-        <is>
-          <t>C.B. TRES CANTOS vs ZENTRO BASKET MADRID</t>
-        </is>
-      </c>
-    </row>
-    <row r="479">
-      <c r="A479" t="inlineStr">
-        <is>
-          <t>2487750</t>
-        </is>
-      </c>
-      <c r="B479" t="inlineStr">
-        <is>
-          <t>C.B. TRES CANTOS</t>
-        </is>
-      </c>
-      <c r="C479" t="inlineStr">
-        <is>
-          <t>G. DIAZ MONTERO | G. LARDIES GUILLEN | J. ATIENZA PEREA | J. DOMINGUEZ LARRE | N. MAIGA</t>
-        </is>
-      </c>
-      <c r="D479" t="n">
-        <v>5</v>
-      </c>
-      <c r="E479" t="n">
-        <v>7</v>
-      </c>
-      <c r="F479" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="G479" t="n">
-        <v>0</v>
-      </c>
-      <c r="H479" t="n">
-        <v>3</v>
-      </c>
-      <c r="I479" t="n">
-        <v>0</v>
-      </c>
-      <c r="J479" t="n">
-        <v>1</v>
-      </c>
-      <c r="K479" t="n">
-        <v>0</v>
-      </c>
-      <c r="L479" t="n">
-        <v>300</v>
-      </c>
-      <c r="M479" t="n">
-        <v>0</v>
-      </c>
-      <c r="N479" t="n">
-        <v>0</v>
-      </c>
-      <c r="O479" t="n">
-        <v>0</v>
-      </c>
-      <c r="P479" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q479" t="n">
-        <v>0</v>
-      </c>
-      <c r="R479" t="n">
-        <v>1</v>
-      </c>
-      <c r="S479" t="n">
-        <v>0</v>
-      </c>
-      <c r="T479" t="n">
-        <v>0</v>
-      </c>
-      <c r="U479" t="n">
-        <v>0</v>
-      </c>
-      <c r="V479" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="W479" t="n">
-        <v>25</v>
-      </c>
-      <c r="X479" t="inlineStr">
-        <is>
-          <t>C.B. TRES CANTOS vs ZENTRO BASKET MADRID</t>
-        </is>
-      </c>
-    </row>
-    <row r="480">
-      <c r="A480" t="inlineStr">
-        <is>
-          <t>2487750</t>
-        </is>
-      </c>
-      <c r="B480" t="inlineStr">
-        <is>
-          <t>C.B. TRES CANTOS</t>
-        </is>
-      </c>
-      <c r="C480" t="inlineStr">
-        <is>
-          <t>G. LARDIES GUILLEN | J. ATIENZA PEREA | J. DE DOMINGO GARAY | J. DOMINGUEZ LARRE | N. MAIGA</t>
-        </is>
-      </c>
-      <c r="D480" t="n">
-        <v>5</v>
-      </c>
-      <c r="E480" t="n">
-        <v>185</v>
-      </c>
-      <c r="F480" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="G480" t="n">
-        <v>5</v>
-      </c>
-      <c r="H480" t="n">
-        <v>4</v>
-      </c>
-      <c r="I480" t="n">
-        <v>3</v>
-      </c>
-      <c r="J480" t="n">
-        <v>5</v>
-      </c>
-      <c r="K480" t="n">
-        <v>166.67</v>
-      </c>
-      <c r="L480" t="n">
-        <v>80</v>
-      </c>
-      <c r="M480" t="n">
-        <v>86.67</v>
-      </c>
-      <c r="N480" t="n">
-        <v>5</v>
-      </c>
-      <c r="O480" t="n">
-        <v>0</v>
-      </c>
-      <c r="P480" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q480" t="n">
-        <v>3</v>
-      </c>
-      <c r="R480" t="n">
-        <v>9</v>
-      </c>
-      <c r="S480" t="n">
-        <v>0</v>
-      </c>
-      <c r="T480" t="n">
-        <v>0</v>
-      </c>
-      <c r="U480" t="n">
-        <v>4</v>
-      </c>
-      <c r="V480" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="W480" t="n">
-        <v>25</v>
-      </c>
-      <c r="X480" t="inlineStr">
-        <is>
-          <t>C.B. TRES CANTOS vs ZENTRO BASKET MADRID</t>
-        </is>
-      </c>
-    </row>
-    <row r="481">
-      <c r="A481" t="inlineStr">
-        <is>
-          <t>2487750</t>
-        </is>
-      </c>
-      <c r="B481" t="inlineStr">
-        <is>
-          <t>ZENTRO BASKET MADRID</t>
-        </is>
-      </c>
-      <c r="C481" t="inlineStr">
-        <is>
-          <t>B. SCHUCH | D. VAL GUTIERREZ | G. GOMA | L. SCHIEBELHUT LUIS | M. ESTAPE ROIZ</t>
-        </is>
-      </c>
-      <c r="D481" t="n">
-        <v>5</v>
-      </c>
-      <c r="E481" t="n">
-        <v>541</v>
-      </c>
-      <c r="F481" t="n">
-        <v>9.02</v>
-      </c>
-      <c r="G481" t="n">
-        <v>14</v>
-      </c>
-      <c r="H481" t="n">
-        <v>14</v>
-      </c>
-      <c r="I481" t="n">
-        <v>15.88</v>
-      </c>
-      <c r="J481" t="n">
-        <v>13.88</v>
-      </c>
-      <c r="K481" t="n">
-        <v>88.16</v>
-      </c>
-      <c r="L481" t="n">
-        <v>100.86</v>
-      </c>
-      <c r="M481" t="n">
-        <v>-12.7</v>
-      </c>
-      <c r="N481" t="n">
-        <v>19</v>
-      </c>
-      <c r="O481" t="n">
-        <v>2</v>
-      </c>
-      <c r="P481" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q481" t="n">
-        <v>7</v>
-      </c>
-      <c r="R481" t="n">
-        <v>15</v>
-      </c>
-      <c r="S481" t="n">
-        <v>2</v>
-      </c>
-      <c r="T481" t="n">
-        <v>3</v>
-      </c>
-      <c r="U481" t="n">
-        <v>5</v>
-      </c>
-      <c r="V481" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="W481" t="n">
-        <v>25</v>
-      </c>
-      <c r="X481" t="inlineStr">
-        <is>
-          <t>C.B. TRES CANTOS vs ZENTRO BASKET MADRID</t>
-        </is>
-      </c>
-    </row>
-    <row r="482">
-      <c r="A482" t="inlineStr">
-        <is>
-          <t>2487750</t>
-        </is>
-      </c>
-      <c r="B482" t="inlineStr">
-        <is>
-          <t>ZENTRO BASKET MADRID</t>
-        </is>
-      </c>
-      <c r="C482" t="inlineStr">
-        <is>
-          <t>D. VAL GUTIERREZ | G. GOMA | L. SCHIEBELHUT LUIS | M. ESTAPE ROIZ | T. VERDERA BENASSAR</t>
-        </is>
-      </c>
-      <c r="D482" t="n">
-        <v>5</v>
-      </c>
-      <c r="E482" t="n">
-        <v>56</v>
-      </c>
-      <c r="F482" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="G482" t="n">
-        <v>7</v>
-      </c>
-      <c r="H482" t="n">
-        <v>4</v>
-      </c>
-      <c r="I482" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="J482" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="K482" t="n">
-        <v>243.06</v>
-      </c>
-      <c r="L482" t="n">
-        <v>144.93</v>
-      </c>
-      <c r="M482" t="n">
-        <v>98.13</v>
-      </c>
-      <c r="N482" t="n">
-        <v>3</v>
-      </c>
-      <c r="O482" t="n">
-        <v>2</v>
-      </c>
-      <c r="P482" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q482" t="n">
-        <v>1</v>
-      </c>
-      <c r="R482" t="n">
-        <v>1</v>
-      </c>
-      <c r="S482" t="n">
-        <v>4</v>
-      </c>
-      <c r="T482" t="n">
-        <v>0</v>
-      </c>
-      <c r="U482" t="n">
-        <v>0</v>
-      </c>
-      <c r="V482" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="W482" t="n">
-        <v>25</v>
-      </c>
-      <c r="X482" t="inlineStr">
-        <is>
-          <t>C.B. TRES CANTOS vs ZENTRO BASKET MADRID</t>
-        </is>
-      </c>
-    </row>
-    <row r="483">
-      <c r="A483" t="inlineStr">
-        <is>
-          <t>2487754</t>
-        </is>
-      </c>
-      <c r="B483" t="inlineStr">
-        <is>
-          <t>ADC BOADILLA</t>
-        </is>
-      </c>
-      <c r="C483" t="inlineStr">
-        <is>
-          <t>A. GOMEZ SERRANO | A. OLMEDO VELASCO | I. BLANCO-ARGIBAY GONZALEZ | J. VILASANCHEZ FREIJOMIL | P. DOMINGUEZ LORENZO</t>
-        </is>
-      </c>
-      <c r="D483" t="n">
-        <v>5</v>
-      </c>
-      <c r="E483" t="n">
-        <v>93</v>
-      </c>
-      <c r="F483" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="G483" t="n">
-        <v>4</v>
-      </c>
-      <c r="H483" t="n">
-        <v>6</v>
-      </c>
-      <c r="I483" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="J483" t="n">
-        <v>3</v>
-      </c>
-      <c r="K483" t="n">
-        <v>138.89</v>
-      </c>
-      <c r="L483" t="n">
-        <v>200</v>
-      </c>
-      <c r="M483" t="n">
-        <v>-61.11</v>
-      </c>
-      <c r="N483" t="n">
-        <v>2</v>
-      </c>
-      <c r="O483" t="n">
-        <v>2</v>
-      </c>
-      <c r="P483" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q483" t="n">
-        <v>0</v>
-      </c>
-      <c r="R483" t="n">
-        <v>4</v>
-      </c>
-      <c r="S483" t="n">
-        <v>0</v>
-      </c>
-      <c r="T483" t="n">
-        <v>0</v>
-      </c>
-      <c r="U483" t="n">
-        <v>1</v>
-      </c>
-      <c r="V483" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="W483" t="n">
-        <v>26</v>
-      </c>
-      <c r="X483" t="inlineStr">
-        <is>
-          <t>ADC BOADILLA vs C.B. TRES CANTOS</t>
-        </is>
-      </c>
-    </row>
-    <row r="484">
-      <c r="A484" t="inlineStr">
-        <is>
-          <t>2487754</t>
-        </is>
-      </c>
-      <c r="B484" t="inlineStr">
-        <is>
-          <t>ADC BOADILLA</t>
-        </is>
-      </c>
-      <c r="C484" t="inlineStr">
-        <is>
-          <t>A. OLMEDO VELASCO | C. CUESTA DE SANTOS | E. BOADA MONTESDEOCA | I. BLANCO-ARGIBAY GONZALEZ | J. VILASANCHEZ FREIJOMIL</t>
-        </is>
-      </c>
-      <c r="D484" t="n">
-        <v>5</v>
-      </c>
-      <c r="E484" t="n">
-        <v>41</v>
-      </c>
-      <c r="F484" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="G484" t="n">
-        <v>0</v>
-      </c>
-      <c r="H484" t="n">
-        <v>0</v>
-      </c>
-      <c r="I484" t="n">
-        <v>2</v>
-      </c>
-      <c r="J484" t="n">
-        <v>0</v>
-      </c>
-      <c r="K484" t="n">
-        <v>0</v>
-      </c>
-      <c r="L484" t="n">
-        <v>0</v>
-      </c>
-      <c r="M484" t="n">
-        <v>0</v>
-      </c>
-      <c r="N484" t="n">
-        <v>1</v>
-      </c>
-      <c r="O484" t="n">
-        <v>0</v>
-      </c>
-      <c r="P484" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q484" t="n">
-        <v>0</v>
-      </c>
-      <c r="R484" t="n">
-        <v>0</v>
-      </c>
-      <c r="S484" t="n">
-        <v>0</v>
-      </c>
-      <c r="T484" t="n">
-        <v>0</v>
-      </c>
-      <c r="U484" t="n">
-        <v>0</v>
-      </c>
-      <c r="V484" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="W484" t="n">
-        <v>26</v>
-      </c>
-      <c r="X484" t="inlineStr">
-        <is>
-          <t>ADC BOADILLA vs C.B. TRES CANTOS</t>
-        </is>
-      </c>
-    </row>
-    <row r="485">
-      <c r="A485" t="inlineStr">
-        <is>
-          <t>2487754</t>
-        </is>
-      </c>
-      <c r="B485" t="inlineStr">
-        <is>
-          <t>ADC BOADILLA</t>
-        </is>
-      </c>
-      <c r="C485" t="inlineStr">
-        <is>
-          <t>A. OLMEDO VELASCO | C. CUESTA DE SANTOS | I. BLANCO-ARGIBAY GONZALEZ | J. VILASANCHEZ FREIJOMIL | P. DOMINGUEZ LORENZO</t>
-        </is>
-      </c>
-      <c r="D485" t="n">
-        <v>5</v>
-      </c>
-      <c r="E485" t="n">
-        <v>106</v>
-      </c>
-      <c r="F485" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="G485" t="n">
-        <v>4</v>
-      </c>
-      <c r="H485" t="n">
-        <v>1</v>
-      </c>
-      <c r="I485" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="J485" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="K485" t="n">
-        <v>172.41</v>
-      </c>
-      <c r="L485" t="n">
-        <v>25.77</v>
-      </c>
-      <c r="M485" t="n">
-        <v>146.64</v>
-      </c>
-      <c r="N485" t="n">
-        <v>1</v>
-      </c>
-      <c r="O485" t="n">
-        <v>3</v>
-      </c>
-      <c r="P485" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q485" t="n">
-        <v>1</v>
-      </c>
-      <c r="R485" t="n">
-        <v>1</v>
-      </c>
-      <c r="S485" t="n">
-        <v>2</v>
-      </c>
-      <c r="T485" t="n">
-        <v>2</v>
-      </c>
-      <c r="U485" t="n">
-        <v>0</v>
-      </c>
-      <c r="V485" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="W485" t="n">
-        <v>26</v>
-      </c>
-      <c r="X485" t="inlineStr">
-        <is>
-          <t>ADC BOADILLA vs C.B. TRES CANTOS</t>
-        </is>
-      </c>
-    </row>
-    <row r="486">
-      <c r="A486" t="inlineStr">
-        <is>
-          <t>2487754</t>
-        </is>
-      </c>
-      <c r="B486" t="inlineStr">
-        <is>
-          <t>C.B. TRES CANTOS</t>
-        </is>
-      </c>
-      <c r="C486" t="inlineStr">
-        <is>
-          <t>A. SIMON DEL CORRAL | D. FERNANDEZ CAÑAS | G. LARDIES GUILLEN | H. PEREZ SANCHEZ | J. ATIENZA PEREA</t>
-        </is>
-      </c>
-      <c r="D486" t="n">
-        <v>5</v>
-      </c>
-      <c r="E486" t="n">
-        <v>33</v>
-      </c>
-      <c r="F486" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="G486" t="n">
-        <v>2</v>
-      </c>
-      <c r="H486" t="n">
-        <v>2</v>
-      </c>
-      <c r="I486" t="n">
-        <v>1</v>
-      </c>
-      <c r="J486" t="n">
-        <v>1</v>
-      </c>
-      <c r="K486" t="n">
-        <v>200</v>
-      </c>
-      <c r="L486" t="n">
-        <v>200</v>
-      </c>
-      <c r="M486" t="n">
-        <v>0</v>
-      </c>
-      <c r="N486" t="n">
-        <v>2</v>
-      </c>
-      <c r="O486" t="n">
-        <v>0</v>
-      </c>
-      <c r="P486" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q486" t="n">
-        <v>1</v>
-      </c>
-      <c r="R486" t="n">
-        <v>1</v>
-      </c>
-      <c r="S486" t="n">
-        <v>0</v>
-      </c>
-      <c r="T486" t="n">
-        <v>0</v>
-      </c>
-      <c r="U486" t="n">
-        <v>0</v>
-      </c>
-      <c r="V486" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="W486" t="n">
-        <v>26</v>
-      </c>
-      <c r="X486" t="inlineStr">
-        <is>
-          <t>ADC BOADILLA vs C.B. TRES CANTOS</t>
-        </is>
-      </c>
-    </row>
-    <row r="487">
-      <c r="A487" t="inlineStr">
-        <is>
-          <t>2487754</t>
-        </is>
-      </c>
-      <c r="B487" t="inlineStr">
-        <is>
-          <t>C.B. TRES CANTOS</t>
-        </is>
-      </c>
-      <c r="C487" t="inlineStr">
-        <is>
-          <t>D. FERNANDEZ CAÑAS | G. DIAZ MONTERO | G. LARDIES GUILLEN | J. ATIENZA PEREA | J. DE DOMINGO GARAY</t>
-        </is>
-      </c>
-      <c r="D487" t="n">
-        <v>5</v>
-      </c>
-      <c r="E487" t="n">
-        <v>60</v>
-      </c>
-      <c r="F487" t="n">
-        <v>1</v>
-      </c>
-      <c r="G487" t="n">
-        <v>4</v>
-      </c>
-      <c r="H487" t="n">
-        <v>2</v>
-      </c>
-      <c r="I487" t="n">
-        <v>2</v>
-      </c>
-      <c r="J487" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="K487" t="n">
-        <v>200</v>
-      </c>
-      <c r="L487" t="n">
-        <v>106.38</v>
-      </c>
-      <c r="M487" t="n">
-        <v>93.62</v>
-      </c>
-      <c r="N487" t="n">
-        <v>2</v>
-      </c>
-      <c r="O487" t="n">
-        <v>0</v>
-      </c>
-      <c r="P487" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q487" t="n">
-        <v>0</v>
-      </c>
-      <c r="R487" t="n">
-        <v>1</v>
-      </c>
-      <c r="S487" t="n">
-        <v>2</v>
-      </c>
-      <c r="T487" t="n">
-        <v>0</v>
-      </c>
-      <c r="U487" t="n">
-        <v>0</v>
-      </c>
-      <c r="V487" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="W487" t="n">
-        <v>26</v>
-      </c>
-      <c r="X487" t="inlineStr">
-        <is>
-          <t>ADC BOADILLA vs C.B. TRES CANTOS</t>
-        </is>
-      </c>
-    </row>
-    <row r="488">
-      <c r="A488" t="inlineStr">
-        <is>
-          <t>2487754</t>
-        </is>
-      </c>
-      <c r="B488" t="inlineStr">
-        <is>
-          <t>C.B. TRES CANTOS</t>
-        </is>
-      </c>
-      <c r="C488" t="inlineStr">
-        <is>
-          <t>D. FERNANDEZ CAÑAS | G. DIAZ MONTERO | J. ATIENZA PEREA | J. DE DOMINGO GARAY | N. MAIGA</t>
-        </is>
-      </c>
-      <c r="D488" t="n">
-        <v>5</v>
-      </c>
-      <c r="E488" t="n">
-        <v>80</v>
-      </c>
-      <c r="F488" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="G488" t="n">
-        <v>0</v>
-      </c>
-      <c r="H488" t="n">
-        <v>2</v>
-      </c>
-      <c r="I488" t="n">
-        <v>2</v>
-      </c>
-      <c r="J488" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="K488" t="n">
-        <v>0</v>
-      </c>
-      <c r="L488" t="n">
-        <v>227.27</v>
-      </c>
-      <c r="M488" t="n">
-        <v>-227.27</v>
-      </c>
-      <c r="N488" t="n">
-        <v>1</v>
-      </c>
-      <c r="O488" t="n">
-        <v>0</v>
-      </c>
-      <c r="P488" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q488" t="n">
-        <v>0</v>
-      </c>
-      <c r="R488" t="n">
-        <v>0</v>
-      </c>
-      <c r="S488" t="n">
-        <v>2</v>
-      </c>
-      <c r="T488" t="n">
-        <v>1</v>
-      </c>
-      <c r="U488" t="n">
-        <v>1</v>
-      </c>
-      <c r="V488" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="W488" t="n">
-        <v>26</v>
-      </c>
-      <c r="X488" t="inlineStr">
-        <is>
-          <t>ADC BOADILLA vs C.B. TRES CANTOS</t>
-        </is>
-      </c>
-    </row>
-    <row r="489">
-      <c r="A489" t="inlineStr">
-        <is>
-          <t>2487754</t>
-        </is>
-      </c>
-      <c r="B489" t="inlineStr">
-        <is>
-          <t>C.B. TRES CANTOS</t>
-        </is>
-      </c>
-      <c r="C489" t="inlineStr">
-        <is>
-          <t>G. DIAZ MONTERO | G. LARDIES GUILLEN | J. ATIENZA PEREA | J. DE DOMINGO GARAY | N. MAIGA</t>
-        </is>
-      </c>
-      <c r="D489" t="n">
-        <v>5</v>
-      </c>
-      <c r="E489" t="n">
-        <v>67</v>
-      </c>
-      <c r="F489" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="G489" t="n">
-        <v>1</v>
-      </c>
-      <c r="H489" t="n">
-        <v>2</v>
-      </c>
-      <c r="I489" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="J489" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="K489" t="n">
-        <v>53.19</v>
-      </c>
-      <c r="L489" t="n">
-        <v>58.14</v>
-      </c>
-      <c r="M489" t="n">
-        <v>-4.95</v>
-      </c>
-      <c r="N489" t="n">
-        <v>0</v>
-      </c>
-      <c r="O489" t="n">
-        <v>2</v>
-      </c>
-      <c r="P489" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q489" t="n">
-        <v>0</v>
-      </c>
-      <c r="R489" t="n">
-        <v>2</v>
-      </c>
-      <c r="S489" t="n">
-        <v>1</v>
-      </c>
-      <c r="T489" t="n">
-        <v>1</v>
-      </c>
-      <c r="U489" t="n">
-        <v>0</v>
-      </c>
-      <c r="V489" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="W489" t="n">
-        <v>26</v>
-      </c>
-      <c r="X489" t="inlineStr">
-        <is>
-          <t>ADC BOADILLA vs C.B. TRES CANTOS</t>
-        </is>
-      </c>
-    </row>
-    <row r="490">
-      <c r="A490" t="inlineStr">
-        <is>
-          <t>2487756</t>
-        </is>
-      </c>
-      <c r="B490" t="inlineStr">
-        <is>
-          <t>GRUPO EGIDO PINTOBASKET</t>
-        </is>
-      </c>
-      <c r="C490" t="inlineStr">
-        <is>
-          <t>J. AYALA AYLLÓN | J. SAEZ BENITO | L. BERMEJO ALCALDE | M. ALARCON ORTIZ | M. BATLLE BERNARDO</t>
-        </is>
-      </c>
-      <c r="D490" t="n">
-        <v>5</v>
-      </c>
-      <c r="E490" t="n">
-        <v>51</v>
-      </c>
-      <c r="F490" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="G490" t="n">
-        <v>2</v>
-      </c>
-      <c r="H490" t="n">
-        <v>0</v>
-      </c>
-      <c r="I490" t="n">
-        <v>0</v>
-      </c>
-      <c r="J490" t="n">
-        <v>2</v>
-      </c>
-      <c r="K490" t="n">
-        <v>0</v>
-      </c>
-      <c r="L490" t="n">
-        <v>0</v>
-      </c>
-      <c r="M490" t="n">
-        <v>0</v>
-      </c>
-      <c r="N490" t="n">
-        <v>1</v>
-      </c>
-      <c r="O490" t="n">
-        <v>0</v>
-      </c>
-      <c r="P490" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q490" t="n">
-        <v>1</v>
-      </c>
-      <c r="R490" t="n">
-        <v>1</v>
-      </c>
-      <c r="S490" t="n">
-        <v>0</v>
-      </c>
-      <c r="T490" t="n">
-        <v>1</v>
-      </c>
-      <c r="U490" t="n">
-        <v>0</v>
-      </c>
-      <c r="V490" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="W490" t="n">
-        <v>26</v>
-      </c>
-      <c r="X490" t="inlineStr">
-        <is>
-          <t>REAL CANOE N.C. vs GRUPO EGIDO PINTOBASKET</t>
-        </is>
-      </c>
-    </row>
-    <row r="491">
-      <c r="A491" t="inlineStr">
-        <is>
-          <t>2487756</t>
-        </is>
-      </c>
-      <c r="B491" t="inlineStr">
-        <is>
-          <t>GRUPO EGIDO PINTOBASKET</t>
-        </is>
-      </c>
-      <c r="C491" t="inlineStr">
-        <is>
-          <t>J. AYALA AYLLÓN | J. SAEZ BENITO | L. BERMEJO ALCALDE | M. BATLLE BERNARDO | S. RODRIGUEZ GREGORIO</t>
-        </is>
-      </c>
-      <c r="D491" t="n">
-        <v>5</v>
-      </c>
-      <c r="E491" t="n">
-        <v>121</v>
-      </c>
-      <c r="F491" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="G491" t="n">
-        <v>2</v>
-      </c>
-      <c r="H491" t="n">
-        <v>5</v>
-      </c>
-      <c r="I491" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="J491" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="K491" t="n">
-        <v>53.19</v>
-      </c>
-      <c r="L491" t="n">
-        <v>215.52</v>
-      </c>
-      <c r="M491" t="n">
-        <v>-162.33</v>
-      </c>
-      <c r="N491" t="n">
-        <v>2</v>
-      </c>
-      <c r="O491" t="n">
-        <v>4</v>
-      </c>
-      <c r="P491" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q491" t="n">
-        <v>1</v>
-      </c>
-      <c r="R491" t="n">
-        <v>3</v>
-      </c>
-      <c r="S491" t="n">
-        <v>3</v>
-      </c>
-      <c r="T491" t="n">
-        <v>0</v>
-      </c>
-      <c r="U491" t="n">
-        <v>2</v>
-      </c>
-      <c r="V491" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="W491" t="n">
-        <v>26</v>
-      </c>
-      <c r="X491" t="inlineStr">
-        <is>
-          <t>REAL CANOE N.C. vs GRUPO EGIDO PINTOBASKET</t>
-        </is>
-      </c>
-    </row>
-    <row r="492">
-      <c r="A492" t="inlineStr">
-        <is>
-          <t>2487756</t>
-        </is>
-      </c>
-      <c r="B492" t="inlineStr">
-        <is>
-          <t>GRUPO EGIDO PINTOBASKET</t>
-        </is>
-      </c>
-      <c r="C492" t="inlineStr">
-        <is>
-          <t>J. AYALA AYLLÓN | J. SAEZ BENITO | M. ALARCON ORTIZ | M. BATLLE BERNARDO | M. DEL VALLE REGALADO</t>
-        </is>
-      </c>
-      <c r="D492" t="n">
-        <v>5</v>
-      </c>
-      <c r="E492" t="n">
-        <v>52</v>
-      </c>
-      <c r="F492" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="G492" t="n">
-        <v>2</v>
-      </c>
-      <c r="H492" t="n">
-        <v>2</v>
-      </c>
-      <c r="I492" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="J492" t="n">
-        <v>1</v>
-      </c>
-      <c r="K492" t="n">
-        <v>69.44</v>
-      </c>
-      <c r="L492" t="n">
-        <v>200</v>
-      </c>
-      <c r="M492" t="n">
-        <v>-130.56</v>
-      </c>
-      <c r="N492" t="n">
-        <v>1</v>
-      </c>
-      <c r="O492" t="n">
-        <v>2</v>
-      </c>
-      <c r="P492" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q492" t="n">
-        <v>0</v>
-      </c>
-      <c r="R492" t="n">
-        <v>1</v>
-      </c>
-      <c r="S492" t="n">
-        <v>0</v>
-      </c>
-      <c r="T492" t="n">
-        <v>1</v>
-      </c>
-      <c r="U492" t="n">
-        <v>1</v>
-      </c>
-      <c r="V492" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="W492" t="n">
-        <v>26</v>
-      </c>
-      <c r="X492" t="inlineStr">
-        <is>
-          <t>REAL CANOE N.C. vs GRUPO EGIDO PINTOBASKET</t>
-        </is>
-      </c>
-    </row>
-    <row r="493">
-      <c r="A493" t="inlineStr">
-        <is>
-          <t>2487756</t>
-        </is>
-      </c>
-      <c r="B493" t="inlineStr">
-        <is>
-          <t>GRUPO EGIDO PINTOBASKET</t>
-        </is>
-      </c>
-      <c r="C493" t="inlineStr">
-        <is>
-          <t>J. AYALA AYLLÓN | L. BERMEJO ALCALDE | M. ALARCON ORTIZ | M. BATLLE BERNARDO | S. RODRIGUEZ GREGORIO</t>
-        </is>
-      </c>
-      <c r="D493" t="n">
-        <v>5</v>
-      </c>
-      <c r="E493" t="n">
-        <v>64</v>
-      </c>
-      <c r="F493" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="G493" t="n">
-        <v>0</v>
-      </c>
-      <c r="H493" t="n">
-        <v>0</v>
-      </c>
-      <c r="I493" t="n">
-        <v>2</v>
-      </c>
-      <c r="J493" t="n">
-        <v>2</v>
-      </c>
-      <c r="K493" t="n">
-        <v>0</v>
-      </c>
-      <c r="L493" t="n">
-        <v>0</v>
-      </c>
-      <c r="M493" t="n">
-        <v>0</v>
-      </c>
-      <c r="N493" t="n">
-        <v>1</v>
-      </c>
-      <c r="O493" t="n">
-        <v>0</v>
-      </c>
-      <c r="P493" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q493" t="n">
-        <v>0</v>
-      </c>
-      <c r="R493" t="n">
-        <v>3</v>
-      </c>
-      <c r="S493" t="n">
-        <v>0</v>
-      </c>
-      <c r="T493" t="n">
-        <v>0</v>
-      </c>
-      <c r="U493" t="n">
-        <v>1</v>
-      </c>
-      <c r="V493" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="W493" t="n">
-        <v>26</v>
-      </c>
-      <c r="X493" t="inlineStr">
-        <is>
-          <t>REAL CANOE N.C. vs GRUPO EGIDO PINTOBASKET</t>
-        </is>
-      </c>
-    </row>
-    <row r="494">
-      <c r="A494" t="inlineStr">
-        <is>
-          <t>2487756</t>
-        </is>
-      </c>
-      <c r="B494" t="inlineStr">
-        <is>
-          <t>REAL CANOE N.C.</t>
-        </is>
-      </c>
-      <c r="C494" t="inlineStr">
-        <is>
-          <t>D. MANZANERO CAMACHO | J. GARCIA-LARRACHE SEGURA | J. LAPASTORA ARACIL | L. GARCIA LARRACHE SEGURA | M. KREISLER LORENTE</t>
-        </is>
-      </c>
-      <c r="D494" t="n">
-        <v>5</v>
-      </c>
-      <c r="E494" t="n">
-        <v>139</v>
-      </c>
-      <c r="F494" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="G494" t="n">
-        <v>5</v>
-      </c>
-      <c r="H494" t="n">
-        <v>2</v>
-      </c>
-      <c r="I494" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="J494" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="K494" t="n">
-        <v>150.6</v>
-      </c>
-      <c r="L494" t="n">
-        <v>53.19</v>
-      </c>
-      <c r="M494" t="n">
-        <v>97.41</v>
-      </c>
-      <c r="N494" t="n">
-        <v>4</v>
-      </c>
-      <c r="O494" t="n">
-        <v>3</v>
-      </c>
-      <c r="P494" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q494" t="n">
-        <v>2</v>
-      </c>
-      <c r="R494" t="n">
-        <v>2</v>
-      </c>
-      <c r="S494" t="n">
-        <v>4</v>
-      </c>
-      <c r="T494" t="n">
-        <v>1</v>
-      </c>
-      <c r="U494" t="n">
-        <v>1</v>
-      </c>
-      <c r="V494" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="W494" t="n">
-        <v>26</v>
-      </c>
-      <c r="X494" t="inlineStr">
-        <is>
-          <t>REAL CANOE N.C. vs GRUPO EGIDO PINTOBASKET</t>
-        </is>
-      </c>
-    </row>
-    <row r="495">
-      <c r="A495" t="inlineStr">
-        <is>
-          <t>2487756</t>
-        </is>
-      </c>
-      <c r="B495" t="inlineStr">
-        <is>
-          <t>REAL CANOE N.C.</t>
-        </is>
-      </c>
-      <c r="C495" t="inlineStr">
-        <is>
-          <t>D. MANZANERO CAMACHO | J. GARCIA-LARRACHE SEGURA | L. GARCIA LARRACHE SEGURA | M. HERMOSO ALCUBILLA | P. FUENTE DIEZ</t>
-        </is>
-      </c>
-      <c r="D495" t="n">
-        <v>5</v>
-      </c>
-      <c r="E495" t="n">
-        <v>52</v>
-      </c>
-      <c r="F495" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="G495" t="n">
-        <v>2</v>
-      </c>
-      <c r="H495" t="n">
-        <v>2</v>
-      </c>
-      <c r="I495" t="n">
-        <v>1</v>
-      </c>
-      <c r="J495" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="K495" t="n">
-        <v>200</v>
-      </c>
-      <c r="L495" t="n">
-        <v>69.44</v>
-      </c>
-      <c r="M495" t="n">
-        <v>130.56</v>
-      </c>
-      <c r="N495" t="n">
-        <v>1</v>
-      </c>
-      <c r="O495" t="n">
-        <v>0</v>
-      </c>
-      <c r="P495" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q495" t="n">
-        <v>1</v>
-      </c>
-      <c r="R495" t="n">
-        <v>1</v>
-      </c>
-      <c r="S495" t="n">
-        <v>2</v>
-      </c>
-      <c r="T495" t="n">
-        <v>1</v>
-      </c>
-      <c r="U495" t="n">
-        <v>0</v>
-      </c>
-      <c r="V495" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="W495" t="n">
-        <v>26</v>
-      </c>
-      <c r="X495" t="inlineStr">
-        <is>
-          <t>REAL CANOE N.C. vs GRUPO EGIDO PINTOBASKET</t>
-        </is>
-      </c>
-    </row>
-    <row r="496">
-      <c r="A496" t="inlineStr">
-        <is>
-          <t>2487756</t>
-        </is>
-      </c>
-      <c r="B496" t="inlineStr">
-        <is>
-          <t>REAL CANOE N.C.</t>
-        </is>
-      </c>
-      <c r="C496" t="inlineStr">
-        <is>
-          <t>D. MANZANERO CAMACHO | J. LAPASTORA ARACIL | L. GARCIA LARRACHE SEGURA | M. HERMOSO ALCUBILLA | P. FUENTE DIEZ</t>
-        </is>
-      </c>
-      <c r="D496" t="n">
-        <v>5</v>
-      </c>
-      <c r="E496" t="n">
-        <v>97</v>
-      </c>
-      <c r="F496" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="G496" t="n">
-        <v>0</v>
-      </c>
-      <c r="H496" t="n">
-        <v>2</v>
-      </c>
-      <c r="I496" t="n">
-        <v>3</v>
-      </c>
-      <c r="J496" t="n">
-        <v>2</v>
-      </c>
-      <c r="K496" t="n">
-        <v>0</v>
-      </c>
-      <c r="L496" t="n">
-        <v>100</v>
-      </c>
-      <c r="M496" t="n">
-        <v>-100</v>
-      </c>
-      <c r="N496" t="n">
-        <v>3</v>
-      </c>
-      <c r="O496" t="n">
-        <v>0</v>
-      </c>
-      <c r="P496" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q496" t="n">
-        <v>1</v>
-      </c>
-      <c r="R496" t="n">
-        <v>2</v>
-      </c>
-      <c r="S496" t="n">
-        <v>0</v>
-      </c>
-      <c r="T496" t="n">
-        <v>1</v>
-      </c>
-      <c r="U496" t="n">
-        <v>1</v>
-      </c>
-      <c r="V496" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="W496" t="n">
-        <v>26</v>
-      </c>
-      <c r="X496" t="inlineStr">
-        <is>
-          <t>REAL CANOE N.C. vs GRUPO EGIDO PINTOBASKET</t>
-        </is>
-      </c>
-    </row>
-    <row r="497">
-      <c r="A497" t="inlineStr">
-        <is>
-          <t>2487758</t>
-        </is>
-      </c>
-      <c r="B497" t="inlineStr">
-        <is>
-          <t>CB ARIDANE</t>
-        </is>
-      </c>
-      <c r="C497" t="inlineStr">
-        <is>
-          <t>A. GASE SECO | G. MEJÍA ACOSTA | G. PIERRE-GABRIEL ANDREA GASTON | J. ABRIL RAMIRO | O. BALSELLS PLAZA</t>
-        </is>
-      </c>
-      <c r="D497" t="n">
-        <v>5</v>
-      </c>
-      <c r="E497" t="n">
-        <v>82</v>
-      </c>
-      <c r="F497" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="G497" t="n">
-        <v>0</v>
-      </c>
-      <c r="H497" t="n">
-        <v>2</v>
-      </c>
-      <c r="I497" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="J497" t="n">
-        <v>3</v>
-      </c>
-      <c r="K497" t="n">
-        <v>0</v>
-      </c>
-      <c r="L497" t="n">
-        <v>66.67</v>
-      </c>
-      <c r="M497" t="n">
-        <v>-66.67</v>
-      </c>
-      <c r="N497" t="n">
-        <v>0</v>
-      </c>
-      <c r="O497" t="n">
-        <v>2</v>
-      </c>
-      <c r="P497" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q497" t="n">
-        <v>0</v>
-      </c>
-      <c r="R497" t="n">
-        <v>5</v>
-      </c>
-      <c r="S497" t="n">
-        <v>0</v>
-      </c>
-      <c r="T497" t="n">
-        <v>0</v>
-      </c>
-      <c r="U497" t="n">
-        <v>2</v>
-      </c>
-      <c r="V497" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="W497" t="n">
-        <v>26</v>
-      </c>
-      <c r="X497" t="inlineStr">
-        <is>
-          <t>CB ARIDANE vs UROS DE RIVAS</t>
-        </is>
-      </c>
-    </row>
-    <row r="498">
-      <c r="A498" t="inlineStr">
-        <is>
-          <t>2487758</t>
-        </is>
-      </c>
-      <c r="B498" t="inlineStr">
-        <is>
-          <t>CB ARIDANE</t>
-        </is>
-      </c>
-      <c r="C498" t="inlineStr">
-        <is>
-          <t>A. GASE SECO | G. MEJÍA ACOSTA | G. PIERRE-GABRIEL ANDREA GASTON | J. GONZÁLEZ CHÁVEZ | K. SKUTYELNIK</t>
-        </is>
-      </c>
-      <c r="D498" t="n">
-        <v>5</v>
-      </c>
-      <c r="E498" t="n">
-        <v>3</v>
-      </c>
-      <c r="F498" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="G498" t="n">
-        <v>2</v>
-      </c>
-      <c r="H498" t="n">
-        <v>0</v>
-      </c>
-      <c r="I498" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="J498" t="n">
-        <v>0</v>
-      </c>
-      <c r="K498" t="n">
-        <v>227.27</v>
-      </c>
-      <c r="L498" t="n">
-        <v>0</v>
-      </c>
-      <c r="M498" t="n">
-        <v>0</v>
-      </c>
-      <c r="N498" t="n">
-        <v>0</v>
-      </c>
-      <c r="O498" t="n">
-        <v>2</v>
-      </c>
-      <c r="P498" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q498" t="n">
-        <v>0</v>
-      </c>
-      <c r="R498" t="n">
-        <v>0</v>
-      </c>
-      <c r="S498" t="n">
-        <v>0</v>
-      </c>
-      <c r="T498" t="n">
-        <v>0</v>
-      </c>
-      <c r="U498" t="n">
-        <v>0</v>
-      </c>
-      <c r="V498" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="W498" t="n">
-        <v>26</v>
-      </c>
-      <c r="X498" t="inlineStr">
-        <is>
-          <t>CB ARIDANE vs UROS DE RIVAS</t>
-        </is>
-      </c>
-    </row>
-    <row r="499">
-      <c r="A499" t="inlineStr">
-        <is>
-          <t>2487758</t>
-        </is>
-      </c>
-      <c r="B499" t="inlineStr">
-        <is>
-          <t>CB ARIDANE</t>
-        </is>
-      </c>
-      <c r="C499" t="inlineStr">
-        <is>
-          <t>A. GASE SECO | G. MEJÍA ACOSTA | G. PIERRE-GABRIEL ANDREA GASTON | J. GONZÁLEZ CHÁVEZ | O. BALSELLS PLAZA</t>
-        </is>
-      </c>
-      <c r="D499" t="n">
-        <v>5</v>
-      </c>
-      <c r="E499" t="n">
-        <v>180</v>
-      </c>
-      <c r="F499" t="n">
-        <v>3</v>
-      </c>
-      <c r="G499" t="n">
-        <v>7</v>
-      </c>
-      <c r="H499" t="n">
-        <v>0</v>
-      </c>
-      <c r="I499" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="J499" t="n">
-        <v>5</v>
-      </c>
-      <c r="K499" t="n">
-        <v>180.41</v>
-      </c>
-      <c r="L499" t="n">
-        <v>0</v>
-      </c>
-      <c r="M499" t="n">
-        <v>180.41</v>
-      </c>
-      <c r="N499" t="n">
-        <v>4</v>
-      </c>
-      <c r="O499" t="n">
-        <v>2</v>
-      </c>
-      <c r="P499" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q499" t="n">
-        <v>3</v>
-      </c>
-      <c r="R499" t="n">
-        <v>6</v>
-      </c>
-      <c r="S499" t="n">
-        <v>0</v>
-      </c>
-      <c r="T499" t="n">
-        <v>0</v>
-      </c>
-      <c r="U499" t="n">
-        <v>1</v>
-      </c>
-      <c r="V499" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="W499" t="n">
-        <v>26</v>
-      </c>
-      <c r="X499" t="inlineStr">
-        <is>
-          <t>CB ARIDANE vs UROS DE RIVAS</t>
-        </is>
-      </c>
-    </row>
-    <row r="500">
-      <c r="A500" t="inlineStr">
-        <is>
-          <t>2487758</t>
-        </is>
-      </c>
-      <c r="B500" t="inlineStr">
-        <is>
-          <t>CB ARIDANE</t>
-        </is>
-      </c>
-      <c r="C500" t="inlineStr">
-        <is>
-          <t>A. GASE SECO | G. MEJÍA ACOSTA | G. PIERRE-GABRIEL ANDREA GASTON | K. SKUTYELNIK | O. BALSELLS PLAZA</t>
-        </is>
-      </c>
-      <c r="D500" t="n">
-        <v>5</v>
-      </c>
-      <c r="E500" t="n">
-        <v>8</v>
-      </c>
-      <c r="F500" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="G500" t="n">
-        <v>2</v>
-      </c>
-      <c r="H500" t="n">
-        <v>4</v>
-      </c>
-      <c r="I500" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="J500" t="n">
-        <v>2</v>
-      </c>
-      <c r="K500" t="n">
-        <v>227.27</v>
-      </c>
-      <c r="L500" t="n">
-        <v>200</v>
-      </c>
-      <c r="M500" t="n">
-        <v>27.27</v>
-      </c>
-      <c r="N500" t="n">
-        <v>0</v>
-      </c>
-      <c r="O500" t="n">
-        <v>2</v>
-      </c>
-      <c r="P500" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q500" t="n">
-        <v>0</v>
-      </c>
-      <c r="R500" t="n">
-        <v>2</v>
-      </c>
-      <c r="S500" t="n">
-        <v>0</v>
-      </c>
-      <c r="T500" t="n">
-        <v>0</v>
-      </c>
-      <c r="U500" t="n">
-        <v>0</v>
-      </c>
-      <c r="V500" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="W500" t="n">
-        <v>26</v>
-      </c>
-      <c r="X500" t="inlineStr">
-        <is>
-          <t>CB ARIDANE vs UROS DE RIVAS</t>
-        </is>
-      </c>
-    </row>
-    <row r="501">
-      <c r="A501" t="inlineStr">
-        <is>
-          <t>2487758</t>
-        </is>
-      </c>
-      <c r="B501" t="inlineStr">
-        <is>
-          <t>CB ARIDANE</t>
-        </is>
-      </c>
-      <c r="C501" t="inlineStr">
-        <is>
-          <t>A. GASE SECO | G. MEJÍA ACOSTA | J. GONZÁLEZ CHÁVEZ | O. BALSELLS PLAZA | S. GUEYE</t>
-        </is>
-      </c>
-      <c r="D501" t="n">
-        <v>5</v>
-      </c>
-      <c r="E501" t="n">
-        <v>19</v>
-      </c>
-      <c r="F501" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="G501" t="n">
-        <v>1</v>
-      </c>
-      <c r="H501" t="n">
-        <v>0</v>
-      </c>
-      <c r="I501" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="J501" t="n">
-        <v>0</v>
-      </c>
-      <c r="K501" t="n">
-        <v>113.64</v>
-      </c>
-      <c r="L501" t="n">
-        <v>0</v>
-      </c>
-      <c r="M501" t="n">
-        <v>0</v>
-      </c>
-      <c r="N501" t="n">
-        <v>1</v>
-      </c>
-      <c r="O501" t="n">
-        <v>2</v>
-      </c>
-      <c r="P501" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q501" t="n">
-        <v>1</v>
-      </c>
-      <c r="R501" t="n">
-        <v>0</v>
-      </c>
-      <c r="S501" t="n">
-        <v>0</v>
-      </c>
-      <c r="T501" t="n">
-        <v>0</v>
-      </c>
-      <c r="U501" t="n">
-        <v>0</v>
-      </c>
-      <c r="V501" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="W501" t="n">
-        <v>26</v>
-      </c>
-      <c r="X501" t="inlineStr">
-        <is>
-          <t>CB ARIDANE vs UROS DE RIVAS</t>
-        </is>
-      </c>
-    </row>
-    <row r="502">
-      <c r="A502" t="inlineStr">
-        <is>
-          <t>2487758</t>
-        </is>
-      </c>
-      <c r="B502" t="inlineStr">
-        <is>
-          <t>UROS DE RIVAS</t>
-        </is>
-      </c>
-      <c r="C502" t="inlineStr">
-        <is>
-          <t>A. BIERSACK LOPEZ | A. GARCIA QUILEZ CUERVAS | A. PEREZ CONTI | O. MENDEZ BLANCO | P. ESTEBANEZ GONZALEZ</t>
-        </is>
-      </c>
-      <c r="D502" t="n">
-        <v>5</v>
-      </c>
-      <c r="E502" t="n">
-        <v>151</v>
-      </c>
-      <c r="F502" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="G502" t="n">
-        <v>0</v>
-      </c>
-      <c r="H502" t="n">
-        <v>3</v>
-      </c>
-      <c r="I502" t="n">
-        <v>4</v>
-      </c>
-      <c r="J502" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="K502" t="n">
-        <v>0</v>
-      </c>
-      <c r="L502" t="n">
-        <v>77.31999999999999</v>
-      </c>
-      <c r="M502" t="n">
-        <v>-77.31999999999999</v>
-      </c>
-      <c r="N502" t="n">
-        <v>7</v>
-      </c>
-      <c r="O502" t="n">
-        <v>0</v>
-      </c>
-      <c r="P502" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q502" t="n">
-        <v>3</v>
-      </c>
-      <c r="R502" t="n">
-        <v>3</v>
-      </c>
-      <c r="S502" t="n">
-        <v>2</v>
-      </c>
-      <c r="T502" t="n">
-        <v>1</v>
-      </c>
-      <c r="U502" t="n">
-        <v>1</v>
-      </c>
-      <c r="V502" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="W502" t="n">
-        <v>26</v>
-      </c>
-      <c r="X502" t="inlineStr">
-        <is>
-          <t>CB ARIDANE vs UROS DE RIVAS</t>
-        </is>
-      </c>
-    </row>
-    <row r="503">
-      <c r="A503" t="inlineStr">
-        <is>
-          <t>2487758</t>
-        </is>
-      </c>
-      <c r="B503" t="inlineStr">
-        <is>
-          <t>UROS DE RIVAS</t>
-        </is>
-      </c>
-      <c r="C503" t="inlineStr">
-        <is>
-          <t>A. BIERSACK LOPEZ | C. CRESPO MONTESINOS | D. MARINEZ FERNANDEZ-URRUTIA | G. MARTIN LOPEZ-LAGO | O. HADI ADEGBITE</t>
-        </is>
-      </c>
-      <c r="D503" t="n">
-        <v>5</v>
-      </c>
-      <c r="E503" t="n">
-        <v>66</v>
-      </c>
-      <c r="F503" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="G503" t="n">
-        <v>0</v>
-      </c>
-      <c r="H503" t="n">
-        <v>3</v>
-      </c>
-      <c r="I503" t="n">
-        <v>2</v>
-      </c>
-      <c r="J503" t="n">
-        <v>1</v>
-      </c>
-      <c r="K503" t="n">
-        <v>0</v>
-      </c>
-      <c r="L503" t="n">
-        <v>300</v>
-      </c>
-      <c r="M503" t="n">
-        <v>-300</v>
-      </c>
-      <c r="N503" t="n">
-        <v>2</v>
-      </c>
-      <c r="O503" t="n">
-        <v>0</v>
-      </c>
-      <c r="P503" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q503" t="n">
-        <v>0</v>
-      </c>
-      <c r="R503" t="n">
-        <v>2</v>
-      </c>
-      <c r="S503" t="n">
-        <v>0</v>
-      </c>
-      <c r="T503" t="n">
-        <v>0</v>
-      </c>
-      <c r="U503" t="n">
-        <v>1</v>
-      </c>
-      <c r="V503" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="W503" t="n">
-        <v>26</v>
-      </c>
-      <c r="X503" t="inlineStr">
-        <is>
-          <t>CB ARIDANE vs UROS DE RIVAS</t>
-        </is>
-      </c>
-    </row>
-    <row r="504">
-      <c r="A504" t="inlineStr">
-        <is>
-          <t>2487758</t>
-        </is>
-      </c>
-      <c r="B504" t="inlineStr">
-        <is>
-          <t>UROS DE RIVAS</t>
-        </is>
-      </c>
-      <c r="C504" t="inlineStr">
-        <is>
-          <t>A. BIERSACK LOPEZ | C. CRESPO MONTESINOS | D. MARINEZ FERNANDEZ-URRUTIA | G. MARTIN LOPEZ-LAGO | O. MENDEZ BLANCO</t>
-        </is>
-      </c>
-      <c r="D504" t="n">
-        <v>5</v>
-      </c>
-      <c r="E504" t="n">
-        <v>41</v>
-      </c>
-      <c r="F504" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="G504" t="n">
-        <v>0</v>
-      </c>
-      <c r="H504" t="n">
-        <v>1</v>
-      </c>
-      <c r="I504" t="n">
-        <v>1</v>
-      </c>
-      <c r="J504" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="K504" t="n">
-        <v>0</v>
-      </c>
-      <c r="L504" t="n">
-        <v>113.64</v>
-      </c>
-      <c r="M504" t="n">
-        <v>-113.64</v>
-      </c>
-      <c r="N504" t="n">
-        <v>1</v>
-      </c>
-      <c r="O504" t="n">
-        <v>0</v>
-      </c>
-      <c r="P504" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q504" t="n">
-        <v>0</v>
-      </c>
-      <c r="R504" t="n">
-        <v>0</v>
-      </c>
-      <c r="S504" t="n">
-        <v>2</v>
-      </c>
-      <c r="T504" t="n">
-        <v>1</v>
-      </c>
-      <c r="U504" t="n">
-        <v>1</v>
-      </c>
-      <c r="V504" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="W504" t="n">
-        <v>26</v>
-      </c>
-      <c r="X504" t="inlineStr">
-        <is>
-          <t>CB ARIDANE vs UROS DE RIVAS</t>
-        </is>
-      </c>
-    </row>
-    <row r="505">
-      <c r="A505" t="inlineStr">
-        <is>
-          <t>2487758</t>
-        </is>
-      </c>
-      <c r="B505" t="inlineStr">
-        <is>
-          <t>UROS DE RIVAS</t>
-        </is>
-      </c>
-      <c r="C505" t="inlineStr">
-        <is>
-          <t>A. BIERSACK LOPEZ | C. CRESPO MONTESINOS | D. MARINEZ FERNANDEZ-URRUTIA | O. HADI ADEGBITE | O. MENDEZ BLANCO</t>
-        </is>
-      </c>
-      <c r="D505" t="n">
-        <v>5</v>
-      </c>
-      <c r="E505" t="n">
-        <v>1</v>
-      </c>
-      <c r="F505" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="G505" t="n">
-        <v>0</v>
-      </c>
-      <c r="H505" t="n">
-        <v>1</v>
-      </c>
-      <c r="I505" t="n">
-        <v>0</v>
-      </c>
-      <c r="J505" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="K505" t="n">
-        <v>0</v>
-      </c>
-      <c r="L505" t="n">
-        <v>0</v>
-      </c>
-      <c r="M505" t="n">
-        <v>0</v>
-      </c>
-      <c r="N505" t="n">
-        <v>0</v>
-      </c>
-      <c r="O505" t="n">
-        <v>0</v>
-      </c>
-      <c r="P505" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q505" t="n">
-        <v>0</v>
-      </c>
-      <c r="R505" t="n">
-        <v>0</v>
-      </c>
-      <c r="S505" t="n">
-        <v>2</v>
-      </c>
-      <c r="T505" t="n">
-        <v>0</v>
-      </c>
-      <c r="U505" t="n">
-        <v>1</v>
-      </c>
-      <c r="V505" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="W505" t="n">
-        <v>26</v>
-      </c>
-      <c r="X505" t="inlineStr">
-        <is>
-          <t>CB ARIDANE vs UROS DE RIVAS</t>
-        </is>
-      </c>
-    </row>
-    <row r="506">
-      <c r="A506" t="inlineStr">
-        <is>
-          <t>2487758</t>
-        </is>
-      </c>
-      <c r="B506" t="inlineStr">
-        <is>
-          <t>UROS DE RIVAS</t>
-        </is>
-      </c>
-      <c r="C506" t="inlineStr">
-        <is>
-          <t>A. GARCIA QUILEZ CUERVAS | A. PEREZ CONTI | O. HADI ADEGBITE | O. MENDEZ BLANCO | P. ESTEBANEZ GONZALEZ</t>
-        </is>
-      </c>
-      <c r="D506" t="n">
-        <v>5</v>
-      </c>
-      <c r="E506" t="n">
-        <v>22</v>
-      </c>
-      <c r="F506" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="G506" t="n">
-        <v>2</v>
-      </c>
-      <c r="H506" t="n">
-        <v>0</v>
-      </c>
-      <c r="I506" t="n">
-        <v>1</v>
-      </c>
-      <c r="J506" t="n">
-        <v>1</v>
-      </c>
-      <c r="K506" t="n">
-        <v>200</v>
-      </c>
-      <c r="L506" t="n">
-        <v>0</v>
-      </c>
-      <c r="M506" t="n">
-        <v>200</v>
-      </c>
-      <c r="N506" t="n">
-        <v>1</v>
-      </c>
-      <c r="O506" t="n">
-        <v>0</v>
-      </c>
-      <c r="P506" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q506" t="n">
-        <v>0</v>
-      </c>
-      <c r="R506" t="n">
-        <v>0</v>
-      </c>
-      <c r="S506" t="n">
-        <v>0</v>
-      </c>
-      <c r="T506" t="n">
-        <v>1</v>
-      </c>
-      <c r="U506" t="n">
-        <v>0</v>
-      </c>
-      <c r="V506" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="W506" t="n">
-        <v>26</v>
-      </c>
-      <c r="X506" t="inlineStr">
-        <is>
-          <t>CB ARIDANE vs UROS DE RIVAS</t>
-        </is>
-      </c>
-    </row>
-    <row r="507">
-      <c r="A507" t="inlineStr">
-        <is>
-          <t>2487758</t>
-        </is>
-      </c>
-      <c r="B507" t="inlineStr">
-        <is>
-          <t>UROS DE RIVAS</t>
-        </is>
-      </c>
-      <c r="C507" t="inlineStr">
-        <is>
-          <t>A. PEREZ CONTI | C. CRESPO MONTESINOS | G. MARTIN LOPEZ-LAGO | O. MENDEZ BLANCO | P. ESTEBANEZ GONZALEZ</t>
-        </is>
-      </c>
-      <c r="D507" t="n">
-        <v>5</v>
-      </c>
-      <c r="E507" t="n">
-        <v>6</v>
-      </c>
-      <c r="F507" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G507" t="n">
-        <v>2</v>
-      </c>
-      <c r="H507" t="n">
-        <v>2</v>
-      </c>
-      <c r="I507" t="n">
-        <v>1</v>
-      </c>
-      <c r="J507" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="K507" t="n">
-        <v>200</v>
-      </c>
-      <c r="L507" t="n">
-        <v>227.27</v>
-      </c>
-      <c r="M507" t="n">
-        <v>-27.27</v>
-      </c>
-      <c r="N507" t="n">
-        <v>1</v>
-      </c>
-      <c r="O507" t="n">
-        <v>0</v>
-      </c>
-      <c r="P507" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q507" t="n">
-        <v>0</v>
-      </c>
-      <c r="R507" t="n">
-        <v>0</v>
-      </c>
-      <c r="S507" t="n">
-        <v>2</v>
-      </c>
-      <c r="T507" t="n">
-        <v>0</v>
-      </c>
-      <c r="U507" t="n">
-        <v>0</v>
-      </c>
-      <c r="V507" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="W507" t="n">
-        <v>26</v>
-      </c>
-      <c r="X507" t="inlineStr">
-        <is>
-          <t>CB ARIDANE vs UROS DE RIVAS</t>
-        </is>
-      </c>
-    </row>
-    <row r="508">
-      <c r="A508" t="inlineStr">
-        <is>
-          <t>2487758</t>
-        </is>
-      </c>
-      <c r="B508" t="inlineStr">
-        <is>
-          <t>UROS DE RIVAS</t>
-        </is>
-      </c>
-      <c r="C508" t="inlineStr">
-        <is>
-          <t>C. CRESPO MONTESINOS | D. MARINEZ FERNANDEZ-URRUTIA | G. MARTIN LOPEZ-LAGO | O. MENDEZ BLANCO | P. ESTEBANEZ GONZALEZ</t>
-        </is>
-      </c>
-      <c r="D508" t="n">
-        <v>5</v>
-      </c>
-      <c r="E508" t="n">
-        <v>5</v>
-      </c>
-      <c r="F508" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="G508" t="n">
-        <v>2</v>
-      </c>
-      <c r="H508" t="n">
-        <v>2</v>
-      </c>
-      <c r="I508" t="n">
-        <v>1</v>
-      </c>
-      <c r="J508" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="K508" t="n">
-        <v>200</v>
-      </c>
-      <c r="L508" t="n">
-        <v>227.27</v>
-      </c>
-      <c r="M508" t="n">
-        <v>-27.27</v>
-      </c>
-      <c r="N508" t="n">
-        <v>1</v>
-      </c>
-      <c r="O508" t="n">
-        <v>0</v>
-      </c>
-      <c r="P508" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q508" t="n">
-        <v>0</v>
-      </c>
-      <c r="R508" t="n">
-        <v>0</v>
-      </c>
-      <c r="S508" t="n">
-        <v>2</v>
-      </c>
-      <c r="T508" t="n">
-        <v>0</v>
-      </c>
-      <c r="U508" t="n">
-        <v>0</v>
-      </c>
-      <c r="V508" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="W508" t="n">
-        <v>26</v>
-      </c>
-      <c r="X508" t="inlineStr">
-        <is>
-          <t>CB ARIDANE vs UROS DE RIVAS</t>
-        </is>
-      </c>
-    </row>
-    <row r="509">
-      <c r="A509" t="inlineStr">
-        <is>
-          <t>2487752</t>
-        </is>
-      </c>
-      <c r="B509" t="inlineStr">
-        <is>
-          <t>BALONCESTO TALAVERA</t>
-        </is>
-      </c>
-      <c r="C509" t="inlineStr">
-        <is>
-          <t>A. VICENTE VIANA | B. GUEYE | C. KLOTZ MAROTO | C. UNANUE CEGARRA | D. LORENZO NEGRETE</t>
-        </is>
-      </c>
-      <c r="D509" t="n">
-        <v>5</v>
-      </c>
-      <c r="E509" t="n">
-        <v>51</v>
-      </c>
-      <c r="F509" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="G509" t="n">
-        <v>3</v>
-      </c>
-      <c r="H509" t="n">
-        <v>2</v>
-      </c>
-      <c r="I509" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="J509" t="n">
-        <v>2</v>
-      </c>
-      <c r="K509" t="n">
-        <v>170.45</v>
-      </c>
-      <c r="L509" t="n">
-        <v>100</v>
-      </c>
-      <c r="M509" t="n">
-        <v>70.45</v>
-      </c>
-      <c r="N509" t="n">
-        <v>1</v>
-      </c>
-      <c r="O509" t="n">
-        <v>4</v>
-      </c>
-      <c r="P509" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q509" t="n">
-        <v>1</v>
-      </c>
-      <c r="R509" t="n">
-        <v>2</v>
-      </c>
-      <c r="S509" t="n">
-        <v>0</v>
-      </c>
-      <c r="T509" t="n">
-        <v>0</v>
-      </c>
-      <c r="U509" t="n">
-        <v>0</v>
-      </c>
-      <c r="V509" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="W509" t="n">
-        <v>26</v>
-      </c>
-      <c r="X509" t="inlineStr">
-        <is>
-          <t>EB FELIPE ANTÓN vs BALONCESTO TALAVERA</t>
-        </is>
-      </c>
-    </row>
-    <row r="510">
-      <c r="A510" t="inlineStr">
-        <is>
-          <t>2487752</t>
-        </is>
-      </c>
-      <c r="B510" t="inlineStr">
-        <is>
-          <t>BALONCESTO TALAVERA</t>
-        </is>
-      </c>
-      <c r="C510" t="inlineStr">
-        <is>
-          <t>A. VICENTE VIANA | B. GUEYE | C. KLOTZ MAROTO | D. LORENZO NEGRETE | S. GACIC</t>
-        </is>
-      </c>
-      <c r="D510" t="n">
-        <v>5</v>
-      </c>
-      <c r="E510" t="n">
-        <v>25</v>
-      </c>
-      <c r="F510" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="G510" t="n">
-        <v>0</v>
-      </c>
-      <c r="H510" t="n">
-        <v>2</v>
-      </c>
-      <c r="I510" t="n">
-        <v>1</v>
-      </c>
-      <c r="J510" t="n">
-        <v>2</v>
-      </c>
-      <c r="K510" t="n">
-        <v>0</v>
-      </c>
-      <c r="L510" t="n">
-        <v>100</v>
-      </c>
-      <c r="M510" t="n">
-        <v>-100</v>
-      </c>
-      <c r="N510" t="n">
-        <v>0</v>
-      </c>
-      <c r="O510" t="n">
-        <v>0</v>
-      </c>
-      <c r="P510" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q510" t="n">
-        <v>0</v>
-      </c>
-      <c r="R510" t="n">
-        <v>2</v>
-      </c>
-      <c r="S510" t="n">
-        <v>0</v>
-      </c>
-      <c r="T510" t="n">
-        <v>0</v>
-      </c>
-      <c r="U510" t="n">
-        <v>0</v>
-      </c>
-      <c r="V510" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="W510" t="n">
-        <v>26</v>
-      </c>
-      <c r="X510" t="inlineStr">
-        <is>
-          <t>EB FELIPE ANTÓN vs BALONCESTO TALAVERA</t>
-        </is>
-      </c>
-    </row>
-    <row r="511">
-      <c r="A511" t="inlineStr">
-        <is>
-          <t>2487752</t>
-        </is>
-      </c>
-      <c r="B511" t="inlineStr">
-        <is>
-          <t>BALONCESTO TALAVERA</t>
-        </is>
-      </c>
-      <c r="C511" t="inlineStr">
-        <is>
-          <t>A. VICENTE VIANA | B. GUEYE | D. LORENZO NEGRETE | S. GACIC | V. ALONSO PASCUAL</t>
-        </is>
-      </c>
-      <c r="D511" t="n">
-        <v>5</v>
-      </c>
-      <c r="E511" t="n">
-        <v>55</v>
-      </c>
-      <c r="F511" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="G511" t="n">
-        <v>1</v>
-      </c>
-      <c r="H511" t="n">
-        <v>2</v>
-      </c>
-      <c r="I511" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="J511" t="n">
-        <v>1</v>
-      </c>
-      <c r="K511" t="n">
-        <v>53.19</v>
-      </c>
-      <c r="L511" t="n">
-        <v>200</v>
-      </c>
-      <c r="M511" t="n">
-        <v>-146.81</v>
-      </c>
-      <c r="N511" t="n">
-        <v>1</v>
-      </c>
-      <c r="O511" t="n">
-        <v>2</v>
-      </c>
-      <c r="P511" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q511" t="n">
-        <v>0</v>
-      </c>
-      <c r="R511" t="n">
-        <v>1</v>
-      </c>
-      <c r="S511" t="n">
-        <v>0</v>
-      </c>
-      <c r="T511" t="n">
-        <v>0</v>
-      </c>
-      <c r="U511" t="n">
-        <v>0</v>
-      </c>
-      <c r="V511" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="W511" t="n">
-        <v>26</v>
-      </c>
-      <c r="X511" t="inlineStr">
-        <is>
-          <t>EB FELIPE ANTÓN vs BALONCESTO TALAVERA</t>
-        </is>
-      </c>
-    </row>
-    <row r="512">
-      <c r="A512" t="inlineStr">
-        <is>
-          <t>2487752</t>
-        </is>
-      </c>
-      <c r="B512" t="inlineStr">
-        <is>
-          <t>EB FELIPE ANTÓN</t>
-        </is>
-      </c>
-      <c r="C512" t="inlineStr">
-        <is>
-          <t>A. SISTAC RODRIGUEZ | B. FERNANDEZ SHEPHARD | J. GALLETTO LAMELA | K. RIVEROL DE LAS CASAS | S. MANERO GUZMAN</t>
-        </is>
-      </c>
-      <c r="D512" t="n">
-        <v>5</v>
-      </c>
-      <c r="E512" t="n">
-        <v>39</v>
-      </c>
-      <c r="F512" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="G512" t="n">
-        <v>2</v>
-      </c>
-      <c r="H512" t="n">
-        <v>1</v>
-      </c>
-      <c r="I512" t="n">
-        <v>1</v>
-      </c>
-      <c r="J512" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="K512" t="n">
-        <v>200</v>
-      </c>
-      <c r="L512" t="n">
-        <v>53.19</v>
-      </c>
-      <c r="M512" t="n">
-        <v>146.81</v>
-      </c>
-      <c r="N512" t="n">
-        <v>1</v>
-      </c>
-      <c r="O512" t="n">
-        <v>0</v>
-      </c>
-      <c r="P512" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q512" t="n">
-        <v>0</v>
-      </c>
-      <c r="R512" t="n">
-        <v>1</v>
-      </c>
-      <c r="S512" t="n">
-        <v>2</v>
-      </c>
-      <c r="T512" t="n">
-        <v>0</v>
-      </c>
-      <c r="U512" t="n">
-        <v>0</v>
-      </c>
-      <c r="V512" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="W512" t="n">
-        <v>26</v>
-      </c>
-      <c r="X512" t="inlineStr">
-        <is>
-          <t>EB FELIPE ANTÓN vs BALONCESTO TALAVERA</t>
-        </is>
-      </c>
-    </row>
-    <row r="513">
-      <c r="A513" t="inlineStr">
-        <is>
-          <t>2487752</t>
-        </is>
-      </c>
-      <c r="B513" t="inlineStr">
-        <is>
-          <t>EB FELIPE ANTÓN</t>
-        </is>
-      </c>
-      <c r="C513" t="inlineStr">
-        <is>
-          <t>A. SISTAC RODRIGUEZ | J. GALLETTO LAMELA | K. RIVEROL DE LAS CASAS | M. NIMAGA | S. MANERO GUZMAN</t>
-        </is>
-      </c>
-      <c r="D513" t="n">
-        <v>5</v>
-      </c>
-      <c r="E513" t="n">
-        <v>90</v>
-      </c>
-      <c r="F513" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="G513" t="n">
-        <v>4</v>
-      </c>
-      <c r="H513" t="n">
-        <v>3</v>
-      </c>
-      <c r="I513" t="n">
-        <v>3</v>
-      </c>
-      <c r="J513" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="K513" t="n">
-        <v>133.33</v>
-      </c>
-      <c r="L513" t="n">
-        <v>79.79000000000001</v>
-      </c>
-      <c r="M513" t="n">
-        <v>53.55</v>
-      </c>
-      <c r="N513" t="n">
-        <v>3</v>
-      </c>
-      <c r="O513" t="n">
-        <v>0</v>
-      </c>
-      <c r="P513" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q513" t="n">
-        <v>0</v>
-      </c>
-      <c r="R513" t="n">
-        <v>1</v>
-      </c>
-      <c r="S513" t="n">
-        <v>4</v>
-      </c>
-      <c r="T513" t="n">
-        <v>1</v>
-      </c>
-      <c r="U513" t="n">
-        <v>0</v>
-      </c>
-      <c r="V513" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="W513" t="n">
-        <v>26</v>
-      </c>
-      <c r="X513" t="inlineStr">
-        <is>
-          <t>EB FELIPE ANTÓN vs BALONCESTO TALAVERA</t>
-        </is>
-      </c>
-    </row>
-    <row r="514">
-      <c r="A514" t="inlineStr">
-        <is>
-          <t>2487752</t>
-        </is>
-      </c>
-      <c r="B514" t="inlineStr">
-        <is>
-          <t>EB FELIPE ANTÓN</t>
-        </is>
-      </c>
-      <c r="C514" t="inlineStr">
-        <is>
-          <t>J. GALLETTO LAMELA | K. RIVEROL DE LAS CASAS | M. NIMAGA | P. ARGÜELLES ELORZA | S. MANERO GUZMAN</t>
-        </is>
-      </c>
-      <c r="D514" t="n">
-        <v>5</v>
-      </c>
-      <c r="E514" t="n">
-        <v>2</v>
-      </c>
-      <c r="F514" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="G514" t="n">
-        <v>0</v>
-      </c>
-      <c r="H514" t="n">
-        <v>0</v>
-      </c>
-      <c r="I514" t="n">
-        <v>1</v>
-      </c>
-      <c r="J514" t="n">
-        <v>-1</v>
-      </c>
-      <c r="K514" t="n">
-        <v>0</v>
-      </c>
-      <c r="L514" t="n">
-        <v>0</v>
-      </c>
-      <c r="M514" t="n">
-        <v>0</v>
-      </c>
-      <c r="N514" t="n">
-        <v>1</v>
-      </c>
-      <c r="O514" t="n">
-        <v>0</v>
-      </c>
-      <c r="P514" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q514" t="n">
-        <v>0</v>
-      </c>
-      <c r="R514" t="n">
-        <v>0</v>
-      </c>
-      <c r="S514" t="n">
-        <v>0</v>
-      </c>
-      <c r="T514" t="n">
-        <v>0</v>
-      </c>
-      <c r="U514" t="n">
-        <v>1</v>
-      </c>
-      <c r="V514" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="W514" t="n">
-        <v>26</v>
-      </c>
-      <c r="X514" t="inlineStr">
-        <is>
-          <t>EB FELIPE ANTÓN vs BALONCESTO TALAVERA</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/3FEB_25_26/clutch_lineups_25_26_3FEB.xlsx
+++ b/data/3FEB_25_26/clutch_lineups_25_26_3FEB.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X431"/>
+  <dimension ref="A1:X514"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36670,6 +36670,6978 @@
         </is>
       </c>
     </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>2487736</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>A. APARICIO IZQUIERDO | A. JIMENEZ FERNANDEZ | D. RODRIGUEZ GARCIA | J. RIES | P. RODRIGUEZ RIVERO</t>
+        </is>
+      </c>
+      <c r="D432" t="n">
+        <v>5</v>
+      </c>
+      <c r="E432" t="n">
+        <v>4</v>
+      </c>
+      <c r="F432" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="G432" t="n">
+        <v>5</v>
+      </c>
+      <c r="H432" t="n">
+        <v>0</v>
+      </c>
+      <c r="I432" t="n">
+        <v>2</v>
+      </c>
+      <c r="J432" t="n">
+        <v>0</v>
+      </c>
+      <c r="K432" t="n">
+        <v>250</v>
+      </c>
+      <c r="L432" t="n">
+        <v>0</v>
+      </c>
+      <c r="M432" t="n">
+        <v>0</v>
+      </c>
+      <c r="N432" t="n">
+        <v>2</v>
+      </c>
+      <c r="O432" t="n">
+        <v>0</v>
+      </c>
+      <c r="P432" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q432" t="n">
+        <v>0</v>
+      </c>
+      <c r="R432" t="n">
+        <v>0</v>
+      </c>
+      <c r="S432" t="n">
+        <v>0</v>
+      </c>
+      <c r="T432" t="n">
+        <v>0</v>
+      </c>
+      <c r="U432" t="n">
+        <v>0</v>
+      </c>
+      <c r="V432" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W432" t="n">
+        <v>23</v>
+      </c>
+      <c r="X432" t="inlineStr">
+        <is>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA vs EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>2487736</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>A. APARICIO IZQUIERDO | A. JIMENEZ FERNANDEZ | D. RODRIGUEZ GARCIA | M. NIANG | P. RODRIGUEZ RIVERO</t>
+        </is>
+      </c>
+      <c r="D433" t="n">
+        <v>5</v>
+      </c>
+      <c r="E433" t="n">
+        <v>46</v>
+      </c>
+      <c r="F433" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="G433" t="n">
+        <v>0</v>
+      </c>
+      <c r="H433" t="n">
+        <v>0</v>
+      </c>
+      <c r="I433" t="n">
+        <v>1</v>
+      </c>
+      <c r="J433" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K433" t="n">
+        <v>0</v>
+      </c>
+      <c r="L433" t="n">
+        <v>0</v>
+      </c>
+      <c r="M433" t="n">
+        <v>0</v>
+      </c>
+      <c r="N433" t="n">
+        <v>1</v>
+      </c>
+      <c r="O433" t="n">
+        <v>0</v>
+      </c>
+      <c r="P433" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q433" t="n">
+        <v>0</v>
+      </c>
+      <c r="R433" t="n">
+        <v>0</v>
+      </c>
+      <c r="S433" t="n">
+        <v>0</v>
+      </c>
+      <c r="T433" t="n">
+        <v>0</v>
+      </c>
+      <c r="U433" t="n">
+        <v>1</v>
+      </c>
+      <c r="V433" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W433" t="n">
+        <v>23</v>
+      </c>
+      <c r="X433" t="inlineStr">
+        <is>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA vs EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>2487736</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>A. APARICIO IZQUIERDO | D. RODRIGUEZ GARCIA | J. RIES | M. NIANG | P. RODRIGUEZ RIVERO</t>
+        </is>
+      </c>
+      <c r="D434" t="n">
+        <v>5</v>
+      </c>
+      <c r="E434" t="n">
+        <v>236</v>
+      </c>
+      <c r="F434" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="G434" t="n">
+        <v>5</v>
+      </c>
+      <c r="H434" t="n">
+        <v>9</v>
+      </c>
+      <c r="I434" t="n">
+        <v>7</v>
+      </c>
+      <c r="J434" t="n">
+        <v>9.52</v>
+      </c>
+      <c r="K434" t="n">
+        <v>71.43000000000001</v>
+      </c>
+      <c r="L434" t="n">
+        <v>94.54000000000001</v>
+      </c>
+      <c r="M434" t="n">
+        <v>-23.11</v>
+      </c>
+      <c r="N434" t="n">
+        <v>8</v>
+      </c>
+      <c r="O434" t="n">
+        <v>0</v>
+      </c>
+      <c r="P434" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q434" t="n">
+        <v>2</v>
+      </c>
+      <c r="R434" t="n">
+        <v>6</v>
+      </c>
+      <c r="S434" t="n">
+        <v>8</v>
+      </c>
+      <c r="T434" t="n">
+        <v>2</v>
+      </c>
+      <c r="U434" t="n">
+        <v>2</v>
+      </c>
+      <c r="V434" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W434" t="n">
+        <v>23</v>
+      </c>
+      <c r="X434" t="inlineStr">
+        <is>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA vs EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>2487736</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>A. SISTAC RODRIGUEZ | B. FERNANDEZ SHEPHARD | K. RIVEROL DE LAS CASAS | P. ARGÜELLES ELORZA</t>
+        </is>
+      </c>
+      <c r="D435" t="n">
+        <v>4</v>
+      </c>
+      <c r="E435" t="n">
+        <v>4</v>
+      </c>
+      <c r="F435" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="G435" t="n">
+        <v>0</v>
+      </c>
+      <c r="H435" t="n">
+        <v>5</v>
+      </c>
+      <c r="I435" t="n">
+        <v>0</v>
+      </c>
+      <c r="J435" t="n">
+        <v>2</v>
+      </c>
+      <c r="K435" t="n">
+        <v>0</v>
+      </c>
+      <c r="L435" t="n">
+        <v>250</v>
+      </c>
+      <c r="M435" t="n">
+        <v>0</v>
+      </c>
+      <c r="N435" t="n">
+        <v>0</v>
+      </c>
+      <c r="O435" t="n">
+        <v>0</v>
+      </c>
+      <c r="P435" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q435" t="n">
+        <v>0</v>
+      </c>
+      <c r="R435" t="n">
+        <v>2</v>
+      </c>
+      <c r="S435" t="n">
+        <v>0</v>
+      </c>
+      <c r="T435" t="n">
+        <v>0</v>
+      </c>
+      <c r="U435" t="n">
+        <v>0</v>
+      </c>
+      <c r="V435" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W435" t="n">
+        <v>23</v>
+      </c>
+      <c r="X435" t="inlineStr">
+        <is>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA vs EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>2487736</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>A. SISTAC RODRIGUEZ | B. FERNANDEZ SHEPHARD | M. KHIVRENKO | P. ARGÜELLES ELORZA</t>
+        </is>
+      </c>
+      <c r="D436" t="n">
+        <v>4</v>
+      </c>
+      <c r="E436" t="n">
+        <v>17</v>
+      </c>
+      <c r="F436" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="G436" t="n">
+        <v>5</v>
+      </c>
+      <c r="H436" t="n">
+        <v>0</v>
+      </c>
+      <c r="I436" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="J436" t="n">
+        <v>0</v>
+      </c>
+      <c r="K436" t="n">
+        <v>189.39</v>
+      </c>
+      <c r="L436" t="n">
+        <v>0</v>
+      </c>
+      <c r="M436" t="n">
+        <v>0</v>
+      </c>
+      <c r="N436" t="n">
+        <v>1</v>
+      </c>
+      <c r="O436" t="n">
+        <v>6</v>
+      </c>
+      <c r="P436" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q436" t="n">
+        <v>1</v>
+      </c>
+      <c r="R436" t="n">
+        <v>1</v>
+      </c>
+      <c r="S436" t="n">
+        <v>0</v>
+      </c>
+      <c r="T436" t="n">
+        <v>0</v>
+      </c>
+      <c r="U436" t="n">
+        <v>1</v>
+      </c>
+      <c r="V436" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W436" t="n">
+        <v>23</v>
+      </c>
+      <c r="X436" t="inlineStr">
+        <is>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA vs EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>2487736</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>A. SISTAC RODRIGUEZ | E. DUQUE NEGRÍN | M. KHIVRENKO | P. ARGÜELLES ELORZA | P. HERNANDEZ RODRIGUEZ</t>
+        </is>
+      </c>
+      <c r="D437" t="n">
+        <v>5</v>
+      </c>
+      <c r="E437" t="n">
+        <v>17</v>
+      </c>
+      <c r="F437" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="G437" t="n">
+        <v>0</v>
+      </c>
+      <c r="H437" t="n">
+        <v>2</v>
+      </c>
+      <c r="I437" t="n">
+        <v>0</v>
+      </c>
+      <c r="J437" t="n">
+        <v>2</v>
+      </c>
+      <c r="K437" t="n">
+        <v>0</v>
+      </c>
+      <c r="L437" t="n">
+        <v>100</v>
+      </c>
+      <c r="M437" t="n">
+        <v>0</v>
+      </c>
+      <c r="N437" t="n">
+        <v>0</v>
+      </c>
+      <c r="O437" t="n">
+        <v>0</v>
+      </c>
+      <c r="P437" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q437" t="n">
+        <v>0</v>
+      </c>
+      <c r="R437" t="n">
+        <v>2</v>
+      </c>
+      <c r="S437" t="n">
+        <v>0</v>
+      </c>
+      <c r="T437" t="n">
+        <v>0</v>
+      </c>
+      <c r="U437" t="n">
+        <v>0</v>
+      </c>
+      <c r="V437" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W437" t="n">
+        <v>23</v>
+      </c>
+      <c r="X437" t="inlineStr">
+        <is>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA vs EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>2487736</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>A. SISTAC RODRIGUEZ | K. RIVEROL DE LAS CASAS | M. KHIVRENKO | P. ARGÜELLES ELORZA</t>
+        </is>
+      </c>
+      <c r="D438" t="n">
+        <v>4</v>
+      </c>
+      <c r="E438" t="n">
+        <v>42</v>
+      </c>
+      <c r="F438" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G438" t="n">
+        <v>1</v>
+      </c>
+      <c r="H438" t="n">
+        <v>0</v>
+      </c>
+      <c r="I438" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="J438" t="n">
+        <v>2</v>
+      </c>
+      <c r="K438" t="n">
+        <v>113.64</v>
+      </c>
+      <c r="L438" t="n">
+        <v>0</v>
+      </c>
+      <c r="M438" t="n">
+        <v>113.64</v>
+      </c>
+      <c r="N438" t="n">
+        <v>0</v>
+      </c>
+      <c r="O438" t="n">
+        <v>2</v>
+      </c>
+      <c r="P438" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q438" t="n">
+        <v>0</v>
+      </c>
+      <c r="R438" t="n">
+        <v>1</v>
+      </c>
+      <c r="S438" t="n">
+        <v>0</v>
+      </c>
+      <c r="T438" t="n">
+        <v>1</v>
+      </c>
+      <c r="U438" t="n">
+        <v>0</v>
+      </c>
+      <c r="V438" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W438" t="n">
+        <v>23</v>
+      </c>
+      <c r="X438" t="inlineStr">
+        <is>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA vs EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>2487736</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>B. FERNANDEZ SHEPHARD | E. DUQUE NEGRÍN | J. GALLETTO LAMELA | K. RIVEROL DE LAS CASAS | M. KHIVRENKO</t>
+        </is>
+      </c>
+      <c r="D439" t="n">
+        <v>5</v>
+      </c>
+      <c r="E439" t="n">
+        <v>22</v>
+      </c>
+      <c r="F439" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="G439" t="n">
+        <v>0</v>
+      </c>
+      <c r="H439" t="n">
+        <v>0</v>
+      </c>
+      <c r="I439" t="n">
+        <v>1</v>
+      </c>
+      <c r="J439" t="n">
+        <v>0</v>
+      </c>
+      <c r="K439" t="n">
+        <v>0</v>
+      </c>
+      <c r="L439" t="n">
+        <v>0</v>
+      </c>
+      <c r="M439" t="n">
+        <v>0</v>
+      </c>
+      <c r="N439" t="n">
+        <v>0</v>
+      </c>
+      <c r="O439" t="n">
+        <v>0</v>
+      </c>
+      <c r="P439" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q439" t="n">
+        <v>0</v>
+      </c>
+      <c r="R439" t="n">
+        <v>0</v>
+      </c>
+      <c r="S439" t="n">
+        <v>0</v>
+      </c>
+      <c r="T439" t="n">
+        <v>0</v>
+      </c>
+      <c r="U439" t="n">
+        <v>0</v>
+      </c>
+      <c r="V439" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W439" t="n">
+        <v>23</v>
+      </c>
+      <c r="X439" t="inlineStr">
+        <is>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA vs EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>2487736</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>B. FERNANDEZ SHEPHARD | E. DUQUE NEGRÍN | K. RIVEROL DE LAS CASAS | M. KHIVRENKO | P. ARGÜELLES ELORZA</t>
+        </is>
+      </c>
+      <c r="D440" t="n">
+        <v>5</v>
+      </c>
+      <c r="E440" t="n">
+        <v>32</v>
+      </c>
+      <c r="F440" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="G440" t="n">
+        <v>0</v>
+      </c>
+      <c r="H440" t="n">
+        <v>0</v>
+      </c>
+      <c r="I440" t="n">
+        <v>1</v>
+      </c>
+      <c r="J440" t="n">
+        <v>1</v>
+      </c>
+      <c r="K440" t="n">
+        <v>0</v>
+      </c>
+      <c r="L440" t="n">
+        <v>0</v>
+      </c>
+      <c r="M440" t="n">
+        <v>0</v>
+      </c>
+      <c r="N440" t="n">
+        <v>1</v>
+      </c>
+      <c r="O440" t="n">
+        <v>0</v>
+      </c>
+      <c r="P440" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q440" t="n">
+        <v>0</v>
+      </c>
+      <c r="R440" t="n">
+        <v>1</v>
+      </c>
+      <c r="S440" t="n">
+        <v>0</v>
+      </c>
+      <c r="T440" t="n">
+        <v>0</v>
+      </c>
+      <c r="U440" t="n">
+        <v>0</v>
+      </c>
+      <c r="V440" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W440" t="n">
+        <v>23</v>
+      </c>
+      <c r="X440" t="inlineStr">
+        <is>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA vs EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>2487736</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>B. FERNANDEZ SHEPHARD | J. GALLETTO LAMELA | K. RIVEROL DE LAS CASAS | M. KHIVRENKO | P. ARGÜELLES ELORZA</t>
+        </is>
+      </c>
+      <c r="D441" t="n">
+        <v>5</v>
+      </c>
+      <c r="E441" t="n">
+        <v>120</v>
+      </c>
+      <c r="F441" t="n">
+        <v>2</v>
+      </c>
+      <c r="G441" t="n">
+        <v>0</v>
+      </c>
+      <c r="H441" t="n">
+        <v>0</v>
+      </c>
+      <c r="I441" t="n">
+        <v>2</v>
+      </c>
+      <c r="J441" t="n">
+        <v>2</v>
+      </c>
+      <c r="K441" t="n">
+        <v>0</v>
+      </c>
+      <c r="L441" t="n">
+        <v>0</v>
+      </c>
+      <c r="M441" t="n">
+        <v>0</v>
+      </c>
+      <c r="N441" t="n">
+        <v>3</v>
+      </c>
+      <c r="O441" t="n">
+        <v>0</v>
+      </c>
+      <c r="P441" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q441" t="n">
+        <v>2</v>
+      </c>
+      <c r="R441" t="n">
+        <v>3</v>
+      </c>
+      <c r="S441" t="n">
+        <v>0</v>
+      </c>
+      <c r="T441" t="n">
+        <v>0</v>
+      </c>
+      <c r="U441" t="n">
+        <v>1</v>
+      </c>
+      <c r="V441" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W441" t="n">
+        <v>23</v>
+      </c>
+      <c r="X441" t="inlineStr">
+        <is>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA vs EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>2487736</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>B. FERNANDEZ SHEPHARD | J. GALLETTO LAMELA | M. KHIVRENKO | P. ARGÜELLES ELORZA | P. HERNANDEZ RODRIGUEZ</t>
+        </is>
+      </c>
+      <c r="D442" t="n">
+        <v>5</v>
+      </c>
+      <c r="E442" t="n">
+        <v>32</v>
+      </c>
+      <c r="F442" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="G442" t="n">
+        <v>3</v>
+      </c>
+      <c r="H442" t="n">
+        <v>3</v>
+      </c>
+      <c r="I442" t="n">
+        <v>1</v>
+      </c>
+      <c r="J442" t="n">
+        <v>1</v>
+      </c>
+      <c r="K442" t="n">
+        <v>300</v>
+      </c>
+      <c r="L442" t="n">
+        <v>300</v>
+      </c>
+      <c r="M442" t="n">
+        <v>0</v>
+      </c>
+      <c r="N442" t="n">
+        <v>1</v>
+      </c>
+      <c r="O442" t="n">
+        <v>0</v>
+      </c>
+      <c r="P442" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q442" t="n">
+        <v>0</v>
+      </c>
+      <c r="R442" t="n">
+        <v>1</v>
+      </c>
+      <c r="S442" t="n">
+        <v>0</v>
+      </c>
+      <c r="T442" t="n">
+        <v>0</v>
+      </c>
+      <c r="U442" t="n">
+        <v>0</v>
+      </c>
+      <c r="V442" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W442" t="n">
+        <v>23</v>
+      </c>
+      <c r="X442" t="inlineStr">
+        <is>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA vs EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>2487737</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>BALONCESTO TELDE</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>A. FERNÁNDEZ GÓMEZ | A. MARTIN GONZALEZ | A. SANTANA OJEDA | G. ARTILES ROMERO | J. JIMENEZ HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D443" t="n">
+        <v>5</v>
+      </c>
+      <c r="E443" t="n">
+        <v>159</v>
+      </c>
+      <c r="F443" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="G443" t="n">
+        <v>4</v>
+      </c>
+      <c r="H443" t="n">
+        <v>7</v>
+      </c>
+      <c r="I443" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="J443" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="K443" t="n">
+        <v>68.03</v>
+      </c>
+      <c r="L443" t="n">
+        <v>253.62</v>
+      </c>
+      <c r="M443" t="n">
+        <v>-185.6</v>
+      </c>
+      <c r="N443" t="n">
+        <v>7</v>
+      </c>
+      <c r="O443" t="n">
+        <v>2</v>
+      </c>
+      <c r="P443" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q443" t="n">
+        <v>2</v>
+      </c>
+      <c r="R443" t="n">
+        <v>3</v>
+      </c>
+      <c r="S443" t="n">
+        <v>4</v>
+      </c>
+      <c r="T443" t="n">
+        <v>1</v>
+      </c>
+      <c r="U443" t="n">
+        <v>3</v>
+      </c>
+      <c r="V443" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W443" t="n">
+        <v>23</v>
+      </c>
+      <c r="X443" t="inlineStr">
+        <is>
+          <t>C.B. TRES CANTOS vs BALONCESTO TELDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>2487737</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>C.B. TRES CANTOS</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>A. SIMON DEL CORRAL | D. FERNANDEZ CAÑAS | G. DIAZ MONTERO | J. ATIENZA PEREA | N. MAIGA</t>
+        </is>
+      </c>
+      <c r="D444" t="n">
+        <v>5</v>
+      </c>
+      <c r="E444" t="n">
+        <v>65</v>
+      </c>
+      <c r="F444" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="G444" t="n">
+        <v>3</v>
+      </c>
+      <c r="H444" t="n">
+        <v>0</v>
+      </c>
+      <c r="I444" t="n">
+        <v>2</v>
+      </c>
+      <c r="J444" t="n">
+        <v>1</v>
+      </c>
+      <c r="K444" t="n">
+        <v>150</v>
+      </c>
+      <c r="L444" t="n">
+        <v>0</v>
+      </c>
+      <c r="M444" t="n">
+        <v>150</v>
+      </c>
+      <c r="N444" t="n">
+        <v>2</v>
+      </c>
+      <c r="O444" t="n">
+        <v>0</v>
+      </c>
+      <c r="P444" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q444" t="n">
+        <v>1</v>
+      </c>
+      <c r="R444" t="n">
+        <v>2</v>
+      </c>
+      <c r="S444" t="n">
+        <v>0</v>
+      </c>
+      <c r="T444" t="n">
+        <v>0</v>
+      </c>
+      <c r="U444" t="n">
+        <v>1</v>
+      </c>
+      <c r="V444" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W444" t="n">
+        <v>23</v>
+      </c>
+      <c r="X444" t="inlineStr">
+        <is>
+          <t>C.B. TRES CANTOS vs BALONCESTO TELDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>2487737</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>C.B. TRES CANTOS</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>A. SIMON DEL CORRAL | G. DIAZ MONTERO | G. LARDIES GUILLEN | J. ATIENZA PEREA | N. MAIGA</t>
+        </is>
+      </c>
+      <c r="D445" t="n">
+        <v>5</v>
+      </c>
+      <c r="E445" t="n">
+        <v>91</v>
+      </c>
+      <c r="F445" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="G445" t="n">
+        <v>4</v>
+      </c>
+      <c r="H445" t="n">
+        <v>4</v>
+      </c>
+      <c r="I445" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="J445" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="K445" t="n">
+        <v>526.3200000000001</v>
+      </c>
+      <c r="L445" t="n">
+        <v>81.97</v>
+      </c>
+      <c r="M445" t="n">
+        <v>444.35</v>
+      </c>
+      <c r="N445" t="n">
+        <v>1</v>
+      </c>
+      <c r="O445" t="n">
+        <v>4</v>
+      </c>
+      <c r="P445" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q445" t="n">
+        <v>2</v>
+      </c>
+      <c r="R445" t="n">
+        <v>5</v>
+      </c>
+      <c r="S445" t="n">
+        <v>2</v>
+      </c>
+      <c r="T445" t="n">
+        <v>0</v>
+      </c>
+      <c r="U445" t="n">
+        <v>1</v>
+      </c>
+      <c r="V445" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W445" t="n">
+        <v>23</v>
+      </c>
+      <c r="X445" t="inlineStr">
+        <is>
+          <t>C.B. TRES CANTOS vs BALONCESTO TELDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>2487737</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>C.B. TRES CANTOS</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>D. FERNANDEZ CAÑAS | G. DIAZ MONTERO | G. LARDIES GUILLEN | J. ATIENZA PEREA | N. MAIGA</t>
+        </is>
+      </c>
+      <c r="D446" t="n">
+        <v>5</v>
+      </c>
+      <c r="E446" t="n">
+        <v>3</v>
+      </c>
+      <c r="F446" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G446" t="n">
+        <v>0</v>
+      </c>
+      <c r="H446" t="n">
+        <v>0</v>
+      </c>
+      <c r="I446" t="n">
+        <v>0</v>
+      </c>
+      <c r="J446" t="n">
+        <v>0</v>
+      </c>
+      <c r="K446" t="n">
+        <v>0</v>
+      </c>
+      <c r="L446" t="n">
+        <v>0</v>
+      </c>
+      <c r="M446" t="n">
+        <v>0</v>
+      </c>
+      <c r="N446" t="n">
+        <v>0</v>
+      </c>
+      <c r="O446" t="n">
+        <v>0</v>
+      </c>
+      <c r="P446" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q446" t="n">
+        <v>0</v>
+      </c>
+      <c r="R446" t="n">
+        <v>0</v>
+      </c>
+      <c r="S446" t="n">
+        <v>0</v>
+      </c>
+      <c r="T446" t="n">
+        <v>0</v>
+      </c>
+      <c r="U446" t="n">
+        <v>0</v>
+      </c>
+      <c r="V446" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W446" t="n">
+        <v>23</v>
+      </c>
+      <c r="X446" t="inlineStr">
+        <is>
+          <t>C.B. TRES CANTOS vs BALONCESTO TELDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>2487732</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>CB ARIDANE</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>A. GASE SECO | D. VIERA LOPEZ | K. SKUTYELNIK | O. BALSELLS PLAZA | S. GUEYE</t>
+        </is>
+      </c>
+      <c r="D447" t="n">
+        <v>5</v>
+      </c>
+      <c r="E447" t="n">
+        <v>64</v>
+      </c>
+      <c r="F447" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="G447" t="n">
+        <v>0</v>
+      </c>
+      <c r="H447" t="n">
+        <v>3</v>
+      </c>
+      <c r="I447" t="n">
+        <v>2</v>
+      </c>
+      <c r="J447" t="n">
+        <v>2</v>
+      </c>
+      <c r="K447" t="n">
+        <v>0</v>
+      </c>
+      <c r="L447" t="n">
+        <v>150</v>
+      </c>
+      <c r="M447" t="n">
+        <v>-150</v>
+      </c>
+      <c r="N447" t="n">
+        <v>2</v>
+      </c>
+      <c r="O447" t="n">
+        <v>0</v>
+      </c>
+      <c r="P447" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q447" t="n">
+        <v>0</v>
+      </c>
+      <c r="R447" t="n">
+        <v>3</v>
+      </c>
+      <c r="S447" t="n">
+        <v>0</v>
+      </c>
+      <c r="T447" t="n">
+        <v>0</v>
+      </c>
+      <c r="U447" t="n">
+        <v>1</v>
+      </c>
+      <c r="V447" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W447" t="n">
+        <v>23</v>
+      </c>
+      <c r="X447" t="inlineStr">
+        <is>
+          <t>CB ARIDANE vs REAL CANOE N.C.</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>2487732</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>CB ARIDANE</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>A. GASE SECO | G. MEJÍA ACOSTA | G. PIERRE-GABRIEL ANDREA GASTON | K. SKUTYELNIK | O. BALSELLS PLAZA</t>
+        </is>
+      </c>
+      <c r="D448" t="n">
+        <v>5</v>
+      </c>
+      <c r="E448" t="n">
+        <v>13</v>
+      </c>
+      <c r="F448" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="G448" t="n">
+        <v>0</v>
+      </c>
+      <c r="H448" t="n">
+        <v>2</v>
+      </c>
+      <c r="I448" t="n">
+        <v>0</v>
+      </c>
+      <c r="J448" t="n">
+        <v>1</v>
+      </c>
+      <c r="K448" t="n">
+        <v>0</v>
+      </c>
+      <c r="L448" t="n">
+        <v>200</v>
+      </c>
+      <c r="M448" t="n">
+        <v>0</v>
+      </c>
+      <c r="N448" t="n">
+        <v>0</v>
+      </c>
+      <c r="O448" t="n">
+        <v>0</v>
+      </c>
+      <c r="P448" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q448" t="n">
+        <v>0</v>
+      </c>
+      <c r="R448" t="n">
+        <v>1</v>
+      </c>
+      <c r="S448" t="n">
+        <v>0</v>
+      </c>
+      <c r="T448" t="n">
+        <v>0</v>
+      </c>
+      <c r="U448" t="n">
+        <v>0</v>
+      </c>
+      <c r="V448" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W448" t="n">
+        <v>23</v>
+      </c>
+      <c r="X448" t="inlineStr">
+        <is>
+          <t>CB ARIDANE vs REAL CANOE N.C.</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>2487732</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>CB ARIDANE</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>A. GASE SECO | G. MEJÍA ACOSTA | K. SKUTYELNIK | O. BALSELLS PLAZA | S. GUEYE</t>
+        </is>
+      </c>
+      <c r="D449" t="n">
+        <v>5</v>
+      </c>
+      <c r="E449" t="n">
+        <v>55</v>
+      </c>
+      <c r="F449" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="G449" t="n">
+        <v>2</v>
+      </c>
+      <c r="H449" t="n">
+        <v>3</v>
+      </c>
+      <c r="I449" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="J449" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="K449" t="n">
+        <v>106.38</v>
+      </c>
+      <c r="L449" t="n">
+        <v>159.57</v>
+      </c>
+      <c r="M449" t="n">
+        <v>-53.19</v>
+      </c>
+      <c r="N449" t="n">
+        <v>1</v>
+      </c>
+      <c r="O449" t="n">
+        <v>2</v>
+      </c>
+      <c r="P449" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q449" t="n">
+        <v>0</v>
+      </c>
+      <c r="R449" t="n">
+        <v>2</v>
+      </c>
+      <c r="S449" t="n">
+        <v>2</v>
+      </c>
+      <c r="T449" t="n">
+        <v>0</v>
+      </c>
+      <c r="U449" t="n">
+        <v>1</v>
+      </c>
+      <c r="V449" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W449" t="n">
+        <v>23</v>
+      </c>
+      <c r="X449" t="inlineStr">
+        <is>
+          <t>CB ARIDANE vs REAL CANOE N.C.</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>2487732</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>REAL CANOE N.C.</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>D. MANZANERO CAMACHO | E. PASCUAL COZAR | J. LAPASTORA ARACIL | J. MARTINEZ SANTOS | N. LASUNCION MARIBLANCA</t>
+        </is>
+      </c>
+      <c r="D450" t="n">
+        <v>5</v>
+      </c>
+      <c r="E450" t="n">
+        <v>23</v>
+      </c>
+      <c r="F450" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="G450" t="n">
+        <v>0</v>
+      </c>
+      <c r="H450" t="n">
+        <v>0</v>
+      </c>
+      <c r="I450" t="n">
+        <v>1</v>
+      </c>
+      <c r="J450" t="n">
+        <v>1</v>
+      </c>
+      <c r="K450" t="n">
+        <v>0</v>
+      </c>
+      <c r="L450" t="n">
+        <v>0</v>
+      </c>
+      <c r="M450" t="n">
+        <v>0</v>
+      </c>
+      <c r="N450" t="n">
+        <v>2</v>
+      </c>
+      <c r="O450" t="n">
+        <v>0</v>
+      </c>
+      <c r="P450" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q450" t="n">
+        <v>1</v>
+      </c>
+      <c r="R450" t="n">
+        <v>1</v>
+      </c>
+      <c r="S450" t="n">
+        <v>0</v>
+      </c>
+      <c r="T450" t="n">
+        <v>0</v>
+      </c>
+      <c r="U450" t="n">
+        <v>0</v>
+      </c>
+      <c r="V450" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W450" t="n">
+        <v>23</v>
+      </c>
+      <c r="X450" t="inlineStr">
+        <is>
+          <t>CB ARIDANE vs REAL CANOE N.C.</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>2487732</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>REAL CANOE N.C.</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>D. MANZANERO CAMACHO | J. LAPASTORA ARACIL | J. MARTINEZ SANTOS | L. GARCIA LARRACHE SEGURA | N. LASUNCION MARIBLANCA</t>
+        </is>
+      </c>
+      <c r="D451" t="n">
+        <v>5</v>
+      </c>
+      <c r="E451" t="n">
+        <v>44</v>
+      </c>
+      <c r="F451" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="G451" t="n">
+        <v>3</v>
+      </c>
+      <c r="H451" t="n">
+        <v>0</v>
+      </c>
+      <c r="I451" t="n">
+        <v>1</v>
+      </c>
+      <c r="J451" t="n">
+        <v>1</v>
+      </c>
+      <c r="K451" t="n">
+        <v>300</v>
+      </c>
+      <c r="L451" t="n">
+        <v>0</v>
+      </c>
+      <c r="M451" t="n">
+        <v>300</v>
+      </c>
+      <c r="N451" t="n">
+        <v>2</v>
+      </c>
+      <c r="O451" t="n">
+        <v>0</v>
+      </c>
+      <c r="P451" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q451" t="n">
+        <v>1</v>
+      </c>
+      <c r="R451" t="n">
+        <v>1</v>
+      </c>
+      <c r="S451" t="n">
+        <v>0</v>
+      </c>
+      <c r="T451" t="n">
+        <v>0</v>
+      </c>
+      <c r="U451" t="n">
+        <v>0</v>
+      </c>
+      <c r="V451" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W451" t="n">
+        <v>23</v>
+      </c>
+      <c r="X451" t="inlineStr">
+        <is>
+          <t>CB ARIDANE vs REAL CANOE N.C.</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>2487732</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>REAL CANOE N.C.</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>J. LAPASTORA ARACIL | J. MARTINEZ SANTOS | L. GARCIA LARRACHE SEGURA | M. HERMOSO ALCUBILLA | N. LASUNCION MARIBLANCA</t>
+        </is>
+      </c>
+      <c r="D452" t="n">
+        <v>5</v>
+      </c>
+      <c r="E452" t="n">
+        <v>65</v>
+      </c>
+      <c r="F452" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="G452" t="n">
+        <v>5</v>
+      </c>
+      <c r="H452" t="n">
+        <v>2</v>
+      </c>
+      <c r="I452" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="J452" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="K452" t="n">
+        <v>173.61</v>
+      </c>
+      <c r="L452" t="n">
+        <v>106.38</v>
+      </c>
+      <c r="M452" t="n">
+        <v>67.23</v>
+      </c>
+      <c r="N452" t="n">
+        <v>2</v>
+      </c>
+      <c r="O452" t="n">
+        <v>2</v>
+      </c>
+      <c r="P452" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q452" t="n">
+        <v>0</v>
+      </c>
+      <c r="R452" t="n">
+        <v>1</v>
+      </c>
+      <c r="S452" t="n">
+        <v>2</v>
+      </c>
+      <c r="T452" t="n">
+        <v>0</v>
+      </c>
+      <c r="U452" t="n">
+        <v>0</v>
+      </c>
+      <c r="V452" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W452" t="n">
+        <v>23</v>
+      </c>
+      <c r="X452" t="inlineStr">
+        <is>
+          <t>CB ARIDANE vs REAL CANOE N.C.</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>2487738</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>BALONCESTO TALAVERA</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>A. VICENTE VIANA | C. UNANUE CEGARRA | D. LORENZO NEGRETE | J. FRANCES PASCUAL | S. GACIC</t>
+        </is>
+      </c>
+      <c r="D453" t="n">
+        <v>5</v>
+      </c>
+      <c r="E453" t="n">
+        <v>133</v>
+      </c>
+      <c r="F453" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="G453" t="n">
+        <v>2</v>
+      </c>
+      <c r="H453" t="n">
+        <v>3</v>
+      </c>
+      <c r="I453" t="n">
+        <v>5</v>
+      </c>
+      <c r="J453" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="K453" t="n">
+        <v>40</v>
+      </c>
+      <c r="L453" t="n">
+        <v>108.7</v>
+      </c>
+      <c r="M453" t="n">
+        <v>-68.7</v>
+      </c>
+      <c r="N453" t="n">
+        <v>4</v>
+      </c>
+      <c r="O453" t="n">
+        <v>0</v>
+      </c>
+      <c r="P453" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q453" t="n">
+        <v>1</v>
+      </c>
+      <c r="R453" t="n">
+        <v>3</v>
+      </c>
+      <c r="S453" t="n">
+        <v>4</v>
+      </c>
+      <c r="T453" t="n">
+        <v>0</v>
+      </c>
+      <c r="U453" t="n">
+        <v>2</v>
+      </c>
+      <c r="V453" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W453" t="n">
+        <v>24</v>
+      </c>
+      <c r="X453" t="inlineStr">
+        <is>
+          <t>BALONCESTO TALAVERA vs BALONCESTO TELDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>2487738</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>BALONCESTO TALAVERA</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>B. GUEYE | C. UNANUE CEGARRA | D. LORENZO NEGRETE | J. FRANCES PASCUAL | S. GACIC</t>
+        </is>
+      </c>
+      <c r="D454" t="n">
+        <v>5</v>
+      </c>
+      <c r="E454" t="n">
+        <v>75</v>
+      </c>
+      <c r="F454" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="G454" t="n">
+        <v>2</v>
+      </c>
+      <c r="H454" t="n">
+        <v>2</v>
+      </c>
+      <c r="I454" t="n">
+        <v>2</v>
+      </c>
+      <c r="J454" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="K454" t="n">
+        <v>100</v>
+      </c>
+      <c r="L454" t="n">
+        <v>69.44</v>
+      </c>
+      <c r="M454" t="n">
+        <v>30.56</v>
+      </c>
+      <c r="N454" t="n">
+        <v>1</v>
+      </c>
+      <c r="O454" t="n">
+        <v>0</v>
+      </c>
+      <c r="P454" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q454" t="n">
+        <v>1</v>
+      </c>
+      <c r="R454" t="n">
+        <v>1</v>
+      </c>
+      <c r="S454" t="n">
+        <v>2</v>
+      </c>
+      <c r="T454" t="n">
+        <v>1</v>
+      </c>
+      <c r="U454" t="n">
+        <v>0</v>
+      </c>
+      <c r="V454" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W454" t="n">
+        <v>24</v>
+      </c>
+      <c r="X454" t="inlineStr">
+        <is>
+          <t>BALONCESTO TALAVERA vs BALONCESTO TELDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>2487738</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>BALONCESTO TALAVERA</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>C. KLOTZ MAROTO | D. LORENZO NEGRETE | J. FRANCES PASCUAL | S. GACIC | V. ALONSO PASCUAL</t>
+        </is>
+      </c>
+      <c r="D455" t="n">
+        <v>5</v>
+      </c>
+      <c r="E455" t="n">
+        <v>49</v>
+      </c>
+      <c r="F455" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="G455" t="n">
+        <v>0</v>
+      </c>
+      <c r="H455" t="n">
+        <v>2</v>
+      </c>
+      <c r="I455" t="n">
+        <v>1</v>
+      </c>
+      <c r="J455" t="n">
+        <v>2</v>
+      </c>
+      <c r="K455" t="n">
+        <v>0</v>
+      </c>
+      <c r="L455" t="n">
+        <v>100</v>
+      </c>
+      <c r="M455" t="n">
+        <v>-100</v>
+      </c>
+      <c r="N455" t="n">
+        <v>1</v>
+      </c>
+      <c r="O455" t="n">
+        <v>0</v>
+      </c>
+      <c r="P455" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q455" t="n">
+        <v>1</v>
+      </c>
+      <c r="R455" t="n">
+        <v>2</v>
+      </c>
+      <c r="S455" t="n">
+        <v>0</v>
+      </c>
+      <c r="T455" t="n">
+        <v>0</v>
+      </c>
+      <c r="U455" t="n">
+        <v>0</v>
+      </c>
+      <c r="V455" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W455" t="n">
+        <v>24</v>
+      </c>
+      <c r="X455" t="inlineStr">
+        <is>
+          <t>BALONCESTO TALAVERA vs BALONCESTO TELDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>2487738</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>BALONCESTO TALAVERA</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>C. UNANUE CEGARRA | D. LORENZO NEGRETE | J. FRANCES PASCUAL | S. GACIC | V. ALONSO PASCUAL</t>
+        </is>
+      </c>
+      <c r="D456" t="n">
+        <v>5</v>
+      </c>
+      <c r="E456" t="n">
+        <v>38</v>
+      </c>
+      <c r="F456" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="G456" t="n">
+        <v>3</v>
+      </c>
+      <c r="H456" t="n">
+        <v>3</v>
+      </c>
+      <c r="I456" t="n">
+        <v>2</v>
+      </c>
+      <c r="J456" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="K456" t="n">
+        <v>150</v>
+      </c>
+      <c r="L456" t="n">
+        <v>340.91</v>
+      </c>
+      <c r="M456" t="n">
+        <v>-190.91</v>
+      </c>
+      <c r="N456" t="n">
+        <v>2</v>
+      </c>
+      <c r="O456" t="n">
+        <v>0</v>
+      </c>
+      <c r="P456" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q456" t="n">
+        <v>0</v>
+      </c>
+      <c r="R456" t="n">
+        <v>1</v>
+      </c>
+      <c r="S456" t="n">
+        <v>2</v>
+      </c>
+      <c r="T456" t="n">
+        <v>0</v>
+      </c>
+      <c r="U456" t="n">
+        <v>1</v>
+      </c>
+      <c r="V456" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W456" t="n">
+        <v>24</v>
+      </c>
+      <c r="X456" t="inlineStr">
+        <is>
+          <t>BALONCESTO TALAVERA vs BALONCESTO TELDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>2487738</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>BALONCESTO TELDE</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>A. FERNÁNDEZ GÓMEZ | A. MARTIN GONZALEZ | A. SANTANA OJEDA | A. VIDAL RODRIGUEZ | G. ARTILES ROMERO</t>
+        </is>
+      </c>
+      <c r="D457" t="n">
+        <v>5</v>
+      </c>
+      <c r="E457" t="n">
+        <v>34</v>
+      </c>
+      <c r="F457" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="G457" t="n">
+        <v>2</v>
+      </c>
+      <c r="H457" t="n">
+        <v>0</v>
+      </c>
+      <c r="I457" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="J457" t="n">
+        <v>1</v>
+      </c>
+      <c r="K457" t="n">
+        <v>106.38</v>
+      </c>
+      <c r="L457" t="n">
+        <v>0</v>
+      </c>
+      <c r="M457" t="n">
+        <v>106.38</v>
+      </c>
+      <c r="N457" t="n">
+        <v>2</v>
+      </c>
+      <c r="O457" t="n">
+        <v>2</v>
+      </c>
+      <c r="P457" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q457" t="n">
+        <v>1</v>
+      </c>
+      <c r="R457" t="n">
+        <v>1</v>
+      </c>
+      <c r="S457" t="n">
+        <v>0</v>
+      </c>
+      <c r="T457" t="n">
+        <v>1</v>
+      </c>
+      <c r="U457" t="n">
+        <v>1</v>
+      </c>
+      <c r="V457" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W457" t="n">
+        <v>24</v>
+      </c>
+      <c r="X457" t="inlineStr">
+        <is>
+          <t>BALONCESTO TALAVERA vs BALONCESTO TELDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>2487738</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>BALONCESTO TELDE</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>A. FERNÁNDEZ GÓMEZ | A. SANTANA OJEDA | A. VIDAL RODRIGUEZ | G. ARTILES ROMERO | J. JIMENEZ HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D458" t="n">
+        <v>5</v>
+      </c>
+      <c r="E458" t="n">
+        <v>233</v>
+      </c>
+      <c r="F458" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="G458" t="n">
+        <v>8</v>
+      </c>
+      <c r="H458" t="n">
+        <v>7</v>
+      </c>
+      <c r="I458" t="n">
+        <v>6.64</v>
+      </c>
+      <c r="J458" t="n">
+        <v>8</v>
+      </c>
+      <c r="K458" t="n">
+        <v>120.48</v>
+      </c>
+      <c r="L458" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="M458" t="n">
+        <v>32.98</v>
+      </c>
+      <c r="N458" t="n">
+        <v>5</v>
+      </c>
+      <c r="O458" t="n">
+        <v>6</v>
+      </c>
+      <c r="P458" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q458" t="n">
+        <v>2</v>
+      </c>
+      <c r="R458" t="n">
+        <v>6</v>
+      </c>
+      <c r="S458" t="n">
+        <v>0</v>
+      </c>
+      <c r="T458" t="n">
+        <v>4</v>
+      </c>
+      <c r="U458" t="n">
+        <v>2</v>
+      </c>
+      <c r="V458" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W458" t="n">
+        <v>24</v>
+      </c>
+      <c r="X458" t="inlineStr">
+        <is>
+          <t>BALONCESTO TALAVERA vs BALONCESTO TELDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>2487738</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>BALONCESTO TELDE</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>A. MARTIN GONZALEZ | A. SANTANA OJEDA | A. VIDAL RODRIGUEZ | G. ARTILES ROMERO | J. JIMENEZ HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D459" t="n">
+        <v>5</v>
+      </c>
+      <c r="E459" t="n">
+        <v>28</v>
+      </c>
+      <c r="F459" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="G459" t="n">
+        <v>0</v>
+      </c>
+      <c r="H459" t="n">
+        <v>0</v>
+      </c>
+      <c r="I459" t="n">
+        <v>0</v>
+      </c>
+      <c r="J459" t="n">
+        <v>1</v>
+      </c>
+      <c r="K459" t="n">
+        <v>0</v>
+      </c>
+      <c r="L459" t="n">
+        <v>0</v>
+      </c>
+      <c r="M459" t="n">
+        <v>0</v>
+      </c>
+      <c r="N459" t="n">
+        <v>0</v>
+      </c>
+      <c r="O459" t="n">
+        <v>0</v>
+      </c>
+      <c r="P459" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q459" t="n">
+        <v>0</v>
+      </c>
+      <c r="R459" t="n">
+        <v>1</v>
+      </c>
+      <c r="S459" t="n">
+        <v>0</v>
+      </c>
+      <c r="T459" t="n">
+        <v>0</v>
+      </c>
+      <c r="U459" t="n">
+        <v>0</v>
+      </c>
+      <c r="V459" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W459" t="n">
+        <v>24</v>
+      </c>
+      <c r="X459" t="inlineStr">
+        <is>
+          <t>BALONCESTO TALAVERA vs BALONCESTO TELDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>2487751</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>BALONCESTO TELDE</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>A. FERNÁNDEZ GÓMEZ | A. MARTIN GONZALEZ | A. SANTANA OJEDA | A. VIDAL RODRIGUEZ | G. ARTILES ROMERO</t>
+        </is>
+      </c>
+      <c r="D460" t="n">
+        <v>5</v>
+      </c>
+      <c r="E460" t="n">
+        <v>61</v>
+      </c>
+      <c r="F460" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="G460" t="n">
+        <v>2</v>
+      </c>
+      <c r="H460" t="n">
+        <v>3</v>
+      </c>
+      <c r="I460" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="J460" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="K460" t="n">
+        <v>106.38</v>
+      </c>
+      <c r="L460" t="n">
+        <v>159.57</v>
+      </c>
+      <c r="M460" t="n">
+        <v>-53.19</v>
+      </c>
+      <c r="N460" t="n">
+        <v>1</v>
+      </c>
+      <c r="O460" t="n">
+        <v>2</v>
+      </c>
+      <c r="P460" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q460" t="n">
+        <v>0</v>
+      </c>
+      <c r="R460" t="n">
+        <v>2</v>
+      </c>
+      <c r="S460" t="n">
+        <v>2</v>
+      </c>
+      <c r="T460" t="n">
+        <v>0</v>
+      </c>
+      <c r="U460" t="n">
+        <v>1</v>
+      </c>
+      <c r="V460" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W460" t="n">
+        <v>25</v>
+      </c>
+      <c r="X460" t="inlineStr">
+        <is>
+          <t>BALONCESTO TELDE vs EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>2487751</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>BALONCESTO TELDE</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>A. FERNÁNDEZ GÓMEZ | A. MARTIN GONZALEZ | A. VIDAL RODRIGUEZ | G. ARTILES ROMERO | P. SÁNCHEZ GUTIERREZ</t>
+        </is>
+      </c>
+      <c r="D461" t="n">
+        <v>5</v>
+      </c>
+      <c r="E461" t="n">
+        <v>131</v>
+      </c>
+      <c r="F461" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="G461" t="n">
+        <v>3</v>
+      </c>
+      <c r="H461" t="n">
+        <v>7</v>
+      </c>
+      <c r="I461" t="n">
+        <v>3</v>
+      </c>
+      <c r="J461" t="n">
+        <v>6</v>
+      </c>
+      <c r="K461" t="n">
+        <v>100</v>
+      </c>
+      <c r="L461" t="n">
+        <v>116.67</v>
+      </c>
+      <c r="M461" t="n">
+        <v>-16.67</v>
+      </c>
+      <c r="N461" t="n">
+        <v>3</v>
+      </c>
+      <c r="O461" t="n">
+        <v>0</v>
+      </c>
+      <c r="P461" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q461" t="n">
+        <v>1</v>
+      </c>
+      <c r="R461" t="n">
+        <v>4</v>
+      </c>
+      <c r="S461" t="n">
+        <v>0</v>
+      </c>
+      <c r="T461" t="n">
+        <v>2</v>
+      </c>
+      <c r="U461" t="n">
+        <v>0</v>
+      </c>
+      <c r="V461" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W461" t="n">
+        <v>25</v>
+      </c>
+      <c r="X461" t="inlineStr">
+        <is>
+          <t>BALONCESTO TELDE vs EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>2487751</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>A. SISTAC RODRIGUEZ | E. DUQUE NEGRÍN | J. GALLETTO LAMELA | M. NIMAGA | S. MANERO GUZMAN</t>
+        </is>
+      </c>
+      <c r="D462" t="n">
+        <v>5</v>
+      </c>
+      <c r="E462" t="n">
+        <v>87</v>
+      </c>
+      <c r="F462" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="G462" t="n">
+        <v>4</v>
+      </c>
+      <c r="H462" t="n">
+        <v>2</v>
+      </c>
+      <c r="I462" t="n">
+        <v>3</v>
+      </c>
+      <c r="J462" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="K462" t="n">
+        <v>133.33</v>
+      </c>
+      <c r="L462" t="n">
+        <v>69.44</v>
+      </c>
+      <c r="M462" t="n">
+        <v>63.89</v>
+      </c>
+      <c r="N462" t="n">
+        <v>4</v>
+      </c>
+      <c r="O462" t="n">
+        <v>0</v>
+      </c>
+      <c r="P462" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q462" t="n">
+        <v>1</v>
+      </c>
+      <c r="R462" t="n">
+        <v>1</v>
+      </c>
+      <c r="S462" t="n">
+        <v>2</v>
+      </c>
+      <c r="T462" t="n">
+        <v>1</v>
+      </c>
+      <c r="U462" t="n">
+        <v>0</v>
+      </c>
+      <c r="V462" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W462" t="n">
+        <v>25</v>
+      </c>
+      <c r="X462" t="inlineStr">
+        <is>
+          <t>BALONCESTO TELDE vs EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>2487751</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>A. SISTAC RODRIGUEZ | E. DUQUE NEGRÍN | J. GALLETTO LAMELA | P. ARGÜELLES ELORZA | S. MANERO GUZMAN</t>
+        </is>
+      </c>
+      <c r="D463" t="n">
+        <v>5</v>
+      </c>
+      <c r="E463" t="n">
+        <v>27</v>
+      </c>
+      <c r="F463" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="G463" t="n">
+        <v>3</v>
+      </c>
+      <c r="H463" t="n">
+        <v>0</v>
+      </c>
+      <c r="I463" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="J463" t="n">
+        <v>0</v>
+      </c>
+      <c r="K463" t="n">
+        <v>159.57</v>
+      </c>
+      <c r="L463" t="n">
+        <v>0</v>
+      </c>
+      <c r="M463" t="n">
+        <v>0</v>
+      </c>
+      <c r="N463" t="n">
+        <v>1</v>
+      </c>
+      <c r="O463" t="n">
+        <v>2</v>
+      </c>
+      <c r="P463" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q463" t="n">
+        <v>0</v>
+      </c>
+      <c r="R463" t="n">
+        <v>0</v>
+      </c>
+      <c r="S463" t="n">
+        <v>0</v>
+      </c>
+      <c r="T463" t="n">
+        <v>0</v>
+      </c>
+      <c r="U463" t="n">
+        <v>0</v>
+      </c>
+      <c r="V463" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W463" t="n">
+        <v>25</v>
+      </c>
+      <c r="X463" t="inlineStr">
+        <is>
+          <t>BALONCESTO TELDE vs EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>2487751</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>A. SISTAC RODRIGUEZ | E. DUQUE NEGRÍN | M. NIMAGA | P. HERNANDEZ RODRIGUEZ | S. MANERO GUZMAN</t>
+        </is>
+      </c>
+      <c r="D464" t="n">
+        <v>5</v>
+      </c>
+      <c r="E464" t="n">
+        <v>78</v>
+      </c>
+      <c r="F464" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="G464" t="n">
+        <v>3</v>
+      </c>
+      <c r="H464" t="n">
+        <v>3</v>
+      </c>
+      <c r="I464" t="n">
+        <v>3</v>
+      </c>
+      <c r="J464" t="n">
+        <v>2</v>
+      </c>
+      <c r="K464" t="n">
+        <v>100</v>
+      </c>
+      <c r="L464" t="n">
+        <v>150</v>
+      </c>
+      <c r="M464" t="n">
+        <v>-50</v>
+      </c>
+      <c r="N464" t="n">
+        <v>1</v>
+      </c>
+      <c r="O464" t="n">
+        <v>0</v>
+      </c>
+      <c r="P464" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q464" t="n">
+        <v>0</v>
+      </c>
+      <c r="R464" t="n">
+        <v>3</v>
+      </c>
+      <c r="S464" t="n">
+        <v>0</v>
+      </c>
+      <c r="T464" t="n">
+        <v>0</v>
+      </c>
+      <c r="U464" t="n">
+        <v>1</v>
+      </c>
+      <c r="V464" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W464" t="n">
+        <v>25</v>
+      </c>
+      <c r="X464" t="inlineStr">
+        <is>
+          <t>BALONCESTO TELDE vs EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>2487749</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>ADC BOADILLA</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>A. GOMEZ SERRANO | A. OLMEDO VELASCO | I. BLANCO-ARGIBAY GONZALEZ | M. SANCHEZ SANCHEZ | P. DOMINGUEZ LORENZO</t>
+        </is>
+      </c>
+      <c r="D465" t="n">
+        <v>5</v>
+      </c>
+      <c r="E465" t="n">
+        <v>85</v>
+      </c>
+      <c r="F465" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="G465" t="n">
+        <v>5</v>
+      </c>
+      <c r="H465" t="n">
+        <v>2</v>
+      </c>
+      <c r="I465" t="n">
+        <v>3</v>
+      </c>
+      <c r="J465" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="K465" t="n">
+        <v>166.67</v>
+      </c>
+      <c r="L465" t="n">
+        <v>86.20999999999999</v>
+      </c>
+      <c r="M465" t="n">
+        <v>80.45999999999999</v>
+      </c>
+      <c r="N465" t="n">
+        <v>3</v>
+      </c>
+      <c r="O465" t="n">
+        <v>0</v>
+      </c>
+      <c r="P465" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q465" t="n">
+        <v>0</v>
+      </c>
+      <c r="R465" t="n">
+        <v>0</v>
+      </c>
+      <c r="S465" t="n">
+        <v>3</v>
+      </c>
+      <c r="T465" t="n">
+        <v>2</v>
+      </c>
+      <c r="U465" t="n">
+        <v>1</v>
+      </c>
+      <c r="V465" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W465" t="n">
+        <v>25</v>
+      </c>
+      <c r="X465" t="inlineStr">
+        <is>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA vs ADC BOADILLA</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>2487749</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>A. APARICIO IZQUIERDO | A. JIMENEZ FERNANDEZ | D. RODRIGUEZ GARCIA | M. NIANG | M. RODRÍGUEZ RIVEROL</t>
+        </is>
+      </c>
+      <c r="D466" t="n">
+        <v>5</v>
+      </c>
+      <c r="E466" t="n">
+        <v>37</v>
+      </c>
+      <c r="F466" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="G466" t="n">
+        <v>2</v>
+      </c>
+      <c r="H466" t="n">
+        <v>3</v>
+      </c>
+      <c r="I466" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="J466" t="n">
+        <v>1</v>
+      </c>
+      <c r="K466" t="n">
+        <v>151.52</v>
+      </c>
+      <c r="L466" t="n">
+        <v>300</v>
+      </c>
+      <c r="M466" t="n">
+        <v>-148.48</v>
+      </c>
+      <c r="N466" t="n">
+        <v>0</v>
+      </c>
+      <c r="O466" t="n">
+        <v>3</v>
+      </c>
+      <c r="P466" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q466" t="n">
+        <v>0</v>
+      </c>
+      <c r="R466" t="n">
+        <v>1</v>
+      </c>
+      <c r="S466" t="n">
+        <v>0</v>
+      </c>
+      <c r="T466" t="n">
+        <v>0</v>
+      </c>
+      <c r="U466" t="n">
+        <v>0</v>
+      </c>
+      <c r="V466" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W466" t="n">
+        <v>25</v>
+      </c>
+      <c r="X466" t="inlineStr">
+        <is>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA vs ADC BOADILLA</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>2487749</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>A. APARICIO IZQUIERDO | D. RODRIGUEZ GARCIA | J. RIES | M. NIANG | M. RODRÍGUEZ RIVEROL</t>
+        </is>
+      </c>
+      <c r="D467" t="n">
+        <v>5</v>
+      </c>
+      <c r="E467" t="n">
+        <v>48</v>
+      </c>
+      <c r="F467" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G467" t="n">
+        <v>0</v>
+      </c>
+      <c r="H467" t="n">
+        <v>2</v>
+      </c>
+      <c r="I467" t="n">
+        <v>1</v>
+      </c>
+      <c r="J467" t="n">
+        <v>2</v>
+      </c>
+      <c r="K467" t="n">
+        <v>0</v>
+      </c>
+      <c r="L467" t="n">
+        <v>100</v>
+      </c>
+      <c r="M467" t="n">
+        <v>-100</v>
+      </c>
+      <c r="N467" t="n">
+        <v>0</v>
+      </c>
+      <c r="O467" t="n">
+        <v>0</v>
+      </c>
+      <c r="P467" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q467" t="n">
+        <v>1</v>
+      </c>
+      <c r="R467" t="n">
+        <v>2</v>
+      </c>
+      <c r="S467" t="n">
+        <v>0</v>
+      </c>
+      <c r="T467" t="n">
+        <v>0</v>
+      </c>
+      <c r="U467" t="n">
+        <v>0</v>
+      </c>
+      <c r="V467" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W467" t="n">
+        <v>25</v>
+      </c>
+      <c r="X467" t="inlineStr">
+        <is>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA vs ADC BOADILLA</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>2487748</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>GRUPO EGIDO PINTOBASKET</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>J. AYALA AYLLÓN | L. BERMEJO ALCALDE | M. ALARCON ORTIZ | M. BATLLE BERNARDO | S. RODRIGUEZ GREGORIO</t>
+        </is>
+      </c>
+      <c r="D468" t="n">
+        <v>5</v>
+      </c>
+      <c r="E468" t="n">
+        <v>6</v>
+      </c>
+      <c r="F468" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G468" t="n">
+        <v>0</v>
+      </c>
+      <c r="H468" t="n">
+        <v>0</v>
+      </c>
+      <c r="I468" t="n">
+        <v>1</v>
+      </c>
+      <c r="J468" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K468" t="n">
+        <v>0</v>
+      </c>
+      <c r="L468" t="n">
+        <v>0</v>
+      </c>
+      <c r="M468" t="n">
+        <v>0</v>
+      </c>
+      <c r="N468" t="n">
+        <v>1</v>
+      </c>
+      <c r="O468" t="n">
+        <v>0</v>
+      </c>
+      <c r="P468" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q468" t="n">
+        <v>0</v>
+      </c>
+      <c r="R468" t="n">
+        <v>0</v>
+      </c>
+      <c r="S468" t="n">
+        <v>0</v>
+      </c>
+      <c r="T468" t="n">
+        <v>0</v>
+      </c>
+      <c r="U468" t="n">
+        <v>1</v>
+      </c>
+      <c r="V468" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W468" t="n">
+        <v>25</v>
+      </c>
+      <c r="X468" t="inlineStr">
+        <is>
+          <t>GRUPO EGIDO PINTOBASKET vs RECUCYM BAZU</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>2487748</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>RECUCYM BAZU</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>E. ECHEVERRIA MATEO | G. HIERRO ABAD | J. BARRA DE LA CRUZ | J. MUNRO | V. FERNANDEZ MORAN</t>
+        </is>
+      </c>
+      <c r="D469" t="n">
+        <v>5</v>
+      </c>
+      <c r="E469" t="n">
+        <v>6</v>
+      </c>
+      <c r="F469" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G469" t="n">
+        <v>0</v>
+      </c>
+      <c r="H469" t="n">
+        <v>0</v>
+      </c>
+      <c r="I469" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J469" t="n">
+        <v>1</v>
+      </c>
+      <c r="K469" t="n">
+        <v>0</v>
+      </c>
+      <c r="L469" t="n">
+        <v>0</v>
+      </c>
+      <c r="M469" t="n">
+        <v>0</v>
+      </c>
+      <c r="N469" t="n">
+        <v>0</v>
+      </c>
+      <c r="O469" t="n">
+        <v>0</v>
+      </c>
+      <c r="P469" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q469" t="n">
+        <v>1</v>
+      </c>
+      <c r="R469" t="n">
+        <v>1</v>
+      </c>
+      <c r="S469" t="n">
+        <v>0</v>
+      </c>
+      <c r="T469" t="n">
+        <v>0</v>
+      </c>
+      <c r="U469" t="n">
+        <v>0</v>
+      </c>
+      <c r="V469" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W469" t="n">
+        <v>25</v>
+      </c>
+      <c r="X469" t="inlineStr">
+        <is>
+          <t>GRUPO EGIDO PINTOBASKET vs RECUCYM BAZU</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>2487746</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>LUJISA GUADALAJARA BASKET</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>A. ARMSTRONG | D. EBOLO OLU-ELIJAH | J. HOYA MARTINEZ | L. VALERA VILLEGAS | M. DIALLO</t>
+        </is>
+      </c>
+      <c r="D470" t="n">
+        <v>5</v>
+      </c>
+      <c r="E470" t="n">
+        <v>219</v>
+      </c>
+      <c r="F470" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="G470" t="n">
+        <v>5</v>
+      </c>
+      <c r="H470" t="n">
+        <v>8</v>
+      </c>
+      <c r="I470" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="J470" t="n">
+        <v>7.88</v>
+      </c>
+      <c r="K470" t="n">
+        <v>56.31</v>
+      </c>
+      <c r="L470" t="n">
+        <v>101.52</v>
+      </c>
+      <c r="M470" t="n">
+        <v>-45.22</v>
+      </c>
+      <c r="N470" t="n">
+        <v>4</v>
+      </c>
+      <c r="O470" t="n">
+        <v>2</v>
+      </c>
+      <c r="P470" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q470" t="n">
+        <v>0</v>
+      </c>
+      <c r="R470" t="n">
+        <v>5</v>
+      </c>
+      <c r="S470" t="n">
+        <v>2</v>
+      </c>
+      <c r="T470" t="n">
+        <v>2</v>
+      </c>
+      <c r="U470" t="n">
+        <v>0</v>
+      </c>
+      <c r="V470" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W470" t="n">
+        <v>25</v>
+      </c>
+      <c r="X470" t="inlineStr">
+        <is>
+          <t>UROS DE RIVAS vs LUJISA GUADALAJARA BASKET</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>2487746</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>UROS DE RIVAS</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>A. BIERSACK LOPEZ | A. PEREZ CONTI | C. CRESPO MONTESINOS | P. ESTEBANEZ GONZALEZ | P. ROSSI</t>
+        </is>
+      </c>
+      <c r="D471" t="n">
+        <v>5</v>
+      </c>
+      <c r="E471" t="n">
+        <v>23</v>
+      </c>
+      <c r="F471" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="G471" t="n">
+        <v>0</v>
+      </c>
+      <c r="H471" t="n">
+        <v>0</v>
+      </c>
+      <c r="I471" t="n">
+        <v>0</v>
+      </c>
+      <c r="J471" t="n">
+        <v>1</v>
+      </c>
+      <c r="K471" t="n">
+        <v>0</v>
+      </c>
+      <c r="L471" t="n">
+        <v>0</v>
+      </c>
+      <c r="M471" t="n">
+        <v>0</v>
+      </c>
+      <c r="N471" t="n">
+        <v>0</v>
+      </c>
+      <c r="O471" t="n">
+        <v>0</v>
+      </c>
+      <c r="P471" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q471" t="n">
+        <v>0</v>
+      </c>
+      <c r="R471" t="n">
+        <v>0</v>
+      </c>
+      <c r="S471" t="n">
+        <v>0</v>
+      </c>
+      <c r="T471" t="n">
+        <v>1</v>
+      </c>
+      <c r="U471" t="n">
+        <v>0</v>
+      </c>
+      <c r="V471" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W471" t="n">
+        <v>25</v>
+      </c>
+      <c r="X471" t="inlineStr">
+        <is>
+          <t>UROS DE RIVAS vs LUJISA GUADALAJARA BASKET</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>2487746</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>UROS DE RIVAS</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>A. BIERSACK LOPEZ | D. MARINEZ FERNANDEZ-URRUTIA | O. MENDEZ BLANCO | P. ESTEBANEZ GONZALEZ | P. ROSSI</t>
+        </is>
+      </c>
+      <c r="D472" t="n">
+        <v>5</v>
+      </c>
+      <c r="E472" t="n">
+        <v>74</v>
+      </c>
+      <c r="F472" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="G472" t="n">
+        <v>5</v>
+      </c>
+      <c r="H472" t="n">
+        <v>2</v>
+      </c>
+      <c r="I472" t="n">
+        <v>2</v>
+      </c>
+      <c r="J472" t="n">
+        <v>2</v>
+      </c>
+      <c r="K472" t="n">
+        <v>250</v>
+      </c>
+      <c r="L472" t="n">
+        <v>100</v>
+      </c>
+      <c r="M472" t="n">
+        <v>150</v>
+      </c>
+      <c r="N472" t="n">
+        <v>2</v>
+      </c>
+      <c r="O472" t="n">
+        <v>0</v>
+      </c>
+      <c r="P472" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q472" t="n">
+        <v>0</v>
+      </c>
+      <c r="R472" t="n">
+        <v>1</v>
+      </c>
+      <c r="S472" t="n">
+        <v>0</v>
+      </c>
+      <c r="T472" t="n">
+        <v>1</v>
+      </c>
+      <c r="U472" t="n">
+        <v>0</v>
+      </c>
+      <c r="V472" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W472" t="n">
+        <v>25</v>
+      </c>
+      <c r="X472" t="inlineStr">
+        <is>
+          <t>UROS DE RIVAS vs LUJISA GUADALAJARA BASKET</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>2487746</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>UROS DE RIVAS</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>A. PEREZ CONTI | C. CRESPO MONTESINOS | D. MARINEZ FERNANDEZ-URRUTIA | P. ESTEBANEZ GONZALEZ | P. ROSSI</t>
+        </is>
+      </c>
+      <c r="D473" t="n">
+        <v>5</v>
+      </c>
+      <c r="E473" t="n">
+        <v>79</v>
+      </c>
+      <c r="F473" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="G473" t="n">
+        <v>2</v>
+      </c>
+      <c r="H473" t="n">
+        <v>2</v>
+      </c>
+      <c r="I473" t="n">
+        <v>3</v>
+      </c>
+      <c r="J473" t="n">
+        <v>3</v>
+      </c>
+      <c r="K473" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="L473" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="M473" t="n">
+        <v>0</v>
+      </c>
+      <c r="N473" t="n">
+        <v>3</v>
+      </c>
+      <c r="O473" t="n">
+        <v>0</v>
+      </c>
+      <c r="P473" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q473" t="n">
+        <v>0</v>
+      </c>
+      <c r="R473" t="n">
+        <v>2</v>
+      </c>
+      <c r="S473" t="n">
+        <v>0</v>
+      </c>
+      <c r="T473" t="n">
+        <v>1</v>
+      </c>
+      <c r="U473" t="n">
+        <v>0</v>
+      </c>
+      <c r="V473" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W473" t="n">
+        <v>25</v>
+      </c>
+      <c r="X473" t="inlineStr">
+        <is>
+          <t>UROS DE RIVAS vs LUJISA GUADALAJARA BASKET</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>2487746</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>UROS DE RIVAS</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>A. PEREZ CONTI | C. CRESPO MONTESINOS | G. MARTIN LOPEZ-LAGO | O. MENDEZ BLANCO | P. ESTEBANEZ GONZALEZ</t>
+        </is>
+      </c>
+      <c r="D474" t="n">
+        <v>5</v>
+      </c>
+      <c r="E474" t="n">
+        <v>10</v>
+      </c>
+      <c r="F474" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="G474" t="n">
+        <v>0</v>
+      </c>
+      <c r="H474" t="n">
+        <v>1</v>
+      </c>
+      <c r="I474" t="n">
+        <v>1</v>
+      </c>
+      <c r="J474" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="K474" t="n">
+        <v>0</v>
+      </c>
+      <c r="L474" t="n">
+        <v>53.19</v>
+      </c>
+      <c r="M474" t="n">
+        <v>-53.19</v>
+      </c>
+      <c r="N474" t="n">
+        <v>0</v>
+      </c>
+      <c r="O474" t="n">
+        <v>0</v>
+      </c>
+      <c r="P474" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q474" t="n">
+        <v>0</v>
+      </c>
+      <c r="R474" t="n">
+        <v>0</v>
+      </c>
+      <c r="S474" t="n">
+        <v>2</v>
+      </c>
+      <c r="T474" t="n">
+        <v>1</v>
+      </c>
+      <c r="U474" t="n">
+        <v>0</v>
+      </c>
+      <c r="V474" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W474" t="n">
+        <v>25</v>
+      </c>
+      <c r="X474" t="inlineStr">
+        <is>
+          <t>UROS DE RIVAS vs LUJISA GUADALAJARA BASKET</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>2487746</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>UROS DE RIVAS</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>A. PEREZ CONTI | D. MARINEZ FERNANDEZ-URRUTIA | O. MENDEZ BLANCO | P. ESTEBANEZ GONZALEZ | P. ROSSI</t>
+        </is>
+      </c>
+      <c r="D475" t="n">
+        <v>5</v>
+      </c>
+      <c r="E475" t="n">
+        <v>33</v>
+      </c>
+      <c r="F475" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="G475" t="n">
+        <v>1</v>
+      </c>
+      <c r="H475" t="n">
+        <v>0</v>
+      </c>
+      <c r="I475" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="J475" t="n">
+        <v>1</v>
+      </c>
+      <c r="K475" t="n">
+        <v>53.19</v>
+      </c>
+      <c r="L475" t="n">
+        <v>0</v>
+      </c>
+      <c r="M475" t="n">
+        <v>53.19</v>
+      </c>
+      <c r="N475" t="n">
+        <v>0</v>
+      </c>
+      <c r="O475" t="n">
+        <v>2</v>
+      </c>
+      <c r="P475" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q475" t="n">
+        <v>0</v>
+      </c>
+      <c r="R475" t="n">
+        <v>1</v>
+      </c>
+      <c r="S475" t="n">
+        <v>0</v>
+      </c>
+      <c r="T475" t="n">
+        <v>0</v>
+      </c>
+      <c r="U475" t="n">
+        <v>0</v>
+      </c>
+      <c r="V475" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W475" t="n">
+        <v>25</v>
+      </c>
+      <c r="X475" t="inlineStr">
+        <is>
+          <t>UROS DE RIVAS vs LUJISA GUADALAJARA BASKET</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>2487750</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>C.B. TRES CANTOS</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>D. GONZALEZ LONGARELA | G. DIAZ MONTERO | J. ATIENZA PEREA | J. DE DOMINGO GARAY | N. MAIGA</t>
+        </is>
+      </c>
+      <c r="D476" t="n">
+        <v>5</v>
+      </c>
+      <c r="E476" t="n">
+        <v>71</v>
+      </c>
+      <c r="F476" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="G476" t="n">
+        <v>2</v>
+      </c>
+      <c r="H476" t="n">
+        <v>0</v>
+      </c>
+      <c r="I476" t="n">
+        <v>2</v>
+      </c>
+      <c r="J476" t="n">
+        <v>0</v>
+      </c>
+      <c r="K476" t="n">
+        <v>100</v>
+      </c>
+      <c r="L476" t="n">
+        <v>0</v>
+      </c>
+      <c r="M476" t="n">
+        <v>0</v>
+      </c>
+      <c r="N476" t="n">
+        <v>3</v>
+      </c>
+      <c r="O476" t="n">
+        <v>0</v>
+      </c>
+      <c r="P476" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q476" t="n">
+        <v>1</v>
+      </c>
+      <c r="R476" t="n">
+        <v>1</v>
+      </c>
+      <c r="S476" t="n">
+        <v>0</v>
+      </c>
+      <c r="T476" t="n">
+        <v>1</v>
+      </c>
+      <c r="U476" t="n">
+        <v>2</v>
+      </c>
+      <c r="V476" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W476" t="n">
+        <v>25</v>
+      </c>
+      <c r="X476" t="inlineStr">
+        <is>
+          <t>C.B. TRES CANTOS vs ZENTRO BASKET MADRID</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>2487750</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>C.B. TRES CANTOS</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>D. GONZALEZ LONGARELA | G. DIAZ MONTERO | J. ATIENZA PEREA | J. DOMINGUEZ LARRE | N. MAIGA</t>
+        </is>
+      </c>
+      <c r="D477" t="n">
+        <v>5</v>
+      </c>
+      <c r="E477" t="n">
+        <v>226</v>
+      </c>
+      <c r="F477" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="G477" t="n">
+        <v>5</v>
+      </c>
+      <c r="H477" t="n">
+        <v>8</v>
+      </c>
+      <c r="I477" t="n">
+        <v>6.88</v>
+      </c>
+      <c r="J477" t="n">
+        <v>9.880000000000001</v>
+      </c>
+      <c r="K477" t="n">
+        <v>72.67</v>
+      </c>
+      <c r="L477" t="n">
+        <v>80.97</v>
+      </c>
+      <c r="M477" t="n">
+        <v>-8.300000000000001</v>
+      </c>
+      <c r="N477" t="n">
+        <v>5</v>
+      </c>
+      <c r="O477" t="n">
+        <v>2</v>
+      </c>
+      <c r="P477" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q477" t="n">
+        <v>1</v>
+      </c>
+      <c r="R477" t="n">
+        <v>8</v>
+      </c>
+      <c r="S477" t="n">
+        <v>2</v>
+      </c>
+      <c r="T477" t="n">
+        <v>2</v>
+      </c>
+      <c r="U477" t="n">
+        <v>1</v>
+      </c>
+      <c r="V477" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W477" t="n">
+        <v>25</v>
+      </c>
+      <c r="X477" t="inlineStr">
+        <is>
+          <t>C.B. TRES CANTOS vs ZENTRO BASKET MADRID</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>2487750</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>C.B. TRES CANTOS</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>G. DIAZ MONTERO | G. LARDIES GUILLEN | J. ATIENZA PEREA | J. DE DOMINGO GARAY | N. MAIGA</t>
+        </is>
+      </c>
+      <c r="D478" t="n">
+        <v>5</v>
+      </c>
+      <c r="E478" t="n">
+        <v>108</v>
+      </c>
+      <c r="F478" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G478" t="n">
+        <v>6</v>
+      </c>
+      <c r="H478" t="n">
+        <v>6</v>
+      </c>
+      <c r="I478" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="J478" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="K478" t="n">
+        <v>126.05</v>
+      </c>
+      <c r="L478" t="n">
+        <v>208.33</v>
+      </c>
+      <c r="M478" t="n">
+        <v>-82.28</v>
+      </c>
+      <c r="N478" t="n">
+        <v>3</v>
+      </c>
+      <c r="O478" t="n">
+        <v>4</v>
+      </c>
+      <c r="P478" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q478" t="n">
+        <v>0</v>
+      </c>
+      <c r="R478" t="n">
+        <v>3</v>
+      </c>
+      <c r="S478" t="n">
+        <v>2</v>
+      </c>
+      <c r="T478" t="n">
+        <v>0</v>
+      </c>
+      <c r="U478" t="n">
+        <v>1</v>
+      </c>
+      <c r="V478" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W478" t="n">
+        <v>25</v>
+      </c>
+      <c r="X478" t="inlineStr">
+        <is>
+          <t>C.B. TRES CANTOS vs ZENTRO BASKET MADRID</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>2487750</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>C.B. TRES CANTOS</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>G. DIAZ MONTERO | G. LARDIES GUILLEN | J. ATIENZA PEREA | J. DOMINGUEZ LARRE | N. MAIGA</t>
+        </is>
+      </c>
+      <c r="D479" t="n">
+        <v>5</v>
+      </c>
+      <c r="E479" t="n">
+        <v>7</v>
+      </c>
+      <c r="F479" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="G479" t="n">
+        <v>0</v>
+      </c>
+      <c r="H479" t="n">
+        <v>3</v>
+      </c>
+      <c r="I479" t="n">
+        <v>0</v>
+      </c>
+      <c r="J479" t="n">
+        <v>1</v>
+      </c>
+      <c r="K479" t="n">
+        <v>0</v>
+      </c>
+      <c r="L479" t="n">
+        <v>300</v>
+      </c>
+      <c r="M479" t="n">
+        <v>0</v>
+      </c>
+      <c r="N479" t="n">
+        <v>0</v>
+      </c>
+      <c r="O479" t="n">
+        <v>0</v>
+      </c>
+      <c r="P479" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q479" t="n">
+        <v>0</v>
+      </c>
+      <c r="R479" t="n">
+        <v>1</v>
+      </c>
+      <c r="S479" t="n">
+        <v>0</v>
+      </c>
+      <c r="T479" t="n">
+        <v>0</v>
+      </c>
+      <c r="U479" t="n">
+        <v>0</v>
+      </c>
+      <c r="V479" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W479" t="n">
+        <v>25</v>
+      </c>
+      <c r="X479" t="inlineStr">
+        <is>
+          <t>C.B. TRES CANTOS vs ZENTRO BASKET MADRID</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>2487750</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>C.B. TRES CANTOS</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>G. LARDIES GUILLEN | J. ATIENZA PEREA | J. DE DOMINGO GARAY | J. DOMINGUEZ LARRE | N. MAIGA</t>
+        </is>
+      </c>
+      <c r="D480" t="n">
+        <v>5</v>
+      </c>
+      <c r="E480" t="n">
+        <v>185</v>
+      </c>
+      <c r="F480" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="G480" t="n">
+        <v>5</v>
+      </c>
+      <c r="H480" t="n">
+        <v>4</v>
+      </c>
+      <c r="I480" t="n">
+        <v>3</v>
+      </c>
+      <c r="J480" t="n">
+        <v>5</v>
+      </c>
+      <c r="K480" t="n">
+        <v>166.67</v>
+      </c>
+      <c r="L480" t="n">
+        <v>80</v>
+      </c>
+      <c r="M480" t="n">
+        <v>86.67</v>
+      </c>
+      <c r="N480" t="n">
+        <v>5</v>
+      </c>
+      <c r="O480" t="n">
+        <v>0</v>
+      </c>
+      <c r="P480" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q480" t="n">
+        <v>3</v>
+      </c>
+      <c r="R480" t="n">
+        <v>9</v>
+      </c>
+      <c r="S480" t="n">
+        <v>0</v>
+      </c>
+      <c r="T480" t="n">
+        <v>0</v>
+      </c>
+      <c r="U480" t="n">
+        <v>4</v>
+      </c>
+      <c r="V480" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W480" t="n">
+        <v>25</v>
+      </c>
+      <c r="X480" t="inlineStr">
+        <is>
+          <t>C.B. TRES CANTOS vs ZENTRO BASKET MADRID</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>2487750</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>ZENTRO BASKET MADRID</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>B. SCHUCH | D. VAL GUTIERREZ | G. GOMA | L. SCHIEBELHUT LUIS | M. ESTAPE ROIZ</t>
+        </is>
+      </c>
+      <c r="D481" t="n">
+        <v>5</v>
+      </c>
+      <c r="E481" t="n">
+        <v>541</v>
+      </c>
+      <c r="F481" t="n">
+        <v>9.02</v>
+      </c>
+      <c r="G481" t="n">
+        <v>14</v>
+      </c>
+      <c r="H481" t="n">
+        <v>14</v>
+      </c>
+      <c r="I481" t="n">
+        <v>15.88</v>
+      </c>
+      <c r="J481" t="n">
+        <v>13.88</v>
+      </c>
+      <c r="K481" t="n">
+        <v>88.16</v>
+      </c>
+      <c r="L481" t="n">
+        <v>100.86</v>
+      </c>
+      <c r="M481" t="n">
+        <v>-12.7</v>
+      </c>
+      <c r="N481" t="n">
+        <v>19</v>
+      </c>
+      <c r="O481" t="n">
+        <v>2</v>
+      </c>
+      <c r="P481" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q481" t="n">
+        <v>7</v>
+      </c>
+      <c r="R481" t="n">
+        <v>15</v>
+      </c>
+      <c r="S481" t="n">
+        <v>2</v>
+      </c>
+      <c r="T481" t="n">
+        <v>3</v>
+      </c>
+      <c r="U481" t="n">
+        <v>5</v>
+      </c>
+      <c r="V481" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W481" t="n">
+        <v>25</v>
+      </c>
+      <c r="X481" t="inlineStr">
+        <is>
+          <t>C.B. TRES CANTOS vs ZENTRO BASKET MADRID</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>2487750</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>ZENTRO BASKET MADRID</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>D. VAL GUTIERREZ | G. GOMA | L. SCHIEBELHUT LUIS | M. ESTAPE ROIZ | T. VERDERA BENASSAR</t>
+        </is>
+      </c>
+      <c r="D482" t="n">
+        <v>5</v>
+      </c>
+      <c r="E482" t="n">
+        <v>56</v>
+      </c>
+      <c r="F482" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="G482" t="n">
+        <v>7</v>
+      </c>
+      <c r="H482" t="n">
+        <v>4</v>
+      </c>
+      <c r="I482" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="J482" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="K482" t="n">
+        <v>243.06</v>
+      </c>
+      <c r="L482" t="n">
+        <v>144.93</v>
+      </c>
+      <c r="M482" t="n">
+        <v>98.13</v>
+      </c>
+      <c r="N482" t="n">
+        <v>3</v>
+      </c>
+      <c r="O482" t="n">
+        <v>2</v>
+      </c>
+      <c r="P482" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q482" t="n">
+        <v>1</v>
+      </c>
+      <c r="R482" t="n">
+        <v>1</v>
+      </c>
+      <c r="S482" t="n">
+        <v>4</v>
+      </c>
+      <c r="T482" t="n">
+        <v>0</v>
+      </c>
+      <c r="U482" t="n">
+        <v>0</v>
+      </c>
+      <c r="V482" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W482" t="n">
+        <v>25</v>
+      </c>
+      <c r="X482" t="inlineStr">
+        <is>
+          <t>C.B. TRES CANTOS vs ZENTRO BASKET MADRID</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>2487754</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>ADC BOADILLA</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>A. GOMEZ SERRANO | A. OLMEDO VELASCO | I. BLANCO-ARGIBAY GONZALEZ | J. VILASANCHEZ FREIJOMIL | P. DOMINGUEZ LORENZO</t>
+        </is>
+      </c>
+      <c r="D483" t="n">
+        <v>5</v>
+      </c>
+      <c r="E483" t="n">
+        <v>93</v>
+      </c>
+      <c r="F483" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="G483" t="n">
+        <v>4</v>
+      </c>
+      <c r="H483" t="n">
+        <v>6</v>
+      </c>
+      <c r="I483" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="J483" t="n">
+        <v>3</v>
+      </c>
+      <c r="K483" t="n">
+        <v>138.89</v>
+      </c>
+      <c r="L483" t="n">
+        <v>200</v>
+      </c>
+      <c r="M483" t="n">
+        <v>-61.11</v>
+      </c>
+      <c r="N483" t="n">
+        <v>2</v>
+      </c>
+      <c r="O483" t="n">
+        <v>2</v>
+      </c>
+      <c r="P483" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q483" t="n">
+        <v>0</v>
+      </c>
+      <c r="R483" t="n">
+        <v>4</v>
+      </c>
+      <c r="S483" t="n">
+        <v>0</v>
+      </c>
+      <c r="T483" t="n">
+        <v>0</v>
+      </c>
+      <c r="U483" t="n">
+        <v>1</v>
+      </c>
+      <c r="V483" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W483" t="n">
+        <v>26</v>
+      </c>
+      <c r="X483" t="inlineStr">
+        <is>
+          <t>ADC BOADILLA vs C.B. TRES CANTOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>2487754</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>ADC BOADILLA</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>A. OLMEDO VELASCO | C. CUESTA DE SANTOS | E. BOADA MONTESDEOCA | I. BLANCO-ARGIBAY GONZALEZ | J. VILASANCHEZ FREIJOMIL</t>
+        </is>
+      </c>
+      <c r="D484" t="n">
+        <v>5</v>
+      </c>
+      <c r="E484" t="n">
+        <v>41</v>
+      </c>
+      <c r="F484" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="G484" t="n">
+        <v>0</v>
+      </c>
+      <c r="H484" t="n">
+        <v>0</v>
+      </c>
+      <c r="I484" t="n">
+        <v>2</v>
+      </c>
+      <c r="J484" t="n">
+        <v>0</v>
+      </c>
+      <c r="K484" t="n">
+        <v>0</v>
+      </c>
+      <c r="L484" t="n">
+        <v>0</v>
+      </c>
+      <c r="M484" t="n">
+        <v>0</v>
+      </c>
+      <c r="N484" t="n">
+        <v>1</v>
+      </c>
+      <c r="O484" t="n">
+        <v>0</v>
+      </c>
+      <c r="P484" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q484" t="n">
+        <v>0</v>
+      </c>
+      <c r="R484" t="n">
+        <v>0</v>
+      </c>
+      <c r="S484" t="n">
+        <v>0</v>
+      </c>
+      <c r="T484" t="n">
+        <v>0</v>
+      </c>
+      <c r="U484" t="n">
+        <v>0</v>
+      </c>
+      <c r="V484" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W484" t="n">
+        <v>26</v>
+      </c>
+      <c r="X484" t="inlineStr">
+        <is>
+          <t>ADC BOADILLA vs C.B. TRES CANTOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>2487754</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>ADC BOADILLA</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>A. OLMEDO VELASCO | C. CUESTA DE SANTOS | I. BLANCO-ARGIBAY GONZALEZ | J. VILASANCHEZ FREIJOMIL | P. DOMINGUEZ LORENZO</t>
+        </is>
+      </c>
+      <c r="D485" t="n">
+        <v>5</v>
+      </c>
+      <c r="E485" t="n">
+        <v>106</v>
+      </c>
+      <c r="F485" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="G485" t="n">
+        <v>4</v>
+      </c>
+      <c r="H485" t="n">
+        <v>1</v>
+      </c>
+      <c r="I485" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="J485" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="K485" t="n">
+        <v>172.41</v>
+      </c>
+      <c r="L485" t="n">
+        <v>25.77</v>
+      </c>
+      <c r="M485" t="n">
+        <v>146.64</v>
+      </c>
+      <c r="N485" t="n">
+        <v>1</v>
+      </c>
+      <c r="O485" t="n">
+        <v>3</v>
+      </c>
+      <c r="P485" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q485" t="n">
+        <v>1</v>
+      </c>
+      <c r="R485" t="n">
+        <v>1</v>
+      </c>
+      <c r="S485" t="n">
+        <v>2</v>
+      </c>
+      <c r="T485" t="n">
+        <v>2</v>
+      </c>
+      <c r="U485" t="n">
+        <v>0</v>
+      </c>
+      <c r="V485" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W485" t="n">
+        <v>26</v>
+      </c>
+      <c r="X485" t="inlineStr">
+        <is>
+          <t>ADC BOADILLA vs C.B. TRES CANTOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>2487754</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>C.B. TRES CANTOS</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>A. SIMON DEL CORRAL | D. FERNANDEZ CAÑAS | G. LARDIES GUILLEN | H. PEREZ SANCHEZ | J. ATIENZA PEREA</t>
+        </is>
+      </c>
+      <c r="D486" t="n">
+        <v>5</v>
+      </c>
+      <c r="E486" t="n">
+        <v>33</v>
+      </c>
+      <c r="F486" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="G486" t="n">
+        <v>2</v>
+      </c>
+      <c r="H486" t="n">
+        <v>2</v>
+      </c>
+      <c r="I486" t="n">
+        <v>1</v>
+      </c>
+      <c r="J486" t="n">
+        <v>1</v>
+      </c>
+      <c r="K486" t="n">
+        <v>200</v>
+      </c>
+      <c r="L486" t="n">
+        <v>200</v>
+      </c>
+      <c r="M486" t="n">
+        <v>0</v>
+      </c>
+      <c r="N486" t="n">
+        <v>2</v>
+      </c>
+      <c r="O486" t="n">
+        <v>0</v>
+      </c>
+      <c r="P486" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q486" t="n">
+        <v>1</v>
+      </c>
+      <c r="R486" t="n">
+        <v>1</v>
+      </c>
+      <c r="S486" t="n">
+        <v>0</v>
+      </c>
+      <c r="T486" t="n">
+        <v>0</v>
+      </c>
+      <c r="U486" t="n">
+        <v>0</v>
+      </c>
+      <c r="V486" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W486" t="n">
+        <v>26</v>
+      </c>
+      <c r="X486" t="inlineStr">
+        <is>
+          <t>ADC BOADILLA vs C.B. TRES CANTOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>2487754</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>C.B. TRES CANTOS</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>D. FERNANDEZ CAÑAS | G. DIAZ MONTERO | G. LARDIES GUILLEN | J. ATIENZA PEREA | J. DE DOMINGO GARAY</t>
+        </is>
+      </c>
+      <c r="D487" t="n">
+        <v>5</v>
+      </c>
+      <c r="E487" t="n">
+        <v>60</v>
+      </c>
+      <c r="F487" t="n">
+        <v>1</v>
+      </c>
+      <c r="G487" t="n">
+        <v>4</v>
+      </c>
+      <c r="H487" t="n">
+        <v>2</v>
+      </c>
+      <c r="I487" t="n">
+        <v>2</v>
+      </c>
+      <c r="J487" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="K487" t="n">
+        <v>200</v>
+      </c>
+      <c r="L487" t="n">
+        <v>106.38</v>
+      </c>
+      <c r="M487" t="n">
+        <v>93.62</v>
+      </c>
+      <c r="N487" t="n">
+        <v>2</v>
+      </c>
+      <c r="O487" t="n">
+        <v>0</v>
+      </c>
+      <c r="P487" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q487" t="n">
+        <v>0</v>
+      </c>
+      <c r="R487" t="n">
+        <v>1</v>
+      </c>
+      <c r="S487" t="n">
+        <v>2</v>
+      </c>
+      <c r="T487" t="n">
+        <v>0</v>
+      </c>
+      <c r="U487" t="n">
+        <v>0</v>
+      </c>
+      <c r="V487" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W487" t="n">
+        <v>26</v>
+      </c>
+      <c r="X487" t="inlineStr">
+        <is>
+          <t>ADC BOADILLA vs C.B. TRES CANTOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>2487754</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>C.B. TRES CANTOS</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>D. FERNANDEZ CAÑAS | G. DIAZ MONTERO | J. ATIENZA PEREA | J. DE DOMINGO GARAY | N. MAIGA</t>
+        </is>
+      </c>
+      <c r="D488" t="n">
+        <v>5</v>
+      </c>
+      <c r="E488" t="n">
+        <v>80</v>
+      </c>
+      <c r="F488" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="G488" t="n">
+        <v>0</v>
+      </c>
+      <c r="H488" t="n">
+        <v>2</v>
+      </c>
+      <c r="I488" t="n">
+        <v>2</v>
+      </c>
+      <c r="J488" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="K488" t="n">
+        <v>0</v>
+      </c>
+      <c r="L488" t="n">
+        <v>227.27</v>
+      </c>
+      <c r="M488" t="n">
+        <v>-227.27</v>
+      </c>
+      <c r="N488" t="n">
+        <v>1</v>
+      </c>
+      <c r="O488" t="n">
+        <v>0</v>
+      </c>
+      <c r="P488" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q488" t="n">
+        <v>0</v>
+      </c>
+      <c r="R488" t="n">
+        <v>0</v>
+      </c>
+      <c r="S488" t="n">
+        <v>2</v>
+      </c>
+      <c r="T488" t="n">
+        <v>1</v>
+      </c>
+      <c r="U488" t="n">
+        <v>1</v>
+      </c>
+      <c r="V488" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W488" t="n">
+        <v>26</v>
+      </c>
+      <c r="X488" t="inlineStr">
+        <is>
+          <t>ADC BOADILLA vs C.B. TRES CANTOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>2487754</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>C.B. TRES CANTOS</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>G. DIAZ MONTERO | G. LARDIES GUILLEN | J. ATIENZA PEREA | J. DE DOMINGO GARAY | N. MAIGA</t>
+        </is>
+      </c>
+      <c r="D489" t="n">
+        <v>5</v>
+      </c>
+      <c r="E489" t="n">
+        <v>67</v>
+      </c>
+      <c r="F489" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="G489" t="n">
+        <v>1</v>
+      </c>
+      <c r="H489" t="n">
+        <v>2</v>
+      </c>
+      <c r="I489" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="J489" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="K489" t="n">
+        <v>53.19</v>
+      </c>
+      <c r="L489" t="n">
+        <v>58.14</v>
+      </c>
+      <c r="M489" t="n">
+        <v>-4.95</v>
+      </c>
+      <c r="N489" t="n">
+        <v>0</v>
+      </c>
+      <c r="O489" t="n">
+        <v>2</v>
+      </c>
+      <c r="P489" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q489" t="n">
+        <v>0</v>
+      </c>
+      <c r="R489" t="n">
+        <v>2</v>
+      </c>
+      <c r="S489" t="n">
+        <v>1</v>
+      </c>
+      <c r="T489" t="n">
+        <v>1</v>
+      </c>
+      <c r="U489" t="n">
+        <v>0</v>
+      </c>
+      <c r="V489" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W489" t="n">
+        <v>26</v>
+      </c>
+      <c r="X489" t="inlineStr">
+        <is>
+          <t>ADC BOADILLA vs C.B. TRES CANTOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>2487756</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>GRUPO EGIDO PINTOBASKET</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>J. AYALA AYLLÓN | J. SAEZ BENITO | L. BERMEJO ALCALDE | M. ALARCON ORTIZ | M. BATLLE BERNARDO</t>
+        </is>
+      </c>
+      <c r="D490" t="n">
+        <v>5</v>
+      </c>
+      <c r="E490" t="n">
+        <v>51</v>
+      </c>
+      <c r="F490" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G490" t="n">
+        <v>2</v>
+      </c>
+      <c r="H490" t="n">
+        <v>0</v>
+      </c>
+      <c r="I490" t="n">
+        <v>0</v>
+      </c>
+      <c r="J490" t="n">
+        <v>2</v>
+      </c>
+      <c r="K490" t="n">
+        <v>0</v>
+      </c>
+      <c r="L490" t="n">
+        <v>0</v>
+      </c>
+      <c r="M490" t="n">
+        <v>0</v>
+      </c>
+      <c r="N490" t="n">
+        <v>1</v>
+      </c>
+      <c r="O490" t="n">
+        <v>0</v>
+      </c>
+      <c r="P490" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q490" t="n">
+        <v>1</v>
+      </c>
+      <c r="R490" t="n">
+        <v>1</v>
+      </c>
+      <c r="S490" t="n">
+        <v>0</v>
+      </c>
+      <c r="T490" t="n">
+        <v>1</v>
+      </c>
+      <c r="U490" t="n">
+        <v>0</v>
+      </c>
+      <c r="V490" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W490" t="n">
+        <v>26</v>
+      </c>
+      <c r="X490" t="inlineStr">
+        <is>
+          <t>REAL CANOE N.C. vs GRUPO EGIDO PINTOBASKET</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>2487756</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>GRUPO EGIDO PINTOBASKET</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>J. AYALA AYLLÓN | J. SAEZ BENITO | L. BERMEJO ALCALDE | M. BATLLE BERNARDO | S. RODRIGUEZ GREGORIO</t>
+        </is>
+      </c>
+      <c r="D491" t="n">
+        <v>5</v>
+      </c>
+      <c r="E491" t="n">
+        <v>121</v>
+      </c>
+      <c r="F491" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="G491" t="n">
+        <v>2</v>
+      </c>
+      <c r="H491" t="n">
+        <v>5</v>
+      </c>
+      <c r="I491" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="J491" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="K491" t="n">
+        <v>53.19</v>
+      </c>
+      <c r="L491" t="n">
+        <v>215.52</v>
+      </c>
+      <c r="M491" t="n">
+        <v>-162.33</v>
+      </c>
+      <c r="N491" t="n">
+        <v>2</v>
+      </c>
+      <c r="O491" t="n">
+        <v>4</v>
+      </c>
+      <c r="P491" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q491" t="n">
+        <v>1</v>
+      </c>
+      <c r="R491" t="n">
+        <v>3</v>
+      </c>
+      <c r="S491" t="n">
+        <v>3</v>
+      </c>
+      <c r="T491" t="n">
+        <v>0</v>
+      </c>
+      <c r="U491" t="n">
+        <v>2</v>
+      </c>
+      <c r="V491" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W491" t="n">
+        <v>26</v>
+      </c>
+      <c r="X491" t="inlineStr">
+        <is>
+          <t>REAL CANOE N.C. vs GRUPO EGIDO PINTOBASKET</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>2487756</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>GRUPO EGIDO PINTOBASKET</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>J. AYALA AYLLÓN | J. SAEZ BENITO | M. ALARCON ORTIZ | M. BATLLE BERNARDO | M. DEL VALLE REGALADO</t>
+        </is>
+      </c>
+      <c r="D492" t="n">
+        <v>5</v>
+      </c>
+      <c r="E492" t="n">
+        <v>52</v>
+      </c>
+      <c r="F492" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="G492" t="n">
+        <v>2</v>
+      </c>
+      <c r="H492" t="n">
+        <v>2</v>
+      </c>
+      <c r="I492" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="J492" t="n">
+        <v>1</v>
+      </c>
+      <c r="K492" t="n">
+        <v>69.44</v>
+      </c>
+      <c r="L492" t="n">
+        <v>200</v>
+      </c>
+      <c r="M492" t="n">
+        <v>-130.56</v>
+      </c>
+      <c r="N492" t="n">
+        <v>1</v>
+      </c>
+      <c r="O492" t="n">
+        <v>2</v>
+      </c>
+      <c r="P492" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q492" t="n">
+        <v>0</v>
+      </c>
+      <c r="R492" t="n">
+        <v>1</v>
+      </c>
+      <c r="S492" t="n">
+        <v>0</v>
+      </c>
+      <c r="T492" t="n">
+        <v>1</v>
+      </c>
+      <c r="U492" t="n">
+        <v>1</v>
+      </c>
+      <c r="V492" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W492" t="n">
+        <v>26</v>
+      </c>
+      <c r="X492" t="inlineStr">
+        <is>
+          <t>REAL CANOE N.C. vs GRUPO EGIDO PINTOBASKET</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>2487756</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>GRUPO EGIDO PINTOBASKET</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>J. AYALA AYLLÓN | L. BERMEJO ALCALDE | M. ALARCON ORTIZ | M. BATLLE BERNARDO | S. RODRIGUEZ GREGORIO</t>
+        </is>
+      </c>
+      <c r="D493" t="n">
+        <v>5</v>
+      </c>
+      <c r="E493" t="n">
+        <v>64</v>
+      </c>
+      <c r="F493" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="G493" t="n">
+        <v>0</v>
+      </c>
+      <c r="H493" t="n">
+        <v>0</v>
+      </c>
+      <c r="I493" t="n">
+        <v>2</v>
+      </c>
+      <c r="J493" t="n">
+        <v>2</v>
+      </c>
+      <c r="K493" t="n">
+        <v>0</v>
+      </c>
+      <c r="L493" t="n">
+        <v>0</v>
+      </c>
+      <c r="M493" t="n">
+        <v>0</v>
+      </c>
+      <c r="N493" t="n">
+        <v>1</v>
+      </c>
+      <c r="O493" t="n">
+        <v>0</v>
+      </c>
+      <c r="P493" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q493" t="n">
+        <v>0</v>
+      </c>
+      <c r="R493" t="n">
+        <v>3</v>
+      </c>
+      <c r="S493" t="n">
+        <v>0</v>
+      </c>
+      <c r="T493" t="n">
+        <v>0</v>
+      </c>
+      <c r="U493" t="n">
+        <v>1</v>
+      </c>
+      <c r="V493" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W493" t="n">
+        <v>26</v>
+      </c>
+      <c r="X493" t="inlineStr">
+        <is>
+          <t>REAL CANOE N.C. vs GRUPO EGIDO PINTOBASKET</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>2487756</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>REAL CANOE N.C.</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>D. MANZANERO CAMACHO | J. GARCIA-LARRACHE SEGURA | J. LAPASTORA ARACIL | L. GARCIA LARRACHE SEGURA | M. KREISLER LORENTE</t>
+        </is>
+      </c>
+      <c r="D494" t="n">
+        <v>5</v>
+      </c>
+      <c r="E494" t="n">
+        <v>139</v>
+      </c>
+      <c r="F494" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="G494" t="n">
+        <v>5</v>
+      </c>
+      <c r="H494" t="n">
+        <v>2</v>
+      </c>
+      <c r="I494" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="J494" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="K494" t="n">
+        <v>150.6</v>
+      </c>
+      <c r="L494" t="n">
+        <v>53.19</v>
+      </c>
+      <c r="M494" t="n">
+        <v>97.41</v>
+      </c>
+      <c r="N494" t="n">
+        <v>4</v>
+      </c>
+      <c r="O494" t="n">
+        <v>3</v>
+      </c>
+      <c r="P494" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q494" t="n">
+        <v>2</v>
+      </c>
+      <c r="R494" t="n">
+        <v>2</v>
+      </c>
+      <c r="S494" t="n">
+        <v>4</v>
+      </c>
+      <c r="T494" t="n">
+        <v>1</v>
+      </c>
+      <c r="U494" t="n">
+        <v>1</v>
+      </c>
+      <c r="V494" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W494" t="n">
+        <v>26</v>
+      </c>
+      <c r="X494" t="inlineStr">
+        <is>
+          <t>REAL CANOE N.C. vs GRUPO EGIDO PINTOBASKET</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>2487756</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>REAL CANOE N.C.</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>D. MANZANERO CAMACHO | J. GARCIA-LARRACHE SEGURA | L. GARCIA LARRACHE SEGURA | M. HERMOSO ALCUBILLA | P. FUENTE DIEZ</t>
+        </is>
+      </c>
+      <c r="D495" t="n">
+        <v>5</v>
+      </c>
+      <c r="E495" t="n">
+        <v>52</v>
+      </c>
+      <c r="F495" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="G495" t="n">
+        <v>2</v>
+      </c>
+      <c r="H495" t="n">
+        <v>2</v>
+      </c>
+      <c r="I495" t="n">
+        <v>1</v>
+      </c>
+      <c r="J495" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="K495" t="n">
+        <v>200</v>
+      </c>
+      <c r="L495" t="n">
+        <v>69.44</v>
+      </c>
+      <c r="M495" t="n">
+        <v>130.56</v>
+      </c>
+      <c r="N495" t="n">
+        <v>1</v>
+      </c>
+      <c r="O495" t="n">
+        <v>0</v>
+      </c>
+      <c r="P495" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q495" t="n">
+        <v>1</v>
+      </c>
+      <c r="R495" t="n">
+        <v>1</v>
+      </c>
+      <c r="S495" t="n">
+        <v>2</v>
+      </c>
+      <c r="T495" t="n">
+        <v>1</v>
+      </c>
+      <c r="U495" t="n">
+        <v>0</v>
+      </c>
+      <c r="V495" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W495" t="n">
+        <v>26</v>
+      </c>
+      <c r="X495" t="inlineStr">
+        <is>
+          <t>REAL CANOE N.C. vs GRUPO EGIDO PINTOBASKET</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>2487756</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>REAL CANOE N.C.</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>D. MANZANERO CAMACHO | J. LAPASTORA ARACIL | L. GARCIA LARRACHE SEGURA | M. HERMOSO ALCUBILLA | P. FUENTE DIEZ</t>
+        </is>
+      </c>
+      <c r="D496" t="n">
+        <v>5</v>
+      </c>
+      <c r="E496" t="n">
+        <v>97</v>
+      </c>
+      <c r="F496" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="G496" t="n">
+        <v>0</v>
+      </c>
+      <c r="H496" t="n">
+        <v>2</v>
+      </c>
+      <c r="I496" t="n">
+        <v>3</v>
+      </c>
+      <c r="J496" t="n">
+        <v>2</v>
+      </c>
+      <c r="K496" t="n">
+        <v>0</v>
+      </c>
+      <c r="L496" t="n">
+        <v>100</v>
+      </c>
+      <c r="M496" t="n">
+        <v>-100</v>
+      </c>
+      <c r="N496" t="n">
+        <v>3</v>
+      </c>
+      <c r="O496" t="n">
+        <v>0</v>
+      </c>
+      <c r="P496" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q496" t="n">
+        <v>1</v>
+      </c>
+      <c r="R496" t="n">
+        <v>2</v>
+      </c>
+      <c r="S496" t="n">
+        <v>0</v>
+      </c>
+      <c r="T496" t="n">
+        <v>1</v>
+      </c>
+      <c r="U496" t="n">
+        <v>1</v>
+      </c>
+      <c r="V496" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W496" t="n">
+        <v>26</v>
+      </c>
+      <c r="X496" t="inlineStr">
+        <is>
+          <t>REAL CANOE N.C. vs GRUPO EGIDO PINTOBASKET</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>2487758</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>CB ARIDANE</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>A. GASE SECO | G. MEJÍA ACOSTA | G. PIERRE-GABRIEL ANDREA GASTON | J. ABRIL RAMIRO | O. BALSELLS PLAZA</t>
+        </is>
+      </c>
+      <c r="D497" t="n">
+        <v>5</v>
+      </c>
+      <c r="E497" t="n">
+        <v>82</v>
+      </c>
+      <c r="F497" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="G497" t="n">
+        <v>0</v>
+      </c>
+      <c r="H497" t="n">
+        <v>2</v>
+      </c>
+      <c r="I497" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="J497" t="n">
+        <v>3</v>
+      </c>
+      <c r="K497" t="n">
+        <v>0</v>
+      </c>
+      <c r="L497" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="M497" t="n">
+        <v>-66.67</v>
+      </c>
+      <c r="N497" t="n">
+        <v>0</v>
+      </c>
+      <c r="O497" t="n">
+        <v>2</v>
+      </c>
+      <c r="P497" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q497" t="n">
+        <v>0</v>
+      </c>
+      <c r="R497" t="n">
+        <v>5</v>
+      </c>
+      <c r="S497" t="n">
+        <v>0</v>
+      </c>
+      <c r="T497" t="n">
+        <v>0</v>
+      </c>
+      <c r="U497" t="n">
+        <v>2</v>
+      </c>
+      <c r="V497" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W497" t="n">
+        <v>26</v>
+      </c>
+      <c r="X497" t="inlineStr">
+        <is>
+          <t>CB ARIDANE vs UROS DE RIVAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>2487758</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>CB ARIDANE</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>A. GASE SECO | G. MEJÍA ACOSTA | G. PIERRE-GABRIEL ANDREA GASTON | J. GONZÁLEZ CHÁVEZ | K. SKUTYELNIK</t>
+        </is>
+      </c>
+      <c r="D498" t="n">
+        <v>5</v>
+      </c>
+      <c r="E498" t="n">
+        <v>3</v>
+      </c>
+      <c r="F498" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G498" t="n">
+        <v>2</v>
+      </c>
+      <c r="H498" t="n">
+        <v>0</v>
+      </c>
+      <c r="I498" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="J498" t="n">
+        <v>0</v>
+      </c>
+      <c r="K498" t="n">
+        <v>227.27</v>
+      </c>
+      <c r="L498" t="n">
+        <v>0</v>
+      </c>
+      <c r="M498" t="n">
+        <v>0</v>
+      </c>
+      <c r="N498" t="n">
+        <v>0</v>
+      </c>
+      <c r="O498" t="n">
+        <v>2</v>
+      </c>
+      <c r="P498" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q498" t="n">
+        <v>0</v>
+      </c>
+      <c r="R498" t="n">
+        <v>0</v>
+      </c>
+      <c r="S498" t="n">
+        <v>0</v>
+      </c>
+      <c r="T498" t="n">
+        <v>0</v>
+      </c>
+      <c r="U498" t="n">
+        <v>0</v>
+      </c>
+      <c r="V498" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W498" t="n">
+        <v>26</v>
+      </c>
+      <c r="X498" t="inlineStr">
+        <is>
+          <t>CB ARIDANE vs UROS DE RIVAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>2487758</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>CB ARIDANE</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>A. GASE SECO | G. MEJÍA ACOSTA | G. PIERRE-GABRIEL ANDREA GASTON | J. GONZÁLEZ CHÁVEZ | O. BALSELLS PLAZA</t>
+        </is>
+      </c>
+      <c r="D499" t="n">
+        <v>5</v>
+      </c>
+      <c r="E499" t="n">
+        <v>180</v>
+      </c>
+      <c r="F499" t="n">
+        <v>3</v>
+      </c>
+      <c r="G499" t="n">
+        <v>7</v>
+      </c>
+      <c r="H499" t="n">
+        <v>0</v>
+      </c>
+      <c r="I499" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="J499" t="n">
+        <v>5</v>
+      </c>
+      <c r="K499" t="n">
+        <v>180.41</v>
+      </c>
+      <c r="L499" t="n">
+        <v>0</v>
+      </c>
+      <c r="M499" t="n">
+        <v>180.41</v>
+      </c>
+      <c r="N499" t="n">
+        <v>4</v>
+      </c>
+      <c r="O499" t="n">
+        <v>2</v>
+      </c>
+      <c r="P499" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q499" t="n">
+        <v>3</v>
+      </c>
+      <c r="R499" t="n">
+        <v>6</v>
+      </c>
+      <c r="S499" t="n">
+        <v>0</v>
+      </c>
+      <c r="T499" t="n">
+        <v>0</v>
+      </c>
+      <c r="U499" t="n">
+        <v>1</v>
+      </c>
+      <c r="V499" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W499" t="n">
+        <v>26</v>
+      </c>
+      <c r="X499" t="inlineStr">
+        <is>
+          <t>CB ARIDANE vs UROS DE RIVAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>2487758</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>CB ARIDANE</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>A. GASE SECO | G. MEJÍA ACOSTA | G. PIERRE-GABRIEL ANDREA GASTON | K. SKUTYELNIK | O. BALSELLS PLAZA</t>
+        </is>
+      </c>
+      <c r="D500" t="n">
+        <v>5</v>
+      </c>
+      <c r="E500" t="n">
+        <v>8</v>
+      </c>
+      <c r="F500" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="G500" t="n">
+        <v>2</v>
+      </c>
+      <c r="H500" t="n">
+        <v>4</v>
+      </c>
+      <c r="I500" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="J500" t="n">
+        <v>2</v>
+      </c>
+      <c r="K500" t="n">
+        <v>227.27</v>
+      </c>
+      <c r="L500" t="n">
+        <v>200</v>
+      </c>
+      <c r="M500" t="n">
+        <v>27.27</v>
+      </c>
+      <c r="N500" t="n">
+        <v>0</v>
+      </c>
+      <c r="O500" t="n">
+        <v>2</v>
+      </c>
+      <c r="P500" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q500" t="n">
+        <v>0</v>
+      </c>
+      <c r="R500" t="n">
+        <v>2</v>
+      </c>
+      <c r="S500" t="n">
+        <v>0</v>
+      </c>
+      <c r="T500" t="n">
+        <v>0</v>
+      </c>
+      <c r="U500" t="n">
+        <v>0</v>
+      </c>
+      <c r="V500" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W500" t="n">
+        <v>26</v>
+      </c>
+      <c r="X500" t="inlineStr">
+        <is>
+          <t>CB ARIDANE vs UROS DE RIVAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>2487758</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>CB ARIDANE</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>A. GASE SECO | G. MEJÍA ACOSTA | J. GONZÁLEZ CHÁVEZ | O. BALSELLS PLAZA | S. GUEYE</t>
+        </is>
+      </c>
+      <c r="D501" t="n">
+        <v>5</v>
+      </c>
+      <c r="E501" t="n">
+        <v>19</v>
+      </c>
+      <c r="F501" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="G501" t="n">
+        <v>1</v>
+      </c>
+      <c r="H501" t="n">
+        <v>0</v>
+      </c>
+      <c r="I501" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="J501" t="n">
+        <v>0</v>
+      </c>
+      <c r="K501" t="n">
+        <v>113.64</v>
+      </c>
+      <c r="L501" t="n">
+        <v>0</v>
+      </c>
+      <c r="M501" t="n">
+        <v>0</v>
+      </c>
+      <c r="N501" t="n">
+        <v>1</v>
+      </c>
+      <c r="O501" t="n">
+        <v>2</v>
+      </c>
+      <c r="P501" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q501" t="n">
+        <v>1</v>
+      </c>
+      <c r="R501" t="n">
+        <v>0</v>
+      </c>
+      <c r="S501" t="n">
+        <v>0</v>
+      </c>
+      <c r="T501" t="n">
+        <v>0</v>
+      </c>
+      <c r="U501" t="n">
+        <v>0</v>
+      </c>
+      <c r="V501" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W501" t="n">
+        <v>26</v>
+      </c>
+      <c r="X501" t="inlineStr">
+        <is>
+          <t>CB ARIDANE vs UROS DE RIVAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>2487758</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>UROS DE RIVAS</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>A. BIERSACK LOPEZ | A. GARCIA QUILEZ CUERVAS | A. PEREZ CONTI | O. MENDEZ BLANCO | P. ESTEBANEZ GONZALEZ</t>
+        </is>
+      </c>
+      <c r="D502" t="n">
+        <v>5</v>
+      </c>
+      <c r="E502" t="n">
+        <v>151</v>
+      </c>
+      <c r="F502" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="G502" t="n">
+        <v>0</v>
+      </c>
+      <c r="H502" t="n">
+        <v>3</v>
+      </c>
+      <c r="I502" t="n">
+        <v>4</v>
+      </c>
+      <c r="J502" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="K502" t="n">
+        <v>0</v>
+      </c>
+      <c r="L502" t="n">
+        <v>77.31999999999999</v>
+      </c>
+      <c r="M502" t="n">
+        <v>-77.31999999999999</v>
+      </c>
+      <c r="N502" t="n">
+        <v>7</v>
+      </c>
+      <c r="O502" t="n">
+        <v>0</v>
+      </c>
+      <c r="P502" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q502" t="n">
+        <v>3</v>
+      </c>
+      <c r="R502" t="n">
+        <v>3</v>
+      </c>
+      <c r="S502" t="n">
+        <v>2</v>
+      </c>
+      <c r="T502" t="n">
+        <v>1</v>
+      </c>
+      <c r="U502" t="n">
+        <v>1</v>
+      </c>
+      <c r="V502" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W502" t="n">
+        <v>26</v>
+      </c>
+      <c r="X502" t="inlineStr">
+        <is>
+          <t>CB ARIDANE vs UROS DE RIVAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>2487758</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>UROS DE RIVAS</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>A. BIERSACK LOPEZ | C. CRESPO MONTESINOS | D. MARINEZ FERNANDEZ-URRUTIA | G. MARTIN LOPEZ-LAGO | O. HADI ADEGBITE</t>
+        </is>
+      </c>
+      <c r="D503" t="n">
+        <v>5</v>
+      </c>
+      <c r="E503" t="n">
+        <v>66</v>
+      </c>
+      <c r="F503" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="G503" t="n">
+        <v>0</v>
+      </c>
+      <c r="H503" t="n">
+        <v>3</v>
+      </c>
+      <c r="I503" t="n">
+        <v>2</v>
+      </c>
+      <c r="J503" t="n">
+        <v>1</v>
+      </c>
+      <c r="K503" t="n">
+        <v>0</v>
+      </c>
+      <c r="L503" t="n">
+        <v>300</v>
+      </c>
+      <c r="M503" t="n">
+        <v>-300</v>
+      </c>
+      <c r="N503" t="n">
+        <v>2</v>
+      </c>
+      <c r="O503" t="n">
+        <v>0</v>
+      </c>
+      <c r="P503" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q503" t="n">
+        <v>0</v>
+      </c>
+      <c r="R503" t="n">
+        <v>2</v>
+      </c>
+      <c r="S503" t="n">
+        <v>0</v>
+      </c>
+      <c r="T503" t="n">
+        <v>0</v>
+      </c>
+      <c r="U503" t="n">
+        <v>1</v>
+      </c>
+      <c r="V503" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W503" t="n">
+        <v>26</v>
+      </c>
+      <c r="X503" t="inlineStr">
+        <is>
+          <t>CB ARIDANE vs UROS DE RIVAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>2487758</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>UROS DE RIVAS</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>A. BIERSACK LOPEZ | C. CRESPO MONTESINOS | D. MARINEZ FERNANDEZ-URRUTIA | G. MARTIN LOPEZ-LAGO | O. MENDEZ BLANCO</t>
+        </is>
+      </c>
+      <c r="D504" t="n">
+        <v>5</v>
+      </c>
+      <c r="E504" t="n">
+        <v>41</v>
+      </c>
+      <c r="F504" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="G504" t="n">
+        <v>0</v>
+      </c>
+      <c r="H504" t="n">
+        <v>1</v>
+      </c>
+      <c r="I504" t="n">
+        <v>1</v>
+      </c>
+      <c r="J504" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="K504" t="n">
+        <v>0</v>
+      </c>
+      <c r="L504" t="n">
+        <v>113.64</v>
+      </c>
+      <c r="M504" t="n">
+        <v>-113.64</v>
+      </c>
+      <c r="N504" t="n">
+        <v>1</v>
+      </c>
+      <c r="O504" t="n">
+        <v>0</v>
+      </c>
+      <c r="P504" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q504" t="n">
+        <v>0</v>
+      </c>
+      <c r="R504" t="n">
+        <v>0</v>
+      </c>
+      <c r="S504" t="n">
+        <v>2</v>
+      </c>
+      <c r="T504" t="n">
+        <v>1</v>
+      </c>
+      <c r="U504" t="n">
+        <v>1</v>
+      </c>
+      <c r="V504" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W504" t="n">
+        <v>26</v>
+      </c>
+      <c r="X504" t="inlineStr">
+        <is>
+          <t>CB ARIDANE vs UROS DE RIVAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>2487758</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>UROS DE RIVAS</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>A. BIERSACK LOPEZ | C. CRESPO MONTESINOS | D. MARINEZ FERNANDEZ-URRUTIA | O. HADI ADEGBITE | O. MENDEZ BLANCO</t>
+        </is>
+      </c>
+      <c r="D505" t="n">
+        <v>5</v>
+      </c>
+      <c r="E505" t="n">
+        <v>1</v>
+      </c>
+      <c r="F505" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G505" t="n">
+        <v>0</v>
+      </c>
+      <c r="H505" t="n">
+        <v>1</v>
+      </c>
+      <c r="I505" t="n">
+        <v>0</v>
+      </c>
+      <c r="J505" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="K505" t="n">
+        <v>0</v>
+      </c>
+      <c r="L505" t="n">
+        <v>0</v>
+      </c>
+      <c r="M505" t="n">
+        <v>0</v>
+      </c>
+      <c r="N505" t="n">
+        <v>0</v>
+      </c>
+      <c r="O505" t="n">
+        <v>0</v>
+      </c>
+      <c r="P505" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q505" t="n">
+        <v>0</v>
+      </c>
+      <c r="R505" t="n">
+        <v>0</v>
+      </c>
+      <c r="S505" t="n">
+        <v>2</v>
+      </c>
+      <c r="T505" t="n">
+        <v>0</v>
+      </c>
+      <c r="U505" t="n">
+        <v>1</v>
+      </c>
+      <c r="V505" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W505" t="n">
+        <v>26</v>
+      </c>
+      <c r="X505" t="inlineStr">
+        <is>
+          <t>CB ARIDANE vs UROS DE RIVAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>2487758</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>UROS DE RIVAS</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>A. GARCIA QUILEZ CUERVAS | A. PEREZ CONTI | O. HADI ADEGBITE | O. MENDEZ BLANCO | P. ESTEBANEZ GONZALEZ</t>
+        </is>
+      </c>
+      <c r="D506" t="n">
+        <v>5</v>
+      </c>
+      <c r="E506" t="n">
+        <v>22</v>
+      </c>
+      <c r="F506" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="G506" t="n">
+        <v>2</v>
+      </c>
+      <c r="H506" t="n">
+        <v>0</v>
+      </c>
+      <c r="I506" t="n">
+        <v>1</v>
+      </c>
+      <c r="J506" t="n">
+        <v>1</v>
+      </c>
+      <c r="K506" t="n">
+        <v>200</v>
+      </c>
+      <c r="L506" t="n">
+        <v>0</v>
+      </c>
+      <c r="M506" t="n">
+        <v>200</v>
+      </c>
+      <c r="N506" t="n">
+        <v>1</v>
+      </c>
+      <c r="O506" t="n">
+        <v>0</v>
+      </c>
+      <c r="P506" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q506" t="n">
+        <v>0</v>
+      </c>
+      <c r="R506" t="n">
+        <v>0</v>
+      </c>
+      <c r="S506" t="n">
+        <v>0</v>
+      </c>
+      <c r="T506" t="n">
+        <v>1</v>
+      </c>
+      <c r="U506" t="n">
+        <v>0</v>
+      </c>
+      <c r="V506" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W506" t="n">
+        <v>26</v>
+      </c>
+      <c r="X506" t="inlineStr">
+        <is>
+          <t>CB ARIDANE vs UROS DE RIVAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>2487758</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>UROS DE RIVAS</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>A. PEREZ CONTI | C. CRESPO MONTESINOS | G. MARTIN LOPEZ-LAGO | O. MENDEZ BLANCO | P. ESTEBANEZ GONZALEZ</t>
+        </is>
+      </c>
+      <c r="D507" t="n">
+        <v>5</v>
+      </c>
+      <c r="E507" t="n">
+        <v>6</v>
+      </c>
+      <c r="F507" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G507" t="n">
+        <v>2</v>
+      </c>
+      <c r="H507" t="n">
+        <v>2</v>
+      </c>
+      <c r="I507" t="n">
+        <v>1</v>
+      </c>
+      <c r="J507" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="K507" t="n">
+        <v>200</v>
+      </c>
+      <c r="L507" t="n">
+        <v>227.27</v>
+      </c>
+      <c r="M507" t="n">
+        <v>-27.27</v>
+      </c>
+      <c r="N507" t="n">
+        <v>1</v>
+      </c>
+      <c r="O507" t="n">
+        <v>0</v>
+      </c>
+      <c r="P507" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q507" t="n">
+        <v>0</v>
+      </c>
+      <c r="R507" t="n">
+        <v>0</v>
+      </c>
+      <c r="S507" t="n">
+        <v>2</v>
+      </c>
+      <c r="T507" t="n">
+        <v>0</v>
+      </c>
+      <c r="U507" t="n">
+        <v>0</v>
+      </c>
+      <c r="V507" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W507" t="n">
+        <v>26</v>
+      </c>
+      <c r="X507" t="inlineStr">
+        <is>
+          <t>CB ARIDANE vs UROS DE RIVAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>2487758</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>UROS DE RIVAS</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>C. CRESPO MONTESINOS | D. MARINEZ FERNANDEZ-URRUTIA | G. MARTIN LOPEZ-LAGO | O. MENDEZ BLANCO | P. ESTEBANEZ GONZALEZ</t>
+        </is>
+      </c>
+      <c r="D508" t="n">
+        <v>5</v>
+      </c>
+      <c r="E508" t="n">
+        <v>5</v>
+      </c>
+      <c r="F508" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="G508" t="n">
+        <v>2</v>
+      </c>
+      <c r="H508" t="n">
+        <v>2</v>
+      </c>
+      <c r="I508" t="n">
+        <v>1</v>
+      </c>
+      <c r="J508" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="K508" t="n">
+        <v>200</v>
+      </c>
+      <c r="L508" t="n">
+        <v>227.27</v>
+      </c>
+      <c r="M508" t="n">
+        <v>-27.27</v>
+      </c>
+      <c r="N508" t="n">
+        <v>1</v>
+      </c>
+      <c r="O508" t="n">
+        <v>0</v>
+      </c>
+      <c r="P508" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q508" t="n">
+        <v>0</v>
+      </c>
+      <c r="R508" t="n">
+        <v>0</v>
+      </c>
+      <c r="S508" t="n">
+        <v>2</v>
+      </c>
+      <c r="T508" t="n">
+        <v>0</v>
+      </c>
+      <c r="U508" t="n">
+        <v>0</v>
+      </c>
+      <c r="V508" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W508" t="n">
+        <v>26</v>
+      </c>
+      <c r="X508" t="inlineStr">
+        <is>
+          <t>CB ARIDANE vs UROS DE RIVAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>2487752</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>BALONCESTO TALAVERA</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>A. VICENTE VIANA | B. GUEYE | C. KLOTZ MAROTO | C. UNANUE CEGARRA | D. LORENZO NEGRETE</t>
+        </is>
+      </c>
+      <c r="D509" t="n">
+        <v>5</v>
+      </c>
+      <c r="E509" t="n">
+        <v>51</v>
+      </c>
+      <c r="F509" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G509" t="n">
+        <v>3</v>
+      </c>
+      <c r="H509" t="n">
+        <v>2</v>
+      </c>
+      <c r="I509" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="J509" t="n">
+        <v>2</v>
+      </c>
+      <c r="K509" t="n">
+        <v>170.45</v>
+      </c>
+      <c r="L509" t="n">
+        <v>100</v>
+      </c>
+      <c r="M509" t="n">
+        <v>70.45</v>
+      </c>
+      <c r="N509" t="n">
+        <v>1</v>
+      </c>
+      <c r="O509" t="n">
+        <v>4</v>
+      </c>
+      <c r="P509" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q509" t="n">
+        <v>1</v>
+      </c>
+      <c r="R509" t="n">
+        <v>2</v>
+      </c>
+      <c r="S509" t="n">
+        <v>0</v>
+      </c>
+      <c r="T509" t="n">
+        <v>0</v>
+      </c>
+      <c r="U509" t="n">
+        <v>0</v>
+      </c>
+      <c r="V509" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W509" t="n">
+        <v>26</v>
+      </c>
+      <c r="X509" t="inlineStr">
+        <is>
+          <t>EB FELIPE ANTÓN vs BALONCESTO TALAVERA</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>2487752</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>BALONCESTO TALAVERA</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>A. VICENTE VIANA | B. GUEYE | C. KLOTZ MAROTO | D. LORENZO NEGRETE | S. GACIC</t>
+        </is>
+      </c>
+      <c r="D510" t="n">
+        <v>5</v>
+      </c>
+      <c r="E510" t="n">
+        <v>25</v>
+      </c>
+      <c r="F510" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="G510" t="n">
+        <v>0</v>
+      </c>
+      <c r="H510" t="n">
+        <v>2</v>
+      </c>
+      <c r="I510" t="n">
+        <v>1</v>
+      </c>
+      <c r="J510" t="n">
+        <v>2</v>
+      </c>
+      <c r="K510" t="n">
+        <v>0</v>
+      </c>
+      <c r="L510" t="n">
+        <v>100</v>
+      </c>
+      <c r="M510" t="n">
+        <v>-100</v>
+      </c>
+      <c r="N510" t="n">
+        <v>0</v>
+      </c>
+      <c r="O510" t="n">
+        <v>0</v>
+      </c>
+      <c r="P510" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q510" t="n">
+        <v>0</v>
+      </c>
+      <c r="R510" t="n">
+        <v>2</v>
+      </c>
+      <c r="S510" t="n">
+        <v>0</v>
+      </c>
+      <c r="T510" t="n">
+        <v>0</v>
+      </c>
+      <c r="U510" t="n">
+        <v>0</v>
+      </c>
+      <c r="V510" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W510" t="n">
+        <v>26</v>
+      </c>
+      <c r="X510" t="inlineStr">
+        <is>
+          <t>EB FELIPE ANTÓN vs BALONCESTO TALAVERA</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>2487752</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>BALONCESTO TALAVERA</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>A. VICENTE VIANA | B. GUEYE | D. LORENZO NEGRETE | S. GACIC | V. ALONSO PASCUAL</t>
+        </is>
+      </c>
+      <c r="D511" t="n">
+        <v>5</v>
+      </c>
+      <c r="E511" t="n">
+        <v>55</v>
+      </c>
+      <c r="F511" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="G511" t="n">
+        <v>1</v>
+      </c>
+      <c r="H511" t="n">
+        <v>2</v>
+      </c>
+      <c r="I511" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="J511" t="n">
+        <v>1</v>
+      </c>
+      <c r="K511" t="n">
+        <v>53.19</v>
+      </c>
+      <c r="L511" t="n">
+        <v>200</v>
+      </c>
+      <c r="M511" t="n">
+        <v>-146.81</v>
+      </c>
+      <c r="N511" t="n">
+        <v>1</v>
+      </c>
+      <c r="O511" t="n">
+        <v>2</v>
+      </c>
+      <c r="P511" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q511" t="n">
+        <v>0</v>
+      </c>
+      <c r="R511" t="n">
+        <v>1</v>
+      </c>
+      <c r="S511" t="n">
+        <v>0</v>
+      </c>
+      <c r="T511" t="n">
+        <v>0</v>
+      </c>
+      <c r="U511" t="n">
+        <v>0</v>
+      </c>
+      <c r="V511" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W511" t="n">
+        <v>26</v>
+      </c>
+      <c r="X511" t="inlineStr">
+        <is>
+          <t>EB FELIPE ANTÓN vs BALONCESTO TALAVERA</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>2487752</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>A. SISTAC RODRIGUEZ | B. FERNANDEZ SHEPHARD | J. GALLETTO LAMELA | K. RIVEROL DE LAS CASAS | S. MANERO GUZMAN</t>
+        </is>
+      </c>
+      <c r="D512" t="n">
+        <v>5</v>
+      </c>
+      <c r="E512" t="n">
+        <v>39</v>
+      </c>
+      <c r="F512" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G512" t="n">
+        <v>2</v>
+      </c>
+      <c r="H512" t="n">
+        <v>1</v>
+      </c>
+      <c r="I512" t="n">
+        <v>1</v>
+      </c>
+      <c r="J512" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="K512" t="n">
+        <v>200</v>
+      </c>
+      <c r="L512" t="n">
+        <v>53.19</v>
+      </c>
+      <c r="M512" t="n">
+        <v>146.81</v>
+      </c>
+      <c r="N512" t="n">
+        <v>1</v>
+      </c>
+      <c r="O512" t="n">
+        <v>0</v>
+      </c>
+      <c r="P512" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q512" t="n">
+        <v>0</v>
+      </c>
+      <c r="R512" t="n">
+        <v>1</v>
+      </c>
+      <c r="S512" t="n">
+        <v>2</v>
+      </c>
+      <c r="T512" t="n">
+        <v>0</v>
+      </c>
+      <c r="U512" t="n">
+        <v>0</v>
+      </c>
+      <c r="V512" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W512" t="n">
+        <v>26</v>
+      </c>
+      <c r="X512" t="inlineStr">
+        <is>
+          <t>EB FELIPE ANTÓN vs BALONCESTO TALAVERA</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>2487752</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>A. SISTAC RODRIGUEZ | J. GALLETTO LAMELA | K. RIVEROL DE LAS CASAS | M. NIMAGA | S. MANERO GUZMAN</t>
+        </is>
+      </c>
+      <c r="D513" t="n">
+        <v>5</v>
+      </c>
+      <c r="E513" t="n">
+        <v>90</v>
+      </c>
+      <c r="F513" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G513" t="n">
+        <v>4</v>
+      </c>
+      <c r="H513" t="n">
+        <v>3</v>
+      </c>
+      <c r="I513" t="n">
+        <v>3</v>
+      </c>
+      <c r="J513" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="K513" t="n">
+        <v>133.33</v>
+      </c>
+      <c r="L513" t="n">
+        <v>79.79000000000001</v>
+      </c>
+      <c r="M513" t="n">
+        <v>53.55</v>
+      </c>
+      <c r="N513" t="n">
+        <v>3</v>
+      </c>
+      <c r="O513" t="n">
+        <v>0</v>
+      </c>
+      <c r="P513" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q513" t="n">
+        <v>0</v>
+      </c>
+      <c r="R513" t="n">
+        <v>1</v>
+      </c>
+      <c r="S513" t="n">
+        <v>4</v>
+      </c>
+      <c r="T513" t="n">
+        <v>1</v>
+      </c>
+      <c r="U513" t="n">
+        <v>0</v>
+      </c>
+      <c r="V513" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W513" t="n">
+        <v>26</v>
+      </c>
+      <c r="X513" t="inlineStr">
+        <is>
+          <t>EB FELIPE ANTÓN vs BALONCESTO TALAVERA</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>2487752</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>J. GALLETTO LAMELA | K. RIVEROL DE LAS CASAS | M. NIMAGA | P. ARGÜELLES ELORZA | S. MANERO GUZMAN</t>
+        </is>
+      </c>
+      <c r="D514" t="n">
+        <v>5</v>
+      </c>
+      <c r="E514" t="n">
+        <v>2</v>
+      </c>
+      <c r="F514" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G514" t="n">
+        <v>0</v>
+      </c>
+      <c r="H514" t="n">
+        <v>0</v>
+      </c>
+      <c r="I514" t="n">
+        <v>1</v>
+      </c>
+      <c r="J514" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K514" t="n">
+        <v>0</v>
+      </c>
+      <c r="L514" t="n">
+        <v>0</v>
+      </c>
+      <c r="M514" t="n">
+        <v>0</v>
+      </c>
+      <c r="N514" t="n">
+        <v>1</v>
+      </c>
+      <c r="O514" t="n">
+        <v>0</v>
+      </c>
+      <c r="P514" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q514" t="n">
+        <v>0</v>
+      </c>
+      <c r="R514" t="n">
+        <v>0</v>
+      </c>
+      <c r="S514" t="n">
+        <v>0</v>
+      </c>
+      <c r="T514" t="n">
+        <v>0</v>
+      </c>
+      <c r="U514" t="n">
+        <v>1</v>
+      </c>
+      <c r="V514" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="W514" t="n">
+        <v>26</v>
+      </c>
+      <c r="X514" t="inlineStr">
+        <is>
+          <t>EB FELIPE ANTÓN vs BALONCESTO TALAVERA</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
